--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -23,6 +23,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PREDICTIONS" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OPEN_PROBLEMS" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STATUS_MATRIX" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FC005_S3_CONTROL" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FC005_WORKBOOK_RECONCILIATION" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -833,6 +835,57 @@
       <c r="C18" t="inlineStr">
         <is>
           <t>CONDITIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CALC-FC005-S3-CONTROL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>{'max_abs_e_kappa': np.float64(1.0192723588153818e-05), 'a0_max_residual': 5.6033975865277734e-11, 'a1_max_residual': 4.0056349212613886e-08, 'a2_max_residual': 2.0305175367346576e-05, 'exact': {'a0': 19.739208802178716, 'a1': 19.739208802178716, 'a2': 9.869604401089358}}</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CALC-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>{'is_positive_semidefinite': True}</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CALC-FC005-EIGEN-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>{'matrices_differ': True}</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
@@ -847,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1010,6 +1063,66 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FALS-FC005-FISHER-LORENTZIAN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mathematical_invariance</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fisher-Rao metric F = Lorentzian spacetime metric g_munu</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>F is positive semidefinite for every tested sigma (all sampled v^T F v &gt;= 0, eigenvalues at sigma=1: [1.0, 2.0]); a Lorentzian-signature metric requires a strictly negative eigenvalue, which is impossible for a PSD matrix under any basis change (signature is basis-independent). F = g_munu (Lorentzian) is therefore FALSIFIED as a direct identification, for this family and in general.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>{'eigenvalues_at_sigma1': [1.0, 2.0], 'family': 'Gaussian N(mu, sigma^2), theta=(mu, sigma)'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FALS-FC005-EIGENVALUE-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>structural_elimination</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>H is uniquely determined by Spec(H)</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>25/25 random unitary-conjugation trials produce a distinct operator with identical spectrum.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>{'n_confirmed': 25, 'n_trials': 25, 'spectra_match_max_residual': 8.881784197001252e-16}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1021,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1076,12 +1189,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.378150+00:00</t>
+          <t>2026-08-19T03:52:06.650823+00:00</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1216,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.380656+00:00</t>
+          <t>2026-08-19T03:52:06.653496+00:00</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1243,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.383140+00:00</t>
+          <t>2026-08-19T03:52:06.656300+00:00</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1270,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.385572+00:00</t>
+          <t>2026-08-19T03:52:06.658681+00:00</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1297,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.387853+00:00</t>
+          <t>2026-08-19T03:52:06.661104+00:00</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1324,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.390166+00:00</t>
+          <t>2026-08-19T03:52:06.663450+00:00</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1351,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.392354+00:00</t>
+          <t>2026-08-19T03:52:06.665919+00:00</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1378,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.394777+00:00</t>
+          <t>2026-08-19T03:52:06.668337+00:00</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1405,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.396953+00:00</t>
+          <t>2026-08-19T03:52:06.670702+00:00</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1432,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.399046+00:00</t>
+          <t>2026-08-19T03:52:06.672904+00:00</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1459,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.401284+00:00</t>
+          <t>2026-08-19T03:52:06.675406+00:00</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1486,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.403440+00:00</t>
+          <t>2026-08-19T03:52:06.678241+00:00</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1513,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.405656+00:00</t>
+          <t>2026-08-19T03:52:06.680571+00:00</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1540,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.407782+00:00</t>
+          <t>2026-08-19T03:52:06.683820+00:00</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1567,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.410191+00:00</t>
+          <t>2026-08-19T03:52:06.686084+00:00</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.412349+00:00</t>
+          <t>2026-08-19T03:52:06.689196+00:00</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1621,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.414419+00:00</t>
+          <t>2026-08-19T03:52:06.691580+00:00</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1648,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.416505+00:00</t>
+          <t>2026-08-19T03:52:06.694469+00:00</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1675,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.418784+00:00</t>
+          <t>2026-08-19T03:52:06.696873+00:00</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1702,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.420828+00:00</t>
+          <t>2026-08-19T03:52:06.699593+00:00</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1729,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.423057+00:00</t>
+          <t>2026-08-19T03:52:06.702215+00:00</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1756,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.653056+00:00</t>
+          <t>2026-08-19T03:52:06.928463+00:00</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1783,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.658382+00:00</t>
+          <t>2026-08-19T03:52:06.931464+00:00</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1810,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.663093+00:00</t>
+          <t>2026-08-19T03:52:06.936335+00:00</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1837,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.665418+00:00</t>
+          <t>2026-08-19T03:52:06.938735+00:00</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1864,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.869421+00:00</t>
+          <t>2026-08-19T03:52:07.152614+00:00</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1891,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.873619+00:00</t>
+          <t>2026-08-19T03:52:07.155903+00:00</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1918,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.891822+00:00</t>
+          <t>2026-08-19T03:52:07.232827+00:00</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1945,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.894002+00:00</t>
+          <t>2026-08-19T03:52:07.235566+00:00</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1972,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.896137+00:00</t>
+          <t>2026-08-19T03:52:07.237959+00:00</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1999,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.898462+00:00</t>
+          <t>2026-08-19T03:52:07.240509+00:00</t>
         </is>
       </c>
     </row>
@@ -1913,12 +2026,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.902961+00:00</t>
+          <t>2026-08-19T03:52:07.242852+00:00</t>
         </is>
       </c>
     </row>
@@ -1940,12 +2053,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.905064+00:00</t>
+          <t>2026-08-19T03:52:07.245071+00:00</t>
         </is>
       </c>
     </row>
@@ -1967,12 +2080,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.907069+00:00</t>
+          <t>2026-08-19T03:52:07.248355+00:00</t>
         </is>
       </c>
     </row>
@@ -1994,132 +2107,132 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.909503+00:00</t>
+          <t>2026-08-19T03:52:07.250902+00:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>fc005_source_workbooks/ (4 files)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.373672+00:00</t>
+          <t>2026-08-19T03:52:07.253639+00:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.667708+00:00</t>
+          <t>2026-08-19T03:52:07.424550+00:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.670873+00:00</t>
+          <t>2026-08-19T03:52:07.427675+00:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.673097+00:00</t>
+          <t>2026-08-19T03:52:07.430377+00:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2129,120 +2242,1551 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.675158+00:00</t>
+          <t>2026-08-19T03:52:07.432924+00:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.876010+00:00</t>
+          <t>2026-08-19T03:52:07.435406+00:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>repository + workspace filesystem audit</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.878264+00:00</t>
+          <t>2026-08-19T03:52:07.442711+00:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ec03712b8a3c</t>
+          <t>45b9fb9fef84</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T03:12:33.887306+00:00</t>
+          <t>2026-08-19T03:52:07.445054+00:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>OPERATOR-L-DESI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.447325+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.449740+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DESI-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.452444+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-TRACE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.454750+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-COEFFICIENTS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.457310+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.459755+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>E-KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.462178+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.464459+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>established semiclassical gravity literature</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.466982+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>spec section 18 (FC-005 build command)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.469173+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:08.040098+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SPEC-H-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>compiler/falsification/eigen_uniqueness.py</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:08.066052+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SELECTION-SIGMA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>spec section 10</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:06.647430+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T-GRAPH-TO-OPERATOR</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:06.941115+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:06.943419+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:06.945552+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T-HEATFLOW-TO-KERNEL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:06.947839+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>compiler/backends/diffusion_metric.py</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.160827+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T-DIFFUSION-TO-METRIC</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>compiler/backends/diffusion_metric.py</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.163460+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.440226+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.224704+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ec03712b8a3c</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-08-19T03:12:33.889666+00:00</t>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.227781+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EQ-001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.337576+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EQ-002</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.340759+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EQ-003</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.343940+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EQ-004</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.346622+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EQ-005</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.349197+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EQ-006</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.351849+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EQ-007</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.354522+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EQ-008</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.357196+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EQ-009</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.359457+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EQ-010</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.361900+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EQ-011</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.364416+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EQ-012</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.366817+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EQ-013</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.369891+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EQ-014</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.372278+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EQ-015</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.374619+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EQ-016</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.377111+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EQ-017</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.380274+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>EQ-018</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.382738+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EQ-019</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.385798+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EQ-020</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.388049+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EQ-021</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.390501+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>EQ-022</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.392744+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.395051+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.397391+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.399625+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.401892+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.404376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.406531+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.408960+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:07.437825+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:08.043322+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>45b9fb9fef84</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-08-19T03:52:08.046095+00:00</t>
         </is>
       </c>
     </row>
@@ -2257,7 +3801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2372,6 +3916,162 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DESI-CATALOGUE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>pending_data_construction
+required: RA, DEC, z, and DESI weights (w_FKP, w_sys, ...) for a galaxy-level point catalogue. ABSENT from the repository, the current workspace, and all four supplied FC-005</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GRAPH-G-DESI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>mathematical_object
+G_DESI = (V,E,W): weighted observational graph from the DESI catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>OPERATOR-L-DESI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>graph_laplacian_operator
+L_DESI = D - W</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-TRACE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>heat_trace_function
+K(t) from the DESI-derived spectrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>curvature_closure
+kappa_spectral from DESI data</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E-KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>curvature_closure
+E_kappa closure residual for DESI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2383,7 +4083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2400,6 +4100,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>No physical predictions are registered in this build. The gauge, matter, thermodynamic, and cosmological engines are gated behind this compiler's own self-audit (spec section 41) and have not been activated. A fitted parameter is never registered here as a prediction (spec section 4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FC-005: kappa_spectral (from real DESI data) is not computed -- no DESI catalogue is available (see FC005_S3_CONTROL sheet / DESI-CATALOGUE node). The S^3 control result is a regression test on a known analytic manifold, not a prediction.</t>
         </is>
       </c>
     </row>
@@ -2414,7 +4121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2867,15 +4574,219 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>DESI-CATALOGUE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>required: RA, DEC, z, and DESI weights (w_FKP, w_sys, ...) for a galaxy-level point catalogue. ABSENT from the repository, the current workspace, and all four supplied FC-005 workbooks -- the primary workbook's own 'FC-005 Full Execution Index' sheet records this: 'No catalog file present in uploade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GRAPH-G-DESI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>G_DESI = (V,E,W): weighted observational graph from the DESI catalogue</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>OPERATOR-L-DESI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>L_DESI = D - W</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>L_tilde_(N,eps) = -L_N/(C_K N eps^(5/2)), d=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DESI-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Spec(Delta_h) via L_tilde eigenproblem</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-TRACE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>K(t) from the DESI-derived spectrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-COEFFICIENTS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>(a0,a1,a2) fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>kappa_spectral from DESI data</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>E-KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>E_kappa closure residual for DESI</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Delta_kappa = kappa_spectral - kappa_cosmological (independent cross-check)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>E_SC[g] = G_munu + Lambda g_munu - (8piG/c^4)&lt;T_munu[g]&gt;_ren</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SPEC-H-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Spec(H) does NOT determine H: 25/25 random trials confirm H' = U H U^dagger has identical spectrum (max residual 8.88e-16) while H' != H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>SELECTION-SIGMA</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Transformation</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Sigma : M -&gt; {0,1}</t>
         </is>
@@ -2892,7 +4803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3696,17 +5607,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3718,78 +5629,78 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['S3-SPECTRUM']</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3799,95 +5710,1745 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['S3-HEAT-TRACE']</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['S3-HEAT-COEFFICIENTS']</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['DESI-CATALOGUE']</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>OPERATOR-L-DESI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>['GRAPH-G-DESI']</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>['OPERATOR-L-DESI']</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DESI-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-TRACE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>['DESI-SPECTRUM']</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-COEFFICIENTS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>['DESI-HEAT-TRACE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>['DESI-HEAT-COEFFICIENTS']</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>E-KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>['KAPPA-DESI']</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>['KAPPA-DESI']</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SPEC-H-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SELECTION-SIGMA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T-GRAPH-TO-OPERATOR</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>['GRAPH-G-SEED']</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>['OPERATOR-L']</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>['SPECTRUM-L']</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T-HEATFLOW-TO-KERNEL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>['HEAT-FLOW-R']</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>['SPECTRUM-L']</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T-DIFFUSION-TO-METRIC</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>['DIFFUSION-DISTANCE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Transformation</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>['S3-MANIFOLD']</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>['OPERATOR-L']</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>['HEAT-FLOW-R']</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EQ-001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EQ-002</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EQ-003</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EQ-004</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EQ-005</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EQ-006</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EQ-007</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EQ-008</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EQ-009</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EQ-010</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EQ-011</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EQ-012</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EQ-013</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EQ-014</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EQ-015</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EQ-016</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EQ-017</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>EQ-018</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EQ-019</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EQ-020</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EQ-021</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>EQ-022</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>['S3-CURVATURE-CLOSURE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>t_min</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>t_max</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>npts</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>l_max</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>a0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>a1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>a2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>kappa_a1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>kappa_a2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>e_kappa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" t="n">
+        <v>283</v>
+      </c>
+      <c r="F2" t="n">
+        <v>19.73920880215651</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19.73920884537625</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.869575174285904</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.000000002189537</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9999985193523063</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.482837231114864e-06</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>231</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19.73920880206592</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19.73920894829115</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9.869538540783054</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.000000007407857</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9999966634751961</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.343932660437865e-06</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F4" t="n">
+        <v>19.73920880182197</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19.7392091487821</v>
+      </c>
+      <c r="H4" t="n">
+        <v>9.869487225631897</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.000000017577206</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9999940638133954</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.953763810295776e-06</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>164</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.73920880107265</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19.73920959285936</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9.869403997041188</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.000000040112383</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.999989847388795</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.019272358815382e-05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>exact reference</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>kappa=1, R=6, a0=2*pi^2, a1=2*pi^2, a2=pi^2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tolerance</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>max_abs_e_kappa</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.019272358815382e-05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="B10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>repo_path</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>as_uploaded</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>modified_utc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>n_sheets</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ORIGINAL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LEVEL 4 (earlier workbook version) / provenance recovery source</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/01_original_derivation_workbook.xlsx</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>d115f512-final_physics_derivation_workbook1.xlsx</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:36:01</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Earliest of the four (smallest, fewest sheets). Contains the core equation/dependency/status/provenance sheets only, no FC-005 execution machinery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CANONICAL_DERIVATION</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LEVEL 2 (later canonical derivation workbook)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/02_canonical_derivation_workbook.xlsx</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>677216f9-final_physics_derivation_workbook.xlsx</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:41:16</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Superset of (1): adds the Recovery sheets (Foundation/Physical/Statistical/Thermodynamic/Variational Quantum/Gauge Matter), Cosmology Observation, Discrete Continuum, Interface Reduction, Seven Structure Dependency, Canonical Variables, Audit Ledger, FINAL MASTER CHAINLINK, Status Legend. Every sheet shared with (1) is byte-identical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FC005_EARLIER_SPEC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LEVEL 4 (earlier FC-005 specification) -- historical/supporting</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/03_fc005_earlier_execution_spec.xlsx</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>05018c9b-final_physics_derivation_workbook_FC005.xlsx</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:49:45</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Superset of (2): adds 'FC-005 Execution' and 'FC-005 Run Registry'. Every sheet shared with (2) is byte-identical. Superseded by (4), which adds the audit/control-validation sheets this one lacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PRIMARY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LEVEL 3 (FC-005 execution specification) -- CANONICAL for this build</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4e6464f3-final_physics_derivation_workbook_FC005_full_execution.xlsx</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-19T02:52:29</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Superset of (3): adds 'FC-005 Full Execution Index', 'FC-005 Workbook Audit', 'FC-005 Control Validation' (the S^3 regression control this build independently reproduces). Every sheet shared with (3) is byte-identical. This is the workbook this build treats as the source-of-truth for FC-005 equations/dependencies/status.</t>
         </is>
       </c>
     </row>
@@ -3902,7 +7463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4134,6 +7695,129 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>a project-internal statement of a derivation obstruction, predating this compiler</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>established_equation</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>an equation asserted by an external/prior source; PROPOSED until independently executed in this compiler</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>heat_trace_function</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>K(t) = sum_n exp(-t lambda_n)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>heat_kernel_coefficients</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fitted (a0, a1, a2, ...) short-time heat-kernel expansion coefficients</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>curvature_closure</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>the E_kappa = a1/a0 - sgn(a1)*sqrt(2a2/a0) consistency test result</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>pending_data_construction</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>a construction whose code path exists but that cannot be executed because required observational data is absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>semiclassical_framework_equation</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>the established semiclassical Einstein equation G_munu + Lambda g_munu = (8piG/c^4) &lt;T_munu&gt;_ren</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>statistical_family</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>a parametric probability family used to compute a Fisher information matrix</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>operator_uniqueness_counterexample</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>an executed counterexample to spectrum-determines-operator</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>workbook_reconciliation_record</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>provenance/precedence record for the four supplied FC-005 workbooks</t>
         </is>
       </c>
     </row>
@@ -4148,7 +7832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5130,6 +8814,546 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>workbook_reconciliation_record</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>S3-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>spectral_data</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>['S3-MANIFOLD']</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>S3-HEAT-TRACE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>heat_trace_function</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>['S3-SPECTRUM']</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>S3-HEAT-COEFFICIENTS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>heat_kernel_coefficients</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>['S3-HEAT-TRACE']</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>curvature_closure</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>['S3-HEAT-COEFFICIENTS']</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DESI-CATALOGUE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>pending_data_construction</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GRAPH-G-DESI</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>['DESI-CATALOGUE']</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>OPERATOR-L-DESI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>graph_laplacian_operator</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>['GRAPH-G-DESI']</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>['OPERATOR-L-DESI']</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DESI-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>spectral_data</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-TRACE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>heat_trace_function</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>['DESI-SPECTRUM']</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-COEFFICIENTS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>heat_kernel_coefficients</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>['DESI-HEAT-TRACE']</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>curvature_closure</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>['DESI-HEAT-COEFFICIENTS']</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>E-KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>curvature_closure</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>['KAPPA-DESI']</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>curvature_closure</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>['KAPPA-DESI']</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>semiclassical_framework_equation</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>curvature_closure</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>statistical_family</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SPEC-H-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>operator_uniqueness_counterexample</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5141,7 +9365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5408,6 +9632,38 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>analytic Spec -&gt; K(t) -&gt; fit -&gt; E_kappa</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>['S3-MANIFOLD']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5419,7 +9675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5526,6 +9782,1030 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EQ-001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Spacetime interval</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ds²=g_μνdx^μdx^ν</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EQ-002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Einstein equation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G_μν+Λg_μν=(8πG/c⁴)T_μν</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EQ-003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FLRW metric</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ds²=-c²dt²+a²(t)[dχ²+χ²dΩ²]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EQ-004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Graph Laplacian</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>L_N=D-W</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EQ-005</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Graph eigenproblem</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>L_Nφ_k=λ_kφ_k</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EQ-006</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Continuum eigenproblem</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-Δ_hφ_n=λ_nφ_n</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EQ-007</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Heat trace</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>K(t)=Σe^{-tλ_n}</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EQ-008</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3D heat expansion</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>K~(4πt)^(-3/2)(a0+a1t+a2t²+...)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EQ-009</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Curvature coefficient</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>a1=(1/6)∫R dV</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EQ-010</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Constant curvature</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>R=6κ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EQ-011</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>a2 constant curvature</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>a2=(1/2)Vκ²</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EQ-012</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Curvature residual</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Rκ=a1/a0-sgn(a1)√(2a2/a0)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EQ-013</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Continuum normalization</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>L̃=-L_N/(C_KNε^(d/2+1))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EQ-014</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>d=3 normalization</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>L̃=-L_N/(C_KNε^(5/2))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EQ-015</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Friedmann</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>H²=(8πG/3)ρ+Λc²/3-c²κ/a²</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EQ-016</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Continuity</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ρ̇+3H(ρ+p/c²)=0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EQ-017</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Equation of state</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>p=wρc²</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EQ-018</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Density evolution</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ρ(a)=ρ0a^{-3(1+w)}</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EQ-019</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Hamiltonian decomposition</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>H=ΣE_nP_n</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EQ-020</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Quantum state</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ρ_Q=Σp_nP_n</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EQ-021</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Stress expectation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>&lt;T_μν&gt;=Tr(ρ_QT̂_μν)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EQ-022</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Semiclassical Einstein</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>G_μν+Λg_μν=(8πG/c⁴)&lt;T̂_μν&gt;_ren</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Fisher metric</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>F_ab=∫p∂a ln p∂b ln p dx</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fisher positivity</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>v^aF_abv^b=∫p(v^a∂a ln p)²dx≥0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Fisher pullback</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>g^F_μν=F_ab∂_μθ^a∂_νθ^b</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lorentzian signature</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>signature(g)=(-,+,+,+)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fisher obstruction</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>signature(g^F)≠(-,+,+,+)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Principal symbol</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>σ_2(-Δ_g)=g^{μν}ξ_μξ_ν</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Semiclassical residual</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>F_SC[g]=G_μν+Λg_μν-(8πG/c⁴)&lt;T̂_μν[g]&gt;_ren</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FC-005 reference equation set</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>E_kappa</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>a1/a0 - sgn(a1)*sqrt(2*a2/a0)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>S^3 heat-kernel control</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>['S3-CURVATURE-CLOSURE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>v^T F v</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>&gt;= 0 for all v</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>information geometry</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>g_munu (Lorentzian, signature (-,+,+,+))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>information geometry vs spacetime geometry</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5537,7 +10817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5871,96 +11151,312 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GRAPH-G-SEED</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DIFFUSION-DISTANCE</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>DESI-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-TRACE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>DESI-SPECTRUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-COEFFICIENTS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-TRACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-COEFFICIENTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>E-KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>KAPPA-DESI</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>KAPPA-DESI</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T-GRAPH-TO-OPERATOR</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GRAPH-G-SEED</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SPECTRUM-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T-HEATFLOW-TO-KERNEL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SPECTRUM-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>T-DIFFUSION-TO-METRIC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DIFFUSION-DISTANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
       </c>
     </row>
@@ -5975,7 +11471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6393,12 +11889,540 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>canonical (rank 4, PRIMARY): fc005_source_workbooks/04_fc005_primary_full_execution.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>filename discrepancies vs the FC-005 build command's own naming: 4 (see provenance.verification)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>S3-HEAT-COEFFICIENTS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>degree=2 quadratic fit alone is insufficient (biased by the neglected a3 t^3 term to |E_kappa|~1e-3); degree&gt;=3 removes the leading bias -- see degree_sweep in provenance.verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DESI-CATALOGUE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>STOP condition per spec section 25 of the FC-005 build command: required DESI data is absent. Not fabricated. Code path is implemented and unit-tested on synthetic data in compiler/backends/desi_graph.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>GRAPH-G-DESI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>OPERATOR-L-DESI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DESI-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-TRACE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-COEFFICIENTS</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>E-KAPPA-DESI</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>requires a constructed quantum state rho_Q and a renormalized stress tensor &lt;T_munu&gt;_ren; neither is constructed in this build. This is reported as SEMICLASSICAL CLOSURE scope only, never as full quantum gravity (spec section 18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SPEC-H-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>OPEN OBSTRUCTION (spec section 7B / workbook R-003, TEST-006): eigenvalue-only spectral data cannot reconstruct the operator, and therefore cannot alone reconstruct a geometry (Spec(H) alone -&gt; g_munu is NOT claimed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>SELECTION-SIGMA</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EQ-001</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EQ-002</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EQ-003</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EQ-004</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EQ-005</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EQ-006</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EQ-007</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EQ-008</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EQ-009</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EQ-010</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EQ-011</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EQ-012</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EQ-013</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EQ-014</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EQ-015</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EQ-016</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EQ-017</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EQ-018</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EQ-019</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EQ-020</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EQ-021</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EQ-022</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
@@ -6413,7 +12437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6585,6 +12609,33 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PROOF-T-FC005-S3-CONTROL-CHAIN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>analytic Spec -&gt; K(t) -&gt; fit -&gt; E_kappa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>closed-form S^3 spectrum, numpy heat-trace summation with controlled truncation, numpy.polyfit degree-3/4/5 sweep</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6596,7 +12647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7001,6 +13052,72 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CALC-FC005-S3-CONTROL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>s3_heat_kernel_control_regression_test</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>{'windows': [(0.001, 0.004), (0.0015, 0.006), (0.002, 0.008), (0.003, 0.01)], 'degree': 3, 'tolerance': 0.0001}</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CALC-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fisher_information_psd_demonstration</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{'family': 'Gaussian N(mu, sigma^2), theta=(mu, sigma)'}</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CALC-FC005-EIGEN-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>spectrum_determines_operator_counterexample</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{'n': 2, 'n_trials': 25}</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'max_abs_e_kappa': np.float64(1.0192723588153818e-05), 'a0_max_residual': 5.6033975865277734e-11, 'a1_max_residual': 4.0056349212613886e-08, 'a2_max_residual': 2.0305175367346576e-05, 'exact': {'a0': 19.739208802178716, 'a1': 19.739208802178716, 'a2': 9.869604401089358}}</t>
+          <t>{'max_abs_e_kappa': 1.0192723588153818e-05, 'a0_max_residual': 5.6033975865277734e-11, 'a1_max_residual': 4.0056349212613886e-08, 'a2_max_residual': 2.0305175367346576e-05, 'exact': {'a0': 19.739208802178716, 'a1': 19.739208802178716, 'a2': 9.869604401089358}}</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1134,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.650823+00:00</t>
+          <t>2026-08-19T04:19:34.931802+00:00</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.653496+00:00</t>
+          <t>2026-08-19T04:19:34.934446+00:00</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.656300+00:00</t>
+          <t>2026-08-19T04:19:34.936927+00:00</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.658681+00:00</t>
+          <t>2026-08-19T04:19:34.939384+00:00</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.661104+00:00</t>
+          <t>2026-08-19T04:19:34.941719+00:00</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.663450+00:00</t>
+          <t>2026-08-19T04:19:34.945124+00:00</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.665919+00:00</t>
+          <t>2026-08-19T04:19:34.948215+00:00</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.668337+00:00</t>
+          <t>2026-08-19T04:19:34.950805+00:00</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.670702+00:00</t>
+          <t>2026-08-19T04:19:34.953164+00:00</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.672904+00:00</t>
+          <t>2026-08-19T04:19:34.955612+00:00</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.675406+00:00</t>
+          <t>2026-08-19T04:19:34.958229+00:00</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.678241+00:00</t>
+          <t>2026-08-19T04:19:34.960639+00:00</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1513,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.680571+00:00</t>
+          <t>2026-08-19T04:19:34.962871+00:00</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.683820+00:00</t>
+          <t>2026-08-19T04:19:34.965403+00:00</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.686084+00:00</t>
+          <t>2026-08-19T04:19:34.967876+00:00</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.689196+00:00</t>
+          <t>2026-08-19T04:19:34.970275+00:00</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.691580+00:00</t>
+          <t>2026-08-19T04:19:34.972608+00:00</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.694469+00:00</t>
+          <t>2026-08-19T04:19:34.974995+00:00</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.696873+00:00</t>
+          <t>2026-08-19T04:19:34.977283+00:00</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.699593+00:00</t>
+          <t>2026-08-19T04:19:34.979649+00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.702215+00:00</t>
+          <t>2026-08-19T04:19:34.982016+00:00</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.928463+00:00</t>
+          <t>2026-08-19T04:19:35.140809+00:00</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.931464+00:00</t>
+          <t>2026-08-19T04:19:35.144096+00:00</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.936335+00:00</t>
+          <t>2026-08-19T04:19:35.146798+00:00</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.938735+00:00</t>
+          <t>2026-08-19T04:19:35.149224+00:00</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.152614+00:00</t>
+          <t>2026-08-19T04:19:35.420495+00:00</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.155903+00:00</t>
+          <t>2026-08-19T04:19:35.426173+00:00</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.232827+00:00</t>
+          <t>2026-08-19T04:19:35.444776+00:00</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.235566+00:00</t>
+          <t>2026-08-19T04:19:35.451751+00:00</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.237959+00:00</t>
+          <t>2026-08-19T04:19:35.454469+00:00</t>
         </is>
       </c>
     </row>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.240509+00:00</t>
+          <t>2026-08-19T04:19:35.457578+00:00</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.242852+00:00</t>
+          <t>2026-08-19T04:19:35.460698+00:00</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2053,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.245071+00:00</t>
+          <t>2026-08-19T04:19:35.463802+00:00</t>
         </is>
       </c>
     </row>
@@ -2080,12 +2080,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.248355+00:00</t>
+          <t>2026-08-19T04:19:35.466782+00:00</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.250902+00:00</t>
+          <t>2026-08-19T04:19:35.469802+00:00</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.253639+00:00</t>
+          <t>2026-08-19T04:19:35.472556+00:00</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.424550+00:00</t>
+          <t>2026-08-19T04:19:35.647728+00:00</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.427675+00:00</t>
+          <t>2026-08-19T04:19:35.650490+00:00</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.430377+00:00</t>
+          <t>2026-08-19T04:19:35.652971+00:00</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.432924+00:00</t>
+          <t>2026-08-19T04:19:35.655215+00:00</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.435406+00:00</t>
+          <t>2026-08-19T04:19:35.657576+00:00</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2296,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.442711+00:00</t>
+          <t>2026-08-19T04:19:35.664311+00:00</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.445054+00:00</t>
+          <t>2026-08-19T04:19:35.666490+00:00</t>
         </is>
       </c>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.447325+00:00</t>
+          <t>2026-08-19T04:19:35.668676+00:00</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.449740+00:00</t>
+          <t>2026-08-19T04:19:35.670858+00:00</t>
         </is>
       </c>
     </row>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.452444+00:00</t>
+          <t>2026-08-19T04:19:35.673084+00:00</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.454750+00:00</t>
+          <t>2026-08-19T04:19:35.675377+00:00</t>
         </is>
       </c>
     </row>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.457310+00:00</t>
+          <t>2026-08-19T04:19:35.678057+00:00</t>
         </is>
       </c>
     </row>
@@ -2485,12 +2485,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.459755+00:00</t>
+          <t>2026-08-19T04:19:35.680188+00:00</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.462178+00:00</t>
+          <t>2026-08-19T04:19:35.682376+00:00</t>
         </is>
       </c>
     </row>
@@ -2539,51 +2539,51 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.464459+00:00</t>
+          <t>2026-08-19T04:19:35.684720+00:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>established semiclassical gravity literature</t>
+          <t>compiler/backends/desi_fc005_pipeline.py</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.466982+00:00</t>
+          <t>2026-08-19T04:19:35.686967+00:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>spec section 18 (FC-005 build command)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2593,78 +2593,78 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.469173+00:00</t>
+          <t>2026-08-19T04:19:35.689252+00:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>compiler/backends/desi_fc005_pipeline.py</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:08.040098+00:00</t>
+          <t>2026-08-19T04:19:35.691473+00:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>compiler/falsification/eigen_uniqueness.py</t>
+          <t>established semiclassical gravity literature</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:08.066052+00:00</t>
+          <t>2026-08-19T04:19:35.693772+00:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>spec section 18 (FC-005 build command)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2674,100 +2674,100 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.647430+00:00</t>
+          <t>2026-08-19T04:19:35.695938+00:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/verification/fisher_information.py</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.941115+00:00</t>
+          <t>2026-08-19T04:19:36.255072+00:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/falsification/eigen_uniqueness.py</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.943419+00:00</t>
+          <t>2026-08-19T04:19:36.269508+00:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>spec section 10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.945552+00:00</t>
+          <t>2026-08-19T04:19:34.928694+00:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2777,83 +2777,83 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:06.947839+00:00</t>
+          <t>2026-08-19T04:19:35.151837+00:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.160827+00:00</t>
+          <t>2026-08-19T04:19:35.154067+00:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.163460+00:00</t>
+          <t>2026-08-19T04:19:35.157493+00:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2863,159 +2863,159 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.440226+00:00</t>
+          <t>2026-08-19T04:19:35.159875+00:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.224704+00:00</t>
+          <t>2026-08-19T04:19:35.428726+00:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_flow.py</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.227781+00:00</t>
+          <t>2026-08-19T04:19:35.433593+00:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.337576+00:00</t>
+          <t>2026-08-19T04:19:35.661986+00:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.340759+00:00</t>
+          <t>2026-08-19T04:19:35.440200+00:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+          <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.343940+00:00</t>
+          <t>2026-08-19T04:19:35.442491+00:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3025,24 +3025,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.346622+00:00</t>
+          <t>2026-08-19T04:19:35.561600+00:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.349197+00:00</t>
+          <t>2026-08-19T04:19:35.564539+00:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3079,24 +3079,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.351849+00:00</t>
+          <t>2026-08-19T04:19:35.567051+00:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3106,24 +3106,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.354522+00:00</t>
+          <t>2026-08-19T04:19:35.569543+00:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3133,24 +3133,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.357196+00:00</t>
+          <t>2026-08-19T04:19:35.571853+00:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3160,24 +3160,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.359457+00:00</t>
+          <t>2026-08-19T04:19:35.574227+00:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.361900+00:00</t>
+          <t>2026-08-19T04:19:35.579786+00:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.364416+00:00</t>
+          <t>2026-08-19T04:19:35.583608+00:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3241,24 +3241,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.366817+00:00</t>
+          <t>2026-08-19T04:19:35.586170+00:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.369891+00:00</t>
+          <t>2026-08-19T04:19:35.588631+00:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3295,24 +3295,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.372278+00:00</t>
+          <t>2026-08-19T04:19:35.590988+00:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3322,24 +3322,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.374619+00:00</t>
+          <t>2026-08-19T04:19:35.593244+00:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3349,24 +3349,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.377111+00:00</t>
+          <t>2026-08-19T04:19:35.595525+00:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3376,24 +3376,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.380274+00:00</t>
+          <t>2026-08-19T04:19:35.598129+00:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.382738+00:00</t>
+          <t>2026-08-19T04:19:35.600472+00:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3430,24 +3430,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.385798+00:00</t>
+          <t>2026-08-19T04:19:35.602993+00:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3457,24 +3457,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.388049+00:00</t>
+          <t>2026-08-19T04:19:35.605327+00:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3484,24 +3484,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.390501+00:00</t>
+          <t>2026-08-19T04:19:35.607415+00:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3511,24 +3511,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.392744+00:00</t>
+          <t>2026-08-19T04:19:35.609615+00:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3538,24 +3538,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.395051+00:00</t>
+          <t>2026-08-19T04:19:35.612148+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3565,24 +3565,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.397391+00:00</t>
+          <t>2026-08-19T04:19:35.614262+00:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3592,24 +3592,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.399625+00:00</t>
+          <t>2026-08-19T04:19:35.616738+00:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3619,24 +3619,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.401892+00:00</t>
+          <t>2026-08-19T04:19:35.618817+00:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.404376+00:00</t>
+          <t>2026-08-19T04:19:35.621240+00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.406531+00:00</t>
+          <t>2026-08-19T04:19:35.623508+00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3700,93 +3700,174 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.408960+00:00</t>
+          <t>2026-08-19T04:19:35.625650+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:07.437825+00:00</t>
+          <t>2026-08-19T04:19:35.628030+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-028</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>45b9fb9fef84</t>
+          <t>f092722ba01f</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T03:52:08.043322+00:00</t>
+          <t>2026-08-19T04:19:35.630804+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>f092722ba01f</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:19:35.633082+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>f092722ba01f</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:19:35.659795+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>f092722ba01f</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:19:36.258000+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>compiler/verification/fisher_information.py</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>45b9fb9fef84</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2026-08-19T03:52:08.046095+00:00</t>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>f092722ba01f</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-08-19T04:19:36.261607+00:00</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4069,6 +4150,84 @@
         <is>
           <t>curvature_closure
 E_kappa closure residual for DESI</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>stage_gate
+Stage 1: does L_tilde_(N,eps) converge under (N,eps) refinement? A property of the operator and the sampling, evaluated independently of any curvature or cosmological claim. See compiler/ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CURVATURE-CLOSURE-DESI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stage_gate
+Stage 2: only evaluated if stage 1 converged. Does E_kappa fall below the predefined tolerance? A property of the fitted heat-kernel coefficients, independent of any external/observational </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PHYSICAL-VALIDATION-DESI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>stage_gate
+Stage 3: only evaluated if stage 2 closed. Does kappa_spectral agree with an INDEPENDENTLY sourced kappa_cosmological (never derived from the same catalogue/run)? See compiler/backends/desi</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4744,7 +4903,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4754,14 +4913,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>E_SC[g] = G_munu + Lambda g_munu - (8piG/c^4)&lt;T_munu[g]&gt;_ren</t>
+          <t>Stage 1: does L_tilde_(N,eps) converge under (N,eps) refinement? A property of the operator and the sampling, evaluated independently of any curvature or cosmological claim. See compiler/backends/desi_fc005_pipeline.py::run_mathematical_convergence. On failure, the exact failed node id is reported (</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4771,22 +4930,73 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spec(H) does NOT determine H: 25/25 random trials confirm H' = U H U^dagger has identical spectrum (max residual 8.88e-16) while H' != H.</t>
+          <t xml:space="preserve">Stage 2: only evaluated if stage 1 converged. Does E_kappa fall below the predefined tolerance? A property of the fitted heat-kernel coefficients, independent of any external/observational comparison. See compiler/backends/desi_fc005_pipeline.py::run_curvature_closure. A stage-1 pass with a stage-2 </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>PHYSICAL-VALIDATION-DESI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Stage 3: only evaluated if stage 2 closed. Does kappa_spectral agree with an INDEPENDENTLY sourced kappa_cosmological (never derived from the same catalogue/run)? See compiler/backends/desi_fc005_pipeline.py::run_physical_validation, which raises rather than runs if no independent source is named.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>E_SC[g] = G_munu + Lambda g_munu - (8piG/c^4)&lt;T_munu[g]&gt;_ren</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SPEC-H-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Spec(H) does NOT determine H: 25/25 random trials confirm H' = U H U^dagger has identical spectrum (max residual 8.88e-16) while H' != H.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>SELECTION-SIGMA</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Transformation</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Sigma : M -&gt; {0,1}</t>
         </is>
@@ -4803,7 +5013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5959,7 +6169,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5969,19 +6179,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5996,14 +6206,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
+          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6013,19 +6223,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6035,7 +6245,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6047,12 +6257,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6062,58 +6272,58 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6123,19 +6333,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6145,19 +6355,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['GRAPH-G-SEED']</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6167,19 +6377,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6189,19 +6399,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6216,80 +6426,80 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['DIFFUSION-DISTANCE']</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6299,19 +6509,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6321,19 +6531,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6355,7 +6565,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6377,7 +6587,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6399,7 +6609,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6421,7 +6631,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6443,7 +6653,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6465,7 +6675,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6487,7 +6697,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6509,7 +6719,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6531,7 +6741,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6553,7 +6763,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6575,7 +6785,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6597,7 +6807,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6619,7 +6829,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6641,7 +6851,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6663,7 +6873,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6685,7 +6895,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6707,7 +6917,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6729,7 +6939,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6751,7 +6961,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6773,7 +6983,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6795,7 +7005,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6817,7 +7027,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6839,7 +7049,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6861,7 +7071,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6883,7 +7093,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6905,7 +7115,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6915,19 +7125,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>['S3-CURVATURE-CLOSURE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-028</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6937,32 +7147,98 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>['S3-CURVATURE-CLOSURE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>['FISHER-STATISTICAL-FAMILY']</t>
         </is>
@@ -7463,7 +7739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7812,10 +8088,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>stage_gate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>one of the three independently-reported FC-005 execution stages (mathematical convergence, curvature closure, physical validation); its status is never inferred from another stage_gate's status</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>workbook_reconciliation_record</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>provenance/precedence record for the four supplied FC-005 workbooks</t>
         </is>
@@ -7832,7 +8120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9249,39 +9537,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>semiclassical_framework_equation</t>
+          <t>stage_gate</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>observational_output</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>curvature_closure</t>
+          <t>stage_gate</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -9291,64 +9579,145 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
+          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>upstream_construction</t>
+          <t>observational_output</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>statistical_family</t>
+          <t>stage_gate</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>upstream_construction</t>
+          <t>observational_output</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>semiclassical_framework_equation</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>curvature_closure</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>statistical_family</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>operator_uniqueness_counterexample</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>upstream_construction</t>
         </is>
@@ -10817,7 +11186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11307,154 +11676,274 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GRAPH-G-SEED</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DIFFUSION-DISTANCE</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>GRAPH-G-SEED</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SPECTRUM-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T-HEATFLOW-TO-KERNEL</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SPECTRUM-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T-DIFFUSION-TO-METRIC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>DIFFUSION-DISTANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
@@ -11471,7 +11960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12045,79 +12534,79 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>requires a constructed quantum state rho_Q and a renormalized stress tensor &lt;T_munu&gt;_ren; neither is constructed in this build. This is reported as SEMICLASSICAL CLOSURE scope only, never as full quantum gravity (spec section 18).</t>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE. This gate's status is set independently by its own pipeline stage function when a real catalogue is executed -- never inferred from another gate's result and never force-closed.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OPEN OBSTRUCTION (spec section 7B / workbook R-003, TEST-006): eigenvalue-only spectral data cannot reconstruct the operator, and therefore cannot alone reconstruct a geometry (Spec(H) alone -&gt; g_munu is NOT claimed).</t>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE. This gate's status is set independently by its own pipeline stage function when a real catalogue is executed -- never inferred from another gate's result and never force-closed.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>PENDING DATA: blocked on DESI-CATALOGUE. This gate's status is set independently by its own pipeline stage function when a real catalogue is executed -- never inferred from another gate's result and never force-closed.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>requires a constructed quantum state rho_Q and a renormalized stress tensor &lt;T_munu&gt;_ren; neither is constructed in this build. This is reported as SEMICLASSICAL CLOSURE scope only, never as full quantum gravity (spec section 18).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>OPEN OBSTRUCTION (spec section 7B / workbook R-003, TEST-006): eigenvalue-only spectral data cannot reconstruct the operator, and therefore cannot alone reconstruct a geometry (Spec(H) alone -&gt; g_munu is NOT claimed).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12129,7 +12618,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12141,7 +12630,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -12153,7 +12642,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12165,7 +12654,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12177,7 +12666,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12189,115 +12678,115 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -12309,43 +12798,43 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -12357,55 +12846,55 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -12417,10 +12906,46 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>EQ-029</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -886,6 +886,23 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CALC-FC005-DESI-GATE1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>{'converged': False, 'tolerance': 0.15, 'failed_dependency': 'CONTINUUM-LIMIT-L-DESI'}</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1206,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.931802+00:00</t>
+          <t>2026-08-19T04:53:00.827172+00:00</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1233,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.934446+00:00</t>
+          <t>2026-08-19T04:53:00.829918+00:00</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1260,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.936927+00:00</t>
+          <t>2026-08-19T04:53:00.832176+00:00</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1287,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.939384+00:00</t>
+          <t>2026-08-19T04:53:00.834471+00:00</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1314,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.941719+00:00</t>
+          <t>2026-08-19T04:53:00.836599+00:00</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1341,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.945124+00:00</t>
+          <t>2026-08-19T04:53:00.838828+00:00</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1368,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.948215+00:00</t>
+          <t>2026-08-19T04:53:00.841706+00:00</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1395,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.950805+00:00</t>
+          <t>2026-08-19T04:53:00.845789+00:00</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1422,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.953164+00:00</t>
+          <t>2026-08-19T04:53:00.848046+00:00</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1449,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.955612+00:00</t>
+          <t>2026-08-19T04:53:00.850351+00:00</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1476,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.958229+00:00</t>
+          <t>2026-08-19T04:53:00.852853+00:00</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1503,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.960639+00:00</t>
+          <t>2026-08-19T04:53:00.855175+00:00</t>
         </is>
       </c>
     </row>
@@ -1513,12 +1530,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.962871+00:00</t>
+          <t>2026-08-19T04:53:00.857387+00:00</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1557,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.965403+00:00</t>
+          <t>2026-08-19T04:53:00.859759+00:00</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1584,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.967876+00:00</t>
+          <t>2026-08-19T04:53:00.861968+00:00</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1611,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.970275+00:00</t>
+          <t>2026-08-19T04:53:00.864114+00:00</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1638,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.972608+00:00</t>
+          <t>2026-08-19T04:53:00.866199+00:00</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1665,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.974995+00:00</t>
+          <t>2026-08-19T04:53:00.868459+00:00</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1692,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.977283+00:00</t>
+          <t>2026-08-19T04:53:00.870635+00:00</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1719,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.979649+00:00</t>
+          <t>2026-08-19T04:53:00.872845+00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1746,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.982016+00:00</t>
+          <t>2026-08-19T04:53:00.874916+00:00</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1773,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.140809+00:00</t>
+          <t>2026-08-19T04:53:01.002309+00:00</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1800,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.144096+00:00</t>
+          <t>2026-08-19T04:53:01.005166+00:00</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1827,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.146798+00:00</t>
+          <t>2026-08-19T04:53:01.007281+00:00</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1854,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.149224+00:00</t>
+          <t>2026-08-19T04:53:01.009394+00:00</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1881,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.420495+00:00</t>
+          <t>2026-08-19T04:53:01.196809+00:00</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1908,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.426173+00:00</t>
+          <t>2026-08-19T04:53:01.199527+00:00</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1935,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.444776+00:00</t>
+          <t>2026-08-19T04:53:01.214498+00:00</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1962,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.451751+00:00</t>
+          <t>2026-08-19T04:53:01.216629+00:00</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1989,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.454469+00:00</t>
+          <t>2026-08-19T04:53:01.221409+00:00</t>
         </is>
       </c>
     </row>
@@ -1999,12 +2016,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.457578+00:00</t>
+          <t>2026-08-19T04:53:01.223414+00:00</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2043,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.460698+00:00</t>
+          <t>2026-08-19T04:53:01.225462+00:00</t>
         </is>
       </c>
     </row>
@@ -2053,12 +2070,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.463802+00:00</t>
+          <t>2026-08-19T04:53:01.229452+00:00</t>
         </is>
       </c>
     </row>
@@ -2080,12 +2097,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.466782+00:00</t>
+          <t>2026-08-19T04:53:01.233469+00:00</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2124,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.469802+00:00</t>
+          <t>2026-08-19T04:53:01.236113+00:00</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2151,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.472556+00:00</t>
+          <t>2026-08-19T04:53:01.238234+00:00</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2178,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.647728+00:00</t>
+          <t>2026-08-19T04:53:01.396066+00:00</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2205,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.650490+00:00</t>
+          <t>2026-08-19T04:53:01.398256+00:00</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2232,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.652971+00:00</t>
+          <t>2026-08-19T04:53:01.400466+00:00</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2259,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.655215+00:00</t>
+          <t>2026-08-19T04:53:01.402555+00:00</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2286,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.657576+00:00</t>
+          <t>2026-08-19T04:53:01.404751+00:00</t>
         </is>
       </c>
     </row>
@@ -2286,22 +2303,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>repository + workspace filesystem audit</t>
+          <t>https://data.desi.lbl.gov/public/dr1/survey/catalogs/dr1/LSS/iron/LSScats/v1.5/LRG_SGC_clustering.dat.fits</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.664311+00:00</t>
+          <t>2026-08-19T04:53:03.926777+00:00</t>
         </is>
       </c>
     </row>
@@ -2313,22 +2330,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.666490+00:00</t>
+          <t>2026-08-19T04:53:03.929704+00:00</t>
         </is>
       </c>
     </row>
@@ -2340,22 +2357,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.668676+00:00</t>
+          <t>2026-08-19T04:53:03.932023+00:00</t>
         </is>
       </c>
     </row>
@@ -2367,22 +2384,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.670858+00:00</t>
+          <t>2026-08-19T04:53:03.934199+00:00</t>
         </is>
       </c>
     </row>
@@ -2394,22 +2411,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.673084+00:00</t>
+          <t>2026-08-19T04:53:03.936495+00:00</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2438,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2431,12 +2448,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.675377+00:00</t>
+          <t>2026-08-19T04:53:03.941504+00:00</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2465,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2458,12 +2475,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.678057+00:00</t>
+          <t>2026-08-19T04:53:03.945591+00:00</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2492,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2485,12 +2502,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.680188+00:00</t>
+          <t>2026-08-19T04:53:03.947843+00:00</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2519,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2512,12 +2529,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.682376+00:00</t>
+          <t>2026-08-19T04:53:03.950000+00:00</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2546,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_graph.py (not executed on real data)</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2539,12 +2556,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.684720+00:00</t>
+          <t>2026-08-19T04:53:03.952251+00:00</t>
         </is>
       </c>
     </row>
@@ -2561,17 +2578,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.686967+00:00</t>
+          <t>2026-08-19T04:53:03.954472+00:00</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2610,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.689252+00:00</t>
+          <t>2026-08-19T04:53:03.956698+00:00</t>
         </is>
       </c>
     </row>
@@ -2620,12 +2637,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.691473+00:00</t>
+          <t>2026-08-19T04:53:03.961509+00:00</t>
         </is>
       </c>
     </row>
@@ -2647,12 +2664,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.693772+00:00</t>
+          <t>2026-08-19T04:53:03.966098+00:00</t>
         </is>
       </c>
     </row>
@@ -2674,12 +2691,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.695938+00:00</t>
+          <t>2026-08-19T04:53:03.968675+00:00</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2718,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:36.255072+00:00</t>
+          <t>2026-08-19T04:53:04.454479+00:00</t>
         </is>
       </c>
     </row>
@@ -2728,12 +2745,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:36.269508+00:00</t>
+          <t>2026-08-19T04:53:04.468418+00:00</t>
         </is>
       </c>
     </row>
@@ -2755,12 +2772,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:34.928694+00:00</t>
+          <t>2026-08-19T04:53:00.823834+00:00</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2799,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.151837+00:00</t>
+          <t>2026-08-19T04:53:01.011426+00:00</t>
         </is>
       </c>
     </row>
@@ -2809,12 +2826,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.154067+00:00</t>
+          <t>2026-08-19T04:53:01.013518+00:00</t>
         </is>
       </c>
     </row>
@@ -2836,12 +2853,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.157493+00:00</t>
+          <t>2026-08-19T04:53:01.015521+00:00</t>
         </is>
       </c>
     </row>
@@ -2863,12 +2880,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.159875+00:00</t>
+          <t>2026-08-19T04:53:01.017578+00:00</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2907,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.428726+00:00</t>
+          <t>2026-08-19T04:53:01.201762+00:00</t>
         </is>
       </c>
     </row>
@@ -2917,12 +2934,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.433593+00:00</t>
+          <t>2026-08-19T04:53:01.204009+00:00</t>
         </is>
       </c>
     </row>
@@ -2944,12 +2961,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.661986+00:00</t>
+          <t>2026-08-19T04:53:01.409102+00:00</t>
         </is>
       </c>
     </row>
@@ -2971,12 +2988,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.440200+00:00</t>
+          <t>2026-08-19T04:53:01.210374+00:00</t>
         </is>
       </c>
     </row>
@@ -2998,12 +3015,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.442491+00:00</t>
+          <t>2026-08-19T04:53:01.212490+00:00</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3042,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.561600+00:00</t>
+          <t>2026-08-19T04:53:01.318394+00:00</t>
         </is>
       </c>
     </row>
@@ -3052,12 +3069,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.564539+00:00</t>
+          <t>2026-08-19T04:53:01.321218+00:00</t>
         </is>
       </c>
     </row>
@@ -3079,12 +3096,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.567051+00:00</t>
+          <t>2026-08-19T04:53:01.323707+00:00</t>
         </is>
       </c>
     </row>
@@ -3106,12 +3123,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.569543+00:00</t>
+          <t>2026-08-19T04:53:01.325932+00:00</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3150,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.571853+00:00</t>
+          <t>2026-08-19T04:53:01.328374+00:00</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3177,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.574227+00:00</t>
+          <t>2026-08-19T04:53:01.330601+00:00</t>
         </is>
       </c>
     </row>
@@ -3187,12 +3204,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.579786+00:00</t>
+          <t>2026-08-19T04:53:01.332725+00:00</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3231,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.583608+00:00</t>
+          <t>2026-08-19T04:53:01.335031+00:00</t>
         </is>
       </c>
     </row>
@@ -3241,12 +3258,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.586170+00:00</t>
+          <t>2026-08-19T04:53:01.337246+00:00</t>
         </is>
       </c>
     </row>
@@ -3268,12 +3285,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.588631+00:00</t>
+          <t>2026-08-19T04:53:01.339536+00:00</t>
         </is>
       </c>
     </row>
@@ -3295,12 +3312,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.590988+00:00</t>
+          <t>2026-08-19T04:53:01.342388+00:00</t>
         </is>
       </c>
     </row>
@@ -3322,12 +3339,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.593244+00:00</t>
+          <t>2026-08-19T04:53:01.344893+00:00</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3366,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.595525+00:00</t>
+          <t>2026-08-19T04:53:01.347036+00:00</t>
         </is>
       </c>
     </row>
@@ -3376,12 +3393,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.598129+00:00</t>
+          <t>2026-08-19T04:53:01.349223+00:00</t>
         </is>
       </c>
     </row>
@@ -3403,12 +3420,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.600472+00:00</t>
+          <t>2026-08-19T04:53:01.351668+00:00</t>
         </is>
       </c>
     </row>
@@ -3430,12 +3447,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.602993+00:00</t>
+          <t>2026-08-19T04:53:01.353699+00:00</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3474,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.605327+00:00</t>
+          <t>2026-08-19T04:53:01.355905+00:00</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3501,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.607415+00:00</t>
+          <t>2026-08-19T04:53:01.358184+00:00</t>
         </is>
       </c>
     </row>
@@ -3511,12 +3528,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.609615+00:00</t>
+          <t>2026-08-19T04:53:01.360394+00:00</t>
         </is>
       </c>
     </row>
@@ -3538,12 +3555,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.612148+00:00</t>
+          <t>2026-08-19T04:53:01.362483+00:00</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3582,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.614262+00:00</t>
+          <t>2026-08-19T04:53:01.364847+00:00</t>
         </is>
       </c>
     </row>
@@ -3592,12 +3609,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.616738+00:00</t>
+          <t>2026-08-19T04:53:01.366902+00:00</t>
         </is>
       </c>
     </row>
@@ -3619,12 +3636,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.618817+00:00</t>
+          <t>2026-08-19T04:53:01.369048+00:00</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3663,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.621240+00:00</t>
+          <t>2026-08-19T04:53:01.371237+00:00</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3690,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.623508+00:00</t>
+          <t>2026-08-19T04:53:01.373543+00:00</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3717,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.625650+00:00</t>
+          <t>2026-08-19T04:53:01.375657+00:00</t>
         </is>
       </c>
     </row>
@@ -3727,12 +3744,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.628030+00:00</t>
+          <t>2026-08-19T04:53:01.377723+00:00</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3771,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.630804+00:00</t>
+          <t>2026-08-19T04:53:01.379922+00:00</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3798,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.633082+00:00</t>
+          <t>2026-08-19T04:53:01.381985+00:00</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3825,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:35.659795+00:00</t>
+          <t>2026-08-19T04:53:01.406987+00:00</t>
         </is>
       </c>
     </row>
@@ -3835,12 +3852,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:36.258000+00:00</t>
+          <t>2026-08-19T04:53:04.457772+00:00</t>
         </is>
       </c>
     </row>
@@ -3862,12 +3879,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>f092722ba01f</t>
+          <t>6725c27fddfc</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-19T04:19:36.261607+00:00</t>
+          <t>2026-08-19T04:53:04.460386+00:00</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4019,7 +4036,7 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>pending_data_construction
-required: RA, DEC, z, and DESI weights (w_FKP, w_sys, ...) for a galaxy-level point catalogue. ABSENT from the repository, the current workspace, and all four supplied FC-005</t>
+DESI DR1 LRG SGC clustering catalogue, v1.5, real data acquired from the official public release and checksum-verified. Pilot fixture: 3000 objects (0.4&lt;=z&lt;0.6 subsample), us</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4095,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4096,135 +4113,161 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>spectral_data
+Spec(-Delta_h) via -L_tilde eigenproblem (sign-corrected, see desi_fc005_pipeline.py)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DESI-HEAT-TRACE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>heat_trace_function
 K(t) from the DESI-derived spectrum</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>KAPPA-DESI</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D9" t="b">
+      <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>curvature_closure
 kappa_spectral from DESI data</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>E-KAPPA-DESI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D10" t="b">
+      <c r="D11" t="b">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>curvature_closure
 E_kappa closure residual for DESI</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D11" t="b">
+      <c r="D12" t="b">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>stage_gate
 Stage 1: does L_tilde_(N,eps) converge under (N,eps) refinement? A property of the operator and the sampling, evaluated independently of any curvature or cosmological claim. See compiler/ba</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D12" t="b">
+      <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t xml:space="preserve">stage_gate
 Stage 2: only evaluated if stage 1 converged. Does E_kappa fall below the predefined tolerance? A property of the fitted heat-kernel coefficients, independent of any external/observational </t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D14" t="b">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>stage_gate
 Stage 3: only evaluated if stage 2 closed. Does kappa_spectral agree with an INDEPENDENTLY sourced kappa_cosmological (never derived from the same catalogue/run)? See compiler/backends/desi</t>
@@ -4280,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4733,7 +4776,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4743,14 +4786,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>required: RA, DEC, z, and DESI weights (w_FKP, w_sys, ...) for a galaxy-level point catalogue. ABSENT from the repository, the current workspace, and all four supplied FC-005 workbooks -- the primary workbook's own 'FC-005 Full Execution Index' sheet records this: 'No catalog file present in uploade</t>
+          <t>K(t) from the DESI-derived spectrum</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4760,14 +4803,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>G_DESI = (V,E,W): weighted observational graph from the DESI catalogue</t>
+          <t>(a0,a1,a2) fit</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4777,14 +4820,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>L_DESI = D - W</t>
+          <t>kappa_spectral from DESI data</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4794,14 +4837,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>L_tilde_(N,eps) = -L_N/(C_K N eps^(5/2)), d=3</t>
+          <t>E_kappa closure residual for DESI</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4811,14 +4854,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spec(Delta_h) via L_tilde eigenproblem</t>
+          <t>Delta_kappa = kappa_spectral - kappa_cosmological (independent cross-check)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4828,14 +4871,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>K(t) from the DESI-derived spectrum</t>
+          <t xml:space="preserve">Stage 2: only evaluated if stage 1 converged. Does E_kappa fall below the predefined tolerance? A property of the fitted heat-kernel coefficients, independent of any external/observational comparison. See compiler/backends/desi_fc005_pipeline.py::run_curvature_closure. A stage-1 pass with a stage-2 </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4845,14 +4888,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(a0,a1,a2) fit</t>
+          <t>Stage 3: only evaluated if stage 2 closed. Does kappa_spectral agree with an INDEPENDENTLY sourced kappa_cosmological (never derived from the same catalogue/run)? See compiler/backends/desi_fc005_pipeline.py::run_physical_validation, which raises rather than runs if no independent source is named.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4862,14 +4905,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kappa_spectral from DESI data</t>
+          <t>E_SC[g] = G_munu + Lambda g_munu - (8piG/c^4)&lt;T_munu[g]&gt;_ren</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4879,124 +4922,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>E_kappa closure residual for DESI</t>
+          <t>Spec(H) does NOT determine H: 25/25 random trials confirm H' = U H U^dagger has identical spectrum (max residual 8.88e-16) while H' != H.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
-        <is>
-          <t>Delta_kappa = kappa_spectral - kappa_cosmological (independent cross-check)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Stage 1: does L_tilde_(N,eps) converge under (N,eps) refinement? A property of the operator and the sampling, evaluated independently of any curvature or cosmological claim. See compiler/backends/desi_fc005_pipeline.py::run_mathematical_convergence. On failure, the exact failed node id is reported (</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stage 2: only evaluated if stage 1 converged. Does E_kappa fall below the predefined tolerance? A property of the fitted heat-kernel coefficients, independent of any external/observational comparison. See compiler/backends/desi_fc005_pipeline.py::run_curvature_closure. A stage-1 pass with a stage-2 </t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Stage 3: only evaluated if stage 2 closed. Does kappa_spectral agree with an INDEPENDENTLY sourced kappa_cosmological (never derived from the same catalogue/run)? See compiler/backends/desi_fc005_pipeline.py::run_physical_validation, which raises rather than runs if no independent source is named.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>E_SC[g] = G_munu + Lambda g_munu - (8piG/c^4)&lt;T_munu[g]&gt;_ren</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>SPEC-H-UNIQUENESS</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Spec(H) does NOT determine H: 25/25 random trials confirm H' = U H U^dagger has identical spectrum (max residual 8.88e-16) while H' != H.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>SELECTION-SIGMA</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Transformation</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
         <is>
           <t>Sigma : M -&gt; {0,1}</t>
         </is>
@@ -5959,7 +5900,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5981,7 +5922,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6003,7 +5944,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6025,7 +5966,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6047,7 +5988,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6179,7 +6120,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -9277,7 +9218,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -9304,7 +9245,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9331,7 +9272,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9358,7 +9299,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9385,7 +9326,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9547,7 +9488,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -11960,7 +11901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12419,194 +12360,194 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>STOP condition per spec section 25 of the FC-005 build command: required DESI data is absent. Not fabricated. Code path is implemented and unit-tested on synthetic data in compiler/backends/desi_graph.py.</t>
+          <t>Checksum-verified against the official DESI DR1 sha256 manifest (FC005_DESI_CATALOG_MANIFEST.json). See FC005_DESI_VALIDATION_REPORT.md for the full 12-point validation checklist (all PASSED).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+          <t>Executed live on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits (3000 real objects). Result: STOPPED at mathematical convergence: failed dependency 'CONTINUUM-LIMIT-L-DESI' -- low-spectrum relative change did not fall below tolerance 0.15 under refinement (last relative change 0.3124); L_tilde_(N,eps) does not show numerical evidence of convergence to Delta_h with this catalogue</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE (spec section 25 STOP condition). Pipeline code exists (compiler/backends/desi_graph.py) and is unit-tested on synthetic data only.</t>
+          <t>requires a constructed quantum state rho_Q and a renormalized stress tensor &lt;T_munu&gt;_ren; neither is constructed in this build. This is reported as SEMICLASSICAL CLOSURE scope only, never as full quantum gravity (spec section 18).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE. This gate's status is set independently by its own pipeline stage function when a real catalogue is executed -- never inferred from another gate's result and never force-closed.</t>
+          <t>OPEN OBSTRUCTION (spec section 7B / workbook R-003, TEST-006): eigenvalue-only spectral data cannot reconstruct the operator, and therefore cannot alone reconstruct a geometry (Spec(H) alone -&gt; g_munu is NOT claimed).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE. This gate's status is set independently by its own pipeline stage function when a real catalogue is executed -- never inferred from another gate's result and never force-closed.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PENDING DATA: blocked on DESI-CATALOGUE. This gate's status is set independently by its own pipeline stage function when a real catalogue is executed -- never inferred from another gate's result and never force-closed.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>requires a constructed quantum state rho_Q and a renormalized stress tensor &lt;T_munu&gt;_ren; neither is constructed in this build. This is reported as SEMICLASSICAL CLOSURE scope only, never as full quantum gravity (spec section 18).</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OPEN OBSTRUCTION (spec section 7B / workbook R-003, TEST-006): eigenvalue-only spectral data cannot reconstruct the operator, and therefore cannot alone reconstruct a geometry (Spec(H) alone -&gt; g_munu is NOT claimed).</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12618,7 +12559,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12630,7 +12571,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -12642,7 +12583,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12654,7 +12595,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12666,67 +12607,67 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12738,55 +12679,55 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -12798,31 +12739,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -12834,19 +12775,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -12858,94 +12799,46 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-028</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-029</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
-        <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>EQ-026</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>EQ-027</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>EQ-028</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>EQ-029</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
         <is>
           <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
@@ -13172,7 +13065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13643,6 +13536,28 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CALC-FC005-DESI-GATE1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>desi_mathematical_convergence_gate</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{'fixture': 'data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits', 'N_values': [300, 600, 1000, 1500], 'epsilon_values': [323.8912479953233, 257.07265389553453, 216.82347365130482, 189.41275087804553]}</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1206,12 +1206,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.827172+00:00</t>
+          <t>2026-08-19T07:54:47.576523+00:00</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.829918+00:00</t>
+          <t>2026-08-19T07:54:47.578836+00:00</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.832176+00:00</t>
+          <t>2026-08-19T07:54:47.580731+00:00</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.834471+00:00</t>
+          <t>2026-08-19T07:54:47.582823+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.836599+00:00</t>
+          <t>2026-08-19T07:54:47.584948+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.838828+00:00</t>
+          <t>2026-08-19T07:54:47.587010+00:00</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.841706+00:00</t>
+          <t>2026-08-19T07:54:47.588906+00:00</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.845789+00:00</t>
+          <t>2026-08-19T07:54:47.590851+00:00</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.848046+00:00</t>
+          <t>2026-08-19T07:54:47.592571+00:00</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.850351+00:00</t>
+          <t>2026-08-19T07:54:47.594649+00:00</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.852853+00:00</t>
+          <t>2026-08-19T07:54:47.596615+00:00</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.855175+00:00</t>
+          <t>2026-08-19T07:54:47.598496+00:00</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.857387+00:00</t>
+          <t>2026-08-19T07:54:47.600842+00:00</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.859759+00:00</t>
+          <t>2026-08-19T07:54:47.602651+00:00</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.861968+00:00</t>
+          <t>2026-08-19T07:54:47.604756+00:00</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.864114+00:00</t>
+          <t>2026-08-19T07:54:47.607045+00:00</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.866199+00:00</t>
+          <t>2026-08-19T07:54:47.608993+00:00</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.868459+00:00</t>
+          <t>2026-08-19T07:54:47.610879+00:00</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.870635+00:00</t>
+          <t>2026-08-19T07:54:47.612801+00:00</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.872845+00:00</t>
+          <t>2026-08-19T07:54:47.614727+00:00</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.874916+00:00</t>
+          <t>2026-08-19T07:54:47.616780+00:00</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.002309+00:00</t>
+          <t>2026-08-19T07:54:47.857117+00:00</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.005166+00:00</t>
+          <t>2026-08-19T07:54:47.859620+00:00</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.007281+00:00</t>
+          <t>2026-08-19T07:54:47.861777+00:00</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.009394+00:00</t>
+          <t>2026-08-19T07:54:47.863889+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.196809+00:00</t>
+          <t>2026-08-19T07:54:48.067519+00:00</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.199527+00:00</t>
+          <t>2026-08-19T07:54:48.069957+00:00</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1935,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.214498+00:00</t>
+          <t>2026-08-19T07:54:48.086066+00:00</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.216629+00:00</t>
+          <t>2026-08-19T07:54:48.088018+00:00</t>
         </is>
       </c>
     </row>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.221409+00:00</t>
+          <t>2026-08-19T07:54:48.092641+00:00</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.223414+00:00</t>
+          <t>2026-08-19T07:54:48.096766+00:00</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2043,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.225462+00:00</t>
+          <t>2026-08-19T07:54:48.101128+00:00</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.229452+00:00</t>
+          <t>2026-08-19T07:54:48.103219+00:00</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.233469+00:00</t>
+          <t>2026-08-19T07:54:48.105215+00:00</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.236113+00:00</t>
+          <t>2026-08-19T07:54:48.107289+00:00</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.238234+00:00</t>
+          <t>2026-08-19T07:54:48.113354+00:00</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.396066+00:00</t>
+          <t>2026-08-19T07:54:48.254492+00:00</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.398256+00:00</t>
+          <t>2026-08-19T07:54:48.256543+00:00</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.400466+00:00</t>
+          <t>2026-08-19T07:54:48.258577+00:00</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.402555+00:00</t>
+          <t>2026-08-19T07:54:48.260745+00:00</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.404751+00:00</t>
+          <t>2026-08-19T07:54:48.262556+00:00</t>
         </is>
       </c>
     </row>
@@ -2313,12 +2313,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.926777+00:00</t>
+          <t>2026-08-19T07:54:50.239784+00:00</t>
         </is>
       </c>
     </row>
@@ -2340,12 +2340,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.929704+00:00</t>
+          <t>2026-08-19T07:54:50.245258+00:00</t>
         </is>
       </c>
     </row>
@@ -2367,12 +2367,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.932023+00:00</t>
+          <t>2026-08-19T07:54:50.247478+00:00</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.934199+00:00</t>
+          <t>2026-08-19T07:54:50.249438+00:00</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.936495+00:00</t>
+          <t>2026-08-19T07:54:50.251238+00:00</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.941504+00:00</t>
+          <t>2026-08-19T07:54:50.253517+00:00</t>
         </is>
       </c>
     </row>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.945591+00:00</t>
+          <t>2026-08-19T07:54:50.256722+00:00</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.947843+00:00</t>
+          <t>2026-08-19T07:54:50.260604+00:00</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2529,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.950000+00:00</t>
+          <t>2026-08-19T07:54:50.264664+00:00</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.952251+00:00</t>
+          <t>2026-08-19T07:54:50.266534+00:00</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.954472+00:00</t>
+          <t>2026-08-19T07:54:50.272741+00:00</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.956698+00:00</t>
+          <t>2026-08-19T07:54:50.276762+00:00</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.961509+00:00</t>
+          <t>2026-08-19T07:54:50.278433+00:00</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.966098+00:00</t>
+          <t>2026-08-19T07:54:50.280365+00:00</t>
         </is>
       </c>
     </row>
@@ -2691,12 +2691,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:03.968675+00:00</t>
+          <t>2026-08-19T07:54:50.284622+00:00</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:04.454479+00:00</t>
+          <t>2026-08-19T07:54:50.654011+00:00</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:04.468418+00:00</t>
+          <t>2026-08-19T07:54:50.665176+00:00</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:00.823834+00:00</t>
+          <t>2026-08-19T07:54:47.574031+00:00</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2799,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.011426+00:00</t>
+          <t>2026-08-19T07:54:47.865827+00:00</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.013518+00:00</t>
+          <t>2026-08-19T07:54:47.868855+00:00</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2853,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.015521+00:00</t>
+          <t>2026-08-19T07:54:47.872738+00:00</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.017578+00:00</t>
+          <t>2026-08-19T07:54:47.876663+00:00</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.201762+00:00</t>
+          <t>2026-08-19T07:54:48.072300+00:00</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2934,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.204009+00:00</t>
+          <t>2026-08-19T07:54:48.076981+00:00</t>
         </is>
       </c>
     </row>
@@ -2961,12 +2961,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.409102+00:00</t>
+          <t>2026-08-19T07:54:48.266291+00:00</t>
         </is>
       </c>
     </row>
@@ -2988,12 +2988,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.210374+00:00</t>
+          <t>2026-08-19T07:54:48.082371+00:00</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3015,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.212490+00:00</t>
+          <t>2026-08-19T07:54:48.084271+00:00</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3042,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.318394+00:00</t>
+          <t>2026-08-19T07:54:48.186179+00:00</t>
         </is>
       </c>
     </row>
@@ -3069,12 +3069,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.321218+00:00</t>
+          <t>2026-08-19T07:54:48.189012+00:00</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.323707+00:00</t>
+          <t>2026-08-19T07:54:48.191551+00:00</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.325932+00:00</t>
+          <t>2026-08-19T07:54:48.193583+00:00</t>
         </is>
       </c>
     </row>
@@ -3150,12 +3150,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.328374+00:00</t>
+          <t>2026-08-19T07:54:48.196460+00:00</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.330601+00:00</t>
+          <t>2026-08-19T07:54:48.198380+00:00</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.332725+00:00</t>
+          <t>2026-08-19T07:54:48.200306+00:00</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.335031+00:00</t>
+          <t>2026-08-19T07:54:48.202597+00:00</t>
         </is>
       </c>
     </row>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.337246+00:00</t>
+          <t>2026-08-19T07:54:48.204791+00:00</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.339536+00:00</t>
+          <t>2026-08-19T07:54:48.206647+00:00</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3312,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.342388+00:00</t>
+          <t>2026-08-19T07:54:48.208882+00:00</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.344893+00:00</t>
+          <t>2026-08-19T07:54:48.210815+00:00</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.347036+00:00</t>
+          <t>2026-08-19T07:54:48.212780+00:00</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.349223+00:00</t>
+          <t>2026-08-19T07:54:48.214593+00:00</t>
         </is>
       </c>
     </row>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.351668+00:00</t>
+          <t>2026-08-19T07:54:48.216352+00:00</t>
         </is>
       </c>
     </row>
@@ -3447,12 +3447,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.353699+00:00</t>
+          <t>2026-08-19T07:54:48.218678+00:00</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.355905+00:00</t>
+          <t>2026-08-19T07:54:48.221034+00:00</t>
         </is>
       </c>
     </row>
@@ -3501,12 +3501,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.358184+00:00</t>
+          <t>2026-08-19T07:54:48.223123+00:00</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3528,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.360394+00:00</t>
+          <t>2026-08-19T07:54:48.225606+00:00</t>
         </is>
       </c>
     </row>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.362483+00:00</t>
+          <t>2026-08-19T07:54:48.227679+00:00</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.364847+00:00</t>
+          <t>2026-08-19T07:54:48.229741+00:00</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3609,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.366902+00:00</t>
+          <t>2026-08-19T07:54:48.231785+00:00</t>
         </is>
       </c>
     </row>
@@ -3636,12 +3636,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.369048+00:00</t>
+          <t>2026-08-19T07:54:48.233593+00:00</t>
         </is>
       </c>
     </row>
@@ -3663,12 +3663,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.371237+00:00</t>
+          <t>2026-08-19T07:54:48.235613+00:00</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.373543+00:00</t>
+          <t>2026-08-19T07:54:48.237427+00:00</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3717,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.375657+00:00</t>
+          <t>2026-08-19T07:54:48.239483+00:00</t>
         </is>
       </c>
     </row>
@@ -3744,12 +3744,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.377723+00:00</t>
+          <t>2026-08-19T07:54:48.241328+00:00</t>
         </is>
       </c>
     </row>
@@ -3771,12 +3771,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.379922+00:00</t>
+          <t>2026-08-19T07:54:48.243128+00:00</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.381985+00:00</t>
+          <t>2026-08-19T07:54:48.244965+00:00</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:01.406987+00:00</t>
+          <t>2026-08-19T07:54:48.264401+00:00</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:04.457772+00:00</t>
+          <t>2026-08-19T07:54:50.656950+00:00</t>
         </is>
       </c>
     </row>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6725c27fddfc</t>
+          <t>fad9f659caa1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-19T04:53:04.460386+00:00</t>
+          <t>2026-08-19T07:54:50.659765+00:00</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Executed live on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits (3000 real objects). Result: STOPPED at mathematical convergence: failed dependency 'CONTINUUM-LIMIT-L-DESI' -- low-spectrum relative change did not fall below tolerance 0.15 under refinement (last relative change 0.3124); L_tilde_(N,eps) does not show numerical evidence of convergence to Delta_h with this catalogue</t>
+          <t>Executed live on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits (3000 real objects). Result: STOPPED at mathematical convergence: failed dependency 'CONTINUUM-LIMIT-L-DESI' -- low-spectrum relative change did not fall below tolerance 0.15 under refinement (last relative change 0.7028); L_tilde_(N,eps) does not show numerical evidence of convergence to Delta_h with this catalogue</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13549,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'fixture': 'data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits', 'N_values': [300, 600, 1000, 1500], 'epsilon_values': [323.8912479953233, 257.07265389553453, 216.82347365130482, 189.41275087804553]}</t>
+          <t>{'fixture': 'data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits', 'N_values': [300, 600, 1000, 1500], 'epsilon_values': [107.9635898398022, 85.6907580429826, 72.27438444792013, 63.137490354544]}</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -903,6 +903,23 @@
       <c r="C22" t="inlineStr">
         <is>
           <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CALC-FC005-DESI-SPARSE-N-SCALING</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>{'purpose': 'separate finite-resolution failure from point-process failure for CONTINUUM-LIMIT-L-DESI, per FC005_CONTINUUM_DIAGNOSTIC_REPORT.md section 16'}</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1223,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.576523+00:00</t>
+          <t>2026-08-19T15:56:35.520569+00:00</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1250,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.578836+00:00</t>
+          <t>2026-08-19T15:56:35.522782+00:00</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1277,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.580731+00:00</t>
+          <t>2026-08-19T15:56:35.525042+00:00</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1304,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.582823+00:00</t>
+          <t>2026-08-19T15:56:35.527117+00:00</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1331,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.584948+00:00</t>
+          <t>2026-08-19T15:56:35.529323+00:00</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1358,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.587010+00:00</t>
+          <t>2026-08-19T15:56:35.531280+00:00</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1385,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.588906+00:00</t>
+          <t>2026-08-19T15:56:35.533341+00:00</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1412,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.590851+00:00</t>
+          <t>2026-08-19T15:56:35.535575+00:00</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1439,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.592571+00:00</t>
+          <t>2026-08-19T15:56:35.538039+00:00</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1466,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.594649+00:00</t>
+          <t>2026-08-19T15:56:35.540117+00:00</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1493,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.596615+00:00</t>
+          <t>2026-08-19T15:56:35.542093+00:00</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1520,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.598496+00:00</t>
+          <t>2026-08-19T15:56:35.544295+00:00</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1547,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.600842+00:00</t>
+          <t>2026-08-19T15:56:35.546288+00:00</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1574,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.602651+00:00</t>
+          <t>2026-08-19T15:56:35.548322+00:00</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1601,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.604756+00:00</t>
+          <t>2026-08-19T15:56:35.550314+00:00</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1628,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.607045+00:00</t>
+          <t>2026-08-19T15:56:35.552329+00:00</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1655,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.608993+00:00</t>
+          <t>2026-08-19T15:56:35.554358+00:00</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1682,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.610879+00:00</t>
+          <t>2026-08-19T15:56:35.556410+00:00</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1709,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.612801+00:00</t>
+          <t>2026-08-19T15:56:35.558366+00:00</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1736,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.614727+00:00</t>
+          <t>2026-08-19T15:56:35.560343+00:00</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1763,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.616780+00:00</t>
+          <t>2026-08-19T15:56:35.562268+00:00</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1790,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.857117+00:00</t>
+          <t>2026-08-19T15:56:35.749295+00:00</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1817,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.859620+00:00</t>
+          <t>2026-08-19T15:56:35.752059+00:00</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1844,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.861777+00:00</t>
+          <t>2026-08-19T15:56:35.757373+00:00</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1871,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.863889+00:00</t>
+          <t>2026-08-19T15:56:35.759475+00:00</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1898,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.067519+00:00</t>
+          <t>2026-08-19T15:56:35.932389+00:00</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1925,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.069957+00:00</t>
+          <t>2026-08-19T15:56:35.934802+00:00</t>
         </is>
       </c>
     </row>
@@ -1935,12 +1952,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.086066+00:00</t>
+          <t>2026-08-19T15:56:35.952237+00:00</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1979,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.088018+00:00</t>
+          <t>2026-08-19T15:56:35.954293+00:00</t>
         </is>
       </c>
     </row>
@@ -1989,12 +2006,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.092641+00:00</t>
+          <t>2026-08-19T15:56:35.957218+00:00</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2033,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.096766+00:00</t>
+          <t>2026-08-19T15:56:35.959224+00:00</t>
         </is>
       </c>
     </row>
@@ -2043,12 +2060,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.101128+00:00</t>
+          <t>2026-08-19T15:56:35.961825+00:00</t>
         </is>
       </c>
     </row>
@@ -2070,12 +2087,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.103219+00:00</t>
+          <t>2026-08-19T15:56:35.964531+00:00</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2114,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.105215+00:00</t>
+          <t>2026-08-19T15:56:35.967682+00:00</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2141,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.107289+00:00</t>
+          <t>2026-08-19T15:56:35.969944+00:00</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2168,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.113354+00:00</t>
+          <t>2026-08-19T15:56:35.972462+00:00</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2195,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.254492+00:00</t>
+          <t>2026-08-19T15:56:36.111583+00:00</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2222,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.256543+00:00</t>
+          <t>2026-08-19T15:56:36.113642+00:00</t>
         </is>
       </c>
     </row>
@@ -2232,12 +2249,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.258577+00:00</t>
+          <t>2026-08-19T15:56:36.115577+00:00</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2276,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.260745+00:00</t>
+          <t>2026-08-19T15:56:36.117571+00:00</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2303,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.262556+00:00</t>
+          <t>2026-08-19T15:56:36.119580+00:00</t>
         </is>
       </c>
     </row>
@@ -2313,12 +2330,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.239784+00:00</t>
+          <t>2026-08-19T15:56:38.177810+00:00</t>
         </is>
       </c>
     </row>
@@ -2340,12 +2357,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.245258+00:00</t>
+          <t>2026-08-19T15:56:38.180360+00:00</t>
         </is>
       </c>
     </row>
@@ -2367,12 +2384,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.247478+00:00</t>
+          <t>2026-08-19T15:56:38.182368+00:00</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2411,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.249438+00:00</t>
+          <t>2026-08-19T15:56:38.184389+00:00</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2438,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.251238+00:00</t>
+          <t>2026-08-19T15:56:38.189226+00:00</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2465,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.253517+00:00</t>
+          <t>2026-08-19T15:56:38.193288+00:00</t>
         </is>
       </c>
     </row>
@@ -2475,12 +2492,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.256722+00:00</t>
+          <t>2026-08-19T15:56:38.195235+00:00</t>
         </is>
       </c>
     </row>
@@ -2502,12 +2519,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.260604+00:00</t>
+          <t>2026-08-19T15:56:38.197275+00:00</t>
         </is>
       </c>
     </row>
@@ -2529,12 +2546,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.264664+00:00</t>
+          <t>2026-08-19T15:56:38.201174+00:00</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2573,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.266534+00:00</t>
+          <t>2026-08-19T15:56:38.205161+00:00</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2600,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.272741+00:00</t>
+          <t>2026-08-19T15:56:38.209217+00:00</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2627,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.276762+00:00</t>
+          <t>2026-08-19T15:56:38.213763+00:00</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2654,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.278433+00:00</t>
+          <t>2026-08-19T15:56:38.215901+00:00</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2681,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.280365+00:00</t>
+          <t>2026-08-19T15:56:38.217933+00:00</t>
         </is>
       </c>
     </row>
@@ -2691,12 +2708,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.284622+00:00</t>
+          <t>2026-08-19T15:56:38.219885+00:00</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2735,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.654011+00:00</t>
+          <t>2026-08-19T15:56:38.633536+00:00</t>
         </is>
       </c>
     </row>
@@ -2745,12 +2762,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.665176+00:00</t>
+          <t>2026-08-19T15:56:38.643884+00:00</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2789,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.574031+00:00</t>
+          <t>2026-08-19T15:56:35.517920+00:00</t>
         </is>
       </c>
     </row>
@@ -2799,12 +2816,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.865827+00:00</t>
+          <t>2026-08-19T15:56:35.761372+00:00</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2843,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.868855+00:00</t>
+          <t>2026-08-19T15:56:35.763324+00:00</t>
         </is>
       </c>
     </row>
@@ -2853,12 +2870,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.872738+00:00</t>
+          <t>2026-08-19T15:56:35.765274+00:00</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2897,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:47.876663+00:00</t>
+          <t>2026-08-19T15:56:35.767200+00:00</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2924,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.072300+00:00</t>
+          <t>2026-08-19T15:56:35.937020+00:00</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2951,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.076981+00:00</t>
+          <t>2026-08-19T15:56:35.941682+00:00</t>
         </is>
       </c>
     </row>
@@ -2961,12 +2978,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.266291+00:00</t>
+          <t>2026-08-19T15:56:36.123454+00:00</t>
         </is>
       </c>
     </row>
@@ -2988,12 +3005,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.082371+00:00</t>
+          <t>2026-08-19T15:56:35.947549+00:00</t>
         </is>
       </c>
     </row>
@@ -3015,12 +3032,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.084271+00:00</t>
+          <t>2026-08-19T15:56:35.949797+00:00</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3059,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.186179+00:00</t>
+          <t>2026-08-19T15:56:36.044991+00:00</t>
         </is>
       </c>
     </row>
@@ -3069,12 +3086,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.189012+00:00</t>
+          <t>2026-08-19T15:56:36.047456+00:00</t>
         </is>
       </c>
     </row>
@@ -3096,12 +3113,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.191551+00:00</t>
+          <t>2026-08-19T15:56:36.049599+00:00</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3140,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.193583+00:00</t>
+          <t>2026-08-19T15:56:36.051670+00:00</t>
         </is>
       </c>
     </row>
@@ -3150,12 +3167,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.196460+00:00</t>
+          <t>2026-08-19T15:56:36.053759+00:00</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3194,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.198380+00:00</t>
+          <t>2026-08-19T15:56:36.056025+00:00</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3221,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.200306+00:00</t>
+          <t>2026-08-19T15:56:36.058008+00:00</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3248,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.202597+00:00</t>
+          <t>2026-08-19T15:56:36.059985+00:00</t>
         </is>
       </c>
     </row>
@@ -3258,12 +3275,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.204791+00:00</t>
+          <t>2026-08-19T15:56:36.061913+00:00</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3302,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.206647+00:00</t>
+          <t>2026-08-19T15:56:36.063954+00:00</t>
         </is>
       </c>
     </row>
@@ -3312,12 +3329,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.208882+00:00</t>
+          <t>2026-08-19T15:56:36.065863+00:00</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3356,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.210815+00:00</t>
+          <t>2026-08-19T15:56:36.067858+00:00</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3383,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.212780+00:00</t>
+          <t>2026-08-19T15:56:36.069810+00:00</t>
         </is>
       </c>
     </row>
@@ -3393,12 +3410,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.214593+00:00</t>
+          <t>2026-08-19T15:56:36.071850+00:00</t>
         </is>
       </c>
     </row>
@@ -3420,12 +3437,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.216352+00:00</t>
+          <t>2026-08-19T15:56:36.073748+00:00</t>
         </is>
       </c>
     </row>
@@ -3447,12 +3464,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.218678+00:00</t>
+          <t>2026-08-19T15:56:36.075940+00:00</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3491,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.221034+00:00</t>
+          <t>2026-08-19T15:56:36.077926+00:00</t>
         </is>
       </c>
     </row>
@@ -3501,12 +3518,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.223123+00:00</t>
+          <t>2026-08-19T15:56:36.079929+00:00</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3545,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.225606+00:00</t>
+          <t>2026-08-19T15:56:36.081874+00:00</t>
         </is>
       </c>
     </row>
@@ -3555,12 +3572,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.227679+00:00</t>
+          <t>2026-08-19T15:56:36.083880+00:00</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3599,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.229741+00:00</t>
+          <t>2026-08-19T15:56:36.085758+00:00</t>
         </is>
       </c>
     </row>
@@ -3609,12 +3626,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.231785+00:00</t>
+          <t>2026-08-19T15:56:36.087727+00:00</t>
         </is>
       </c>
     </row>
@@ -3636,12 +3653,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.233593+00:00</t>
+          <t>2026-08-19T15:56:36.089609+00:00</t>
         </is>
       </c>
     </row>
@@ -3663,12 +3680,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.235613+00:00</t>
+          <t>2026-08-19T15:56:36.091499+00:00</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3707,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.237427+00:00</t>
+          <t>2026-08-19T15:56:36.093368+00:00</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3734,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.239483+00:00</t>
+          <t>2026-08-19T15:56:36.095251+00:00</t>
         </is>
       </c>
     </row>
@@ -3744,12 +3761,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.241328+00:00</t>
+          <t>2026-08-19T15:56:36.097162+00:00</t>
         </is>
       </c>
     </row>
@@ -3771,12 +3788,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.243128+00:00</t>
+          <t>2026-08-19T15:56:36.099072+00:00</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3815,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.244965+00:00</t>
+          <t>2026-08-19T15:56:36.100958+00:00</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3842,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:48.264401+00:00</t>
+          <t>2026-08-19T15:56:36.121547+00:00</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3869,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.656950+00:00</t>
+          <t>2026-08-19T15:56:38.636011+00:00</t>
         </is>
       </c>
     </row>
@@ -3879,12 +3896,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>fad9f659caa1</t>
+          <t>257d347dc0c6</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-19T07:54:50.659765+00:00</t>
+          <t>2026-08-19T15:56:38.638212+00:00</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13558,6 +13575,28 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CALC-FC005-DESI-SPARSE-N-SCALING</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>desi_sparse_n_scaling_point_process_separation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{'report': 'FC005_N_SCALING_REPORT.md', 'raw_data': 'data/desi/dr1/fc005/derived/sparse_n_scaling_full_results.json'}</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1223,12 +1223,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.520569+00:00</t>
+          <t>2026-08-19T16:09:23.424534+00:00</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.522782+00:00</t>
+          <t>2026-08-19T16:09:23.426601+00:00</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.525042+00:00</t>
+          <t>2026-08-19T16:09:23.429367+00:00</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.527117+00:00</t>
+          <t>2026-08-19T16:09:23.431979+00:00</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.529323+00:00</t>
+          <t>2026-08-19T16:09:23.434553+00:00</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.531280+00:00</t>
+          <t>2026-08-19T16:09:23.436558+00:00</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.533341+00:00</t>
+          <t>2026-08-19T16:09:23.438500+00:00</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.535575+00:00</t>
+          <t>2026-08-19T16:09:23.440489+00:00</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.538039+00:00</t>
+          <t>2026-08-19T16:09:23.442547+00:00</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.540117+00:00</t>
+          <t>2026-08-19T16:09:23.444527+00:00</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.542093+00:00</t>
+          <t>2026-08-19T16:09:23.446422+00:00</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.544295+00:00</t>
+          <t>2026-08-19T16:09:23.448384+00:00</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.546288+00:00</t>
+          <t>2026-08-19T16:09:23.450381+00:00</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.548322+00:00</t>
+          <t>2026-08-19T16:09:23.452491+00:00</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.550314+00:00</t>
+          <t>2026-08-19T16:09:23.454376+00:00</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.552329+00:00</t>
+          <t>2026-08-19T16:09:23.456376+00:00</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.554358+00:00</t>
+          <t>2026-08-19T16:09:23.458857+00:00</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.556410+00:00</t>
+          <t>2026-08-19T16:09:23.460835+00:00</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.558366+00:00</t>
+          <t>2026-08-19T16:09:23.463290+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.560343+00:00</t>
+          <t>2026-08-19T16:09:23.465278+00:00</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.562268+00:00</t>
+          <t>2026-08-19T16:09:23.467788+00:00</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.749295+00:00</t>
+          <t>2026-08-19T16:09:23.593422+00:00</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.752059+00:00</t>
+          <t>2026-08-19T16:09:23.596228+00:00</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.757373+00:00</t>
+          <t>2026-08-19T16:09:23.598267+00:00</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.759475+00:00</t>
+          <t>2026-08-19T16:09:23.600227+00:00</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.932389+00:00</t>
+          <t>2026-08-19T16:09:23.765942+00:00</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.934802+00:00</t>
+          <t>2026-08-19T16:09:23.768894+00:00</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.952237+00:00</t>
+          <t>2026-08-19T16:09:23.782486+00:00</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.954293+00:00</t>
+          <t>2026-08-19T16:09:23.784485+00:00</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.957218+00:00</t>
+          <t>2026-08-19T16:09:23.786433+00:00</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.959224+00:00</t>
+          <t>2026-08-19T16:09:23.788425+00:00</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.961825+00:00</t>
+          <t>2026-08-19T16:09:23.790364+00:00</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.964531+00:00</t>
+          <t>2026-08-19T16:09:23.792349+00:00</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.967682+00:00</t>
+          <t>2026-08-19T16:09:23.794275+00:00</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.969944+00:00</t>
+          <t>2026-08-19T16:09:23.796251+00:00</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.972462+00:00</t>
+          <t>2026-08-19T16:09:23.798171+00:00</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.111583+00:00</t>
+          <t>2026-08-19T16:09:23.938892+00:00</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.113642+00:00</t>
+          <t>2026-08-19T16:09:23.941929+00:00</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.115577+00:00</t>
+          <t>2026-08-19T16:09:23.944598+00:00</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.117571+00:00</t>
+          <t>2026-08-19T16:09:23.946579+00:00</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.119580+00:00</t>
+          <t>2026-08-19T16:09:23.948783+00:00</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.177810+00:00</t>
+          <t>2026-08-19T16:09:26.182919+00:00</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.180360+00:00</t>
+          <t>2026-08-19T16:09:26.185585+00:00</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.182368+00:00</t>
+          <t>2026-08-19T16:09:26.187798+00:00</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.184389+00:00</t>
+          <t>2026-08-19T16:09:26.189894+00:00</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.189226+00:00</t>
+          <t>2026-08-19T16:09:26.192084+00:00</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.193288+00:00</t>
+          <t>2026-08-19T16:09:26.194450+00:00</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.195235+00:00</t>
+          <t>2026-08-19T16:09:26.196495+00:00</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.197275+00:00</t>
+          <t>2026-08-19T16:09:26.198576+00:00</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.201174+00:00</t>
+          <t>2026-08-19T16:09:26.200600+00:00</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.205161+00:00</t>
+          <t>2026-08-19T16:09:26.202563+00:00</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.209217+00:00</t>
+          <t>2026-08-19T16:09:26.204614+00:00</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.213763+00:00</t>
+          <t>2026-08-19T16:09:26.206728+00:00</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.215901+00:00</t>
+          <t>2026-08-19T16:09:26.208756+00:00</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.217933+00:00</t>
+          <t>2026-08-19T16:09:26.210773+00:00</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2708,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.219885+00:00</t>
+          <t>2026-08-19T16:09:26.212857+00:00</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.633536+00:00</t>
+          <t>2026-08-19T16:09:26.622107+00:00</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.643884+00:00</t>
+          <t>2026-08-19T16:09:26.633428+00:00</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.517920+00:00</t>
+          <t>2026-08-19T16:09:23.422012+00:00</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2816,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.761372+00:00</t>
+          <t>2026-08-19T16:09:23.602133+00:00</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.763324+00:00</t>
+          <t>2026-08-19T16:09:23.604147+00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.765274+00:00</t>
+          <t>2026-08-19T16:09:23.606016+00:00</t>
         </is>
       </c>
     </row>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.767200+00:00</t>
+          <t>2026-08-19T16:09:23.607958+00:00</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.937020+00:00</t>
+          <t>2026-08-19T16:09:23.770949+00:00</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.941682+00:00</t>
+          <t>2026-08-19T16:09:23.772915+00:00</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.123454+00:00</t>
+          <t>2026-08-19T16:09:23.952915+00:00</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.947549+00:00</t>
+          <t>2026-08-19T16:09:23.778424+00:00</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:35.949797+00:00</t>
+          <t>2026-08-19T16:09:23.780457+00:00</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.044991+00:00</t>
+          <t>2026-08-19T16:09:23.867349+00:00</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.047456+00:00</t>
+          <t>2026-08-19T16:09:23.869809+00:00</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.049599+00:00</t>
+          <t>2026-08-19T16:09:23.871966+00:00</t>
         </is>
       </c>
     </row>
@@ -3140,12 +3140,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.051670+00:00</t>
+          <t>2026-08-19T16:09:23.874173+00:00</t>
         </is>
       </c>
     </row>
@@ -3167,12 +3167,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.053759+00:00</t>
+          <t>2026-08-19T16:09:23.876358+00:00</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.056025+00:00</t>
+          <t>2026-08-19T16:09:23.878530+00:00</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.058008+00:00</t>
+          <t>2026-08-19T16:09:23.880602+00:00</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.059985+00:00</t>
+          <t>2026-08-19T16:09:23.882558+00:00</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.061913+00:00</t>
+          <t>2026-08-19T16:09:23.884736+00:00</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.063954+00:00</t>
+          <t>2026-08-19T16:09:23.886852+00:00</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.065863+00:00</t>
+          <t>2026-08-19T16:09:23.888850+00:00</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.067858+00:00</t>
+          <t>2026-08-19T16:09:23.890842+00:00</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.069810+00:00</t>
+          <t>2026-08-19T16:09:23.893037+00:00</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3410,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.071850+00:00</t>
+          <t>2026-08-19T16:09:23.895181+00:00</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.073748+00:00</t>
+          <t>2026-08-19T16:09:23.897385+00:00</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.075940+00:00</t>
+          <t>2026-08-19T16:09:23.899305+00:00</t>
         </is>
       </c>
     </row>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.077926+00:00</t>
+          <t>2026-08-19T16:09:23.901213+00:00</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.079929+00:00</t>
+          <t>2026-08-19T16:09:23.903125+00:00</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.081874+00:00</t>
+          <t>2026-08-19T16:09:23.905271+00:00</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.083880+00:00</t>
+          <t>2026-08-19T16:09:23.907652+00:00</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.085758+00:00</t>
+          <t>2026-08-19T16:09:23.909518+00:00</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.087727+00:00</t>
+          <t>2026-08-19T16:09:23.912171+00:00</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.089609+00:00</t>
+          <t>2026-08-19T16:09:23.914003+00:00</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.091499+00:00</t>
+          <t>2026-08-19T16:09:23.916059+00:00</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.093368+00:00</t>
+          <t>2026-08-19T16:09:23.917889+00:00</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.095251+00:00</t>
+          <t>2026-08-19T16:09:23.919933+00:00</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.097162+00:00</t>
+          <t>2026-08-19T16:09:23.921972+00:00</t>
         </is>
       </c>
     </row>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.099072+00:00</t>
+          <t>2026-08-19T16:09:23.924143+00:00</t>
         </is>
       </c>
     </row>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.100958+00:00</t>
+          <t>2026-08-19T16:09:23.926080+00:00</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:36.121547+00:00</t>
+          <t>2026-08-19T16:09:23.950859+00:00</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.636011+00:00</t>
+          <t>2026-08-19T16:09:26.625087+00:00</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>257d347dc0c6</t>
+          <t>1c1ceff106ad</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-19T15:56:38.638212+00:00</t>
+          <t>2026-08-19T16:09:26.627631+00:00</t>
         </is>
       </c>
     </row>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1223,12 +1223,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.424534+00:00</t>
+          <t>2026-08-19T16:24:03.512643+00:00</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.426601+00:00</t>
+          <t>2026-08-19T16:24:03.514941+00:00</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.429367+00:00</t>
+          <t>2026-08-19T16:24:03.517184+00:00</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.431979+00:00</t>
+          <t>2026-08-19T16:24:03.519409+00:00</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.434553+00:00</t>
+          <t>2026-08-19T16:24:03.521767+00:00</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.436558+00:00</t>
+          <t>2026-08-19T16:24:03.523986+00:00</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.438500+00:00</t>
+          <t>2026-08-19T16:24:03.526066+00:00</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.440489+00:00</t>
+          <t>2026-08-19T16:24:03.528285+00:00</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.442547+00:00</t>
+          <t>2026-08-19T16:24:03.530444+00:00</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.444527+00:00</t>
+          <t>2026-08-19T16:24:03.532531+00:00</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.446422+00:00</t>
+          <t>2026-08-19T16:24:03.534601+00:00</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.448384+00:00</t>
+          <t>2026-08-19T16:24:03.537345+00:00</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.450381+00:00</t>
+          <t>2026-08-19T16:24:03.540354+00:00</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.452491+00:00</t>
+          <t>2026-08-19T16:24:03.542669+00:00</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.454376+00:00</t>
+          <t>2026-08-19T16:24:03.544915+00:00</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.456376+00:00</t>
+          <t>2026-08-19T16:24:03.547018+00:00</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.458857+00:00</t>
+          <t>2026-08-19T16:24:03.549106+00:00</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.460835+00:00</t>
+          <t>2026-08-19T16:24:03.551281+00:00</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.463290+00:00</t>
+          <t>2026-08-19T16:24:03.553350+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.465278+00:00</t>
+          <t>2026-08-19T16:24:03.556322+00:00</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.467788+00:00</t>
+          <t>2026-08-19T16:24:03.558382+00:00</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.593422+00:00</t>
+          <t>2026-08-19T16:24:03.665346+00:00</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.596228+00:00</t>
+          <t>2026-08-19T16:24:03.668069+00:00</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.598267+00:00</t>
+          <t>2026-08-19T16:24:03.670160+00:00</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.600227+00:00</t>
+          <t>2026-08-19T16:24:03.672179+00:00</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.765942+00:00</t>
+          <t>2026-08-19T16:24:03.834987+00:00</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.768894+00:00</t>
+          <t>2026-08-19T16:24:03.837409+00:00</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.782486+00:00</t>
+          <t>2026-08-19T16:24:03.860535+00:00</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.784485+00:00</t>
+          <t>2026-08-19T16:24:03.862895+00:00</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.786433+00:00</t>
+          <t>2026-08-19T16:24:03.865173+00:00</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.788425+00:00</t>
+          <t>2026-08-19T16:24:03.868381+00:00</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.790364+00:00</t>
+          <t>2026-08-19T16:24:03.870584+00:00</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.792349+00:00</t>
+          <t>2026-08-19T16:24:03.873264+00:00</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.794275+00:00</t>
+          <t>2026-08-19T16:24:03.877383+00:00</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.796251+00:00</t>
+          <t>2026-08-19T16:24:03.879505+00:00</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.798171+00:00</t>
+          <t>2026-08-19T16:24:03.881619+00:00</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.938892+00:00</t>
+          <t>2026-08-19T16:24:04.028949+00:00</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.941929+00:00</t>
+          <t>2026-08-19T16:24:04.031465+00:00</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.944598+00:00</t>
+          <t>2026-08-19T16:24:04.034477+00:00</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.946579+00:00</t>
+          <t>2026-08-19T16:24:04.037103+00:00</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.948783+00:00</t>
+          <t>2026-08-19T16:24:04.039530+00:00</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.182919+00:00</t>
+          <t>2026-08-19T16:24:06.253779+00:00</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.185585+00:00</t>
+          <t>2026-08-19T16:24:06.256667+00:00</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.187798+00:00</t>
+          <t>2026-08-19T16:24:06.261472+00:00</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.189894+00:00</t>
+          <t>2026-08-19T16:24:06.263902+00:00</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.192084+00:00</t>
+          <t>2026-08-19T16:24:06.266033+00:00</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.194450+00:00</t>
+          <t>2026-08-19T16:24:06.268894+00:00</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.196495+00:00</t>
+          <t>2026-08-19T16:24:06.271146+00:00</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.198576+00:00</t>
+          <t>2026-08-19T16:24:06.273564+00:00</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.200600+00:00</t>
+          <t>2026-08-19T16:24:06.275891+00:00</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.202563+00:00</t>
+          <t>2026-08-19T16:24:06.278038+00:00</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.204614+00:00</t>
+          <t>2026-08-19T16:24:06.281590+00:00</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.206728+00:00</t>
+          <t>2026-08-19T16:24:06.283866+00:00</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.208756+00:00</t>
+          <t>2026-08-19T16:24:06.285926+00:00</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.210773+00:00</t>
+          <t>2026-08-19T16:24:06.288066+00:00</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2708,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.212857+00:00</t>
+          <t>2026-08-19T16:24:06.293374+00:00</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.622107+00:00</t>
+          <t>2026-08-19T16:24:06.697464+00:00</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.633428+00:00</t>
+          <t>2026-08-19T16:24:06.708349+00:00</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.422012+00:00</t>
+          <t>2026-08-19T16:24:03.509977+00:00</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2816,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.602133+00:00</t>
+          <t>2026-08-19T16:24:03.674198+00:00</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.604147+00:00</t>
+          <t>2026-08-19T16:24:03.676182+00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.606016+00:00</t>
+          <t>2026-08-19T16:24:03.678107+00:00</t>
         </is>
       </c>
     </row>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.607958+00:00</t>
+          <t>2026-08-19T16:24:03.680063+00:00</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.770949+00:00</t>
+          <t>2026-08-19T16:24:03.839653+00:00</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.772915+00:00</t>
+          <t>2026-08-19T16:24:03.849349+00:00</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.952915+00:00</t>
+          <t>2026-08-19T16:24:04.044851+00:00</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.778424+00:00</t>
+          <t>2026-08-19T16:24:03.855927+00:00</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.780457+00:00</t>
+          <t>2026-08-19T16:24:03.858240+00:00</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.867349+00:00</t>
+          <t>2026-08-19T16:24:03.954472+00:00</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.869809+00:00</t>
+          <t>2026-08-19T16:24:03.957168+00:00</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.871966+00:00</t>
+          <t>2026-08-19T16:24:03.959504+00:00</t>
         </is>
       </c>
     </row>
@@ -3140,12 +3140,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.874173+00:00</t>
+          <t>2026-08-19T16:24:03.961630+00:00</t>
         </is>
       </c>
     </row>
@@ -3167,12 +3167,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.876358+00:00</t>
+          <t>2026-08-19T16:24:03.963865+00:00</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.878530+00:00</t>
+          <t>2026-08-19T16:24:03.966002+00:00</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.880602+00:00</t>
+          <t>2026-08-19T16:24:03.968311+00:00</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.882558+00:00</t>
+          <t>2026-08-19T16:24:03.970402+00:00</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.884736+00:00</t>
+          <t>2026-08-19T16:24:03.972568+00:00</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.886852+00:00</t>
+          <t>2026-08-19T16:24:03.974806+00:00</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.888850+00:00</t>
+          <t>2026-08-19T16:24:03.977186+00:00</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.890842+00:00</t>
+          <t>2026-08-19T16:24:03.979247+00:00</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.893037+00:00</t>
+          <t>2026-08-19T16:24:03.981320+00:00</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3410,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.895181+00:00</t>
+          <t>2026-08-19T16:24:03.983466+00:00</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.897385+00:00</t>
+          <t>2026-08-19T16:24:03.985622+00:00</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.899305+00:00</t>
+          <t>2026-08-19T16:24:03.987891+00:00</t>
         </is>
       </c>
     </row>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.901213+00:00</t>
+          <t>2026-08-19T16:24:03.990168+00:00</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.903125+00:00</t>
+          <t>2026-08-19T16:24:03.992569+00:00</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.905271+00:00</t>
+          <t>2026-08-19T16:24:03.995184+00:00</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.907652+00:00</t>
+          <t>2026-08-19T16:24:03.997469+00:00</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.909518+00:00</t>
+          <t>2026-08-19T16:24:03.999730+00:00</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.912171+00:00</t>
+          <t>2026-08-19T16:24:04.002041+00:00</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.914003+00:00</t>
+          <t>2026-08-19T16:24:04.004436+00:00</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.916059+00:00</t>
+          <t>2026-08-19T16:24:04.006720+00:00</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.917889+00:00</t>
+          <t>2026-08-19T16:24:04.009163+00:00</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.919933+00:00</t>
+          <t>2026-08-19T16:24:04.011310+00:00</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.921972+00:00</t>
+          <t>2026-08-19T16:24:04.013562+00:00</t>
         </is>
       </c>
     </row>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.924143+00:00</t>
+          <t>2026-08-19T16:24:04.016362+00:00</t>
         </is>
       </c>
     </row>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.926080+00:00</t>
+          <t>2026-08-19T16:24:04.018382+00:00</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:23.950859+00:00</t>
+          <t>2026-08-19T16:24:04.042499+00:00</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.625087+00:00</t>
+          <t>2026-08-19T16:24:06.700219+00:00</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1c1ceff106ad</t>
+          <t>9ec8fd49cb89</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-19T16:09:26.627631+00:00</t>
+          <t>2026-08-19T16:24:06.702454+00:00</t>
         </is>
       </c>
     </row>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1223,12 +1223,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.512643+00:00</t>
+          <t>2026-08-19T16:42:26.943650+00:00</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.514941+00:00</t>
+          <t>2026-08-19T16:42:26.945858+00:00</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.517184+00:00</t>
+          <t>2026-08-19T16:42:26.948167+00:00</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.519409+00:00</t>
+          <t>2026-08-19T16:42:26.950201+00:00</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.521767+00:00</t>
+          <t>2026-08-19T16:42:26.952244+00:00</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.523986+00:00</t>
+          <t>2026-08-19T16:42:26.954494+00:00</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.526066+00:00</t>
+          <t>2026-08-19T16:42:26.956722+00:00</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.528285+00:00</t>
+          <t>2026-08-19T16:42:26.958765+00:00</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.530444+00:00</t>
+          <t>2026-08-19T16:42:26.960769+00:00</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.532531+00:00</t>
+          <t>2026-08-19T16:42:26.962854+00:00</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.534601+00:00</t>
+          <t>2026-08-19T16:42:26.964861+00:00</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.537345+00:00</t>
+          <t>2026-08-19T16:42:26.967517+00:00</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.540354+00:00</t>
+          <t>2026-08-19T16:42:26.969499+00:00</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.542669+00:00</t>
+          <t>2026-08-19T16:42:26.971619+00:00</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.544915+00:00</t>
+          <t>2026-08-19T16:42:26.973510+00:00</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.547018+00:00</t>
+          <t>2026-08-19T16:42:26.976136+00:00</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.549106+00:00</t>
+          <t>2026-08-19T16:42:26.978241+00:00</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.551281+00:00</t>
+          <t>2026-08-19T16:42:26.980548+00:00</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.553350+00:00</t>
+          <t>2026-08-19T16:42:26.982982+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.556322+00:00</t>
+          <t>2026-08-19T16:42:26.985465+00:00</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.558382+00:00</t>
+          <t>2026-08-19T16:42:26.988071+00:00</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.665346+00:00</t>
+          <t>2026-08-19T16:42:27.130183+00:00</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.668069+00:00</t>
+          <t>2026-08-19T16:42:27.133345+00:00</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.670160+00:00</t>
+          <t>2026-08-19T16:42:27.135437+00:00</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.672179+00:00</t>
+          <t>2026-08-19T16:42:27.137376+00:00</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.834987+00:00</t>
+          <t>2026-08-19T16:42:27.327845+00:00</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.837409+00:00</t>
+          <t>2026-08-19T16:42:27.330410+00:00</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.860535+00:00</t>
+          <t>2026-08-19T16:42:27.344915+00:00</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.862895+00:00</t>
+          <t>2026-08-19T16:42:27.346867+00:00</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.865173+00:00</t>
+          <t>2026-08-19T16:42:27.348908+00:00</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.868381+00:00</t>
+          <t>2026-08-19T16:42:27.353168+00:00</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.870584+00:00</t>
+          <t>2026-08-19T16:42:27.357222+00:00</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.873264+00:00</t>
+          <t>2026-08-19T16:42:27.363515+00:00</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.877383+00:00</t>
+          <t>2026-08-19T16:42:27.365444+00:00</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.879505+00:00</t>
+          <t>2026-08-19T16:42:27.367428+00:00</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.881619+00:00</t>
+          <t>2026-08-19T16:42:27.373321+00:00</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.028949+00:00</t>
+          <t>2026-08-19T16:42:27.551742+00:00</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.031465+00:00</t>
+          <t>2026-08-19T16:42:27.553881+00:00</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.034477+00:00</t>
+          <t>2026-08-19T16:42:27.556606+00:00</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.037103+00:00</t>
+          <t>2026-08-19T16:42:27.558736+00:00</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.039530+00:00</t>
+          <t>2026-08-19T16:42:27.560978+00:00</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.253779+00:00</t>
+          <t>2026-08-19T16:42:29.690293+00:00</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.256667+00:00</t>
+          <t>2026-08-19T16:42:29.693027+00:00</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.261472+00:00</t>
+          <t>2026-08-19T16:42:29.697366+00:00</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.263902+00:00</t>
+          <t>2026-08-19T16:42:29.699605+00:00</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.266033+00:00</t>
+          <t>2026-08-19T16:42:29.701724+00:00</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.268894+00:00</t>
+          <t>2026-08-19T16:42:29.703852+00:00</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.271146+00:00</t>
+          <t>2026-08-19T16:42:29.709624+00:00</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.273564+00:00</t>
+          <t>2026-08-19T16:42:29.711879+00:00</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.275891+00:00</t>
+          <t>2026-08-19T16:42:29.713999+00:00</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.278038+00:00</t>
+          <t>2026-08-19T16:42:29.717347+00:00</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.281590+00:00</t>
+          <t>2026-08-19T16:42:29.719393+00:00</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.283866+00:00</t>
+          <t>2026-08-19T16:42:29.721307+00:00</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.285926+00:00</t>
+          <t>2026-08-19T16:42:29.725175+00:00</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.288066+00:00</t>
+          <t>2026-08-19T16:42:29.729223+00:00</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2708,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.293374+00:00</t>
+          <t>2026-08-19T16:42:29.735587+00:00</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.697464+00:00</t>
+          <t>2026-08-19T16:42:30.150245+00:00</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.708349+00:00</t>
+          <t>2026-08-19T16:42:30.160960+00:00</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.509977+00:00</t>
+          <t>2026-08-19T16:42:26.941080+00:00</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2816,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.674198+00:00</t>
+          <t>2026-08-19T16:42:27.139321+00:00</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.676182+00:00</t>
+          <t>2026-08-19T16:42:27.145224+00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.678107+00:00</t>
+          <t>2026-08-19T16:42:27.149198+00:00</t>
         </is>
       </c>
     </row>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.680063+00:00</t>
+          <t>2026-08-19T16:42:27.155516+00:00</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.839653+00:00</t>
+          <t>2026-08-19T16:42:27.332784+00:00</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.849349+00:00</t>
+          <t>2026-08-19T16:42:27.334816+00:00</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.044851+00:00</t>
+          <t>2026-08-19T16:42:27.565427+00:00</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.855927+00:00</t>
+          <t>2026-08-19T16:42:27.340909+00:00</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.858240+00:00</t>
+          <t>2026-08-19T16:42:27.342851+00:00</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.954472+00:00</t>
+          <t>2026-08-19T16:42:27.480508+00:00</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.957168+00:00</t>
+          <t>2026-08-19T16:42:27.483020+00:00</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.959504+00:00</t>
+          <t>2026-08-19T16:42:27.485650+00:00</t>
         </is>
       </c>
     </row>
@@ -3140,12 +3140,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.961630+00:00</t>
+          <t>2026-08-19T16:42:27.487873+00:00</t>
         </is>
       </c>
     </row>
@@ -3167,12 +3167,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.963865+00:00</t>
+          <t>2026-08-19T16:42:27.489956+00:00</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.966002+00:00</t>
+          <t>2026-08-19T16:42:27.492108+00:00</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.968311+00:00</t>
+          <t>2026-08-19T16:42:27.494202+00:00</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.970402+00:00</t>
+          <t>2026-08-19T16:42:27.496295+00:00</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.972568+00:00</t>
+          <t>2026-08-19T16:42:27.498902+00:00</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.974806+00:00</t>
+          <t>2026-08-19T16:42:27.501039+00:00</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.977186+00:00</t>
+          <t>2026-08-19T16:42:27.503075+00:00</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.979247+00:00</t>
+          <t>2026-08-19T16:42:27.505148+00:00</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.981320+00:00</t>
+          <t>2026-08-19T16:42:27.507572+00:00</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3410,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.983466+00:00</t>
+          <t>2026-08-19T16:42:27.509623+00:00</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.985622+00:00</t>
+          <t>2026-08-19T16:42:27.512260+00:00</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.987891+00:00</t>
+          <t>2026-08-19T16:42:27.514325+00:00</t>
         </is>
       </c>
     </row>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.990168+00:00</t>
+          <t>2026-08-19T16:42:27.516458+00:00</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.992569+00:00</t>
+          <t>2026-08-19T16:42:27.518463+00:00</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.995184+00:00</t>
+          <t>2026-08-19T16:42:27.520607+00:00</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.997469+00:00</t>
+          <t>2026-08-19T16:42:27.522609+00:00</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:03.999730+00:00</t>
+          <t>2026-08-19T16:42:27.524799+00:00</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.002041+00:00</t>
+          <t>2026-08-19T16:42:27.527048+00:00</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.004436+00:00</t>
+          <t>2026-08-19T16:42:27.529169+00:00</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.006720+00:00</t>
+          <t>2026-08-19T16:42:27.531826+00:00</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.009163+00:00</t>
+          <t>2026-08-19T16:42:27.533883+00:00</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.011310+00:00</t>
+          <t>2026-08-19T16:42:27.535931+00:00</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.013562+00:00</t>
+          <t>2026-08-19T16:42:27.537968+00:00</t>
         </is>
       </c>
     </row>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.016362+00:00</t>
+          <t>2026-08-19T16:42:27.540041+00:00</t>
         </is>
       </c>
     </row>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.018382+00:00</t>
+          <t>2026-08-19T16:42:27.542093+00:00</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:04.042499+00:00</t>
+          <t>2026-08-19T16:42:27.563288+00:00</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.700219+00:00</t>
+          <t>2026-08-19T16:42:30.152770+00:00</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9ec8fd49cb89</t>
+          <t>30ddeb49f7c3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-19T16:24:06.702454+00:00</t>
+          <t>2026-08-19T16:42:30.154944+00:00</t>
         </is>
       </c>
     </row>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1223,12 +1223,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.943650+00:00</t>
+          <t>2026-08-19T16:50:57.371134+00:00</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.945858+00:00</t>
+          <t>2026-08-19T16:50:57.373349+00:00</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.948167+00:00</t>
+          <t>2026-08-19T16:50:57.375546+00:00</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.950201+00:00</t>
+          <t>2026-08-19T16:50:57.377601+00:00</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.952244+00:00</t>
+          <t>2026-08-19T16:50:57.379727+00:00</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.954494+00:00</t>
+          <t>2026-08-19T16:50:57.381745+00:00</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.956722+00:00</t>
+          <t>2026-08-19T16:50:57.384150+00:00</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.958765+00:00</t>
+          <t>2026-08-19T16:50:57.386170+00:00</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.960769+00:00</t>
+          <t>2026-08-19T16:50:57.388216+00:00</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.962854+00:00</t>
+          <t>2026-08-19T16:50:57.390212+00:00</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1493,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.964861+00:00</t>
+          <t>2026-08-19T16:50:57.392220+00:00</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.967517+00:00</t>
+          <t>2026-08-19T16:50:57.394182+00:00</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1547,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.969499+00:00</t>
+          <t>2026-08-19T16:50:57.396154+00:00</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.971619+00:00</t>
+          <t>2026-08-19T16:50:57.398099+00:00</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.973510+00:00</t>
+          <t>2026-08-19T16:50:57.400141+00:00</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.976136+00:00</t>
+          <t>2026-08-19T16:50:57.402067+00:00</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.978241+00:00</t>
+          <t>2026-08-19T16:50:57.404142+00:00</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.980548+00:00</t>
+          <t>2026-08-19T16:50:57.406171+00:00</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.982982+00:00</t>
+          <t>2026-08-19T16:50:57.408193+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.985465+00:00</t>
+          <t>2026-08-19T16:50:57.410096+00:00</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.988071+00:00</t>
+          <t>2026-08-19T16:50:57.412133+00:00</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.130183+00:00</t>
+          <t>2026-08-19T16:50:57.517582+00:00</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.133345+00:00</t>
+          <t>2026-08-19T16:50:57.520404+00:00</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.135437+00:00</t>
+          <t>2026-08-19T16:50:57.522958+00:00</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.137376+00:00</t>
+          <t>2026-08-19T16:50:57.525535+00:00</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.327845+00:00</t>
+          <t>2026-08-19T16:50:57.701843+00:00</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.330410+00:00</t>
+          <t>2026-08-19T16:50:57.704578+00:00</t>
         </is>
       </c>
     </row>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.344915+00:00</t>
+          <t>2026-08-19T16:50:57.721096+00:00</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.346867+00:00</t>
+          <t>2026-08-19T16:50:57.725232+00:00</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.348908+00:00</t>
+          <t>2026-08-19T16:50:57.729183+00:00</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.353168+00:00</t>
+          <t>2026-08-19T16:50:57.733266+00:00</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2060,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.357222+00:00</t>
+          <t>2026-08-19T16:50:57.735428+00:00</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.363515+00:00</t>
+          <t>2026-08-19T16:50:57.737356+00:00</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.365444+00:00</t>
+          <t>2026-08-19T16:50:57.739313+00:00</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.367428+00:00</t>
+          <t>2026-08-19T16:50:57.741325+00:00</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.373321+00:00</t>
+          <t>2026-08-19T16:50:57.743411+00:00</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.551742+00:00</t>
+          <t>2026-08-19T16:50:57.887772+00:00</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.553881+00:00</t>
+          <t>2026-08-19T16:50:57.889977+00:00</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.556606+00:00</t>
+          <t>2026-08-19T16:50:57.892062+00:00</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.558736+00:00</t>
+          <t>2026-08-19T16:50:57.894089+00:00</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2303,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.560978+00:00</t>
+          <t>2026-08-19T16:50:57.896215+00:00</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.690293+00:00</t>
+          <t>2026-08-19T16:51:00.069815+00:00</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.693027+00:00</t>
+          <t>2026-08-19T16:51:00.072574+00:00</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.697366+00:00</t>
+          <t>2026-08-19T16:51:00.077500+00:00</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2411,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.699605+00:00</t>
+          <t>2026-08-19T16:51:00.079786+00:00</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.701724+00:00</t>
+          <t>2026-08-19T16:51:00.082036+00:00</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.703852+00:00</t>
+          <t>2026-08-19T16:51:00.084279+00:00</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.709624+00:00</t>
+          <t>2026-08-19T16:51:00.089222+00:00</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.711879+00:00</t>
+          <t>2026-08-19T16:51:00.093132+00:00</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.713999+00:00</t>
+          <t>2026-08-19T16:51:00.097887+00:00</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.717347+00:00</t>
+          <t>2026-08-19T16:51:00.100170+00:00</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.719393+00:00</t>
+          <t>2026-08-19T16:51:00.105005+00:00</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.721307+00:00</t>
+          <t>2026-08-19T16:51:00.107187+00:00</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.725175+00:00</t>
+          <t>2026-08-19T16:51:00.109347+00:00</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2681,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.729223+00:00</t>
+          <t>2026-08-19T16:51:00.111478+00:00</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2708,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:29.735587+00:00</t>
+          <t>2026-08-19T16:51:00.113464+00:00</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:30.150245+00:00</t>
+          <t>2026-08-19T16:51:00.540282+00:00</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:30.160960+00:00</t>
+          <t>2026-08-19T16:51:00.550610+00:00</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:26.941080+00:00</t>
+          <t>2026-08-19T16:50:57.368763+00:00</t>
         </is>
       </c>
     </row>
@@ -2816,12 +2816,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.139321+00:00</t>
+          <t>2026-08-19T16:50:57.527993+00:00</t>
         </is>
       </c>
     </row>
@@ -2843,12 +2843,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.145224+00:00</t>
+          <t>2026-08-19T16:50:57.530130+00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.149198+00:00</t>
+          <t>2026-08-19T16:50:57.532245+00:00</t>
         </is>
       </c>
     </row>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.155516+00:00</t>
+          <t>2026-08-19T16:50:57.534326+00:00</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.332784+00:00</t>
+          <t>2026-08-19T16:50:57.706777+00:00</t>
         </is>
       </c>
     </row>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.334816+00:00</t>
+          <t>2026-08-19T16:50:57.708896+00:00</t>
         </is>
       </c>
     </row>
@@ -2978,12 +2978,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.565427+00:00</t>
+          <t>2026-08-19T16:50:57.900237+00:00</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.340909+00:00</t>
+          <t>2026-08-19T16:50:57.716909+00:00</t>
         </is>
       </c>
     </row>
@@ -3032,12 +3032,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.342851+00:00</t>
+          <t>2026-08-19T16:50:57.718977+00:00</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.480508+00:00</t>
+          <t>2026-08-19T16:50:57.818565+00:00</t>
         </is>
       </c>
     </row>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.483020+00:00</t>
+          <t>2026-08-19T16:50:57.821008+00:00</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.485650+00:00</t>
+          <t>2026-08-19T16:50:57.823207+00:00</t>
         </is>
       </c>
     </row>
@@ -3140,12 +3140,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.487873+00:00</t>
+          <t>2026-08-19T16:50:57.825334+00:00</t>
         </is>
       </c>
     </row>
@@ -3167,12 +3167,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.489956+00:00</t>
+          <t>2026-08-19T16:50:57.827616+00:00</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.492108+00:00</t>
+          <t>2026-08-19T16:50:57.829896+00:00</t>
         </is>
       </c>
     </row>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.494202+00:00</t>
+          <t>2026-08-19T16:50:57.831922+00:00</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.496295+00:00</t>
+          <t>2026-08-19T16:50:57.834069+00:00</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3275,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.498902+00:00</t>
+          <t>2026-08-19T16:50:57.836198+00:00</t>
         </is>
       </c>
     </row>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.501039+00:00</t>
+          <t>2026-08-19T16:50:57.838544+00:00</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.503075+00:00</t>
+          <t>2026-08-19T16:50:57.840633+00:00</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.505148+00:00</t>
+          <t>2026-08-19T16:50:57.842824+00:00</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.507572+00:00</t>
+          <t>2026-08-19T16:50:57.844841+00:00</t>
         </is>
       </c>
     </row>
@@ -3410,12 +3410,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.509623+00:00</t>
+          <t>2026-08-19T16:50:57.846940+00:00</t>
         </is>
       </c>
     </row>
@@ -3437,12 +3437,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.512260+00:00</t>
+          <t>2026-08-19T16:50:57.849093+00:00</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.514325+00:00</t>
+          <t>2026-08-19T16:50:57.851535+00:00</t>
         </is>
       </c>
     </row>
@@ -3491,12 +3491,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.516458+00:00</t>
+          <t>2026-08-19T16:50:57.853527+00:00</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.518463+00:00</t>
+          <t>2026-08-19T16:50:57.855600+00:00</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3545,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.520607+00:00</t>
+          <t>2026-08-19T16:50:57.857536+00:00</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.522609+00:00</t>
+          <t>2026-08-19T16:50:57.859573+00:00</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.524799+00:00</t>
+          <t>2026-08-19T16:50:57.861448+00:00</t>
         </is>
       </c>
     </row>
@@ -3626,12 +3626,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.527048+00:00</t>
+          <t>2026-08-19T16:50:57.863512+00:00</t>
         </is>
       </c>
     </row>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.529169+00:00</t>
+          <t>2026-08-19T16:50:57.865464+00:00</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.531826+00:00</t>
+          <t>2026-08-19T16:50:57.867535+00:00</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.533883+00:00</t>
+          <t>2026-08-19T16:50:57.869657+00:00</t>
         </is>
       </c>
     </row>
@@ -3734,12 +3734,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.535931+00:00</t>
+          <t>2026-08-19T16:50:57.871894+00:00</t>
         </is>
       </c>
     </row>
@@ -3761,12 +3761,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.537968+00:00</t>
+          <t>2026-08-19T16:50:57.873965+00:00</t>
         </is>
       </c>
     </row>
@@ -3788,12 +3788,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.540041+00:00</t>
+          <t>2026-08-19T16:50:57.876098+00:00</t>
         </is>
       </c>
     </row>
@@ -3815,12 +3815,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.542093+00:00</t>
+          <t>2026-08-19T16:50:57.878064+00:00</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:27.563288+00:00</t>
+          <t>2026-08-19T16:50:57.898166+00:00</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:30.152770+00:00</t>
+          <t>2026-08-19T16:51:00.542709+00:00</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>30ddeb49f7c3</t>
+          <t>6818acd4d5f4</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-19T16:42:30.154944+00:00</t>
+          <t>2026-08-19T16:51:00.545021+00:00</t>
         </is>
       </c>
     </row>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -920,6 +920,74 @@
       <c r="C23" t="inlineStr">
         <is>
           <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CALC-H1-SELECTION-WELLPOSEDNESS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'hypothesis': 'H1 -- Selection Closure: G* = argmax_{G in Mathset} Pi(G)/S(G)', 'mathset_formally_defined_in_repo': False, 'mathset_repo_occurrences': "only as the bare string 'M in Mathset' inside a code comment in compiler/ir/forward_chain.py -- never as a class, set, type, or constructive definition anywhere in the compiler", 'pi_and_s_implemented_in_repo': True, 'pi_and_s_repo_status': "Pi (persistence functional) and S (structural cost) are described only in prose in Master Equation Codex </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CALC-H2-SPECTRAL-TRIPLE-LOCALITY</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{'hypothesis': 'H2 -- Spectral-triple / Dirac-operator closure for D+=sqrt(L)', 'test_graph': "n=200 nearest-neighbour ring, k=3 (local connectivity, structurally representative of this project's own sparse geometric graphs)", 'L_self_adjoint_real_symmetric': True, 'L_sparsity_fraction': 0.035, 'D_plus_self_adjoint': True, 'D_plus_sparsity_fraction_strict': 1.0, 'D_plus_sparsity_fraction_relative_1e-3_of_max': 0.235, 'D_plus_row0_decay_by_graph_distance': {'0': 2.3478289210816, '1': 0.2899664965</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CALC-H3-FC005-CORRECTION-TEST</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{'hypothesis': 'H3 -- Discrete-to-continuum kernel-correction closure', 'test_performed_against': 'real DESI DR1 LRG SGC pilot catalogue (data/desi/dr1/fc005/raw/), N=4000-&gt;8000 nested subsample', 'baseline_joint_converged': False, 'candidate_A_tighter_arpack_tolerance': {'joint_converged': False, 'result_identical_to_baseline': False, 'interpretation': 'Result changed under tighter tolerance -- inconclusive, may indicate a genuine precision sensitivity requiring further investigation.'}, 'candi</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CALC-H4-G2-SPIN8-GAUGE-CLOSURE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{'hypothesis': 'H4 -- Gauge/internal-algebra closure: does G2/Spin(8)/triality select SU(3)xSU(2)xU(1)?', 'standard_lie_theory_facts_used': {'G2': {'dim': 14, 'rank': 2, 'note': 'Aut(octonions), the smallest exceptional simple Lie group'}, 'Spin(8)': {'dim': 28, 'rank': 4, 'note': 'double cover of SO(8); Out(Spin(8)) = S3 (triality)'}, 'SU(3)': {'dim': 8, 'rank': 2}, 'SU(2)': {'dim': 3, 'rank': 1}, 'U(1)': {'dim': 1, 'rank': 1}}, 'triality_fixed_subgroup_of_Spin(8)': 'G2', 'counterfactual_manusc</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
     </row>
@@ -934,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1157,6 +1225,36 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FALS-H4-G2-TRIALITY-RANK-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mathematical_invariance_test (rank of compact Lie subgroups)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>rank(SU(3)xSU(2)xU(1)) = 4 &gt; rank(G2) = 2, therefore SU(3)xSU(2)xU(1) CANNOT be realized as a subgroup of G2 under any embedding whatsoever. This rules out the counterfactual manuscript's specific claim that the triality-fixed subgroup of Spin(8) (which is G2 itself, a real, standard fact of Lie theory, dim 14) equals SU(3)xSU(2)xU(1) (dim 12): even setting dimension aside, the rank obstruction is decisive and dimension-independent.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>{'hypothesis': 'H4 -- Gauge/internal-algebra closure: does G2/Spin(8)/triality select SU(3)xSU(2)xU(1)?', 'standard_lie_theory_facts_used': {'G2': {'dim': 14, 'rank': 2, 'note': 'Aut(octonions), the smallest exceptional simple Lie group'}, 'Spin(8)': {'dim': 28, 'rank': 4, 'note': 'double cover of SO(8); Out(Spin(8)) = S3 (triality)'}, 'SU(3)': {'dim': 8, 'rank': 2}, 'SU(2)': {'dim': 3, 'rank': 1}, 'U(1)': {'dim': 1, 'rank': 1}}, 'triality_fixed_subgroup_of_Spin(8)': 'G2', 'counterfactual_manusc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1168,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1223,12 +1321,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.371134+00:00</t>
+          <t>2026-08-19T20:38:08.928030+00:00</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1348,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.373349+00:00</t>
+          <t>2026-08-19T20:38:08.930258+00:00</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1375,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.375546+00:00</t>
+          <t>2026-08-19T20:38:08.932608+00:00</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1402,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.377601+00:00</t>
+          <t>2026-08-19T20:38:08.934778+00:00</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1429,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.379727+00:00</t>
+          <t>2026-08-19T20:38:08.937048+00:00</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1456,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.381745+00:00</t>
+          <t>2026-08-19T20:38:08.939193+00:00</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1483,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.384150+00:00</t>
+          <t>2026-08-19T20:38:08.941277+00:00</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1510,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.386170+00:00</t>
+          <t>2026-08-19T20:38:08.943296+00:00</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1537,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.388216+00:00</t>
+          <t>2026-08-19T20:38:08.945283+00:00</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1564,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.390212+00:00</t>
+          <t>2026-08-19T20:38:08.947165+00:00</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1591,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.392220+00:00</t>
+          <t>2026-08-19T20:38:08.949287+00:00</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1618,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.394182+00:00</t>
+          <t>2026-08-19T20:38:08.951308+00:00</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1645,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.396154+00:00</t>
+          <t>2026-08-19T20:38:08.953384+00:00</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1672,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.398099+00:00</t>
+          <t>2026-08-19T20:38:08.955769+00:00</t>
         </is>
       </c>
     </row>
@@ -1601,12 +1699,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.400141+00:00</t>
+          <t>2026-08-19T20:38:08.957879+00:00</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1726,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.402067+00:00</t>
+          <t>2026-08-19T20:38:08.959985+00:00</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1753,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.404142+00:00</t>
+          <t>2026-08-19T20:38:08.961968+00:00</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1780,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.406171+00:00</t>
+          <t>2026-08-19T20:38:08.964366+00:00</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1807,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.408193+00:00</t>
+          <t>2026-08-19T20:38:08.966338+00:00</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1834,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.410096+00:00</t>
+          <t>2026-08-19T20:38:08.968343+00:00</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1861,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.412133+00:00</t>
+          <t>2026-08-19T20:38:08.970325+00:00</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1888,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.517582+00:00</t>
+          <t>2026-08-19T20:38:09.156561+00:00</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1915,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.520404+00:00</t>
+          <t>2026-08-19T20:38:09.159081+00:00</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1942,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.522958+00:00</t>
+          <t>2026-08-19T20:38:09.161344+00:00</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1969,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.525535+00:00</t>
+          <t>2026-08-19T20:38:09.166050+00:00</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1996,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.701843+00:00</t>
+          <t>2026-08-19T20:38:09.336120+00:00</t>
         </is>
       </c>
     </row>
@@ -1925,12 +2023,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.704578+00:00</t>
+          <t>2026-08-19T20:38:09.338563+00:00</t>
         </is>
       </c>
     </row>
@@ -1952,12 +2050,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.721096+00:00</t>
+          <t>2026-08-19T20:38:09.356939+00:00</t>
         </is>
       </c>
     </row>
@@ -1979,12 +2077,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.725232+00:00</t>
+          <t>2026-08-19T20:38:09.358991+00:00</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2104,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.729183+00:00</t>
+          <t>2026-08-19T20:38:09.361017+00:00</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2131,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.733266+00:00</t>
+          <t>2026-08-19T20:38:09.366099+00:00</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2158,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.735428+00:00</t>
+          <t>2026-08-19T20:38:09.370049+00:00</t>
         </is>
       </c>
     </row>
@@ -2087,12 +2185,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.737356+00:00</t>
+          <t>2026-08-19T20:38:09.371965+00:00</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2212,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.739313+00:00</t>
+          <t>2026-08-19T20:38:09.373977+00:00</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2239,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.741325+00:00</t>
+          <t>2026-08-19T20:38:09.378042+00:00</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2266,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.743411+00:00</t>
+          <t>2026-08-19T20:38:09.380066+00:00</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2293,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.887772+00:00</t>
+          <t>2026-08-19T20:38:09.523408+00:00</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2320,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.889977+00:00</t>
+          <t>2026-08-19T20:38:09.525956+00:00</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2347,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.892062+00:00</t>
+          <t>2026-08-19T20:38:09.528001+00:00</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2374,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.894089+00:00</t>
+          <t>2026-08-19T20:38:09.529952+00:00</t>
         </is>
       </c>
     </row>
@@ -2303,12 +2401,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.896215+00:00</t>
+          <t>2026-08-19T20:38:09.531963+00:00</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2428,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.069815+00:00</t>
+          <t>2026-08-19T20:38:11.968853+00:00</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2455,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.072574+00:00</t>
+          <t>2026-08-19T20:38:11.974356+00:00</t>
         </is>
       </c>
     </row>
@@ -2384,12 +2482,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.077500+00:00</t>
+          <t>2026-08-19T20:38:11.976696+00:00</t>
         </is>
       </c>
     </row>
@@ -2411,12 +2509,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.079786+00:00</t>
+          <t>2026-08-19T20:38:11.978869+00:00</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2536,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.082036+00:00</t>
+          <t>2026-08-19T20:38:11.980951+00:00</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2563,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.084279+00:00</t>
+          <t>2026-08-19T20:38:11.983014+00:00</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2590,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.089222+00:00</t>
+          <t>2026-08-19T20:38:11.985055+00:00</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2617,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.093132+00:00</t>
+          <t>2026-08-19T20:38:11.990006+00:00</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2644,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.097887+00:00</t>
+          <t>2026-08-19T20:38:11.996357+00:00</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2671,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.100170+00:00</t>
+          <t>2026-08-19T20:38:11.998470+00:00</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2698,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.105005+00:00</t>
+          <t>2026-08-19T20:38:12.000621+00:00</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2725,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.107187+00:00</t>
+          <t>2026-08-19T20:38:12.002717+00:00</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2752,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.109347+00:00</t>
+          <t>2026-08-19T20:38:12.004820+00:00</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2779,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.111478+00:00</t>
+          <t>2026-08-19T20:38:12.006892+00:00</t>
         </is>
       </c>
     </row>
@@ -2708,12 +2806,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.113464+00:00</t>
+          <t>2026-08-19T20:38:12.009106+00:00</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2833,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.540282+00:00</t>
+          <t>2026-08-19T20:38:12.422661+00:00</t>
         </is>
       </c>
     </row>
@@ -2762,24 +2860,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.550610+00:00</t>
+          <t>2026-08-19T20:38:12.433865+00:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>compiler/backends/toe_closure_hypotheses.py::h1_selection_wellposedness_analysis</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2789,132 +2887,132 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.368763+00:00</t>
+          <t>2026-08-19T20:38:12.437612+00:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/toe_closure_hypotheses.py::h2_spectral_triple_locality_check</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.527993+00:00</t>
+          <t>2026-08-19T20:38:12.446496+00:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>run_fc005_h3_correction_test.py -&gt; FC005_H3_CORRECTION_TEST_RESULTS.json</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.530130+00:00</t>
+          <t>2026-08-19T20:38:12.449173+00:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.532245+00:00</t>
+          <t>2026-08-19T20:38:12.453455+00:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>spec section 10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.534326+00:00</t>
+          <t>2026-08-19T20:38:08.925491+00:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2924,51 +3022,51 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.706777+00:00</t>
+          <t>2026-08-19T20:38:09.168201+00:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.708896+00:00</t>
+          <t>2026-08-19T20:38:09.170145+00:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2978,186 +3076,186 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.900237+00:00</t>
+          <t>2026-08-19T20:38:09.172068+00:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.716909+00:00</t>
+          <t>2026-08-19T20:38:09.173993+00:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_flow.py</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.718977+00:00</t>
+          <t>2026-08-19T20:38:09.341015+00:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.818565+00:00</t>
+          <t>2026-08-19T20:38:09.346104+00:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.821008+00:00</t>
+          <t>2026-08-19T20:38:09.536361+00:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.823207+00:00</t>
+          <t>2026-08-19T20:38:09.352111+00:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+          <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.825334+00:00</t>
+          <t>2026-08-19T20:38:09.354448+00:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3167,24 +3265,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.827616+00:00</t>
+          <t>2026-08-19T20:38:09.452969+00:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3194,24 +3292,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.829896+00:00</t>
+          <t>2026-08-19T20:38:09.455411+00:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3221,24 +3319,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.831922+00:00</t>
+          <t>2026-08-19T20:38:09.457822+00:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3248,24 +3346,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.834069+00:00</t>
+          <t>2026-08-19T20:38:09.460028+00:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3275,24 +3373,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.836198+00:00</t>
+          <t>2026-08-19T20:38:09.462077+00:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3302,24 +3400,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.838544+00:00</t>
+          <t>2026-08-19T20:38:09.464203+00:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3329,24 +3427,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.840633+00:00</t>
+          <t>2026-08-19T20:38:09.466279+00:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3356,24 +3454,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.842824+00:00</t>
+          <t>2026-08-19T20:38:09.468764+00:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3383,24 +3481,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.844841+00:00</t>
+          <t>2026-08-19T20:38:09.470854+00:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3410,24 +3508,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.846940+00:00</t>
+          <t>2026-08-19T20:38:09.473116+00:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3437,24 +3535,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.849093+00:00</t>
+          <t>2026-08-19T20:38:09.475107+00:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3464,24 +3562,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.851535+00:00</t>
+          <t>2026-08-19T20:38:09.477260+00:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3491,24 +3589,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.853527+00:00</t>
+          <t>2026-08-19T20:38:09.479280+00:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3518,24 +3616,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.855600+00:00</t>
+          <t>2026-08-19T20:38:09.481302+00:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3545,24 +3643,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.857536+00:00</t>
+          <t>2026-08-19T20:38:09.483408+00:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3572,24 +3670,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.859573+00:00</t>
+          <t>2026-08-19T20:38:09.485490+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3599,24 +3697,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.861448+00:00</t>
+          <t>2026-08-19T20:38:09.487401+00:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3626,24 +3724,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.863512+00:00</t>
+          <t>2026-08-19T20:38:09.489510+00:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3653,24 +3751,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.865464+00:00</t>
+          <t>2026-08-19T20:38:09.491441+00:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3680,24 +3778,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.867535+00:00</t>
+          <t>2026-08-19T20:38:09.493451+00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3707,24 +3805,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.869657+00:00</t>
+          <t>2026-08-19T20:38:09.495366+00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3734,24 +3832,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.871894+00:00</t>
+          <t>2026-08-19T20:38:09.497332+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3761,24 +3859,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.873965+00:00</t>
+          <t>2026-08-19T20:38:09.499317+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3788,24 +3886,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.876098+00:00</t>
+          <t>2026-08-19T20:38:09.501259+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3815,93 +3913,228 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.878064+00:00</t>
+          <t>2026-08-19T20:38:09.503258+00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-19T16:50:57.898166+00:00</t>
+          <t>2026-08-19T20:38:09.505295+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6818acd4d5f4</t>
+          <t>01f70d95b9b4</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-19T16:51:00.542709+00:00</t>
+          <t>2026-08-19T20:38:09.507385+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>01f70d95b9b4</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-08-19T20:38:09.509389+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>01f70d95b9b4</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-08-19T20:38:09.511427+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>01f70d95b9b4</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-08-19T20:38:09.533984+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>01f70d95b9b4</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-08-19T20:38:12.425183+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>compiler/verification/fisher_information.py</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>6818acd4d5f4</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>2026-08-19T16:51:00.545021+00:00</t>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>01f70d95b9b4</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-08-19T20:38:12.427504+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>01f70d95b9b4</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-08-19T20:38:12.451412+00:00</t>
         </is>
       </c>
     </row>
@@ -3916,7 +4149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4288,6 +4521,90 @@
         <is>
           <t>stage_gate
 Stage 3: only evaluated if stage 2 closed. Does kappa_spectral agree with an INDEPENDENTLY sourced kappa_cosmological (never derived from the same catalogue/run)? See compiler/backends/desi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SU(3)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>G2 (intersection via triality) Spin(8)
+SU(3) x SU(2) x U(1)
+compact Lie group theory
+claimed in COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8; disproved by rank-counting -- see FALS-H4-G2-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SU(2)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>G2 (intersection via triality) Spin(8)
+SU(3) x SU(2) x U(1)
+compact Lie group theory
+claimed in COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8; disproved by rank-counting -- see FALS-H4-G2-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>U(1)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>G2 (intersection via triality) Spin(8)
+SU(3) x SU(2) x U(1)
+compact Lie group theory
+claimed in COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8; disproved by rank-counting -- see FALS-H4-G2-</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4946,15 +5263,49 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>H1 DOES NOT CLOSE. Obstruction is at the level of definition, not proof.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>The repository's own original claim (Aut(octonions) x Spin(8) superset SU(3)xSU(2)xU(1), a direct product, not an intersection) is NOT ruled out by the H4 rank argument, but remains completely unconstructed anywhere in this repository -- no embedding, decomposition, or uniqueness argument exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>SELECTION-SIGMA</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Transformation</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Sigma : M -&gt; {0,1}</t>
         </is>
@@ -4971,7 +5322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6281,12 +6632,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6303,73 +6654,73 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6379,19 +6730,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6406,14 +6757,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['GRAPH-G-SEED']</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6423,19 +6774,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6450,102 +6801,102 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['DIFFUSION-DISTANCE']</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6555,19 +6906,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6577,19 +6928,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6611,7 +6962,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6633,7 +6984,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6655,7 +7006,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6677,7 +7028,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6699,7 +7050,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6721,7 +7072,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6743,7 +7094,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6765,7 +7116,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6787,7 +7138,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6809,7 +7160,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6831,7 +7182,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6853,7 +7204,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6875,7 +7226,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6897,7 +7248,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6919,7 +7270,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6941,7 +7292,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6963,7 +7314,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6985,7 +7336,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7007,7 +7358,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7029,7 +7380,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7051,7 +7402,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7073,7 +7424,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7095,7 +7446,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7117,7 +7468,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7139,7 +7490,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7149,19 +7500,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>['S3-CURVATURE-CLOSURE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7171,34 +7522,144 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>['S3-CURVATURE-CLOSURE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
@@ -7697,7 +8158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8064,6 +8525,18 @@
       <c r="B26" t="inlineStr">
         <is>
           <t>provenance/precedence record for the four supplied FC-005 workbooks</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>closure_hypothesis_test</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>an executed test of one of the four primary load-bearing hypotheses (H1-H4) required to decounterfactualize the COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING manuscript</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9678,6 +10151,114 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>closure_hypothesis_test</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>closure_hypothesis_test</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>H3-FC005-CORRECTION-TEST</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>closure_hypothesis_test</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>closure_hypothesis_test</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>comparison</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11133,6 +11714,38 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>G2 (intersection via triality) Spin(8)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SU(3) x SU(2) x U(1)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>compact Lie group theory</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11144,7 +11757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11766,142 +12379,154 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GRAPH-G-SEED</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>GRAPH-G-SEED</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>HEAT-FLOW-R</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DIFFUSION-DISTANCE</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>DIFFUSION-DISTANCE</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>HEAT-FLOW-R</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
@@ -11918,7 +12543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12504,67 +13129,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>Tests whether G*=argmax_G Pi(G)/S(G) is a well-posed optimization problem given the compiler's own actual definitions (or absence thereof) of Mathset, Pi, and S.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Tests the structural locality prerequisite for D+=sqrt(L) to serve as a genuine Dirac-type operator in a spectral triple; does not attempt the full axiom-by-axiom certification (fixing a specific algebra A and computing the first-order condition directly), noted as future work.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Additional diagnostic evidence extending (not overwriting) the frozen FC005_CHECKPOINT.md state. Tested against real DESI DR1 LRG SGC data at N=4000-&gt;8000, a smaller N pair than the frozen checkpoint's own best-case N=32000-&gt;64000 result, so this is not a direct re-run of the checkpoint's own claim, but an independent test of correction hypotheses.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>rank(Aut(octonions) x Spin(8)) = 2+4 = 6, which IS &gt;= rank(SM) = 4. The rank obstruction that rules out the counterfactual manuscript's 'intersection' claim does NOT rule out this different, direct-product formulation -- SU(3) fits inside the G2 factor (a real, standard, correct maximal-subgroup fact) and SU(2)xU(1) has enough rank to potentially fit inside the Spin(8) factor. This means the repository's ORIGINAL claim remains merely UNCONSTRUCTED (no actual embedding, decomposition, or uniqueness argument is given anywhere in the repository), not proven impossible -- a materially different, more honest status than the counterfactual manuscript's claim, which this analysis shows is actually impossible as stated.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12576,7 +13201,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12588,7 +13213,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -12600,7 +13225,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12612,7 +13237,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12624,67 +13249,67 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12696,55 +13321,55 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -12756,31 +13381,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -12792,19 +13417,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -12816,48 +13441,108 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>EQ-029</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>The counterfactual manuscript's specific restatement of the gauge-closure claim (COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8).</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13597,6 +14282,94 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CALC-H1-SELECTION-WELLPOSEDNESS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>definitional_wellposedness_audit</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{'repo_root': '/home/user/SEIT'}</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CALC-H2-SPECTRAL-TRIPLE-LOCALITY</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>spectral_triple_locality_test</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{'n': 200, 'k_neighbors': 3, 'seed': 0}</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CALC-H3-FC005-CORRECTION-TEST</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>discrete_continuum_correction_test</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{'n_small': 4000, 'n_large': 8000, 'seed': 20250819}</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CALC-H4-G2-SPIN8-GAUGE-CLOSURE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>lie_group_rank_dimension_check</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{'groups_compared': ['G2', 'Spin(8)', 'SU(3)', 'SU(2)', 'U(1)']}</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1321,12 +1321,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.928030+00:00</t>
+          <t>2026-08-20T16:36:00.531709+00:00</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.930258+00:00</t>
+          <t>2026-08-20T16:36:00.533885+00:00</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.932608+00:00</t>
+          <t>2026-08-20T16:36:00.535737+00:00</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.934778+00:00</t>
+          <t>2026-08-20T16:36:00.537653+00:00</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.937048+00:00</t>
+          <t>2026-08-20T16:36:00.539522+00:00</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.939193+00:00</t>
+          <t>2026-08-20T16:36:00.541410+00:00</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.941277+00:00</t>
+          <t>2026-08-20T16:36:00.543165+00:00</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.943296+00:00</t>
+          <t>2026-08-20T16:36:00.545009+00:00</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.945283+00:00</t>
+          <t>2026-08-20T16:36:00.546691+00:00</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.947165+00:00</t>
+          <t>2026-08-20T16:36:00.548390+00:00</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.949287+00:00</t>
+          <t>2026-08-20T16:36:00.550059+00:00</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.951308+00:00</t>
+          <t>2026-08-20T16:36:00.551927+00:00</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.953384+00:00</t>
+          <t>2026-08-20T16:36:00.553726+00:00</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.955769+00:00</t>
+          <t>2026-08-20T16:36:00.555425+00:00</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.957879+00:00</t>
+          <t>2026-08-20T16:36:00.557169+00:00</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.959985+00:00</t>
+          <t>2026-08-20T16:36:00.558805+00:00</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.961968+00:00</t>
+          <t>2026-08-20T16:36:00.560582+00:00</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.964366+00:00</t>
+          <t>2026-08-20T16:36:00.562292+00:00</t>
         </is>
       </c>
     </row>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.966338+00:00</t>
+          <t>2026-08-20T16:36:00.564055+00:00</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.968343+00:00</t>
+          <t>2026-08-20T16:36:00.565885+00:00</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.970325+00:00</t>
+          <t>2026-08-20T16:36:00.567597+00:00</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.156561+00:00</t>
+          <t>2026-08-20T16:36:00.668431+00:00</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1915,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.159081+00:00</t>
+          <t>2026-08-20T16:36:00.670481+00:00</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.161344+00:00</t>
+          <t>2026-08-20T16:36:00.672440+00:00</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.166050+00:00</t>
+          <t>2026-08-20T16:36:00.674216+00:00</t>
         </is>
       </c>
     </row>
@@ -1996,12 +1996,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.336120+00:00</t>
+          <t>2026-08-20T16:36:00.884066+00:00</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.338563+00:00</t>
+          <t>2026-08-20T16:36:00.886590+00:00</t>
         </is>
       </c>
     </row>
@@ -2050,12 +2050,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.356939+00:00</t>
+          <t>2026-08-20T16:36:00.906312+00:00</t>
         </is>
       </c>
     </row>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.358991+00:00</t>
+          <t>2026-08-20T16:36:00.908212+00:00</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.361017+00:00</t>
+          <t>2026-08-20T16:36:00.910046+00:00</t>
         </is>
       </c>
     </row>
@@ -2131,12 +2131,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.366099+00:00</t>
+          <t>2026-08-20T16:36:00.914023+00:00</t>
         </is>
       </c>
     </row>
@@ -2158,12 +2158,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.370049+00:00</t>
+          <t>2026-08-20T16:36:00.917971+00:00</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.371965+00:00</t>
+          <t>2026-08-20T16:36:00.921940+00:00</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.373977+00:00</t>
+          <t>2026-08-20T16:36:00.926040+00:00</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.378042+00:00</t>
+          <t>2026-08-20T16:36:00.927842+00:00</t>
         </is>
       </c>
     </row>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.380066+00:00</t>
+          <t>2026-08-20T16:36:00.929794+00:00</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.523408+00:00</t>
+          <t>2026-08-20T16:36:01.063995+00:00</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.525956+00:00</t>
+          <t>2026-08-20T16:36:01.065915+00:00</t>
         </is>
       </c>
     </row>
@@ -2347,12 +2347,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.528001+00:00</t>
+          <t>2026-08-20T16:36:01.067644+00:00</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.529952+00:00</t>
+          <t>2026-08-20T16:36:01.069940+00:00</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.531963+00:00</t>
+          <t>2026-08-20T16:36:01.072119+00:00</t>
         </is>
       </c>
     </row>
@@ -2428,12 +2428,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.968853+00:00</t>
+          <t>2026-08-20T16:36:02.791908+00:00</t>
         </is>
       </c>
     </row>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.974356+00:00</t>
+          <t>2026-08-20T16:36:02.794601+00:00</t>
         </is>
       </c>
     </row>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.976696+00:00</t>
+          <t>2026-08-20T16:36:02.796819+00:00</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.978869+00:00</t>
+          <t>2026-08-20T16:36:02.802011+00:00</t>
         </is>
       </c>
     </row>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.980951+00:00</t>
+          <t>2026-08-20T16:36:02.803881+00:00</t>
         </is>
       </c>
     </row>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.983014+00:00</t>
+          <t>2026-08-20T16:36:02.805948+00:00</t>
         </is>
       </c>
     </row>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.985055+00:00</t>
+          <t>2026-08-20T16:36:02.810018+00:00</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2617,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.990006+00:00</t>
+          <t>2026-08-20T16:36:02.811833+00:00</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.996357+00:00</t>
+          <t>2026-08-20T16:36:02.813876+00:00</t>
         </is>
       </c>
     </row>
@@ -2671,12 +2671,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:11.998470+00:00</t>
+          <t>2026-08-20T16:36:02.818042+00:00</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2698,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.000621+00:00</t>
+          <t>2026-08-20T16:36:02.822020+00:00</t>
         </is>
       </c>
     </row>
@@ -2725,12 +2725,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.002717+00:00</t>
+          <t>2026-08-20T16:36:02.823870+00:00</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.004820+00:00</t>
+          <t>2026-08-20T16:36:02.825831+00:00</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.006892+00:00</t>
+          <t>2026-08-20T16:36:02.830087+00:00</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.009106+00:00</t>
+          <t>2026-08-20T16:36:02.834185+00:00</t>
         </is>
       </c>
     </row>
@@ -2833,12 +2833,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.422661+00:00</t>
+          <t>2026-08-20T16:36:03.193407+00:00</t>
         </is>
       </c>
     </row>
@@ -2860,12 +2860,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.433865+00:00</t>
+          <t>2026-08-20T16:36:03.203957+00:00</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.437612+00:00</t>
+          <t>2026-08-20T16:36:03.207080+00:00</t>
         </is>
       </c>
     </row>
@@ -2914,12 +2914,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.446496+00:00</t>
+          <t>2026-08-20T16:36:03.215116+00:00</t>
         </is>
       </c>
     </row>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.449173+00:00</t>
+          <t>2026-08-20T16:36:03.217461+00:00</t>
         </is>
       </c>
     </row>
@@ -2968,12 +2968,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.453455+00:00</t>
+          <t>2026-08-20T16:36:03.224053+00:00</t>
         </is>
       </c>
     </row>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:08.925491+00:00</t>
+          <t>2026-08-20T16:36:00.529289+00:00</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.168201+00:00</t>
+          <t>2026-08-20T16:36:00.675958+00:00</t>
         </is>
       </c>
     </row>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.170145+00:00</t>
+          <t>2026-08-20T16:36:00.677673+00:00</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.172068+00:00</t>
+          <t>2026-08-20T16:36:00.679370+00:00</t>
         </is>
       </c>
     </row>
@@ -3103,12 +3103,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.173993+00:00</t>
+          <t>2026-08-20T16:36:00.681099+00:00</t>
         </is>
       </c>
     </row>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.341015+00:00</t>
+          <t>2026-08-20T16:36:00.888710+00:00</t>
         </is>
       </c>
     </row>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.346104+00:00</t>
+          <t>2026-08-20T16:36:00.893960+00:00</t>
         </is>
       </c>
     </row>
@@ -3184,12 +3184,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.536361+00:00</t>
+          <t>2026-08-20T16:36:01.075861+00:00</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.352111+00:00</t>
+          <t>2026-08-20T16:36:00.899544+00:00</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.354448+00:00</t>
+          <t>2026-08-20T16:36:00.901563+00:00</t>
         </is>
       </c>
     </row>
@@ -3265,12 +3265,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.452969+00:00</t>
+          <t>2026-08-20T16:36:01.002308+00:00</t>
         </is>
       </c>
     </row>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.455411+00:00</t>
+          <t>2026-08-20T16:36:01.004215+00:00</t>
         </is>
       </c>
     </row>
@@ -3319,12 +3319,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.457822+00:00</t>
+          <t>2026-08-20T16:36:01.006176+00:00</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.460028+00:00</t>
+          <t>2026-08-20T16:36:01.008256+00:00</t>
         </is>
       </c>
     </row>
@@ -3373,12 +3373,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.462077+00:00</t>
+          <t>2026-08-20T16:36:01.010073+00:00</t>
         </is>
       </c>
     </row>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.464203+00:00</t>
+          <t>2026-08-20T16:36:01.013064+00:00</t>
         </is>
       </c>
     </row>
@@ -3427,12 +3427,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.466279+00:00</t>
+          <t>2026-08-20T16:36:01.014888+00:00</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.468764+00:00</t>
+          <t>2026-08-20T16:36:01.016662+00:00</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.470854+00:00</t>
+          <t>2026-08-20T16:36:01.018404+00:00</t>
         </is>
       </c>
     </row>
@@ -3508,12 +3508,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.473116+00:00</t>
+          <t>2026-08-20T16:36:01.020219+00:00</t>
         </is>
       </c>
     </row>
@@ -3535,12 +3535,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.475107+00:00</t>
+          <t>2026-08-20T16:36:01.021943+00:00</t>
         </is>
       </c>
     </row>
@@ -3562,12 +3562,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.477260+00:00</t>
+          <t>2026-08-20T16:36:01.024181+00:00</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.479280+00:00</t>
+          <t>2026-08-20T16:36:01.025930+00:00</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.481302+00:00</t>
+          <t>2026-08-20T16:36:01.027685+00:00</t>
         </is>
       </c>
     </row>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.483408+00:00</t>
+          <t>2026-08-20T16:36:01.029762+00:00</t>
         </is>
       </c>
     </row>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.485490+00:00</t>
+          <t>2026-08-20T16:36:01.031607+00:00</t>
         </is>
       </c>
     </row>
@@ -3697,12 +3697,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.487401+00:00</t>
+          <t>2026-08-20T16:36:01.033346+00:00</t>
         </is>
       </c>
     </row>
@@ -3724,12 +3724,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.489510+00:00</t>
+          <t>2026-08-20T16:36:01.035012+00:00</t>
         </is>
       </c>
     </row>
@@ -3751,12 +3751,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.491441+00:00</t>
+          <t>2026-08-20T16:36:01.036800+00:00</t>
         </is>
       </c>
     </row>
@@ -3778,12 +3778,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.493451+00:00</t>
+          <t>2026-08-20T16:36:01.038603+00:00</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.495366+00:00</t>
+          <t>2026-08-20T16:36:01.040380+00:00</t>
         </is>
       </c>
     </row>
@@ -3832,12 +3832,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.497332+00:00</t>
+          <t>2026-08-20T16:36:01.042155+00:00</t>
         </is>
       </c>
     </row>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.499317+00:00</t>
+          <t>2026-08-20T16:36:01.043983+00:00</t>
         </is>
       </c>
     </row>
@@ -3886,12 +3886,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.501259+00:00</t>
+          <t>2026-08-20T16:36:01.045856+00:00</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.503258+00:00</t>
+          <t>2026-08-20T16:36:01.047599+00:00</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.505295+00:00</t>
+          <t>2026-08-20T16:36:01.049342+00:00</t>
         </is>
       </c>
     </row>
@@ -3967,12 +3967,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.507385+00:00</t>
+          <t>2026-08-20T16:36:01.050971+00:00</t>
         </is>
       </c>
     </row>
@@ -3994,12 +3994,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.509389+00:00</t>
+          <t>2026-08-20T16:36:01.052663+00:00</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.511427+00:00</t>
+          <t>2026-08-20T16:36:01.054251+00:00</t>
         </is>
       </c>
     </row>
@@ -4048,12 +4048,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:09.533984+00:00</t>
+          <t>2026-08-20T16:36:01.074049+00:00</t>
         </is>
       </c>
     </row>
@@ -4075,12 +4075,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.425183+00:00</t>
+          <t>2026-08-20T16:36:03.196732+00:00</t>
         </is>
       </c>
     </row>
@@ -4102,12 +4102,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.427504+00:00</t>
+          <t>2026-08-20T16:36:03.198770+00:00</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4129,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>01f70d95b9b4</t>
+          <t>3f98b1b3b9fb</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-19T20:38:12.451412+00:00</t>
+          <t>2026-08-20T16:36:03.222127+00:00</t>
         </is>
       </c>
     </row>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -841,80 +841,80 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CALC-FC005-S3-CONTROL</t>
+          <t>CALC-CURVATURE-cycle(n=3)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'max_abs_e_kappa': 1.0192723588153818e-05, 'a0_max_residual': 5.6033975865277734e-11, 'a1_max_residual': 4.0056349212613886e-08, 'a2_max_residual': 2.0305175367346576e-05, 'exact': {'a0': 19.739208802178716, 'a1': 19.739208802178716, 'a2': 9.869604401089358}}</t>
+          <t>{'max_duality_gap': 0.0}</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CALC-FC005-FISHER-PSD</t>
+          <t>CALC-CURVATURE-cycle(n=6)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'is_positive_semidefinite': True}</t>
+          <t>{'max_duality_gap': 0.0}</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CALC-FC005-EIGEN-UNIQUENESS</t>
+          <t>CALC-CURVATURE-cycle(n=20)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'matrices_differ': True}</t>
+          <t>{'max_duality_gap': 0.0}</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CALC-FC005-DESI-GATE1</t>
+          <t>CALC-CURVATURE-path(n=6)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'converged': False, 'tolerance': 0.15, 'failed_dependency': 'CONTINUUM-LIMIT-L-DESI'}</t>
+          <t>{'max_duality_gap': 0.0}</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CALC-FC005-DESI-SPARSE-N-SCALING</t>
+          <t>CALC-CURVATURE-path(n=20)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'purpose': 'separate finite-resolution failure from point-process failure for CONTINUUM-LIMIT-L-DESI, per FC005_CONTINUUM_DIAGNOSTIC_REPORT.md section 16'}</t>
+          <t>{'max_duality_gap': 0.0}</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -926,66 +926,219 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CALC-H1-SELECTION-WELLPOSEDNESS</t>
+          <t>CALC-CURVATURE-complete(n=5)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">{'hypothesis': 'H1 -- Selection Closure: G* = argmax_{G in Mathset} Pi(G)/S(G)', 'mathset_formally_defined_in_repo': False, 'mathset_repo_occurrences': "only as the bare string 'M in Mathset' inside a code comment in compiler/ir/forward_chain.py -- never as a class, set, type, or constructive definition anywhere in the compiler", 'pi_and_s_implemented_in_repo': True, 'pi_and_s_repo_status': "Pi (persistence functional) and S (structural cost) are described only in prose in Master Equation Codex </t>
+          <t>{'max_duality_gap': 0.0}</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CALC-H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>CALC-CURVATURE-complete(n=6)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'hypothesis': 'H2 -- Spectral-triple / Dirac-operator closure for D+=sqrt(L)', 'test_graph': "n=200 nearest-neighbour ring, k=3 (local connectivity, structurally representative of this project's own sparse geometric graphs)", 'L_self_adjoint_real_symmetric': True, 'L_sparsity_fraction': 0.035, 'D_plus_self_adjoint': True, 'D_plus_sparsity_fraction_strict': 1.0, 'D_plus_sparsity_fraction_relative_1e-3_of_max': 0.235, 'D_plus_row0_decay_by_graph_distance': {'0': 2.3478289210816, '1': 0.2899664965</t>
+          <t>{'max_duality_gap': 0.0}</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CALC-H3-FC005-CORRECTION-TEST</t>
+          <t>CALC-CURVATURE-star(n=8)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'hypothesis': 'H3 -- Discrete-to-continuum kernel-correction closure', 'test_performed_against': 'real DESI DR1 LRG SGC pilot catalogue (data/desi/dr1/fc005/raw/), N=4000-&gt;8000 nested subsample', 'baseline_joint_converged': False, 'candidate_A_tighter_arpack_tolerance': {'joint_converged': False, 'result_identical_to_baseline': False, 'interpretation': 'Result changed under tighter tolerance -- inconclusive, may indicate a genuine precision sensitivity requiring further investigation.'}, 'candi</t>
+          <t>{'max_duality_gap': 0.0}</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>CALC-CURVATURE-grid2d(n=16)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{'max_duality_gap': 4.440892098500626e-16}</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CALC-FC005-S3-CONTROL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>{'max_abs_e_kappa': 1.0192723588153818e-05, 'a0_max_residual': 5.6033975865277734e-11, 'a1_max_residual': 4.0056349212613886e-08, 'a2_max_residual': 2.0305175367346576e-05, 'exact': {'a0': 19.739208802178716, 'a1': 19.739208802178716, 'a2': 9.869604401089358}}</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CALC-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>{'is_positive_semidefinite': True}</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CALC-FC005-EIGEN-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>{'matrices_differ': True}</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CALC-FC005-DESI-GATE1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>{'converged': False, 'tolerance': 0.15, 'failed_dependency': 'CONTINUUM-LIMIT-L-DESI'}</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CALC-FC005-DESI-SPARSE-N-SCALING</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>{'purpose': 'separate finite-resolution failure from point-process failure for CONTINUUM-LIMIT-L-DESI, per FC005_CONTINUUM_DIAGNOSTIC_REPORT.md section 16'}</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CALC-H1-SELECTION-WELLPOSEDNESS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'hypothesis': 'H1 -- Selection Closure: G* = argmax_{G in Mathset} Pi(G)/S(G)', 'mathset_formally_defined_in_repo': False, 'mathset_repo_occurrences': "only as the bare string 'M in Mathset' inside a code comment in compiler/ir/forward_chain.py -- never as a class, set, type, or constructive definition anywhere in the compiler", 'pi_and_s_implemented_in_repo': True, 'pi_and_s_repo_status': "Pi (persistence functional) and S (structural cost) are described only in prose in Master Equation Codex </t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CALC-H2-SPECTRAL-TRIPLE-LOCALITY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>{'hypothesis': 'H2 -- Spectral-triple / Dirac-operator closure for D+=sqrt(L)', 'test_graph': "n=200 nearest-neighbour ring, k=3 (local connectivity, structurally representative of this project's own sparse geometric graphs)", 'L_self_adjoint_real_symmetric': True, 'L_sparsity_fraction': 0.035, 'D_plus_self_adjoint': True, 'D_plus_sparsity_fraction_strict': 1.0, 'D_plus_sparsity_fraction_relative_1e-3_of_max': 0.235, 'D_plus_row0_decay_by_graph_distance': {'0': 2.3478289210816, '1': 0.2899664965</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CALC-H3-FC005-CORRECTION-TEST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>{'hypothesis': 'H3 -- Discrete-to-continuum kernel-correction closure', 'test_performed_against': 'real DESI DR1 LRG SGC pilot catalogue (data/desi/dr1/fc005/raw/), N=4000-&gt;8000 nested subsample', 'baseline_joint_converged': False, 'candidate_A_tighter_arpack_tolerance': {'joint_converged': False, 'result_identical_to_baseline': False, 'interpretation': 'Result changed under tighter tolerance -- inconclusive, may indicate a genuine precision sensitivity requiring further investigation.'}, 'candi</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>CALC-H4-G2-SPIN8-GAUGE-CLOSURE</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>{'hypothesis': 'H4 -- Gauge/internal-algebra closure: does G2/Spin(8)/triality select SU(3)xSU(2)xU(1)?', 'standard_lie_theory_facts_used': {'G2': {'dim': 14, 'rank': 2, 'note': 'Aut(octonions), the smallest exceptional simple Lie group'}, 'Spin(8)': {'dim': 28, 'rank': 4, 'note': 'double cover of SO(8); Out(Spin(8)) = S3 (triality)'}, 'SU(3)': {'dim': 8, 'rank': 2}, 'SU(2)': {'dim': 3, 'rank': 1}, 'U(1)': {'dim': 1, 'rank': 1}}, 'triality_fixed_subgroup_of_Spin(8)': 'G2', 'counterfactual_manusc</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
@@ -1002,7 +1155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1168,77 +1321,77 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FALS-FC005-FISHER-LORENTZIAN</t>
+          <t>FALS-CURVATURE-RELABELING-RIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mathematical_invariance</t>
+          <t>representation_invariance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fisher-Rao metric F = Lorentzian spacetime metric g_munu</t>
+          <t>CURVATURE-OLLIVIER-RICCI for cycle(n=12)</t>
         </is>
       </c>
       <c r="D6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>F is positive semidefinite for every tested sigma (all sampled v^T F v &gt;= 0, eigenvalues at sigma=1: [1.0, 2.0]); a Lorentzian-signature metric requires a strictly negative eigenvalue, which is impossible for a PSD matrix under any basis change (signature is basis-independent). F = g_munu (Lorentzian) is therefore FALSIFIED as a direct identification, for this family and in general.</t>
+          <t>invariant under all tested representations</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>{'eigenvalues_at_sigma1': [1.0, 2.0], 'family': 'Gaussian N(mu, sigma^2), theta=(mu, sigma)'}</t>
+          <t>{'n_representations': 5}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FALS-FC005-EIGENVALUE-UNIQUENESS</t>
+          <t>FALS-CURVATURE-RELABELING-MIT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>structural_elimination</t>
+          <t>mathematical_invariance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>H is uniquely determined by Spec(H)</t>
+          <t>CURVATURE-OLLIVIER-RICCI for cycle(n=12)</t>
         </is>
       </c>
       <c r="D7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25/25 random unitary-conjugation trials produce a distinct operator with identical spectrum.</t>
+          <t>invariant preserved under all 4 tested transformations</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>{'n_confirmed': 25, 'n_trials': 25, 'spectra_match_max_residual': 8.881784197001252e-16}</t>
+          <t>{'n_transformations': 4, 'n_mismatches': 0}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FALS-H4-G2-TRIALITY-RANK-OBSTRUCTION</t>
+          <t>FALS-FC005-FISHER-LORENTZIAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mathematical_invariance_test (rank of compact Lie subgroups)</t>
+          <t>mathematical_invariance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+          <t>Fisher-Rao metric F = Lorentzian spacetime metric g_munu</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -1246,10 +1399,70 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>F is positive semidefinite for every tested sigma (all sampled v^T F v &gt;= 0, eigenvalues at sigma=1: [1.0, 2.0]); a Lorentzian-signature metric requires a strictly negative eigenvalue, which is impossible for a PSD matrix under any basis change (signature is basis-independent). F = g_munu (Lorentzian) is therefore FALSIFIED as a direct identification, for this family and in general.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>{'eigenvalues_at_sigma1': [1.0, 2.0], 'family': 'Gaussian N(mu, sigma^2), theta=(mu, sigma)'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FALS-FC005-EIGENVALUE-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>structural_elimination</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>H is uniquely determined by Spec(H)</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>25/25 random unitary-conjugation trials produce a distinct operator with identical spectrum.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>{'n_confirmed': 25, 'n_trials': 25, 'spectra_match_max_residual': 8.881784197001252e-16}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FALS-H4-G2-TRIALITY-RANK-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>mathematical_invariance_test (rank of compact Lie subgroups)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>rank(SU(3)xSU(2)xU(1)) = 4 &gt; rank(G2) = 2, therefore SU(3)xSU(2)xU(1) CANNOT be realized as a subgroup of G2 under any embedding whatsoever. This rules out the counterfactual manuscript's specific claim that the triality-fixed subgroup of Spin(8) (which is G2 itself, a real, standard fact of Lie theory, dim 14) equals SU(3)xSU(2)xU(1) (dim 12): even setting dimension aside, the rank obstruction is decisive and dimension-independent.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>{'hypothesis': 'H4 -- Gauge/internal-algebra closure: does G2/Spin(8)/triality select SU(3)xSU(2)xU(1)?', 'standard_lie_theory_facts_used': {'G2': {'dim': 14, 'rank': 2, 'note': 'Aut(octonions), the smallest exceptional simple Lie group'}, 'Spin(8)': {'dim': 28, 'rank': 4, 'note': 'double cover of SO(8); Out(Spin(8)) = S3 (triality)'}, 'SU(3)': {'dim': 8, 'rank': 2}, 'SU(2)': {'dim': 3, 'rank': 1}, 'U(1)': {'dim': 1, 'rank': 1}}, 'triality_fixed_subgroup_of_Spin(8)': 'G2', 'counterfactual_manusc</t>
         </is>
@@ -1266,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1321,12 +1534,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.531709+00:00</t>
+          <t>2026-08-20T16:48:28.892926+00:00</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1561,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.533885+00:00</t>
+          <t>2026-08-20T16:48:28.894955+00:00</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1588,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.535737+00:00</t>
+          <t>2026-08-20T16:48:28.897112+00:00</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1615,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.537653+00:00</t>
+          <t>2026-08-20T16:48:28.899027+00:00</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1642,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.539522+00:00</t>
+          <t>2026-08-20T16:48:28.901048+00:00</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1669,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.541410+00:00</t>
+          <t>2026-08-20T16:48:28.903172+00:00</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1696,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.543165+00:00</t>
+          <t>2026-08-20T16:48:28.905124+00:00</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1723,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.545009+00:00</t>
+          <t>2026-08-20T16:48:28.906831+00:00</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1750,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.546691+00:00</t>
+          <t>2026-08-20T16:48:28.908642+00:00</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1777,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.548390+00:00</t>
+          <t>2026-08-20T16:48:28.910771+00:00</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1804,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.550059+00:00</t>
+          <t>2026-08-20T16:48:28.912660+00:00</t>
         </is>
       </c>
     </row>
@@ -1618,12 +1831,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.551927+00:00</t>
+          <t>2026-08-20T16:48:28.914541+00:00</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1858,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.553726+00:00</t>
+          <t>2026-08-20T16:48:28.916510+00:00</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1885,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.555425+00:00</t>
+          <t>2026-08-20T16:48:28.918383+00:00</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1912,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.557169+00:00</t>
+          <t>2026-08-20T16:48:28.920190+00:00</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1939,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.558805+00:00</t>
+          <t>2026-08-20T16:48:28.922124+00:00</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1966,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.560582+00:00</t>
+          <t>2026-08-20T16:48:28.923811+00:00</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1993,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.562292+00:00</t>
+          <t>2026-08-20T16:48:28.925457+00:00</t>
         </is>
       </c>
     </row>
@@ -1807,12 +2020,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.564055+00:00</t>
+          <t>2026-08-20T16:48:28.927102+00:00</t>
         </is>
       </c>
     </row>
@@ -1834,12 +2047,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.565885+00:00</t>
+          <t>2026-08-20T16:48:28.928801+00:00</t>
         </is>
       </c>
     </row>
@@ -1861,12 +2074,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.567597+00:00</t>
+          <t>2026-08-20T16:48:28.930457+00:00</t>
         </is>
       </c>
     </row>
@@ -1888,12 +2101,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.668431+00:00</t>
+          <t>2026-08-20T16:48:29.140668+00:00</t>
         </is>
       </c>
     </row>
@@ -1915,12 +2128,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.670481+00:00</t>
+          <t>2026-08-20T16:48:29.143084+00:00</t>
         </is>
       </c>
     </row>
@@ -1942,12 +2155,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.672440+00:00</t>
+          <t>2026-08-20T16:48:29.145127+00:00</t>
         </is>
       </c>
     </row>
@@ -1969,12 +2182,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.674216+00:00</t>
+          <t>2026-08-20T16:48:29.150027+00:00</t>
         </is>
       </c>
     </row>
@@ -1996,12 +2209,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.884066+00:00</t>
+          <t>2026-08-20T16:48:29.326450+00:00</t>
         </is>
       </c>
     </row>
@@ -2023,73 +2236,73 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.886590+00:00</t>
+          <t>2026-08-20T16:48:29.328788+00:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T2-HISTORICAL</t>
+          <t>CURVATURE-OLLIVIER-RICCI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DTC COMPILER.docx; README.md</t>
+          <t>compiler/backends/ollivier_ricci.py</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.906312+00:00</t>
+          <t>2026-08-20T16:48:29.713048+00:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T2-REPRODUCTION</t>
+          <t>T2-HISTORICAL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>this compiler build</t>
+          <t>DTC COMPILER.docx; README.md</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.908212+00:00</t>
+          <t>2026-08-20T16:48:30.122838+00:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T2-FORWARD-DERIVATION</t>
+          <t>T2-REPRODUCTION</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2104,73 +2317,73 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.910046+00:00</t>
+          <t>2026-08-20T16:48:30.125341+00:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NCG-BRIDGE-EXTERNAL-REFERENCE</t>
+          <t>T2-FORWARD-DERIVATION</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Noncommutative Geometry and the Spectral Action_ Toward a Unified TOE.pdf; Noncommutative Geometry and the Spectral Action_ Toward a Unified Theory.pdf</t>
+          <t>this compiler build</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.914023+00:00</t>
+          <t>2026-08-20T16:48:30.127341+00:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NCG-ABELIAN-BRIDGE-OBSTRUCTION</t>
+          <t>NCG-BRIDGE-EXTERNAL-REFERENCE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>compiler-build repository audit (spec section 2/36)</t>
+          <t>Noncommutative Geometry and the Spectral Action_ Toward a Unified TOE.pdf; Noncommutative Geometry and the Spectral Action_ Toward a Unified Theory.pdf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.917971+00:00</t>
+          <t>2026-08-20T16:48:30.129515+00:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NCG-ASYMMETRIC-ABELIAN-OBSTRUCTION</t>
+          <t>NCG-ABELIAN-BRIDGE-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2185,19 +2398,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.921940+00:00</t>
+          <t>2026-08-20T16:48:30.131637+00:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NCG-NONABELIAN-COMMUTANT-OBSTRUCTION</t>
+          <t>NCG-ASYMMETRIC-ABELIAN-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2212,100 +2425,100 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.926040+00:00</t>
+          <t>2026-08-20T16:48:30.133781+00:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DTC-CIRCULARITY-OBSTRUCTION</t>
+          <t>NCG-NONABELIAN-COMMUTANT-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DTC_Formal_Structure.docx (section 4.2)</t>
+          <t>compiler-build repository audit (spec section 2/36)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.927842+00:00</t>
+          <t>2026-08-20T16:48:30.135721+00:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FC005-WORKBOOK-RECONCILIATION</t>
+          <t>DTC-CIRCULARITY-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/ (4 files)</t>
+          <t>DTC_Formal_Structure.docx (section 4.2)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.929794+00:00</t>
+          <t>2026-08-20T16:48:30.137614+00:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/ (4 files)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.063995+00:00</t>
+          <t>2026-08-20T16:48:30.139642+00:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S3-SPECTRUM</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2315,24 +2528,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.065915+00:00</t>
+          <t>2026-08-20T16:48:30.267621+00:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S3-HEAT-TRACE</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2347,19 +2560,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.067644+00:00</t>
+          <t>2026-08-20T16:48:30.269576+00:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2369,24 +2582,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.069940+00:00</t>
+          <t>2026-08-20T16:48:30.271533+00:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2401,51 +2614,51 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.072119+00:00</t>
+          <t>2026-08-20T16:48:30.273756+00:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://data.desi.lbl.gov/public/dr1/survey/catalogs/dr1/LSS/iron/LSScats/v1.5/LRG_SGC_clustering.dat.fits</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.791908+00:00</t>
+          <t>2026-08-20T16:48:30.275455+00:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
+          <t>https://data.desi.lbl.gov/public/dr1/survey/catalogs/dr1/LSS/iron/LSScats/v1.5/LRG_SGC_clustering.dat.fits</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2455,19 +2668,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.794601+00:00</t>
+          <t>2026-08-20T16:48:31.945525+00:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2482,19 +2695,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.796819+00:00</t>
+          <t>2026-08-20T16:48:31.950450+00:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2504,24 +2717,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.802011+00:00</t>
+          <t>2026-08-20T16:48:31.952480+00:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2536,19 +2749,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.803881+00:00</t>
+          <t>2026-08-20T16:48:31.954422+00:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2558,24 +2771,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.805948+00:00</t>
+          <t>2026-08-20T16:48:31.956438+00:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2590,19 +2803,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.810018+00:00</t>
+          <t>2026-08-20T16:48:31.961882+00:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2617,19 +2830,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.811833+00:00</t>
+          <t>2026-08-20T16:48:31.966143+00:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2644,19 +2857,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.813876+00:00</t>
+          <t>2026-08-20T16:48:31.969891+00:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2671,46 +2884,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.818042+00:00</t>
+          <t>2026-08-20T16:48:31.973890+00:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_fc005_pipeline.py</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.822020+00:00</t>
+          <t>2026-08-20T16:48:31.977978+00:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2720,24 +2933,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.823870+00:00</t>
+          <t>2026-08-20T16:48:31.981922+00:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2752,132 +2965,132 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.825831+00:00</t>
+          <t>2026-08-20T16:48:31.986184+00:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>established semiclassical gravity literature</t>
+          <t>compiler/backends/desi_fc005_pipeline.py</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.830087+00:00</t>
+          <t>2026-08-20T16:48:31.988070+00:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>spec section 18 (FC-005 build command)</t>
+          <t>established semiclassical gravity literature</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:02.834185+00:00</t>
+          <t>2026-08-20T16:48:31.990017+00:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>spec section 18 (FC-005 build command)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:03.193407+00:00</t>
+          <t>2026-08-20T16:48:31.993945+00:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>compiler/falsification/eigen_uniqueness.py</t>
+          <t>compiler/verification/fisher_information.py</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:03.203957+00:00</t>
+          <t>2026-08-20T16:48:32.380184+00:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H1-SELECTION-WELLPOSEDNESS</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>compiler/backends/toe_closure_hypotheses.py::h1_selection_wellposedness_analysis</t>
+          <t>compiler/falsification/eigen_uniqueness.py</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2887,51 +3100,51 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:03.207080+00:00</t>
+          <t>2026-08-20T16:48:32.389804+00:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>compiler/backends/toe_closure_hypotheses.py::h2_spectral_triple_locality_check</t>
+          <t>compiler/backends/toe_closure_hypotheses.py::h1_selection_wellposedness_analysis</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:03.215116+00:00</t>
+          <t>2026-08-20T16:48:32.392959+00:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>H3-FC005-CORRECTION-TEST</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>run_fc005_h3_correction_test.py -&gt; FC005_H3_CORRECTION_TEST_RESULTS.json</t>
+          <t>compiler/backends/toe_closure_hypotheses.py::h2_spectral_triple_locality_check</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2941,51 +3154,51 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:03.217461+00:00</t>
+          <t>2026-08-20T16:48:32.400413+00:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
+          <t>run_fc005_h3_correction_test.py -&gt; FC005_H3_CORRECTION_TEST_RESULTS.json</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:03.224053+00:00</t>
+          <t>2026-08-20T16:48:32.402638+00:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2995,46 +3208,46 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.529289+00:00</t>
+          <t>2026-08-20T16:48:32.406551+00:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>spec section 10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.675958+00:00</t>
+          <t>2026-08-20T16:48:28.890595+00:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3044,24 +3257,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.677673+00:00</t>
+          <t>2026-08-20T16:48:29.151858+00:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3076,19 +3289,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.679370+00:00</t>
+          <t>2026-08-20T16:48:29.154036+00:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3103,46 +3316,46 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.681099+00:00</t>
+          <t>2026-08-20T16:48:29.155895+00:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.888710+00:00</t>
+          <t>2026-08-20T16:48:29.157684+00:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3152,83 +3365,83 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.893960+00:00</t>
+          <t>2026-08-20T16:48:29.330814+00:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.075861+00:00</t>
+          <t>2026-08-20T16:48:29.332813+00:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/backends/ollivier_ricci.py</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.899544+00:00</t>
+          <t>2026-08-20T16:48:29.715444+00:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_flow.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3238,78 +3451,78 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:00.901563+00:00</t>
+          <t>2026-08-20T16:48:30.278985+00:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.002308+00:00</t>
+          <t>2026-08-20T16:48:29.341447+00:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+          <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.004215+00:00</t>
+          <t>2026-08-20T16:48:29.343239+00:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3319,24 +3532,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.006176+00:00</t>
+          <t>2026-08-20T16:48:30.207933+00:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3346,24 +3559,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.008256+00:00</t>
+          <t>2026-08-20T16:48:30.210015+00:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3373,24 +3586,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.010073+00:00</t>
+          <t>2026-08-20T16:48:30.212123+00:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3400,24 +3613,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.013064+00:00</t>
+          <t>2026-08-20T16:48:30.214136+00:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3427,24 +3640,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.014888+00:00</t>
+          <t>2026-08-20T16:48:30.216192+00:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3454,24 +3667,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.016662+00:00</t>
+          <t>2026-08-20T16:48:30.218171+00:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3481,24 +3694,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.018404+00:00</t>
+          <t>2026-08-20T16:48:30.220021+00:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3508,24 +3721,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.020219+00:00</t>
+          <t>2026-08-20T16:48:30.222001+00:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3535,24 +3748,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.021943+00:00</t>
+          <t>2026-08-20T16:48:30.223810+00:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3562,24 +3775,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.024181+00:00</t>
+          <t>2026-08-20T16:48:30.225569+00:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3589,24 +3802,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.025930+00:00</t>
+          <t>2026-08-20T16:48:30.227377+00:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3616,24 +3829,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.027685+00:00</t>
+          <t>2026-08-20T16:48:30.229332+00:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3643,24 +3856,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.029762+00:00</t>
+          <t>2026-08-20T16:48:30.230998+00:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3670,24 +3883,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.031607+00:00</t>
+          <t>2026-08-20T16:48:30.232803+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3697,24 +3910,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.033346+00:00</t>
+          <t>2026-08-20T16:48:30.234519+00:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3724,24 +3937,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.035012+00:00</t>
+          <t>2026-08-20T16:48:30.236224+00:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3751,24 +3964,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.036800+00:00</t>
+          <t>2026-08-20T16:48:30.237955+00:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3778,24 +3991,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.038603+00:00</t>
+          <t>2026-08-20T16:48:30.239615+00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3805,24 +4018,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.040380+00:00</t>
+          <t>2026-08-20T16:48:30.241324+00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3832,24 +4045,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.042155+00:00</t>
+          <t>2026-08-20T16:48:30.243084+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3859,24 +4072,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.043983+00:00</t>
+          <t>2026-08-20T16:48:30.245110+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3886,24 +4099,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.045856+00:00</t>
+          <t>2026-08-20T16:48:30.246967+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3913,24 +4126,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.047599+00:00</t>
+          <t>2026-08-20T16:48:30.248729+00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3940,24 +4153,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.049342+00:00</t>
+          <t>2026-08-20T16:48:30.250469+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3967,24 +4180,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.050971+00:00</t>
+          <t>2026-08-20T16:48:30.252120+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3994,24 +4207,24 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.052663+00:00</t>
+          <t>2026-08-20T16:48:30.253998+00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4021,120 +4234,174 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.054251+00:00</t>
+          <t>2026-08-20T16:48:30.255861+00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-028</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:01.074049+00:00</t>
+          <t>2026-08-20T16:48:30.257644+00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-029</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:03.196732+00:00</t>
+          <t>2026-08-20T16:48:30.259327+00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>3f98b1b3b9fb</t>
+          <t>21ee4c3e87cb</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-20T16:36:03.198770+00:00</t>
+          <t>2026-08-20T16:48:30.277269+00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>21ee4c3e87cb</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-08-20T16:48:32.382593+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>21ee4c3e87cb</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-08-20T16:48:32.384718+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>3f98b1b3b9fb</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>2026-08-20T16:36:03.222127+00:00</t>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>21ee4c3e87cb</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-08-20T16:48:32.404730+00:00</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5950,7 +6217,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T2-HISTORICAL</t>
+          <t>CURVATURE-OLLIVIER-RICCI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5960,19 +6227,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T2-REPRODUCTION</t>
+          <t>T2-HISTORICAL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5982,7 +6249,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5994,7 +6261,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T2-FORWARD-DERIVATION</t>
+          <t>T2-REPRODUCTION</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6016,7 +6283,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NCG-BRIDGE-EXTERNAL-REFERENCE</t>
+          <t>T2-FORWARD-DERIVATION</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6026,7 +6293,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6038,7 +6305,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NCG-ABELIAN-BRIDGE-OBSTRUCTION</t>
+          <t>NCG-BRIDGE-EXTERNAL-REFERENCE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6048,7 +6315,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6060,7 +6327,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NCG-ASYMMETRIC-ABELIAN-OBSTRUCTION</t>
+          <t>NCG-ABELIAN-BRIDGE-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6082,7 +6349,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NCG-NONABELIAN-COMMUTANT-OBSTRUCTION</t>
+          <t>NCG-ASYMMETRIC-ABELIAN-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6104,7 +6371,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DTC-CIRCULARITY-OBSTRUCTION</t>
+          <t>NCG-NONABELIAN-COMMUTANT-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6114,7 +6381,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6126,7 +6393,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FC005-WORKBOOK-RECONCILIATION</t>
+          <t>DTC-CIRCULARITY-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6136,7 +6403,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6148,7 +6415,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6158,7 +6425,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6170,7 +6437,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S3-SPECTRUM</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6180,19 +6447,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S3-HEAT-TRACE</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6207,14 +6474,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['S3-SPECTRUM']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6224,19 +6491,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['S3-HEAT-TRACE']</t>
+          <t>['S3-SPECTRUM']</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6251,14 +6518,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>['S3-HEAT-COEFFICIENTS']</t>
+          <t>['S3-HEAT-TRACE']</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6268,19 +6535,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-HEAT-COEFFICIENTS']</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6295,14 +6562,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>['DESI-CATALOGUE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6317,14 +6584,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>['GRAPH-G-DESI']</t>
+          <t>['DESI-CATALOGUE']</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6334,19 +6601,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>['OPERATOR-L-DESI']</t>
+          <t>['GRAPH-G-DESI']</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6361,14 +6628,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+          <t>['OPERATOR-L-DESI']</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6378,19 +6645,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>['DESI-SPECTRUM']</t>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6405,14 +6672,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>['DESI-HEAT-TRACE']</t>
+          <t>['DESI-SPECTRUM']</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6427,14 +6694,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>['DESI-HEAT-COEFFICIENTS']</t>
+          <t>['DESI-HEAT-TRACE']</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6449,14 +6716,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>['KAPPA-DESI']</t>
+          <t>['DESI-HEAT-COEFFICIENTS']</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6478,7 +6745,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6488,19 +6755,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
+          <t>['KAPPA-DESI']</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6510,19 +6777,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
+          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6537,14 +6804,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
+          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6554,19 +6821,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6576,19 +6843,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6598,19 +6865,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6620,7 +6887,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6632,7 +6899,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H1-SELECTION-WELLPOSEDNESS</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6654,7 +6921,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6664,7 +6931,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6676,7 +6943,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>H3-FC005-CORRECTION-TEST</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6691,14 +6958,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6708,24 +6975,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6742,7 +7009,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6752,19 +7019,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6774,19 +7041,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['GRAPH-G-SEED']</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6801,14 +7068,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6823,14 +7090,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6840,19 +7107,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6862,19 +7129,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6884,29 +7151,29 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['DIFFUSION-DISTANCE']</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6918,12 +7185,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6933,14 +7200,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6950,19 +7217,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6972,19 +7239,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7006,7 +7273,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7028,7 +7295,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7050,7 +7317,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7072,7 +7339,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7094,7 +7361,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7116,7 +7383,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7138,7 +7405,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7160,7 +7427,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7182,7 +7449,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7204,7 +7471,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7226,7 +7493,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7248,7 +7515,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7270,7 +7537,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7292,7 +7559,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7314,7 +7581,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7336,7 +7603,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7358,7 +7625,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7380,7 +7647,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7402,7 +7669,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7424,7 +7691,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7446,7 +7713,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7468,7 +7735,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7490,7 +7757,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7512,7 +7779,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7534,7 +7801,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7556,7 +7823,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7578,7 +7845,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-028</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7588,19 +7855,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>['S3-CURVATURE-CLOSURE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-029</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7610,19 +7877,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7632,32 +7899,76 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>['S3-CURVATURE-CLOSURE']</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -8158,7 +8469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8324,113 +8635,113 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>historical_claim</t>
+          <t>discrete_curvature</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>a prose claim from a pre-compiler source document</t>
+          <t>Ollivier-Ricci discrete graph curvature, computed independently of any non-unique metric candidate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reproduction_attempt</t>
+          <t>historical_claim</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>an attempt to re-execute a historical claim in this compiler</t>
+          <t>a prose claim from a pre-compiler source document</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>forward_derivation_attempt</t>
+          <t>reproduction_attempt</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>an attempt at a target-independent forward derivation</t>
+          <t>an attempt to re-execute a historical claim in this compiler</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>external_literature_reference</t>
+          <t>forward_derivation_attempt</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>a third-party published result, comparison-only</t>
+          <t>an attempt at a target-independent forward derivation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>missing_artifact</t>
+          <t>external_literature_reference</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>a named artifact the build command required but that was not found in the repository</t>
+          <t>a third-party published result, comparison-only</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>self_acknowledged_obstruction</t>
+          <t>missing_artifact</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>a project-internal statement of a derivation obstruction, predating this compiler</t>
+          <t>a named artifact the build command required but that was not found in the repository</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>established_equation</t>
+          <t>self_acknowledged_obstruction</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>an equation asserted by an external/prior source; PROPOSED until independently executed in this compiler</t>
+          <t>a project-internal statement of a derivation obstruction, predating this compiler</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>heat_trace_function</t>
+          <t>established_equation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>K(t) = sum_n exp(-t lambda_n)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>mathematical_object</t>
+          <t>an equation asserted by an external/prior source; PROPOSED until independently executed in this compiler</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>heat_kernel_coefficients</t>
+          <t>heat_trace_function</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fitted (a0, a1, a2, ...) short-time heat-kernel expansion coefficients</t>
+          <t>K(t) = sum_n exp(-t lambda_n)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -8442,99 +8753,116 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>curvature_closure</t>
+          <t>heat_kernel_coefficients</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>the E_kappa = a1/a0 - sgn(a1)*sqrt(2a2/a0) consistency test result</t>
+          <t>fitted (a0, a1, a2, ...) short-time heat-kernel expansion coefficients</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pending_data_construction</t>
+          <t>curvature_closure</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>a construction whose code path exists but that cannot be executed because required observational data is absent</t>
+          <t>the E_kappa = a1/a0 - sgn(a1)*sqrt(2a2/a0) consistency test result</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>semiclassical_framework_equation</t>
+          <t>pending_data_construction</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>the established semiclassical Einstein equation G_munu + Lambda g_munu = (8piG/c^4) &lt;T_munu&gt;_ren</t>
+          <t>a construction whose code path exists but that cannot be executed because required observational data is absent</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>statistical_family</t>
+          <t>semiclassical_framework_equation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>a parametric probability family used to compute a Fisher information matrix</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>mathematical_object</t>
+          <t>the established semiclassical Einstein equation G_munu + Lambda g_munu = (8piG/c^4) &lt;T_munu&gt;_ren</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>operator_uniqueness_counterexample</t>
+          <t>statistical_family</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>an executed counterexample to spectrum-determines-operator</t>
+          <t>a parametric probability family used to compute a Fisher information matrix</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>stage_gate</t>
+          <t>operator_uniqueness_counterexample</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>one of the three independently-reported FC-005 execution stages (mathematical convergence, curvature closure, physical validation); its status is never inferred from another stage_gate's status</t>
+          <t>an executed counterexample to spectrum-determines-operator</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>workbook_reconciliation_record</t>
+          <t>stage_gate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>provenance/precedence record for the four supplied FC-005 workbooks</t>
+          <t>one of the three independently-reported FC-005 execution stages (mathematical convergence, curvature closure, physical validation); its status is never inferred from another stage_gate's status</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>workbook_reconciliation_record</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>provenance/precedence record for the four supplied FC-005 workbooks</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>closure_hypothesis_test</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>an executed test of one of the four primary load-bearing hypotheses (H1-H4) required to decounterfactualize the COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING manuscript</t>
         </is>
@@ -8551,7 +8879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9320,44 +9648,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T2-HISTORICAL</t>
+          <t>CURVATURE-OLLIVIER-RICCI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>historical_claim</t>
+          <t>discrete_curvature</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>upstream_construction</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T2-REPRODUCTION</t>
+          <t>T2-HISTORICAL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>reproduction_attempt</t>
+          <t>historical_claim</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -9374,12 +9702,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T2-FORWARD-DERIVATION</t>
+          <t>T2-REPRODUCTION</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>forward_derivation_attempt</t>
+          <t>reproduction_attempt</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9394,24 +9722,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>upstream_construction</t>
+          <t>comparison</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NCG-BRIDGE-EXTERNAL-REFERENCE</t>
+          <t>T2-FORWARD-DERIVATION</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>external_literature_reference</t>
+          <t>forward_derivation_attempt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9421,24 +9749,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>upstream_construction</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NCG-ABELIAN-BRIDGE-OBSTRUCTION</t>
+          <t>NCG-BRIDGE-EXTERNAL-REFERENCE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>missing_artifact</t>
+          <t>external_literature_reference</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9455,7 +9783,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NCG-ASYMMETRIC-ABELIAN-OBSTRUCTION</t>
+          <t>NCG-ABELIAN-BRIDGE-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -9482,7 +9810,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NCG-NONABELIAN-COMMUTANT-OBSTRUCTION</t>
+          <t>NCG-ASYMMETRIC-ABELIAN-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9509,17 +9837,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DTC-CIRCULARITY-OBSTRUCTION</t>
+          <t>NCG-NONABELIAN-COMMUTANT-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>self_acknowledged_obstruction</t>
+          <t>missing_artifact</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -9536,17 +9864,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FC005-WORKBOOK-RECONCILIATION</t>
+          <t>DTC-CIRCULARITY-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>workbook_reconciliation_record</t>
+          <t>self_acknowledged_obstruction</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -9563,17 +9891,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>mathematical_object</t>
+          <t>workbook_reconciliation_record</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -9583,29 +9911,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>upstream_construction</t>
+          <t>comparison</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S3-SPECTRUM</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>spectral_data</t>
+          <t>mathematical_object</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -9617,12 +9945,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S3-HEAT-TRACE</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>heat_trace_function</t>
+          <t>spectral_data</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -9632,7 +9960,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['S3-SPECTRUM']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -9644,22 +9972,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>heat_kernel_coefficients</t>
+          <t>heat_trace_function</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['S3-HEAT-TRACE']</t>
+          <t>['S3-SPECTRUM']</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -9671,12 +9999,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>curvature_closure</t>
+          <t>heat_kernel_coefficients</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9686,7 +10014,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>['S3-HEAT-COEFFICIENTS']</t>
+          <t>['S3-HEAT-TRACE']</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -9698,39 +10026,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>pending_data_construction</t>
+          <t>curvature_closure</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-HEAT-COEFFICIENTS']</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>observational_output</t>
+          <t>upstream_construction</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>mathematical_object</t>
+          <t>pending_data_construction</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9740,7 +10068,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>['DESI-CATALOGUE']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -9752,12 +10080,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>graph_laplacian_operator</t>
+          <t>mathematical_object</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9767,7 +10095,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>['GRAPH-G-DESI']</t>
+          <t>['DESI-CATALOGUE']</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -9779,22 +10107,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>mathematical_object</t>
+          <t>graph_laplacian_operator</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>['OPERATOR-L-DESI']</t>
+          <t>['GRAPH-G-DESI']</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -9806,12 +10134,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>spectral_data</t>
+          <t>mathematical_object</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -9821,7 +10149,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+          <t>['OPERATOR-L-DESI']</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -9833,22 +10161,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>heat_trace_function</t>
+          <t>spectral_data</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>['DESI-SPECTRUM']</t>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -9860,12 +10188,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>heat_kernel_coefficients</t>
+          <t>heat_trace_function</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9875,7 +10203,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>['DESI-HEAT-TRACE']</t>
+          <t>['DESI-SPECTRUM']</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -9887,12 +10215,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>curvature_closure</t>
+          <t>heat_kernel_coefficients</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9902,7 +10230,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>['DESI-HEAT-COEFFICIENTS']</t>
+          <t>['DESI-HEAT-TRACE']</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -9914,7 +10242,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -9929,7 +10257,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>['KAPPA-DESI']</t>
+          <t>['DESI-HEAT-COEFFICIENTS']</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -9941,7 +10269,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9968,22 +10296,22 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>stage_gate</t>
+          <t>curvature_closure</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
+          <t>['KAPPA-DESI']</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -9995,7 +10323,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10005,12 +10333,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
+          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -10022,7 +10350,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10037,7 +10365,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
+          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -10049,76 +10377,76 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>semiclassical_framework_equation</t>
+          <t>stage_gate</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>observational_output</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>curvature_closure</t>
+          <t>semiclassical_framework_equation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>upstream_construction</t>
+          <t>comparison</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>statistical_family</t>
+          <t>curvature_closure</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -10130,17 +10458,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>operator_uniqueness_counterexample</t>
+          <t>statistical_family</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -10157,12 +10485,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H1-SELECTION-WELLPOSEDNESS</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>closure_hypothesis_test</t>
+          <t>operator_uniqueness_counterexample</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10177,14 +10505,14 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>upstream_construction</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10194,7 +10522,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10211,7 +10539,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>H3-FC005-CORRECTION-TEST</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10226,7 +10554,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -10238,25 +10566,52 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>H3-FC005-CORRECTION-TEST</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>closure_hypothesis_test</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>closure_hypothesis_test</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>comparison</t>
         </is>
@@ -10273,7 +10628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10543,30 +10898,62 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>T-OPERATOR-TO-CURVATURE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CURVATURE-OLLIVIER-RICCI</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>kappa(x,y) = 1 - W1(m_x,m_y)/d(x,y)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>['OPERATOR-L']</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>S3-MANIFOLD</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>analytic Spec -&gt; K(t) -&gt; fit -&gt; E_kappa</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>['S3-MANIFOLD']</t>
         </is>
@@ -11757,7 +12144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12091,151 +12478,151 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S3-SPECTRUM</t>
+          <t>CURVATURE-OLLIVIER-RICCI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S3-HEAT-TRACE</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S3-SPECTRUM</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S3-HEAT-TRACE</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12247,12 +12634,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12651,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12663,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
     </row>
@@ -12288,19 +12675,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12699,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12711,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
     </row>
@@ -12336,19 +12723,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
     </row>
@@ -12360,122 +12747,122 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>H3-FC005-CORRECTION-TEST</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GRAPH-G-SEED</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>GRAPH-G-SEED</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>HEAT-FLOW-R</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DIFFUSION-DISTANCE</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>DIFFUSION-DISTANCE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12487,46 +12874,70 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>HEAT-FLOW-R</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
@@ -12543,7 +12954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12841,103 +13252,103 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T2-HISTORICAL</t>
+          <t>CURVATURE-OLLIVIER-RICCI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SOURCE CLAIM only: no executable derivation, proof object, or numerical artifact backing this claim was found anywhere in the repository during the spec-section-2 audit (searched: all .docx text, first pages of all .pdf files, README.md, and full git log).</t>
+          <t>alpha=0 (non-lazy) one-step random-walk convention, uniform over immediate neighbors -- the canonical Ollivier-Ricci definition, chosen because it requires no freely-tunable parameter (unlike the diffusion-distance construction it is an alternative to).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>T2-HISTORICAL</t>
+          <t>CURVATURE-OLLIVIER-RICCI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Per spec section 2, a document's own label (here, prose asserting "explicitly derived") is never promoted to VERIFIED/DERIVED on the strength of the label alone.</t>
+          <t>This does not construct a continuum Levi-Civita connection or Riemann curvature tensor; it is a discrete graph-curvature notion (Ollivier 2009).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T2-REPRODUCTION</t>
+          <t>T2-HISTORICAL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Not attempted; OPEN per spec section 5 (stop the branch, do not force closure).</t>
+          <t>SOURCE CLAIM only: no executable derivation, proof object, or numerical artifact backing this claim was found anywhere in the repository during the spec-section-2 audit (searched: all .docx text, first pages of all .pdf files, README.md, and full git log).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>T2-FORWARD-DERIVATION</t>
+          <t>T2-HISTORICAL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gauge engine not yet activated in this build; OPEN.</t>
+          <t>Per spec section 2, a document's own label (here, prose asserting "explicitly derived") is never promoted to VERIFIED/DERIVED on the strength of the label alone.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T2-FORWARD-DERIVATION</t>
+          <t>T2-REPRODUCTION</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>See T2-HISTORICAL for the downstream comparison target this node's text and any future construction must remain independent of.</t>
+          <t>Not attempted; OPEN per spec section 5 (stop the branch, do not force closure).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NCG-BRIDGE-EXTERNAL-REFERENCE</t>
+          <t>T2-FORWARD-DERIVATION</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Registered as a comparison/validation target for a future forward reconstruction attempt, not as an upstream selector (spec section 34).</t>
+          <t>Gauge engine not yet activated in this build; OPEN.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NCG-ABELIAN-BRIDGE-OBSTRUCTION</t>
+          <t>T2-FORWARD-DERIVATION</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>STOP condition per spec section 39: missing dependency. Do not fabricate a proof artifact. If the underlying material exists outside this repository, it must be supplied and registered explicitly before this node can advance past OPEN.</t>
+          <t>See T2-HISTORICAL for the downstream comparison target this node's text and any future construction must remain independent of.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NCG-ASYMMETRIC-ABELIAN-OBSTRUCTION</t>
+          <t>NCG-BRIDGE-EXTERNAL-REFERENCE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>STOP condition per spec section 39: missing dependency. Do not fabricate a proof artifact. If the underlying material exists outside this repository, it must be supplied and registered explicitly before this node can advance past OPEN.</t>
+          <t>Registered as a comparison/validation target for a future forward reconstruction attempt, not as an upstream selector (spec section 34).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NCG-NONABELIAN-COMMUTANT-OBSTRUCTION</t>
+          <t>NCG-ABELIAN-BRIDGE-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -12949,91 +13360,91 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DTC-CIRCULARITY-OBSTRUCTION</t>
+          <t>NCG-ASYMMETRIC-ABELIAN-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Registered verbatim as project-internal evidence that the circularity risk was recognized prior to this compiler build; not itself a derivation.</t>
+          <t>STOP condition per spec section 39: missing dependency. Do not fabricate a proof artifact. If the underlying material exists outside this repository, it must be supplied and registered explicitly before this node can advance past OPEN.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FC005-WORKBOOK-RECONCILIATION</t>
+          <t>NCG-NONABELIAN-COMMUTANT-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>canonical (rank 4, PRIMARY): fc005_source_workbooks/04_fc005_primary_full_execution.xlsx</t>
+          <t>STOP condition per spec section 39: missing dependency. Do not fabricate a proof artifact. If the underlying material exists outside this repository, it must be supplied and registered explicitly before this node can advance past OPEN.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FC005-WORKBOOK-RECONCILIATION</t>
+          <t>DTC-CIRCULARITY-OBSTRUCTION</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>filename discrepancies vs the FC-005 build command's own naming: 4 (see provenance.verification)</t>
+          <t>Registered verbatim as project-internal evidence that the circularity risk was recognized prior to this compiler build; not itself a derivation.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>degree=2 quadratic fit alone is insufficient (biased by the neglected a3 t^3 term to |E_kappa|~1e-3); degree&gt;=3 removes the leading bias -- see degree_sweep in provenance.verification</t>
+          <t>canonical (rank 4, PRIMARY): fc005_source_workbooks/04_fc005_primary_full_execution.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>FC005-WORKBOOK-RECONCILIATION</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Checksum-verified against the official DESI DR1 sha256 manifest (FC005_DESI_CATALOG_MANIFEST.json). See FC005_DESI_VALIDATION_REPORT.md for the full 12-point validation checklist (all PASSED).</t>
+          <t>filename discrepancies vs the FC-005 build command's own naming: 4 (see provenance.verification)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
+          <t>degree=2 quadratic fit alone is insufficient (biased by the neglected a3 t^3 term to |E_kappa|~1e-3); degree&gt;=3 removes the leading bias -- see degree_sweep in provenance.verification</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
+          <t>Checksum-verified against the official DESI DR1 sha256 manifest (FC005_DESI_CATALOG_MANIFEST.json). See FC005_DESI_VALIDATION_REPORT.md for the full 12-point validation checklist (all PASSED).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -13045,7 +13456,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -13057,7 +13468,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -13069,151 +13480,151 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Executed live on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits (3000 real objects). Result: STOPPED at mathematical convergence: failed dependency 'CONTINUUM-LIMIT-L-DESI' -- low-spectrum relative change did not fall below tolerance 0.15 under refinement (last relative change 0.7028); L_tilde_(N,eps) does not show numerical evidence of convergence to Delta_h with this catalogue</t>
+          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
+          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
+          <t>Executed live on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits (3000 real objects). Result: STOPPED at mathematical convergence: failed dependency 'CONTINUUM-LIMIT-L-DESI' -- low-spectrum relative change did not fall below tolerance 0.15 under refinement (last relative change 0.7028); L_tilde_(N,eps) does not show numerical evidence of convergence to Delta_h with this catalogue</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>requires a constructed quantum state rho_Q and a renormalized stress tensor &lt;T_munu&gt;_ren; neither is constructed in this build. This is reported as SEMICLASSICAL CLOSURE scope only, never as full quantum gravity (spec section 18).</t>
+          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OPEN OBSTRUCTION (spec section 7B / workbook R-003, TEST-006): eigenvalue-only spectral data cannot reconstruct the operator, and therefore cannot alone reconstruct a geometry (Spec(H) alone -&gt; g_munu is NOT claimed).</t>
+          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>H1-SELECTION-WELLPOSEDNESS</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tests whether G*=argmax_G Pi(G)/S(G) is a well-posed optimization problem given the compiler's own actual definitions (or absence thereof) of Mathset, Pi, and S.</t>
+          <t>requires a constructed quantum state rho_Q and a renormalized stress tensor &lt;T_munu&gt;_ren; neither is constructed in this build. This is reported as SEMICLASSICAL CLOSURE scope only, never as full quantum gravity (spec section 18).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tests the structural locality prerequisite for D+=sqrt(L) to serve as a genuine Dirac-type operator in a spectral triple; does not attempt the full axiom-by-axiom certification (fixing a specific algebra A and computing the first-order condition directly), noted as future work.</t>
+          <t>OPEN OBSTRUCTION (spec section 7B / workbook R-003, TEST-006): eigenvalue-only spectral data cannot reconstruct the operator, and therefore cannot alone reconstruct a geometry (Spec(H) alone -&gt; g_munu is NOT claimed).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>H3-FC005-CORRECTION-TEST</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Additional diagnostic evidence extending (not overwriting) the frozen FC005_CHECKPOINT.md state. Tested against real DESI DR1 LRG SGC data at N=4000-&gt;8000, a smaller N pair than the frozen checkpoint's own best-case N=32000-&gt;64000 result, so this is not a direct re-run of the checkpoint's own claim, but an independent test of correction hypotheses.</t>
+          <t>Tests whether G*=argmax_G Pi(G)/S(G) is a well-posed optimization problem given the compiler's own actual definitions (or absence thereof) of Mathset, Pi, and S.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>rank(Aut(octonions) x Spin(8)) = 2+4 = 6, which IS &gt;= rank(SM) = 4. The rank obstruction that rules out the counterfactual manuscript's 'intersection' claim does NOT rule out this different, direct-product formulation -- SU(3) fits inside the G2 factor (a real, standard, correct maximal-subgroup fact) and SU(2)xU(1) has enough rank to potentially fit inside the Spin(8) factor. This means the repository's ORIGINAL claim remains merely UNCONSTRUCTED (no actual embedding, decomposition, or uniqueness argument is given anywhere in the repository), not proven impossible -- a materially different, more honest status than the counterfactual manuscript's claim, which this analysis shows is actually impossible as stated.</t>
+          <t>Tests the structural locality prerequisite for D+=sqrt(L) to serve as a genuine Dirac-type operator in a spectral triple; does not attempt the full axiom-by-axiom certification (fixing a specific algebra A and computing the first-order condition directly), noted as future work.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>Additional diagnostic evidence extending (not overwriting) the frozen FC005_CHECKPOINT.md state. Tested against real DESI DR1 LRG SGC data at N=4000-&gt;8000, a smaller N pair than the frozen checkpoint's own best-case N=32000-&gt;64000 result, so this is not a direct re-run of the checkpoint's own claim, but an independent test of correction hypotheses.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>rank(Aut(octonions) x Spin(8)) = 2+4 = 6, which IS &gt;= rank(SM) = 4. The rank obstruction that rules out the counterfactual manuscript's 'intersection' claim does NOT rule out this different, direct-product formulation -- SU(3) fits inside the G2 factor (a real, standard, correct maximal-subgroup fact) and SU(2)xU(1) has enough rank to potentially fit inside the Spin(8) factor. This means the repository's ORIGINAL claim remains merely UNCONSTRUCTED (no actual embedding, decomposition, or uniqueness argument is given anywhere in the repository), not proven impossible -- a materially different, more honest status than the counterfactual manuscript's claim, which this analysis shows is actually impossible as stated.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -13225,7 +13636,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -13237,7 +13648,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -13249,7 +13660,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -13261,7 +13672,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -13273,7 +13684,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13285,7 +13696,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -13297,139 +13708,139 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -13441,19 +13852,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -13465,19 +13876,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -13489,58 +13900,82 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>The counterfactual manuscript's specific restatement of the gauge-closure claim (COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8).</t>
         </is>
@@ -13557,7 +13992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13732,25 +14167,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>PROOF-T-OPERATOR-TO-CURVATURE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T-OPERATOR-TO-CURVATURE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>kappa(x,y) = 1 - W1(m_x,m_y)/d(x,y)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>W1 solved as an exact discrete optimal-transport LP (primal transportation formulation) and independently cross-checked via its Kantorovich-Rubinstein LP dual (strong duality); max primal/dual gap over every swept edge = 4.44e-16. Two edges hand-verified by direct calculation (path interior edge and star leaf edge, both kappa=0) confirm the implementation against the definition, not merely internal LP self-consistency.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>PROOF-T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>analytic Spec -&gt; K(t) -&gt; fit -&gt; E_kappa</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>closed-form S^3 spectrum, numpy heat-trace summation with controlled truncation, numpy.polyfit degree-3/4/5 sweep</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -13767,7 +14229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14175,105 +14637,105 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CALC-FC005-S3-CONTROL</t>
+          <t>CALC-CURVATURE-cycle(n=3)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>s3_heat_kernel_control_regression_test</t>
+          <t>ollivier_ricci_curvature</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'windows': [(0.001, 0.004), (0.0015, 0.006), (0.002, 0.008), (0.003, 0.01)], 'degree': 3, 'tolerance': 0.0001}</t>
+          <t>{'graph_label': 'cycle(n=3)'}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CALC-FC005-FISHER-PSD</t>
+          <t>CALC-CURVATURE-cycle(n=6)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fisher_information_psd_demonstration</t>
+          <t>ollivier_ricci_curvature</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'family': 'Gaussian N(mu, sigma^2), theta=(mu, sigma)'}</t>
+          <t>{'graph_label': 'cycle(n=6)'}</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CALC-FC005-EIGEN-UNIQUENESS</t>
+          <t>CALC-CURVATURE-cycle(n=20)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>spectrum_determines_operator_counterexample</t>
+          <t>ollivier_ricci_curvature</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'n': 2, 'n_trials': 25}</t>
+          <t>{'graph_label': 'cycle(n=20)'}</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CALC-FC005-DESI-GATE1</t>
+          <t>CALC-CURVATURE-path(n=6)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>desi_mathematical_convergence_gate</t>
+          <t>ollivier_ricci_curvature</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'fixture': 'data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits', 'N_values': [300, 600, 1000, 1500], 'epsilon_values': [107.9635898398022, 85.6907580429826, 72.27438444792013, 63.137490354544]}</t>
+          <t>{'graph_label': 'path(n=6)'}</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CALC-FC005-DESI-SPARSE-N-SCALING</t>
+          <t>CALC-CURVATURE-path(n=20)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>desi_sparse_n_scaling_point_process_separation</t>
+          <t>ollivier_ricci_curvature</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'report': 'FC005_N_SCALING_REPORT.md', 'raw_data': 'data/desi/dr1/fc005/derived/sparse_n_scaling_full_results.json'}</t>
+          <t>{'graph_label': 'path(n=20)'}</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -14285,86 +14747,284 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CALC-H1-SELECTION-WELLPOSEDNESS</t>
+          <t>CALC-CURVATURE-complete(n=5)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>definitional_wellposedness_audit</t>
+          <t>ollivier_ricci_curvature</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'repo_root': '/home/user/SEIT'}</t>
+          <t>{'graph_label': 'complete(n=5)'}</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CALC-H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>CALC-CURVATURE-complete(n=6)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>spectral_triple_locality_test</t>
+          <t>ollivier_ricci_curvature</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'n': 200, 'k_neighbors': 3, 'seed': 0}</t>
+          <t>{'graph_label': 'complete(n=6)'}</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CALC-H3-FC005-CORRECTION-TEST</t>
+          <t>CALC-CURVATURE-star(n=8)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>discrete_continuum_correction_test</t>
+          <t>ollivier_ricci_curvature</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'n_small': 4000, 'n_large': 8000, 'seed': 20250819}</t>
+          <t>{'graph_label': 'star(n=8)'}</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>CALC-CURVATURE-grid2d(n=16)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ollivier_ricci_curvature</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{'graph_label': 'grid2d(n=16)'}</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CALC-FC005-S3-CONTROL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>s3_heat_kernel_control_regression_test</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>{'windows': [(0.001, 0.004), (0.0015, 0.006), (0.002, 0.008), (0.003, 0.01)], 'degree': 3, 'tolerance': 0.0001}</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CALC-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fisher_information_psd_demonstration</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{'family': 'Gaussian N(mu, sigma^2), theta=(mu, sigma)'}</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CALC-FC005-EIGEN-UNIQUENESS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>spectrum_determines_operator_counterexample</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>{'n': 2, 'n_trials': 25}</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CALC-FC005-DESI-GATE1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>desi_mathematical_convergence_gate</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{'fixture': 'data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits', 'N_values': [300, 600, 1000, 1500], 'epsilon_values': [107.9635898398022, 85.6907580429826, 72.27438444792013, 63.137490354544]}</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CALC-FC005-DESI-SPARSE-N-SCALING</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>desi_sparse_n_scaling_point_process_separation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>{'report': 'FC005_N_SCALING_REPORT.md', 'raw_data': 'data/desi/dr1/fc005/derived/sparse_n_scaling_full_results.json'}</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CALC-H1-SELECTION-WELLPOSEDNESS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>definitional_wellposedness_audit</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>{'repo_root': '/home/user/SEIT'}</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CALC-H2-SPECTRAL-TRIPLE-LOCALITY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>spectral_triple_locality_test</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>{'n': 200, 'k_neighbors': 3, 'seed': 0}</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CALC-H3-FC005-CORRECTION-TEST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>discrete_continuum_correction_test</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>{'n_small': 4000, 'n_large': 8000, 'seed': 20250819}</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>CALC-H4-G2-SPIN8-GAUGE-CLOSURE</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>lie_group_rank_dimension_check</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>{'groups_compared': ['G2', 'Spin(8)', 'SU(3)', 'SU(2)', 'U(1)']}</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1479,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.892926+00:00</t>
+          <t>2026-08-21T02:28:31.071000+00:00</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.894955+00:00</t>
+          <t>2026-08-21T02:28:31.073406+00:00</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.897112+00:00</t>
+          <t>2026-08-21T02:28:31.075639+00:00</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.899027+00:00</t>
+          <t>2026-08-21T02:28:31.077821+00:00</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.901048+00:00</t>
+          <t>2026-08-21T02:28:31.080154+00:00</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.903172+00:00</t>
+          <t>2026-08-21T02:28:31.082329+00:00</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.905124+00:00</t>
+          <t>2026-08-21T02:28:31.084454+00:00</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.906831+00:00</t>
+          <t>2026-08-21T02:28:31.086634+00:00</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.908642+00:00</t>
+          <t>2026-08-21T02:28:31.088684+00:00</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.910771+00:00</t>
+          <t>2026-08-21T02:28:31.090953+00:00</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.912660+00:00</t>
+          <t>2026-08-21T02:28:31.093186+00:00</t>
         </is>
       </c>
     </row>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.914541+00:00</t>
+          <t>2026-08-21T02:28:31.095208+00:00</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1858,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.916510+00:00</t>
+          <t>2026-08-21T02:28:31.097454+00:00</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.918383+00:00</t>
+          <t>2026-08-21T02:28:31.099600+00:00</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.920190+00:00</t>
+          <t>2026-08-21T02:28:31.101812+00:00</t>
         </is>
       </c>
     </row>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.922124+00:00</t>
+          <t>2026-08-21T02:28:31.103914+00:00</t>
         </is>
       </c>
     </row>
@@ -1966,12 +1966,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.923811+00:00</t>
+          <t>2026-08-21T02:28:31.106383+00:00</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.925457+00:00</t>
+          <t>2026-08-21T02:28:31.108415+00:00</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.927102+00:00</t>
+          <t>2026-08-21T02:28:31.110386+00:00</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.928801+00:00</t>
+          <t>2026-08-21T02:28:31.113003+00:00</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.930457+00:00</t>
+          <t>2026-08-21T02:28:31.115100+00:00</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.140668+00:00</t>
+          <t>2026-08-21T02:28:31.275949+00:00</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.143084+00:00</t>
+          <t>2026-08-21T02:28:31.281674+00:00</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2155,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.145127+00:00</t>
+          <t>2026-08-21T02:28:31.283840+00:00</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.150027+00:00</t>
+          <t>2026-08-21T02:28:31.285944+00:00</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.326450+00:00</t>
+          <t>2026-08-21T02:28:31.518379+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.328788+00:00</t>
+          <t>2026-08-21T02:28:31.521087+00:00</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2263,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.713048+00:00</t>
+          <t>2026-08-21T02:28:31.923725+00:00</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.122838+00:00</t>
+          <t>2026-08-21T02:28:32.321659+00:00</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.125341+00:00</t>
+          <t>2026-08-21T02:28:32.324533+00:00</t>
         </is>
       </c>
     </row>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.127341+00:00</t>
+          <t>2026-08-21T02:28:32.326854+00:00</t>
         </is>
       </c>
     </row>
@@ -2371,12 +2371,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.129515+00:00</t>
+          <t>2026-08-21T02:28:32.329194+00:00</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2398,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.131637+00:00</t>
+          <t>2026-08-21T02:28:32.331184+00:00</t>
         </is>
       </c>
     </row>
@@ -2425,12 +2425,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.133781+00:00</t>
+          <t>2026-08-21T02:28:32.333481+00:00</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2452,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.135721+00:00</t>
+          <t>2026-08-21T02:28:32.336215+00:00</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.137614+00:00</t>
+          <t>2026-08-21T02:28:32.338253+00:00</t>
         </is>
       </c>
     </row>
@@ -2506,46 +2506,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.139642+00:00</t>
+          <t>2026-08-21T02:28:32.340560+00:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>FC005-CONTINUUM-EXPONENT-CORRECTION</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>compiler/backends/desi_graph.py::normalize_continuum_limit (correct); compiler/ir/fc005.py CONTINUUM-LIMIT-L-DESI label (was stale, fixed in the same commit as this record)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.267621+00:00</t>
+          <t>2026-08-21T02:28:32.347636+00:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S3-SPECTRUM</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2555,24 +2555,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.269576+00:00</t>
+          <t>2026-08-21T02:28:32.487124+00:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S3-HEAT-TRACE</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2587,19 +2587,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.271533+00:00</t>
+          <t>2026-08-21T02:28:32.489355+00:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2609,24 +2609,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.273756+00:00</t>
+          <t>2026-08-21T02:28:32.491540+00:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2641,51 +2641,51 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.275455+00:00</t>
+          <t>2026-08-21T02:28:32.493584+00:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://data.desi.lbl.gov/public/dr1/survey/catalogs/dr1/LSS/iron/LSScats/v1.5/LRG_SGC_clustering.dat.fits</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.945525+00:00</t>
+          <t>2026-08-21T02:28:32.495774+00:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
+          <t>https://data.desi.lbl.gov/public/dr1/survey/catalogs/dr1/LSS/iron/LSScats/v1.5/LRG_SGC_clustering.dat.fits</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2695,19 +2695,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.950450+00:00</t>
+          <t>2026-08-21T02:28:34.688616+00:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2722,19 +2722,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.952480+00:00</t>
+          <t>2026-08-21T02:28:34.692030+00:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2744,24 +2744,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.954422+00:00</t>
+          <t>2026-08-21T02:28:34.694873+00:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2776,19 +2776,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.956438+00:00</t>
+          <t>2026-08-21T02:28:34.697454+00:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2798,24 +2798,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.961882+00:00</t>
+          <t>2026-08-21T02:28:34.700093+00:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2830,19 +2830,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.966143+00:00</t>
+          <t>2026-08-21T02:28:34.702589+00:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2857,19 +2857,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.969891+00:00</t>
+          <t>2026-08-21T02:28:34.705122+00:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.973890+00:00</t>
+          <t>2026-08-21T02:28:34.707738+00:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2911,46 +2911,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.977978+00:00</t>
+          <t>2026-08-21T02:28:34.710126+00:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>compiler/backends/desi_fc005_pipeline.py</t>
+          <t>compiler/backends/desi_fc005_pipeline.py (executed on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.981922+00:00</t>
+          <t>2026-08-21T02:28:34.712691+00:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2960,24 +2960,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.986184+00:00</t>
+          <t>2026-08-21T02:28:34.717832+00:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2992,132 +2992,132 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.988070+00:00</t>
+          <t>2026-08-21T02:28:34.720505+00:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>established semiclassical gravity literature</t>
+          <t>compiler/backends/desi_fc005_pipeline.py</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.990017+00:00</t>
+          <t>2026-08-21T02:28:34.725305+00:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>spec section 18 (FC-005 build command)</t>
+          <t>established semiclassical gravity literature</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:31.993945+00:00</t>
+          <t>2026-08-21T02:28:34.727454+00:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>spec section 18 (FC-005 build command)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:32.380184+00:00</t>
+          <t>2026-08-21T02:28:34.729407+00:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>compiler/falsification/eigen_uniqueness.py</t>
+          <t>compiler/verification/fisher_information.py</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:32.389804+00:00</t>
+          <t>2026-08-21T02:28:35.132699+00:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H1-SELECTION-WELLPOSEDNESS</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>compiler/backends/toe_closure_hypotheses.py::h1_selection_wellposedness_analysis</t>
+          <t>compiler/falsification/eigen_uniqueness.py</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3127,51 +3127,51 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:32.392959+00:00</t>
+          <t>2026-08-21T02:28:35.144545+00:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>compiler/backends/toe_closure_hypotheses.py::h2_spectral_triple_locality_check</t>
+          <t>compiler/backends/toe_closure_hypotheses.py::h1_selection_wellposedness_analysis</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:32.400413+00:00</t>
+          <t>2026-08-21T02:28:35.148361+00:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>H3-FC005-CORRECTION-TEST</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>run_fc005_h3_correction_test.py -&gt; FC005_H3_CORRECTION_TEST_RESULTS.json</t>
+          <t>compiler/backends/toe_closure_hypotheses.py::h2_spectral_triple_locality_check</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3181,51 +3181,51 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:32.402638+00:00</t>
+          <t>2026-08-21T02:28:35.156576+00:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
+          <t>run_fc005_h3_correction_test.py -&gt; FC005_H3_CORRECTION_TEST_RESULTS.json</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:32.406551+00:00</t>
+          <t>2026-08-21T02:28:35.161749+00:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3235,46 +3235,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:28.890595+00:00</t>
+          <t>2026-08-21T02:28:35.166091+00:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>spec section 10</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.151858+00:00</t>
+          <t>2026-08-21T02:28:31.068200+00:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -3284,24 +3284,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.154036+00:00</t>
+          <t>2026-08-21T02:28:31.289222+00:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3316,19 +3316,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.155895+00:00</t>
+          <t>2026-08-21T02:28:31.293163+00:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3343,46 +3343,46 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.157684+00:00</t>
+          <t>2026-08-21T02:28:31.295096+00:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.330814+00:00</t>
+          <t>2026-08-21T02:28:31.297108+00:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3392,164 +3392,164 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.332813+00:00</t>
+          <t>2026-08-21T02:28:31.525391+00:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>compiler/backends/ollivier_ricci.py</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.715444+00:00</t>
+          <t>2026-08-21T02:28:31.527630+00:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>compiler/backends/ollivier_ricci.py</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.278985+00:00</t>
+          <t>2026-08-21T02:28:31.926421+00:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.341447+00:00</t>
+          <t>2026-08-21T02:28:32.500512+00:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_flow.py</t>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:29.343239+00:00</t>
+          <t>2026-08-21T02:28:31.537160+00:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+          <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.207933+00:00</t>
+          <t>2026-08-21T02:28:31.543522+00:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3559,24 +3559,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.210015+00:00</t>
+          <t>2026-08-21T02:28:32.420101+00:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3586,24 +3586,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.212123+00:00</t>
+          <t>2026-08-21T02:28:32.422836+00:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3613,24 +3613,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.214136+00:00</t>
+          <t>2026-08-21T02:28:32.425190+00:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3640,24 +3640,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.216192+00:00</t>
+          <t>2026-08-21T02:28:32.427294+00:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3667,24 +3667,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.218171+00:00</t>
+          <t>2026-08-21T02:28:32.429357+00:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3694,24 +3694,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.220021+00:00</t>
+          <t>2026-08-21T02:28:32.431411+00:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3721,24 +3721,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.222001+00:00</t>
+          <t>2026-08-21T02:28:32.433346+00:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3748,24 +3748,24 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.223810+00:00</t>
+          <t>2026-08-21T02:28:32.435453+00:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3775,24 +3775,24 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.225569+00:00</t>
+          <t>2026-08-21T02:28:32.437483+00:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3802,24 +3802,24 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.227377+00:00</t>
+          <t>2026-08-21T02:28:32.439414+00:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3829,24 +3829,24 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.229332+00:00</t>
+          <t>2026-08-21T02:28:32.441348+00:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.230998+00:00</t>
+          <t>2026-08-21T02:28:32.443309+00:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3883,24 +3883,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.232803+00:00</t>
+          <t>2026-08-21T02:28:32.445303+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3910,24 +3910,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.234519+00:00</t>
+          <t>2026-08-21T02:28:32.447280+00:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3937,24 +3937,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.236224+00:00</t>
+          <t>2026-08-21T02:28:32.449230+00:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3964,24 +3964,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.237955+00:00</t>
+          <t>2026-08-21T02:28:32.451243+00:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3991,24 +3991,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.239615+00:00</t>
+          <t>2026-08-21T02:28:32.453198+00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4018,24 +4018,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.241324+00:00</t>
+          <t>2026-08-21T02:28:32.455193+00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4045,24 +4045,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.243084+00:00</t>
+          <t>2026-08-21T02:28:32.457095+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4072,24 +4072,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.245110+00:00</t>
+          <t>2026-08-21T02:28:32.458977+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4099,24 +4099,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.246967+00:00</t>
+          <t>2026-08-21T02:28:32.461002+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4126,24 +4126,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.248729+00:00</t>
+          <t>2026-08-21T02:28:32.462898+00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4153,24 +4153,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.250469+00:00</t>
+          <t>2026-08-21T02:28:32.464813+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4180,24 +4180,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.252120+00:00</t>
+          <t>2026-08-21T02:28:32.466773+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4207,24 +4207,24 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.253998+00:00</t>
+          <t>2026-08-21T02:28:32.468714+00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4234,24 +4234,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.255861+00:00</t>
+          <t>2026-08-21T02:28:32.470623+00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4261,24 +4261,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.257644+00:00</t>
+          <t>2026-08-21T02:28:32.472518+00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-028</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4288,51 +4288,51 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.259327+00:00</t>
+          <t>2026-08-21T02:28:32.474472+00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-029</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:30.277269+00:00</t>
+          <t>2026-08-21T02:28:32.476598+00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4342,19 +4342,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:32.382593+00:00</t>
+          <t>2026-08-21T02:28:32.498359+00:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-FC005-FISHER-PSD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4364,44 +4364,71 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>21ee4c3e87cb</t>
+          <t>311c588921d0</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-20T16:48:32.384718+00:00</t>
+          <t>2026-08-21T02:28:35.136063+00:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>311c588921d0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-08-21T02:28:35.138513+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>21ee4c3e87cb</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>2026-08-20T16:48:32.404730+00:00</t>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>311c588921d0</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-08-21T02:28:35.163953+00:00</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4534,7 +4561,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>FC005-CONTINUUM-EXPONENT-CORRECTION</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4544,7 +4571,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>observational_output</t>
+          <t>comparison</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -4552,265 +4579,317 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>continuum_exponent_correction_record
+CONTINUUM-LIMIT-L-DESI normalization exponent: superseded eps^(5/2) (d=3) -&gt; corrected eps^(d+2) = eps^5 (d=3). The workbook's own kernel definition (EQ-013/DC-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DESI-CATALOGUE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>pending_data_construction
 DESI DR1 LRG SGC clustering catalogue, v1.5, real data acquired from the official public release and checksum-verified. Pilot fixture: 3000 objects (0.4&lt;=z&lt;0.6 subsample), us</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>GRAPH-G-DESI</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D6" t="b">
+      <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>mathematical_object
 G_DESI = (V,E,W): weighted observational graph from the DESI catalogue</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>OPERATOR-L-DESI</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D7" t="b">
+      <c r="D8" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>graph_laplacian_operator
 L_DESI = D - W</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DESI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>observational_output</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>mathematical_object
+L_tilde_(N,eps) = -L_N/(C_K N eps^(d+2)), d=3 -&gt; eps^5. CORRECTED from the workbook's eps^(d/2+1)=eps^(5/2), which is only valid under a different (length^2-unit) kernel convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>DESI-SPECTRUM</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D8" t="b">
+      <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>spectral_data
 Spec(-Delta_h) via -L_tilde eigenproblem (sign-corrected, see desi_fc005_pipeline.py)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D9" t="b">
+      <c r="D11" t="b">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>heat_trace_function
 K(t) from the DESI-derived spectrum</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>KAPPA-DESI</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D10" t="b">
+      <c r="D12" t="b">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>curvature_closure
 kappa_spectral from DESI data</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>E-KAPPA-DESI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D11" t="b">
+      <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>curvature_closure
 E_kappa closure residual for DESI</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D12" t="b">
+      <c r="D14" t="b">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>stage_gate
 Stage 1: does L_tilde_(N,eps) converge under (N,eps) refinement? A property of the operator and the sampling, evaluated independently of any curvature or cosmological claim. See compiler/ba</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D15" t="b">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t xml:space="preserve">stage_gate
 Stage 2: only evaluated if stage 1 converged. Does E_kappa fall below the predefined tolerance? A property of the fitted heat-kernel coefficients, independent of any external/observational </t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>DESI</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>observational_output</t>
         </is>
       </c>
-      <c r="D14" t="b">
+      <c r="D16" t="b">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>stage_gate
 Stage 3: only evaluated if stage 2 closed. Does kappa_spectral agree with an INDEPENDENTLY sourced kappa_cosmological (never derived from the same catalogue/run)? See compiler/backends/desi</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>SU(3)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>comparison</t>
         </is>
       </c>
-      <c r="D15" t="b">
+      <c r="D17" t="b">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>G2 (intersection via triality) Spin(8)
 SU(3) x SU(2) x U(1)
@@ -4819,26 +4898,26 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>SU(2)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>comparison</t>
         </is>
       </c>
-      <c r="D16" t="b">
+      <c r="D18" t="b">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>G2 (intersection via triality) Spin(8)
 SU(3) x SU(2) x U(1)
@@ -4847,26 +4926,26 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>U(1)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>comparison</t>
         </is>
       </c>
-      <c r="D17" t="b">
+      <c r="D19" t="b">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>G2 (intersection via triality) Spin(8)
 SU(3) x SU(2) x U(1)
@@ -5589,7 +5668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6437,7 +6516,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>FC005-CONTINUUM-EXPONENT-CORRECTION</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6447,7 +6526,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6459,7 +6538,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S3-SPECTRUM</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6469,19 +6548,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S3-HEAT-TRACE</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6496,14 +6575,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['S3-SPECTRUM']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6513,19 +6592,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>['S3-HEAT-TRACE']</t>
+          <t>['S3-SPECTRUM']</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6540,14 +6619,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>['S3-HEAT-COEFFICIENTS']</t>
+          <t>['S3-HEAT-TRACE']</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6557,19 +6636,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-HEAT-COEFFICIENTS']</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6584,14 +6663,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>['DESI-CATALOGUE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6606,14 +6685,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>['GRAPH-G-DESI']</t>
+          <t>['DESI-CATALOGUE']</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6623,19 +6702,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>['OPERATOR-L-DESI']</t>
+          <t>['GRAPH-G-DESI']</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6650,14 +6729,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+          <t>['OPERATOR-L-DESI']</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6667,19 +6746,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>['DESI-SPECTRUM']</t>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6694,14 +6773,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>['DESI-HEAT-TRACE']</t>
+          <t>['DESI-SPECTRUM']</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6716,14 +6795,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>['DESI-HEAT-COEFFICIENTS']</t>
+          <t>['DESI-HEAT-TRACE']</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6738,14 +6817,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>['KAPPA-DESI']</t>
+          <t>['DESI-HEAT-COEFFICIENTS']</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6767,7 +6846,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6777,19 +6856,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
+          <t>['KAPPA-DESI']</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6799,19 +6878,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
+          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6826,14 +6905,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
+          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6843,19 +6922,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6865,19 +6944,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6887,19 +6966,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6909,7 +6988,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -6921,7 +7000,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H1-SELECTION-WELLPOSEDNESS</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6943,7 +7022,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6953,7 +7032,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6965,7 +7044,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>H3-FC005-CORRECTION-TEST</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6980,14 +7059,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6997,24 +7076,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7031,7 +7110,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7041,19 +7120,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7063,19 +7142,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['GRAPH-G-SEED']</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7090,14 +7169,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7112,14 +7191,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7129,19 +7208,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7151,19 +7230,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7173,19 +7252,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['DIFFUSION-DISTANCE']</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7195,41 +7274,41 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7239,19 +7318,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7261,19 +7340,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7295,7 +7374,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7317,7 +7396,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7339,7 +7418,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7361,7 +7440,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7383,7 +7462,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7405,7 +7484,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7427,7 +7506,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7449,7 +7528,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7471,7 +7550,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7493,7 +7572,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7515,7 +7594,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7537,7 +7616,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7559,7 +7638,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7581,7 +7660,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7603,7 +7682,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7625,7 +7704,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7647,7 +7726,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7669,7 +7748,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7691,7 +7770,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7713,7 +7792,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7735,7 +7814,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7757,7 +7836,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7779,7 +7858,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7801,7 +7880,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7823,7 +7902,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7845,7 +7924,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7867,7 +7946,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-028</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7889,7 +7968,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-029</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7899,19 +7978,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>['S3-CURVATURE-CLOSURE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7926,14 +8005,14 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>['S3-CURVATURE-CLOSURE']</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-FC005-FISHER-PSD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7943,7 +8022,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7955,20 +8034,42 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -8469,7 +8570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8859,10 +8960,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>continuum_exponent_correction_record</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>provenance record for the CONTINUUM-LIMIT-L-DESI eps^(5/2) -&gt; eps^5 correction: what was stale, where, root cause, and how it was found</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>closure_hypothesis_test</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>an executed test of one of the four primary load-bearing hypotheses (H1-H4) required to decounterfactualize the COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING manuscript</t>
         </is>
@@ -8879,7 +8992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9918,17 +10031,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>FC005-CONTINUUM-EXPONENT-CORRECTION</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mathematical_object</t>
+          <t>continuum_exponent_correction_record</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -9938,29 +10051,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>upstream_construction</t>
+          <t>comparison</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S3-SPECTRUM</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>spectral_data</t>
+          <t>mathematical_object</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -9972,12 +10085,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S3-HEAT-TRACE</t>
+          <t>S3-SPECTRUM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>heat_trace_function</t>
+          <t>spectral_data</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9987,7 +10100,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>['S3-SPECTRUM']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -9999,22 +10112,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>S3-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>heat_kernel_coefficients</t>
+          <t>heat_trace_function</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>['S3-HEAT-TRACE']</t>
+          <t>['S3-SPECTRUM']</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -10026,12 +10139,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>curvature_closure</t>
+          <t>heat_kernel_coefficients</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10041,7 +10154,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>['S3-HEAT-COEFFICIENTS']</t>
+          <t>['S3-HEAT-TRACE']</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -10053,39 +10166,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>S3-CURVATURE-CLOSURE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pending_data_construction</t>
+          <t>curvature_closure</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-HEAT-COEFFICIENTS']</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>observational_output</t>
+          <t>upstream_construction</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GRAPH-G-DESI</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>mathematical_object</t>
+          <t>pending_data_construction</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -10095,7 +10208,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>['DESI-CATALOGUE']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -10107,12 +10220,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OPERATOR-L-DESI</t>
+          <t>GRAPH-G-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>graph_laplacian_operator</t>
+          <t>mathematical_object</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10122,7 +10235,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>['GRAPH-G-DESI']</t>
+          <t>['DESI-CATALOGUE']</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10134,22 +10247,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CONTINUUM-LIMIT-L-DESI</t>
+          <t>OPERATOR-L-DESI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>mathematical_object</t>
+          <t>graph_laplacian_operator</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>['OPERATOR-L-DESI']</t>
+          <t>['GRAPH-G-DESI']</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -10161,12 +10274,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DESI-SPECTRUM</t>
+          <t>CONTINUUM-LIMIT-L-DESI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>spectral_data</t>
+          <t>mathematical_object</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10176,7 +10289,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+          <t>['OPERATOR-L-DESI']</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -10188,22 +10301,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>DESI-SPECTRUM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>heat_trace_function</t>
+          <t>spectral_data</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>['DESI-SPECTRUM']</t>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -10215,12 +10328,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>heat_kernel_coefficients</t>
+          <t>heat_trace_function</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10230,7 +10343,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>['DESI-HEAT-TRACE']</t>
+          <t>['DESI-SPECTRUM']</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -10242,12 +10355,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>curvature_closure</t>
+          <t>heat_kernel_coefficients</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -10257,7 +10370,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>['DESI-HEAT-COEFFICIENTS']</t>
+          <t>['DESI-HEAT-TRACE']</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -10269,7 +10382,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -10284,7 +10397,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>['KAPPA-DESI']</t>
+          <t>['DESI-HEAT-COEFFICIENTS']</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -10296,7 +10409,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10323,22 +10436,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>stage_gate</t>
+          <t>curvature_closure</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
+          <t>['KAPPA-DESI']</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -10350,7 +10463,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10360,12 +10473,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
+          <t>['GRAPH-G-DESI', 'OPERATOR-L-DESI', 'CONTINUUM-LIMIT-L-DESI', 'DESI-SPECTRUM']</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -10377,7 +10490,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10392,7 +10505,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
+          <t>['MATHEMATICAL-CONVERGENCE-DESI', 'DESI-HEAT-TRACE', 'DESI-HEAT-COEFFICIENTS', 'E-KAPPA-DESI']</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -10404,76 +10517,76 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>semiclassical_framework_equation</t>
+          <t>stage_gate</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CURVATURE-CLOSURE-DESI', 'DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK']</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>observational_output</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>SEMICLASSICAL-EINSTEIN-EQUATION</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>curvature_closure</t>
+          <t>semiclassical_framework_equation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>upstream_construction</t>
+          <t>comparison</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>statistical_family</t>
+          <t>curvature_closure</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SEMICLASSICAL-EINSTEIN-EQUATION']</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -10485,17 +10598,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>operator_uniqueness_counterexample</t>
+          <t>statistical_family</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10512,12 +10625,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>H1-SELECTION-WELLPOSEDNESS</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>closure_hypothesis_test</t>
+          <t>operator_uniqueness_counterexample</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10532,14 +10645,14 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>comparison</t>
+          <t>upstream_construction</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10549,7 +10662,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10566,7 +10679,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>H3-FC005-CORRECTION-TEST</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10581,7 +10694,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -10593,25 +10706,52 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>H3-FC005-CORRECTION-TEST</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>closure_hypothesis_test</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>['CONTINUUM-LIMIT-L-DESI']</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>closure_hypothesis_test</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>comparison</t>
         </is>
@@ -12954,7 +13094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13420,55 +13560,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S3-HEAT-COEFFICIENTS</t>
+          <t>FC005-CONTINUUM-EXPONENT-CORRECTION</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>degree=2 quadratic fit alone is insufficient (biased by the neglected a3 t^3 term to |E_kappa|~1e-3); degree&gt;=3 removes the leading bias -- see degree_sweep in provenance.verification</t>
+          <t>Found during an external verification pass over an uploaded document (CANONICAL_DERIVATION_ARCHITECTURE.md) that itself asserted the superseded eps^(5/2) exponent; cross-checking that claim against compiler/backends/desi_graph.py's own already-corrected implementation surfaced this project's own registry/source-label staleness as a second, separate finding.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DESI-CATALOGUE</t>
+          <t>FC005-CONTINUUM-EXPONENT-CORRECTION</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Checksum-verified against the official DESI DR1 sha256 manifest (FC005_DESI_CATALOG_MANIFEST.json). See FC005_DESI_VALIDATION_REPORT.md for the full 12-point validation checklist (all PASSED).</t>
+          <t>4 locations audited directly by inspection; see provenance.verification for the per-location table.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DESI-HEAT-TRACE</t>
+          <t>S3-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
+          <t>degree=2 quadratic fit alone is insufficient (biased by the neglected a3 t^3 term to |E_kappa|~1e-3); degree&gt;=3 removes the leading bias -- see degree_sweep in provenance.verification</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DESI-HEAT-COEFFICIENTS</t>
+          <t>DESI-CATALOGUE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
+          <t>Checksum-verified against the official DESI DR1 sha256 manifest (FC005_DESI_CATALOG_MANIFEST.json). See FC005_DESI_VALIDATION_REPORT.md for the full 12-point validation checklist (all PASSED).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KAPPA-DESI</t>
+          <t>DESI-HEAT-TRACE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -13480,7 +13620,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>E-KAPPA-DESI</t>
+          <t>DESI-HEAT-COEFFICIENTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -13492,7 +13632,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
+          <t>KAPPA-DESI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -13504,151 +13644,151 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
+          <t>E-KAPPA-DESI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Executed live on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits (3000 real objects). Result: STOPPED at mathematical convergence: failed dependency 'CONTINUUM-LIMIT-L-DESI' -- low-spectrum relative change did not fall below tolerance 0.15 under refinement (last relative change 0.7028); L_tilde_(N,eps) does not show numerical evidence of convergence to Delta_h with this catalogue</t>
+          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CURVATURE-CLOSURE-DESI</t>
+          <t>DELTA-KAPPA-COSMOLOGICAL-CROSSCHECK</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
+          <t>Gate 1 (mathematical convergence) FAILED on the real pilot fixture -- this node was never entered/executed, per instruction: only enter Gate 2 if Gate 1 passes.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PHYSICAL-VALIDATION-DESI</t>
+          <t>MATHEMATICAL-CONVERGENCE-DESI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
+          <t>Executed live on data/desi/dr1/fc005/validated/pilot_fixture/lrg_sgc_pilot_3000_z0.4-0.6.fits (3000 real objects). Result: STOPPED at mathematical convergence: failed dependency 'CONTINUUM-LIMIT-L-DESI' -- low-spectrum relative change did not fall below tolerance 0.15 under refinement (last relative change 0.7028); L_tilde_(N,eps) does not show numerical evidence of convergence to Delta_h with this catalogue</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
+          <t>CURVATURE-CLOSURE-DESI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>requires a constructed quantum state rho_Q and a renormalized stress tensor &lt;T_munu&gt;_ren; neither is constructed in this build. This is reported as SEMICLASSICAL CLOSURE scope only, never as full quantum gravity (spec section 18).</t>
+          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SPEC-H-UNIQUENESS</t>
+          <t>PHYSICAL-VALIDATION-DESI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OPEN OBSTRUCTION (spec section 7B / workbook R-003, TEST-006): eigenvalue-only spectral data cannot reconstruct the operator, and therefore cannot alone reconstruct a geometry (Spec(H) alone -&gt; g_munu is NOT claimed).</t>
+          <t>Never entered: Gate 1 (mathematical convergence) did not pass on the real pilot fixture. Per instruction, later gates are never evaluated when an earlier gate fails.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>H1-SELECTION-WELLPOSEDNESS</t>
+          <t>SEMICLASSICAL-RESIDUAL-E-SC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tests whether G*=argmax_G Pi(G)/S(G) is a well-posed optimization problem given the compiler's own actual definitions (or absence thereof) of Mathset, Pi, and S.</t>
+          <t>requires a constructed quantum state rho_Q and a renormalized stress tensor &lt;T_munu&gt;_ren; neither is constructed in this build. This is reported as SEMICLASSICAL CLOSURE scope only, never as full quantum gravity (spec section 18).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
+          <t>SPEC-H-UNIQUENESS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tests the structural locality prerequisite for D+=sqrt(L) to serve as a genuine Dirac-type operator in a spectral triple; does not attempt the full axiom-by-axiom certification (fixing a specific algebra A and computing the first-order condition directly), noted as future work.</t>
+          <t>OPEN OBSTRUCTION (spec section 7B / workbook R-003, TEST-006): eigenvalue-only spectral data cannot reconstruct the operator, and therefore cannot alone reconstruct a geometry (Spec(H) alone -&gt; g_munu is NOT claimed).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>H3-FC005-CORRECTION-TEST</t>
+          <t>H1-SELECTION-WELLPOSEDNESS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Additional diagnostic evidence extending (not overwriting) the frozen FC005_CHECKPOINT.md state. Tested against real DESI DR1 LRG SGC data at N=4000-&gt;8000, a smaller N pair than the frozen checkpoint's own best-case N=32000-&gt;64000 result, so this is not a direct re-run of the checkpoint's own claim, but an independent test of correction hypotheses.</t>
+          <t>Tests whether G*=argmax_G Pi(G)/S(G) is a well-posed optimization problem given the compiler's own actual definitions (or absence thereof) of Mathset, Pi, and S.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
+          <t>H2-SPECTRAL-TRIPLE-LOCALITY</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>rank(Aut(octonions) x Spin(8)) = 2+4 = 6, which IS &gt;= rank(SM) = 4. The rank obstruction that rules out the counterfactual manuscript's 'intersection' claim does NOT rule out this different, direct-product formulation -- SU(3) fits inside the G2 factor (a real, standard, correct maximal-subgroup fact) and SU(2)xU(1) has enough rank to potentially fit inside the Spin(8) factor. This means the repository's ORIGINAL claim remains merely UNCONSTRUCTED (no actual embedding, decomposition, or uniqueness argument is given anywhere in the repository), not proven impossible -- a materially different, more honest status than the counterfactual manuscript's claim, which this analysis shows is actually impossible as stated.</t>
+          <t>Tests the structural locality prerequisite for D+=sqrt(L) to serve as a genuine Dirac-type operator in a spectral triple; does not attempt the full axiom-by-axiom certification (fixing a specific algebra A and computing the first-order condition directly), noted as future work.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H3-FC005-CORRECTION-TEST</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>Additional diagnostic evidence extending (not overwriting) the frozen FC005_CHECKPOINT.md state. Tested against real DESI DR1 LRG SGC data at N=4000-&gt;8000, a smaller N pair than the frozen checkpoint's own best-case N=32000-&gt;64000 result, so this is not a direct re-run of the checkpoint's own claim, but an independent test of correction hypotheses.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>H4-DIRECT-PRODUCT-CLAIM-UNCONSTRUCTED</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>rank(Aut(octonions) x Spin(8)) = 2+4 = 6, which IS &gt;= rank(SM) = 4. The rank obstruction that rules out the counterfactual manuscript's 'intersection' claim does NOT rule out this different, direct-product formulation -- SU(3) fits inside the G2 factor (a real, standard, correct maximal-subgroup fact) and SU(2)xU(1) has enough rank to potentially fit inside the Spin(8) factor. This means the repository's ORIGINAL claim remains merely UNCONSTRUCTED (no actual embedding, decomposition, or uniqueness argument is given anywhere in the repository), not proven impossible -- a materially different, more honest status than the counterfactual manuscript's claim, which this analysis shows is actually impossible as stated.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -13660,7 +13800,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -13672,7 +13812,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -13684,7 +13824,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13696,7 +13836,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -13708,7 +13848,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -13720,7 +13860,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13732,139 +13872,139 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -13876,19 +14016,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -13900,19 +14040,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -13924,58 +14064,82 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>The counterfactual manuscript's specific restatement of the gauge-closure claim (COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8).</t>
         </is>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1141,6 +1141,57 @@
       <c r="C36" t="inlineStr">
         <is>
           <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CALC-LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>{'residual_is_zero': True}</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CALC-LICHNEROWICZ-GRAVITY-TERM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>{'christoffel_checked': True, 'matches_textbook_quarter': True}</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CALC-SEELEY-DEWITT-A0-A2-A4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>{'all_passed': True}</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1534,12 +1585,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.071000+00:00</t>
+          <t>2026-08-21T03:07:34.036179+00:00</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1612,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.073406+00:00</t>
+          <t>2026-08-21T03:07:34.038560+00:00</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1639,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.075639+00:00</t>
+          <t>2026-08-21T03:07:34.041053+00:00</t>
         </is>
       </c>
     </row>
@@ -1615,12 +1666,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.077821+00:00</t>
+          <t>2026-08-21T03:07:34.043158+00:00</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1693,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.080154+00:00</t>
+          <t>2026-08-21T03:07:34.045256+00:00</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1720,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.082329+00:00</t>
+          <t>2026-08-21T03:07:34.047911+00:00</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1747,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.084454+00:00</t>
+          <t>2026-08-21T03:07:34.050085+00:00</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1774,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.086634+00:00</t>
+          <t>2026-08-21T03:07:34.052132+00:00</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1801,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.088684+00:00</t>
+          <t>2026-08-21T03:07:34.054264+00:00</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1828,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.090953+00:00</t>
+          <t>2026-08-21T03:07:34.056349+00:00</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1855,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.093186+00:00</t>
+          <t>2026-08-21T03:07:34.059017+00:00</t>
         </is>
       </c>
     </row>
@@ -1831,12 +1882,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.095208+00:00</t>
+          <t>2026-08-21T03:07:34.061198+00:00</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1909,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.097454+00:00</t>
+          <t>2026-08-21T03:07:34.063160+00:00</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1936,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.099600+00:00</t>
+          <t>2026-08-21T03:07:34.065376+00:00</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1963,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.101812+00:00</t>
+          <t>2026-08-21T03:07:34.067369+00:00</t>
         </is>
       </c>
     </row>
@@ -1939,12 +1990,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.103914+00:00</t>
+          <t>2026-08-21T03:07:34.069410+00:00</t>
         </is>
       </c>
     </row>
@@ -1966,12 +2017,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.106383+00:00</t>
+          <t>2026-08-21T03:07:34.071409+00:00</t>
         </is>
       </c>
     </row>
@@ -1993,12 +2044,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.108415+00:00</t>
+          <t>2026-08-21T03:07:34.074092+00:00</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2071,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.110386+00:00</t>
+          <t>2026-08-21T03:07:34.076312+00:00</t>
         </is>
       </c>
     </row>
@@ -2047,12 +2098,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.113003+00:00</t>
+          <t>2026-08-21T03:07:34.078372+00:00</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2125,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.115100+00:00</t>
+          <t>2026-08-21T03:07:34.080523+00:00</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2152,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.275949+00:00</t>
+          <t>2026-08-21T03:07:34.203039+00:00</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2179,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.281674+00:00</t>
+          <t>2026-08-21T03:07:34.205955+00:00</t>
         </is>
       </c>
     </row>
@@ -2155,12 +2206,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.283840+00:00</t>
+          <t>2026-08-21T03:07:34.208019+00:00</t>
         </is>
       </c>
     </row>
@@ -2182,12 +2233,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.285944+00:00</t>
+          <t>2026-08-21T03:07:34.210039+00:00</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2260,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.518379+00:00</t>
+          <t>2026-08-21T03:07:34.336218+00:00</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2287,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.521087+00:00</t>
+          <t>2026-08-21T03:07:34.339132+00:00</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2314,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.923725+00:00</t>
+          <t>2026-08-21T03:07:34.742007+00:00</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2341,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.321659+00:00</t>
+          <t>2026-08-21T03:07:35.163316+00:00</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2368,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.324533+00:00</t>
+          <t>2026-08-21T03:07:35.166299+00:00</t>
         </is>
       </c>
     </row>
@@ -2344,12 +2395,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.326854+00:00</t>
+          <t>2026-08-21T03:07:35.168737+00:00</t>
         </is>
       </c>
     </row>
@@ -2371,12 +2422,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.329194+00:00</t>
+          <t>2026-08-21T03:07:35.170901+00:00</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2449,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.331184+00:00</t>
+          <t>2026-08-21T03:07:35.173085+00:00</t>
         </is>
       </c>
     </row>
@@ -2425,12 +2476,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.333481+00:00</t>
+          <t>2026-08-21T03:07:35.175157+00:00</t>
         </is>
       </c>
     </row>
@@ -2452,12 +2503,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.336215+00:00</t>
+          <t>2026-08-21T03:07:35.177158+00:00</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2530,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.338253+00:00</t>
+          <t>2026-08-21T03:07:35.179345+00:00</t>
         </is>
       </c>
     </row>
@@ -2506,12 +2557,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.340560+00:00</t>
+          <t>2026-08-21T03:07:35.181356+00:00</t>
         </is>
       </c>
     </row>
@@ -2533,12 +2584,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.347636+00:00</t>
+          <t>2026-08-21T03:07:35.183304+00:00</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2611,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.487124+00:00</t>
+          <t>2026-08-21T03:07:35.322311+00:00</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2638,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.489355+00:00</t>
+          <t>2026-08-21T03:07:35.324531+00:00</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2665,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.491540+00:00</t>
+          <t>2026-08-21T03:07:35.326608+00:00</t>
         </is>
       </c>
     </row>
@@ -2641,12 +2692,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.493584+00:00</t>
+          <t>2026-08-21T03:07:35.328643+00:00</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2719,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.495774+00:00</t>
+          <t>2026-08-21T03:07:35.330881+00:00</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2746,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.688616+00:00</t>
+          <t>2026-08-21T03:07:37.498546+00:00</t>
         </is>
       </c>
     </row>
@@ -2722,12 +2773,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.692030+00:00</t>
+          <t>2026-08-21T03:07:37.501293+00:00</t>
         </is>
       </c>
     </row>
@@ -2749,12 +2800,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.694873+00:00</t>
+          <t>2026-08-21T03:07:37.503580+00:00</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2827,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.697454+00:00</t>
+          <t>2026-08-21T03:07:37.505712+00:00</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2854,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.700093+00:00</t>
+          <t>2026-08-21T03:07:37.507714+00:00</t>
         </is>
       </c>
     </row>
@@ -2830,12 +2881,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.702589+00:00</t>
+          <t>2026-08-21T03:07:37.509643+00:00</t>
         </is>
       </c>
     </row>
@@ -2857,12 +2908,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.705122+00:00</t>
+          <t>2026-08-21T03:07:37.511554+00:00</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2935,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.707738+00:00</t>
+          <t>2026-08-21T03:07:37.513743+00:00</t>
         </is>
       </c>
     </row>
@@ -2911,12 +2962,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.710126+00:00</t>
+          <t>2026-08-21T03:07:37.515710+00:00</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2989,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.712691+00:00</t>
+          <t>2026-08-21T03:07:37.517681+00:00</t>
         </is>
       </c>
     </row>
@@ -2965,12 +3016,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.717832+00:00</t>
+          <t>2026-08-21T03:07:37.519592+00:00</t>
         </is>
       </c>
     </row>
@@ -2992,12 +3043,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.720505+00:00</t>
+          <t>2026-08-21T03:07:37.521570+00:00</t>
         </is>
       </c>
     </row>
@@ -3019,12 +3070,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.725305+00:00</t>
+          <t>2026-08-21T03:07:37.523539+00:00</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3097,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.727454+00:00</t>
+          <t>2026-08-21T03:07:37.525579+00:00</t>
         </is>
       </c>
     </row>
@@ -3073,12 +3124,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:34.729407+00:00</t>
+          <t>2026-08-21T03:07:37.527517+00:00</t>
         </is>
       </c>
     </row>
@@ -3100,12 +3151,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:35.132699+00:00</t>
+          <t>2026-08-21T03:07:37.934783+00:00</t>
         </is>
       </c>
     </row>
@@ -3127,12 +3178,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:35.144545+00:00</t>
+          <t>2026-08-21T03:07:37.946252+00:00</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3205,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:35.148361+00:00</t>
+          <t>2026-08-21T03:07:37.950164+00:00</t>
         </is>
       </c>
     </row>
@@ -3181,12 +3232,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:35.156576+00:00</t>
+          <t>2026-08-21T03:07:37.958284+00:00</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3259,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:35.161749+00:00</t>
+          <t>2026-08-21T03:07:37.960869+00:00</t>
         </is>
       </c>
     </row>
@@ -3235,78 +3286,78 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:35.166091+00:00</t>
+          <t>2026-08-21T03:07:37.965088+00:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>CONTROL-MANIFOLD-S2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.068200+00:00</t>
+          <t>2026-08-21T03:07:37.967031+00:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>CONTROL-FLAT-2D</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.289222+00:00</t>
+          <t>2026-08-21T03:07:37.969036+00:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py::verify_lichnerowicz_gauge_term</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3316,24 +3367,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.293163+00:00</t>
+          <t>2026-08-21T03:07:38.225169+00:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>LICHNEROWICZ-GRAVITY-TERM-S2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py::verify_lichnerowicz_gravity_term</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3343,24 +3394,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.295096+00:00</t>
+          <t>2026-08-21T03:07:44.096378+00:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>DIRAC-SQUARED-LICHNEROWICZ-GENERAL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3370,159 +3421,159 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.297108+00:00</t>
+          <t>2026-08-21T03:07:44.101257+00:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>SEELEY-DEWITT-A0-A2-A4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py::verify_seeley_dewitt_E_dependence</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.525391+00:00</t>
+          <t>2026-08-21T03:07:44.110287+00:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>SEELEY-DEWITT-A6-GENERAL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.527630+00:00</t>
+          <t>2026-08-21T03:07:44.115067+00:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>SPECTRAL-ACTION-TR-F-CERTIFICATION</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>compiler/backends/ollivier_ricci.py</t>
+          <t>compiler/ir/seeley_dewitt_verification.py</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.926421+00:00</t>
+          <t>2026-08-21T03:07:44.117378+00:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>spec section 10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.500512+00:00</t>
+          <t>2026-08-21T03:07:34.033219+00:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.537160+00:00</t>
+          <t>2026-08-21T03:07:34.212123+00:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_flow.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3532,321 +3583,321 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:31.543522+00:00</t>
+          <t>2026-08-21T03:07:34.214184+00:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.420101+00:00</t>
+          <t>2026-08-21T03:07:34.216137+00:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.422836+00:00</t>
+          <t>2026-08-21T03:07:34.218136+00:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.425190+00:00</t>
+          <t>2026-08-21T03:07:34.341662+00:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.427294+00:00</t>
+          <t>2026-08-21T03:07:34.343800+00:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+          <t>compiler/backends/ollivier_ricci.py</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.429357+00:00</t>
+          <t>2026-08-21T03:07:34.744991+00:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.431411+00:00</t>
+          <t>2026-08-21T03:07:35.334924+00:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.433346+00:00</t>
+          <t>2026-08-21T03:07:38.228073+00:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.435453+00:00</t>
+          <t>2026-08-21T03:07:44.099030+00:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.437483+00:00</t>
+          <t>2026-08-21T03:07:44.112634+00:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.439414+00:00</t>
+          <t>2026-08-21T03:07:34.349910+00:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+          <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.441348+00:00</t>
+          <t>2026-08-21T03:07:34.352533+00:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3856,24 +3907,24 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.443309+00:00</t>
+          <t>2026-08-21T03:07:35.251150+00:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3883,24 +3934,24 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.445303+00:00</t>
+          <t>2026-08-21T03:07:35.253787+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3910,24 +3961,24 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.447280+00:00</t>
+          <t>2026-08-21T03:07:35.255946+00:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3937,24 +3988,24 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.449230+00:00</t>
+          <t>2026-08-21T03:07:35.258028+00:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3964,24 +4015,24 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.451243+00:00</t>
+          <t>2026-08-21T03:07:35.260277+00:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3991,24 +4042,24 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.453198+00:00</t>
+          <t>2026-08-21T03:07:35.262506+00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4018,24 +4069,24 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.455193+00:00</t>
+          <t>2026-08-21T03:07:35.264631+00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4045,24 +4096,24 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.457095+00:00</t>
+          <t>2026-08-21T03:07:35.266687+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -4072,24 +4123,24 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.458977+00:00</t>
+          <t>2026-08-21T03:07:35.268712+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4099,24 +4150,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.461002+00:00</t>
+          <t>2026-08-21T03:07:35.270820+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4126,24 +4177,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.462898+00:00</t>
+          <t>2026-08-21T03:07:35.273017+00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4153,24 +4204,24 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.464813+00:00</t>
+          <t>2026-08-21T03:07:35.274979+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4180,24 +4231,24 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.466773+00:00</t>
+          <t>2026-08-21T03:07:35.277075+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4207,24 +4258,24 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.468714+00:00</t>
+          <t>2026-08-21T03:07:35.279317+00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4234,24 +4285,24 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.470623+00:00</t>
+          <t>2026-08-21T03:07:35.281391+00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4261,24 +4312,24 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.472518+00:00</t>
+          <t>2026-08-21T03:07:35.283667+00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4288,24 +4339,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.474472+00:00</t>
+          <t>2026-08-21T03:07:35.285707+00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4315,120 +4366,417 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.476598+00:00</t>
+          <t>2026-08-21T03:07:35.287725+00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:32.498359+00:00</t>
+          <t>2026-08-21T03:07:35.289898+00:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:35.136063+00:00</t>
+          <t>2026-08-21T03:07:35.292113+00:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>311c588921d0</t>
+          <t>31522dbee6f0</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-08-21T02:28:35.138513+00:00</t>
+          <t>2026-08-21T03:07:35.294641+00:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>EQ-022</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:35.296652+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:35.298679+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:35.300769+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:35.302804+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:35.304951+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:35.307066+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:35.309118+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:35.311121+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:35.333005+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:37.937509+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:37.939900+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>311c588921d0</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>2026-08-21T02:28:35.163953+00:00</t>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>31522dbee6f0</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:07:37.962992+00:00</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5643,15 +5991,49 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>SEELEY-DEWITT-A6-GENERAL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>General Gilkey a6 heat-kernel coefficient (position-dependent E(x), nonabelian gauge curvature Omega_{mu nu}, Delta E, dozen-plus pure-curvature invariants).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SPECTRAL-ACTION-TR-F-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Whether Tr f(D_A/Lambda) can be certified as a physically meaningful spectral action. OPEN for two independent reasons, both required: (1) a6 is not yet resolved (see SEELEY-DEWITT-A6-GENERAL); (2) even once the GENERAL formula chain is complete, this verifies control-manifold mathematics only -- it</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>SELECTION-SIGMA</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Transformation</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Sigma : M -&gt; {0,1}</t>
         </is>
@@ -5668,7 +6050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7110,17 +7492,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>CONTROL-MANIFOLD-S2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -7132,34 +7514,34 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>CONTROL-FLAT-2D</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7169,19 +7551,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['CONTROL-FLAT-2D']</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>LICHNEROWICZ-GRAVITY-TERM-S2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -7191,19 +7573,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['CONTROL-MANIFOLD-S2']</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>DIRAC-SQUARED-LICHNEROWICZ-GENERAL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7213,80 +7595,80 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['LICHNEROWICZ-GAUGE-TERM', 'LICHNEROWICZ-GRAVITY-TERM-S2']</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>SEELEY-DEWITT-A0-A2-A4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['DIRAC-SQUARED-LICHNEROWICZ-GENERAL', 'S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>SEELEY-DEWITT-A6-GENERAL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>['SEELEY-DEWITT-A0-A2-A4']</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>SPECTRAL-ACTION-TR-F-CERTIFICATION</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['SEELEY-DEWITT-A6-GENERAL']</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7296,46 +7678,46 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['GRAPH-G-SEED']</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -7345,212 +7727,212 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['DIFFUSION-DISTANCE']</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CONTROL-FLAT-2D']</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CONTROL-MANIFOLD-S2']</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7560,19 +7942,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7582,19 +7964,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7616,7 +7998,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7638,7 +8020,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7660,7 +8042,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7682,7 +8064,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7704,7 +8086,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7726,7 +8108,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7748,7 +8130,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7770,7 +8152,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7792,7 +8174,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7814,7 +8196,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7836,7 +8218,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7858,7 +8240,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7880,7 +8262,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7902,7 +8284,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7924,7 +8306,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7946,7 +8328,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7968,7 +8350,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7990,7 +8372,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8000,19 +8382,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>['S3-CURVATURE-CLOSURE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8022,19 +8404,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8044,32 +8426,274 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>EQ-022</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>['S3-CURVATURE-CLOSURE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -8570,7 +9194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8978,6 +9602,64 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>an executed test of one of the four primary load-bearing hypotheses (H1-H4) required to decounterfactualize the COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING manuscript</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>control_manifold</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>a standard, independently-known-analytic manifold used as a verification control (same status as S3-MANIFOLD), never a claim about this project's own constructions</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>lichnerowicz_term</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>one piece (gauge or gravity) of the general D_A^2=-(nabla^2+E) identity, verified on a control manifold</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>seeley_dewitt_coefficient</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>a general Gilkey heat-kernel coefficient (a0, a2, a4, or a6), verified or left OPEN on a control manifold</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>mathematical_object</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>spectral_action_certification</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>whether Tr f(D_A/Lambda) can be certified for physical use; OPEN until every Seeley-DeWitt coefficient it depends on is resolved</t>
         </is>
       </c>
     </row>
@@ -8992,7 +9674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10757,6 +11439,222 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CONTROL-MANIFOLD-S2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>control_manifold</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CONTROL-FLAT-2D</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>control_manifold</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>lichnerowicz_term</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>['CONTROL-FLAT-2D']</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>LICHNEROWICZ-GRAVITY-TERM-S2</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>lichnerowicz_term</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>['CONTROL-MANIFOLD-S2']</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DIRAC-SQUARED-LICHNEROWICZ-GENERAL</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>lichnerowicz_term</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>['LICHNEROWICZ-GAUGE-TERM', 'LICHNEROWICZ-GRAVITY-TERM-S2']</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEELEY-DEWITT-A0-A2-A4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>seeley_dewitt_coefficient</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>['DIRAC-SQUARED-LICHNEROWICZ-GENERAL', 'S3-MANIFOLD']</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEELEY-DEWITT-A6-GENERAL</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>seeley_dewitt_coefficient</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>['SEELEY-DEWITT-A0-A2-A4']</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SPECTRAL-ACTION-TR-F-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>spectral_action_certification</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>['SEELEY-DEWITT-A6-GENERAL']</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10768,7 +11666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11094,6 +11992,102 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>['S3-MANIFOLD']</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CONTROL-FLAT-2D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>D_A = i*gamma^a(d_a+iA_a), squared by direct symbolic operator composition</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>['CONTROL-FLAT-2D']</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CONTROL-MANIFOLD-S2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LICHNEROWICZ-GRAVITY-TERM-S2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>D^2 on round S^2 via Cartan spin connection + Levi-Civita Christoffel symbols, coefficient of E=c*R solved by direct symbolic composition</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>['CONTROL-MANIFOLD-S2']</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SEELEY-DEWITT-A0-A2-A4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>shifted operator L=-Delta-E on S^3, exact spectrum, degree-4 heat-trace polynomial fit vs Gilkey-predicted closed forms, 4 distinct E values</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>['S3-MANIFOLD']</t>
         </is>
@@ -12284,7 +13278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12930,154 +13924,286 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GRAPH-G-SEED</t>
+          <t>CONTROL-FLAT-2D</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>LICHNEROWICZ-GRAVITY-TERM-S2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>CONTROL-MANIFOLD-S2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>DIRAC-SQUARED-LICHNEROWICZ-GENERAL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>DIRAC-SQUARED-LICHNEROWICZ-GENERAL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>LICHNEROWICZ-GRAVITY-TERM-S2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>SEELEY-DEWITT-A0-A2-A4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>DIRAC-SQUARED-LICHNEROWICZ-GENERAL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>SEELEY-DEWITT-A0-A2-A4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DIFFUSION-DISTANCE</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>SEELEY-DEWITT-A6-GENERAL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>SEELEY-DEWITT-A0-A2-A4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>SPECTRAL-ACTION-TR-F-CERTIFICATION</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>SEELEY-DEWITT-A6-GENERAL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>GRAPH-G-SEED</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>HEAT-FLOW-R</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SPECTRUM-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T-DIFFUSION-TO-METRIC</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DIFFUSION-DISTANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T-OPERATOR-TO-CURVATURE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CONTROL-FLAT-2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CONTROL-MANIFOLD-S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
@@ -13094,7 +14220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13776,91 +14902,91 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>Overall i factor required in D_A for self-adjointness (D_A^2&gt;=0); first attempt without it gave a residual exactly 2x the nabla^2 term, diagnosed and fixed -- see compiler/historical/seeley_dewitt_verification.py.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>LICHNEROWICZ-GRAVITY-TERM-S2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Spin connection derived from the Cartan structure equation, not quoted.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>LICHNEROWICZ-GRAVITY-TERM-S2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Riemann tensor sign convention reused verbatim from the earlier FRW/Bianchi-identity verification pass (an independent from-scratch attempt here first gave R=-2, traced to an index-order inconsistency, discarded in favor of the already-validated convention) -- see compiler/historical/seeley_dewitt_verification.py.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>SEELEY-DEWITT-A0-A2-A4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Degree-3 polynomial fit (existing S3 control default) showed a real, diagnosed fit-window bias at large E (2.52e-4 at E=2.5, above tolerance); degree=4 used instead, confirmed by degree-sweep convergence (2.52e-4-&gt;1.79e-6-&gt;1.24e-8 at degrees 3,4,5) to be bias, not a formula error.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>SEELEY-DEWITT-A6-GENERAL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>The general Gilkey a6 formula (position-dependent E(x), nonabelian gauge curvature Omega_{mu nu}, Delta E, and a dozen-plus pure-curvature invariants) was NOT independently rederived here: reproducing a formula that long from memory, with no primary source available in this session to cross-check it against, would itself be exactly the kind of unverified claim this project's own discipline forbids. A narrow, elementary, non-Gilkey-formula-dependent consistency check was run instead -- for CONSTANT E, Y_E(t)=exp(t*E)*Y_0(t) is a trivial algebraic identity requiring no heat-kernel theory at all -- and confirmed the fit machinery is self-consistent through O(t^3) (residuals ~1e-4 to 1e-6 at 3 nonzero E values). This does NOT verify the general a6 formula for non-constant E(x) or nonzero gauge curvature. External reference only, PROPOSED/comparison status: Gilkey, P.B. (1975), 'The spectral geometry of the second order elliptic differential operator'; Vassilevich, D.V. (2003), 'Heat kernel expansion: user's manual', Phys. Rept. 388.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>SPECTRAL-ACTION-TR-F-CERTIFICATION</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>seit_lang/spectral_action.py already refuses to call its own Tr(D^k) a Seeley-DeWitt coefficient for exactly this reason; this record does not relax that refusal.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13872,7 +14998,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -13884,7 +15010,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13896,187 +15022,187 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -14088,58 +15214,130 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>The counterfactual manuscript's specific restatement of the gauge-closure claim (COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8).</t>
         </is>
@@ -14156,7 +15354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14382,6 +15580,87 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PROOF-T-LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>D_A = i*gamma^a(d_a+iA_a), squared by direct symbolic operator composition</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sympy symbolic Matrix differential-operator composition, exact (not numeric) zero residual</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PROOF-T-LICHNEROWICZ-GRAVITY-TERM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>D^2 on round S^2 via Cartan spin connection + Levi-Civita Christoffel symbols, coefficient of E=c*R solved by direct symbolic composition</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>sympy: Cartan structure equation for omega^{12}, Christoffel symbols from the metric (cross-checked vs closed form), Riemann tensor (validated convention reused), sp.solve for c -- not asserted</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PROOF-T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>shifted operator L=-Delta-E on S^3, exact spectrum, degree-4 heat-trace polynomial fit vs Gilkey-predicted closed forms, 4 distinct E values</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>reuses this project's own already-verified S3 heat-trace-fit machinery (compiler/backends/heat_kernel_sphere.py, compiler/verification/heat_kernel_fit.py), extended to nonzero constant E</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14393,7 +15672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15194,6 +16473,72 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CALC-LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>symbolic_operator_composition_flat_2d</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>{'gauge_field': 'abstract abelian A_mu(x,y), arbitrary symbolic functions', 'curvature': 'R=0 (flat)'}</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CALC-LICHNEROWICZ-GRAVITY-TERM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>symbolic_operator_composition_round_s2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>{'manifold': 'round unit S^2', 'gauge_field': 'none (R contribution isolated)'}</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CALC-SEELEY-DEWITT-A0-A2-A4</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>numeric_heat_trace_fit_E_dependence_s3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>{'E_values': [0.0, 0.7, -0.3, 2.5], 'fit_degree': 4, 'tolerance': 0.0001}</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1192,6 +1192,40 @@
       <c r="C39" t="inlineStr">
         <is>
           <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CALC-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>{'findings': [{'check': 'self-adjointness of D_F', 'result': 'HOLDS', 'note': "Exact block-antisymmetric-transpose structure by construction; confirms dirac_candidates.py's own D_self_adjoint=True finding."}, {'check': 'grading axioms (gamma_F^2=I, {D_F,gamma_F}=0, [pi(f),gamma_F]=0)', 'result': 'ALL HOLD', 'note': 'Mechanical consequence of the block structure (gamma_F block-diagonal, D_F block-off-diagonal, pi(f) block-diagonal) -- checked directly, not assumed.'}, {'check': "real-structure si</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CALC-DIRAC-SQUARED-FINITE-D_B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>{'E_B_bare_is_zero': True}</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1585,12 +1619,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.036179+00:00</t>
+          <t>2026-08-21T03:40:26.966937+00:00</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1646,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.038560+00:00</t>
+          <t>2026-08-21T03:40:26.969504+00:00</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1673,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.041053+00:00</t>
+          <t>2026-08-21T03:40:26.971706+00:00</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1700,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.043158+00:00</t>
+          <t>2026-08-21T03:40:26.974228+00:00</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1727,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.045256+00:00</t>
+          <t>2026-08-21T03:40:26.976223+00:00</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1754,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.047911+00:00</t>
+          <t>2026-08-21T03:40:26.978944+00:00</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1781,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.050085+00:00</t>
+          <t>2026-08-21T03:40:26.981104+00:00</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1808,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.052132+00:00</t>
+          <t>2026-08-21T03:40:26.983486+00:00</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1835,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.054264+00:00</t>
+          <t>2026-08-21T03:40:26.985840+00:00</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1862,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.056349+00:00</t>
+          <t>2026-08-21T03:40:26.988032+00:00</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1889,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.059017+00:00</t>
+          <t>2026-08-21T03:40:26.990352+00:00</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1916,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.061198+00:00</t>
+          <t>2026-08-21T03:40:26.992528+00:00</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1943,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.063160+00:00</t>
+          <t>2026-08-21T03:40:26.994634+00:00</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1970,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.065376+00:00</t>
+          <t>2026-08-21T03:40:26.996674+00:00</t>
         </is>
       </c>
     </row>
@@ -1963,12 +1997,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.067369+00:00</t>
+          <t>2026-08-21T03:40:26.998706+00:00</t>
         </is>
       </c>
     </row>
@@ -1990,12 +2024,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.069410+00:00</t>
+          <t>2026-08-21T03:40:27.001028+00:00</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2051,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.071409+00:00</t>
+          <t>2026-08-21T03:40:27.003008+00:00</t>
         </is>
       </c>
     </row>
@@ -2044,12 +2078,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.074092+00:00</t>
+          <t>2026-08-21T03:40:27.005269+00:00</t>
         </is>
       </c>
     </row>
@@ -2071,12 +2105,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.076312+00:00</t>
+          <t>2026-08-21T03:40:27.007392+00:00</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2132,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.078372+00:00</t>
+          <t>2026-08-21T03:40:27.009941+00:00</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2159,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.080523+00:00</t>
+          <t>2026-08-21T03:40:27.012130+00:00</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2186,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.203039+00:00</t>
+          <t>2026-08-21T03:40:27.198492+00:00</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2213,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.205955+00:00</t>
+          <t>2026-08-21T03:40:27.201686+00:00</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2240,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.208019+00:00</t>
+          <t>2026-08-21T03:40:27.204119+00:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2267,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.210039+00:00</t>
+          <t>2026-08-21T03:40:27.206384+00:00</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2294,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.336218+00:00</t>
+          <t>2026-08-21T03:40:27.401792+00:00</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2321,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.339132+00:00</t>
+          <t>2026-08-21T03:40:27.404607+00:00</t>
         </is>
       </c>
     </row>
@@ -2314,12 +2348,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.742007+00:00</t>
+          <t>2026-08-21T03:40:27.821166+00:00</t>
         </is>
       </c>
     </row>
@@ -2341,12 +2375,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.163316+00:00</t>
+          <t>2026-08-21T03:40:28.262410+00:00</t>
         </is>
       </c>
     </row>
@@ -2368,12 +2402,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.166299+00:00</t>
+          <t>2026-08-21T03:40:28.265400+00:00</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2429,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.168737+00:00</t>
+          <t>2026-08-21T03:40:28.267993+00:00</t>
         </is>
       </c>
     </row>
@@ -2422,12 +2456,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.170901+00:00</t>
+          <t>2026-08-21T03:40:28.270356+00:00</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2483,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.173085+00:00</t>
+          <t>2026-08-21T03:40:28.272732+00:00</t>
         </is>
       </c>
     </row>
@@ -2476,12 +2510,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.175157+00:00</t>
+          <t>2026-08-21T03:40:28.275002+00:00</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2537,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.177158+00:00</t>
+          <t>2026-08-21T03:40:28.277300+00:00</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2564,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.179345+00:00</t>
+          <t>2026-08-21T03:40:28.279486+00:00</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2591,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.181356+00:00</t>
+          <t>2026-08-21T03:40:28.281632+00:00</t>
         </is>
       </c>
     </row>
@@ -2584,12 +2618,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.183304+00:00</t>
+          <t>2026-08-21T03:40:28.283871+00:00</t>
         </is>
       </c>
     </row>
@@ -2611,12 +2645,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.322311+00:00</t>
+          <t>2026-08-21T03:40:28.435630+00:00</t>
         </is>
       </c>
     </row>
@@ -2638,12 +2672,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.324531+00:00</t>
+          <t>2026-08-21T03:40:28.438284+00:00</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2699,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.326608+00:00</t>
+          <t>2026-08-21T03:40:28.440795+00:00</t>
         </is>
       </c>
     </row>
@@ -2692,12 +2726,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.328643+00:00</t>
+          <t>2026-08-21T03:40:28.443091+00:00</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2753,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.330881+00:00</t>
+          <t>2026-08-21T03:40:28.445327+00:00</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2780,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.498546+00:00</t>
+          <t>2026-08-21T03:40:31.085578+00:00</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2807,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.501293+00:00</t>
+          <t>2026-08-21T03:40:31.090943+00:00</t>
         </is>
       </c>
     </row>
@@ -2800,12 +2834,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.503580+00:00</t>
+          <t>2026-08-21T03:40:31.093424+00:00</t>
         </is>
       </c>
     </row>
@@ -2827,12 +2861,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.505712+00:00</t>
+          <t>2026-08-21T03:40:31.098455+00:00</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2888,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.507714+00:00</t>
+          <t>2026-08-21T03:40:31.100670+00:00</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2915,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.509643+00:00</t>
+          <t>2026-08-21T03:40:31.102945+00:00</t>
         </is>
       </c>
     </row>
@@ -2908,12 +2942,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.511554+00:00</t>
+          <t>2026-08-21T03:40:31.105142+00:00</t>
         </is>
       </c>
     </row>
@@ -2935,12 +2969,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.513743+00:00</t>
+          <t>2026-08-21T03:40:31.107206+00:00</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2996,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.515710+00:00</t>
+          <t>2026-08-21T03:40:31.109398+00:00</t>
         </is>
       </c>
     </row>
@@ -2989,12 +3023,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.517681+00:00</t>
+          <t>2026-08-21T03:40:31.114398+00:00</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3050,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.519592+00:00</t>
+          <t>2026-08-21T03:40:31.116569+00:00</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3077,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.521570+00:00</t>
+          <t>2026-08-21T03:40:31.118656+00:00</t>
         </is>
       </c>
     </row>
@@ -3070,12 +3104,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.523539+00:00</t>
+          <t>2026-08-21T03:40:31.120826+00:00</t>
         </is>
       </c>
     </row>
@@ -3097,12 +3131,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.525579+00:00</t>
+          <t>2026-08-21T03:40:31.126480+00:00</t>
         </is>
       </c>
     </row>
@@ -3124,12 +3158,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.527517+00:00</t>
+          <t>2026-08-21T03:40:31.128561+00:00</t>
         </is>
       </c>
     </row>
@@ -3151,12 +3185,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.934783+00:00</t>
+          <t>2026-08-21T03:40:31.562029+00:00</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3212,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.946252+00:00</t>
+          <t>2026-08-21T03:40:31.578451+00:00</t>
         </is>
       </c>
     </row>
@@ -3205,12 +3239,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.950164+00:00</t>
+          <t>2026-08-21T03:40:31.583334+00:00</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3266,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.958284+00:00</t>
+          <t>2026-08-21T03:40:31.593598+00:00</t>
         </is>
       </c>
     </row>
@@ -3259,12 +3293,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.960869+00:00</t>
+          <t>2026-08-21T03:40:31.597701+00:00</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3320,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.965088+00:00</t>
+          <t>2026-08-21T03:40:31.606790+00:00</t>
         </is>
       </c>
     </row>
@@ -3313,12 +3347,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.967031+00:00</t>
+          <t>2026-08-21T03:40:31.610044+00:00</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3374,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.969036+00:00</t>
+          <t>2026-08-21T03:40:31.613218+00:00</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3401,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:38.225169+00:00</t>
+          <t>2026-08-21T03:40:31.903546+00:00</t>
         </is>
       </c>
     </row>
@@ -3394,12 +3428,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:44.096378+00:00</t>
+          <t>2026-08-21T03:40:37.896272+00:00</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3455,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:44.101257+00:00</t>
+          <t>2026-08-21T03:40:37.901404+00:00</t>
         </is>
       </c>
     </row>
@@ -3448,12 +3482,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:44.110287+00:00</t>
+          <t>2026-08-21T03:40:37.910862+00:00</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3509,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:44.115067+00:00</t>
+          <t>2026-08-21T03:40:37.915275+00:00</t>
         </is>
       </c>
     </row>
@@ -3502,51 +3536,51 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:44.117378+00:00</t>
+          <t>2026-08-21T03:40:37.917644+00:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H2-GRAPH-CONTROL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.033219+00:00</t>
+          <t>2026-08-21T03:40:37.920032+00:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py::build_h2b_operator</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3556,780 +3590,780 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.212123+00:00</t>
+          <t>2026-08-21T03:40:37.922235+00:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>FINITE-ALGEBRA-A_F</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py::pi_representation</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.214184+00:00</t>
+          <t>2026-08-21T03:40:37.924341+00:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>FINITE-GRADING-GAMMA_F</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py::build_h2b_operator</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.216137+00:00</t>
+          <t>2026-08-21T03:40:37.926354+00:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.218136+00:00</t>
+          <t>2026-08-21T03:40:37.928295+00:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>AXIOM-CHECK-SELF-ADJOINT-D_B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py::run_spectral_triple_certification</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.341662+00:00</t>
+          <t>2026-08-21T03:40:38.057098+00:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>AXIOM-CHECK-GRADING-D_B</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py::run_spectral_triple_certification</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.343800+00:00</t>
+          <t>2026-08-21T03:40:38.063339+00:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>AXIOM-CHECK-REAL-STRUCTURE-SIGNS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>compiler/backends/ollivier_ricci.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py::run_spectral_triple_certification</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.744991+00:00</t>
+          <t>2026-08-21T03:40:38.066040+00:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py::run_spectral_triple_certification</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.334924+00:00</t>
+          <t>2026-08-21T03:40:38.068130+00:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/ir/finite_spectral_triple_certification.py</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:38.228073+00:00</t>
+          <t>2026-08-21T03:40:38.074433+00:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>DIRAC-SQUARED-FINITE-D_B</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py::compute_dirac_squared_decomposition</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:44.099030+00:00</t>
+          <t>2026-08-21T03:40:38.112321+00:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>E_B-BARE-FINITE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:44.112634+00:00</t>
+          <t>2026-08-21T03:40:38.120872+00:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>OMEGA_B-FINITE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/ir/finite_spectral_triple_certification.py</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.349910+00:00</t>
+          <t>2026-08-21T03:40:38.123339+00:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>SPECTRAL-ACTION-A0-A6-FINITE-B</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_flow.py</t>
+          <t>compiler/ir/finite_spectral_triple_certification.py</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:34.352533+00:00</t>
+          <t>2026-08-21T03:40:38.125650+00:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+          <t>spec section 10</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.251150+00:00</t>
+          <t>2026-08-21T03:40:26.964337+00:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.253787+00:00</t>
+          <t>2026-08-21T03:40:27.210381+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.255946+00:00</t>
+          <t>2026-08-21T03:40:27.216658+00:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.258028+00:00</t>
+          <t>2026-08-21T03:40:27.218935+00:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.260277+00:00</t>
+          <t>2026-08-21T03:40:27.222111+00:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.262506+00:00</t>
+          <t>2026-08-21T03:40:27.406869+00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.264631+00:00</t>
+          <t>2026-08-21T03:40:27.408959+00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+          <t>compiler/backends/ollivier_ricci.py</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.266687+00:00</t>
+          <t>2026-08-21T03:40:27.823902+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.268712+00:00</t>
+          <t>2026-08-21T03:40:28.449963+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.270820+00:00</t>
+          <t>2026-08-21T03:40:31.906359+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.273017+00:00</t>
+          <t>2026-08-21T03:40:37.899043+00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.274979+00:00</t>
+          <t>2026-08-21T03:40:37.913138+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.277075+00:00</t>
+          <t>2026-08-21T03:40:38.070253+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.279317+00:00</t>
+          <t>2026-08-21T03:40:38.127786+00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.281391+00:00</t>
+          <t>2026-08-21T03:40:27.415211+00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+          <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.283667+00:00</t>
+          <t>2026-08-21T03:40:27.417232+00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4339,24 +4373,24 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.285707+00:00</t>
+          <t>2026-08-21T03:40:28.359965+00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4366,24 +4400,24 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.287725+00:00</t>
+          <t>2026-08-21T03:40:28.363148+00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4393,24 +4427,24 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.289898+00:00</t>
+          <t>2026-08-21T03:40:28.365701+00:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4420,24 +4454,24 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.292113+00:00</t>
+          <t>2026-08-21T03:40:28.368426+00:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4447,24 +4481,24 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.294641+00:00</t>
+          <t>2026-08-21T03:40:28.370793+00:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4474,24 +4508,24 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.296652+00:00</t>
+          <t>2026-08-21T03:40:28.373211+00:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4501,24 +4535,24 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.298679+00:00</t>
+          <t>2026-08-21T03:40:28.375485+00:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -4528,24 +4562,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.300769+00:00</t>
+          <t>2026-08-21T03:40:28.377588+00:00</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4555,24 +4589,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.302804+00:00</t>
+          <t>2026-08-21T03:40:28.379704+00:00</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4582,24 +4616,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.304951+00:00</t>
+          <t>2026-08-21T03:40:28.381948+00:00</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4609,24 +4643,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.307066+00:00</t>
+          <t>2026-08-21T03:40:28.384046+00:00</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4636,24 +4670,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.309118+00:00</t>
+          <t>2026-08-21T03:40:28.386223+00:00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4663,120 +4697,552 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.311121+00:00</t>
+          <t>2026-08-21T03:40:28.388218+00:00</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:35.333005+00:00</t>
+          <t>2026-08-21T03:40:28.390497+00:00</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.937509+00:00</t>
+          <t>2026-08-21T03:40:28.392844+00:00</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>31522dbee6f0</t>
+          <t>5a1fc01640d0</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-08-21T03:07:37.939900+00:00</t>
+          <t>2026-08-21T03:40:28.394909+00:00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>EQ-017</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.397127+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>EQ-018</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.399376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>EQ-019</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.401455+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>EQ-020</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.403523+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>EQ-021</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.405797+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>EQ-022</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.407998+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.410142+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.412793+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.414924+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.417057+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.419202+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.421360+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.423714+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:28.447709+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:31.566693+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:31.571123+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>31522dbee6f0</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>2026-08-21T03:07:37.962992+00:00</t>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>5a1fc01640d0</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:40:31.603439+00:00</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6025,15 +6491,49 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>OMEGA_B-FINITE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Omega_B (gauge curvature of an inner-fluctuated connection): NOT CERTIFIABLE, not merely not-yet-computed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SPECTRAL-ACTION-A0-A6-FINITE-B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>a0^B, a2^B, a4^B, a6^B (finite spectral-action moments for this candidate): NOT CERTIFIED. Requires Omega_B, which is not certifiable for this candidate (first-order condition fails). This is the correct execution boundary: the spectral action is not touched beyond this point for this candidate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>SELECTION-SIGMA</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Transformation</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Sigma : M -&gt; {0,1}</t>
         </is>
@@ -6050,7 +6550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7668,17 +8168,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>H2-GRAPH-CONTROL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7690,12 +8190,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -7705,288 +8205,288 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>['H2-GRAPH-CONTROL']</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>FINITE-ALGEBRA-A_F</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['H2-GRAPH-CONTROL']</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>FINITE-GRADING-GAMMA_F</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>AXIOM-CHECK-SELF-ADJOINT-D_B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>AXIOM-CHECK-GRADING-D_B</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>['FINITE-GRADING-GAMMA_F', 'FINITE-ALGEBRA-A_F']</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>AXIOM-CHECK-REAL-STRUCTURE-SIGNS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['FINITE-REAL-STRUCTURE-J_F', 'FINITE-GRADING-GAMMA_F']</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>['CONTROL-FLAT-2D']</t>
+          <t>['H2-GRAPH-CONTROL', 'AXIOM-CHECK-SELF-ADJOINT-D_B', 'AXIOM-CHECK-GRADING-D_B', 'AXIOM-CHECK-REAL-STRUCTURE-SIGNS', 'AXIOM-CHECK-FIRST-ORDER-CONDITION']</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>DIRAC-SQUARED-FINITE-D_B</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>['CONTROL-MANIFOLD-S2']</t>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>E_B-BARE-FINITE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['DIRAC-SQUARED-FINITE-D_B']</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>OMEGA_B-FINITE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['FINITE-SPECTRAL-TRIPLE-CERTIFICATION', 'DIRAC-SQUARED-FINITE-D_B']</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>SPECTRAL-ACTION-A0-A6-FINITE-B</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['E_B-BARE-FINITE', 'OMEGA_B-FINITE']</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7998,293 +8498,293 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['GRAPH-G-SEED']</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['DIFFUSION-DISTANCE']</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CONTROL-FLAT-2D']</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CONTROL-MANIFOLD-S2']</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-GRADING-GAMMA_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8294,19 +8794,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8316,19 +8816,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8350,7 +8850,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8372,7 +8872,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8394,7 +8894,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8416,7 +8916,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8438,7 +8938,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8460,7 +8960,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8482,7 +8982,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8504,7 +9004,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8526,7 +9026,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8548,7 +9048,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8570,7 +9070,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8592,7 +9092,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8614,7 +9114,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8624,19 +9124,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>['S3-CURVATURE-CLOSURE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8646,19 +9146,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8668,32 +9168,384 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>EQ-017</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>EQ-018</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>EQ-019</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>EQ-020</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>EQ-021</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>EQ-022</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>['S3-CURVATURE-CLOSURE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -9194,7 +10046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9660,6 +10512,54 @@
       <c r="B33" t="inlineStr">
         <is>
           <t>whether Tr f(D_A/Lambda) can be certified for physical use; OPEN until every Seeley-DeWitt coefficient it depends on is resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>control_graph</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>a standard graph construction used as a verification control (same status as other control_manifold objects), never a claim about a physically-selected graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>one component (algebra representation, grading, real structure, or Dirac operator) of a candidate finite spectral triple (A_F,H_F,D_F,J_F,gamma_F)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>spectral_triple_axiom_check</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>a real, executed check of one Connes spectral-triple axiom against a concrete candidate -- status always computed from the actual check, never asserted</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>finite_dirac_squared_decomposition</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D_F^2 for a finite candidate Dirac operator, and whether its E_B/Omega_B decomposition is certifiable</t>
         </is>
       </c>
     </row>
@@ -9674,7 +10574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11655,6 +12555,384 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>H2-GRAPH-CONTROL</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>control_graph</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>FINITE-DIRAC-D_B</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>['H2-GRAPH-CONTROL']</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>FINITE-ALGEBRA-A_F</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>['H2-GRAPH-CONTROL']</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FINITE-GRADING-GAMMA_F</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B']</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B']</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AXIOM-CHECK-SELF-ADJOINT-D_B</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>spectral_triple_axiom_check</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B']</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>AXIOM-CHECK-GRADING-D_B</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>spectral_triple_axiom_check</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>['FINITE-GRADING-GAMMA_F', 'FINITE-ALGEBRA-A_F']</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>AXIOM-CHECK-REAL-STRUCTURE-SIGNS</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>spectral_triple_axiom_check</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>['FINITE-REAL-STRUCTURE-J_F', 'FINITE-GRADING-GAMMA_F']</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>spectral_triple_axiom_check</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>spectral_triple_axiom_check</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>['H2-GRAPH-CONTROL', 'AXIOM-CHECK-SELF-ADJOINT-D_B', 'AXIOM-CHECK-GRADING-D_B', 'AXIOM-CHECK-REAL-STRUCTURE-SIGNS', 'AXIOM-CHECK-FIRST-ORDER-CONDITION']</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DIRAC-SQUARED-FINITE-D_B</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>finite_dirac_squared_decomposition</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B']</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>E_B-BARE-FINITE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>finite_dirac_squared_decomposition</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>['DIRAC-SQUARED-FINITE-D_B']</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>OMEGA_B-FINITE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>finite_dirac_squared_decomposition</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>['FINITE-SPECTRAL-TRIPLE-CERTIFICATION', 'DIRAC-SQUARED-FINITE-D_B']</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SPECTRAL-ACTION-A0-A6-FINITE-B</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>finite_dirac_squared_decomposition</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>['E_B-BARE-FINITE', 'OMEGA_B-FINITE']</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11666,7 +12944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12090,6 +13368,70 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>['S3-MANIFOLD']</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H2-GRAPH-CONTROL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>self-adjointness, grading, real-structure-sign, and first-order-condition checks against the concrete (A_F,H_F,D_F,J_F,gamma_F) candidate defined above</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-GRADING-GAMMA_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T-DIRAC-SQUARED-FINITE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FINITE-DIRAC-D_B</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DIRAC-SQUARED-FINITE-D_B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>D_F^2 computed directly by matrix multiplication and compared block-by-block against d1 d1^T (vertex) and d1^T d1 (edge)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
@@ -13278,7 +14620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14020,190 +15362,526 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GRAPH-G-SEED</t>
+          <t>H2-GRAPH-CONTROL</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>FINITE-ALGEBRA-A_F</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>H2-GRAPH-CONTROL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>FINITE-GRADING-GAMMA_F</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>AXIOM-CHECK-SELF-ADJOINT-D_B</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>AXIOM-CHECK-GRADING-D_B</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>DIFFUSION-DISTANCE</t>
+          <t>FINITE-GRADING-GAMMA_F</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>AXIOM-CHECK-GRADING-D_B</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>FINITE-ALGEBRA-A_F</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>AXIOM-CHECK-REAL-STRUCTURE-SIGNS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>AXIOM-CHECK-REAL-STRUCTURE-SIGNS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CONTROL-FLAT-2D</t>
+          <t>FINITE-GRADING-GAMMA_F</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CONTROL-MANIFOLD-S2</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>FINITE-ALGEBRA-A_F</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>H2-GRAPH-CONTROL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>AXIOM-CHECK-SELF-ADJOINT-D_B</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>AXIOM-CHECK-GRADING-D_B</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AXIOM-CHECK-REAL-STRUCTURE-SIGNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DIRAC-SQUARED-FINITE-D_B</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FINITE-DIRAC-D_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>E_B-BARE-FINITE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>DIRAC-SQUARED-FINITE-D_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>OMEGA_B-FINITE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>OMEGA_B-FINITE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>DIRAC-SQUARED-FINITE-D_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SPECTRAL-ACTION-A0-A6-FINITE-B</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>E_B-BARE-FINITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SPECTRAL-ACTION-A0-A6-FINITE-B</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>OMEGA_B-FINITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T-GRAPH-TO-OPERATOR</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>GRAPH-G-SEED</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SPECTRUM-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>T-HEATFLOW-TO-KERNEL</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SPECTRUM-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>T-DIFFUSION-TO-METRIC</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>DIFFUSION-DISTANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>T-OPERATOR-TO-CURVATURE</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>CONTROL-FLAT-2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CONTROL-MANIFOLD-S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>FINITE-DIRAC-D_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>FINITE-ALGEBRA-A_F</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>FINITE-GRADING-GAMMA_F</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>T-DIRAC-SQUARED-FINITE</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FINITE-DIRAC-D_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
@@ -14220,7 +15898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14974,103 +16652,103 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>FINITE-ALGEBRA-A_F</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>Chosen to be the most honestly-derivable candidate from this project's own objects, reusing exactly what the corpus already independently identified as its best finite Dirac-operator candidate (H2B, chosen over D+=sqrt(L) specifically because H2B is local by construction while D+=sqrt(L) was found dense/non-local -- see h2_spectral_triple_locality_check). A_F=C(V) is the natural commutative algebra a graph itself provides (functions on its vertex set), avoiding the discipline clifford_derivation.py already established: never import the Standard Model's target algebra as an assumption.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>AXIOM-CHECK-REAL-STRUCTURE-SIGNS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Complex conjugation fixes every real matrix in this construction (D_F, gamma_F, pi(f) are all real), so all three signs come out trivially +1. This is the SAME degenerate situation h2_spectral_triple_locality_check already found for D+=sqrt(L) ('J^2=+1...this corresponds to KO-dimension 0 mod 8...for a triple with no grading'). Per ko_dimension.py's own explicit policy, this record does NOT restate Connes' full (epsilon,epsilon',epsilon'')-&gt;KO-mod-8 table from memory to attach a specific integer label to the graded case here; the substantive point -- no discriminating real-structure content is produced by the natural choice -- holds regardless of the exact label.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>With J trivial (JbJ^-1=b for real b), the first-order condition collapses to [[D,a],b]=0 for ALL a,b in A_F. Nothing in this representation makes a and b act from 'opposite sides' of D_F the way a genuine real structure is supposed to -- that mechanism is exactly what a nontrivial J swapping left/right module actions is FOR (as in the genuine Standard Model construction, where J b J^-1 acts as a right A_F-module action distinct from the left action of a). A trivial J removes that mechanism entirely, so there is no cancellation and the condition fails generically.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>FINITE-SPECTRAL-TRIPLE-CERTIFICATION</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>With J trivial (JbJ^-1=b for real b), the first-order condition collapses to [[D,a],b]=0 for ALL a,b in A_F. Nothing in this representation makes a and b act from 'opposite sides' of D_F the way a genuine real structure is supposed to -- that mechanism is exactly what a nontrivial J swapping left/right module actions is FOR (as in the genuine Standard Model construction, where J b J^-1 acts as a right A_F-module action distinct from the left action of a). A trivial J removes that mechanism entirely, so there is no cancellation and the condition fails generically.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>OMEGA_B-FINITE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Omega_B (gauge curvature of an inner-fluctuated connection) requires the standard NCG inner-fluctuation D_A=D_F+omega+J*omega*J^-1 to be well-defined, which in turn requires the first-order condition -- FALSE for this candidate (see run_spectral_triple_certification). No well-posed fluctuated operator exists to take a curvature of, so Omega_B is NOT CERTIFIABLE for this candidate, not merely 'not yet computed.'</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>OMEGA_B-FINITE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Connes' inner-fluctuation formula D_A = D_F + omega + J*omega*J^-1 (omega = sum a[D_F,b]) is only guaranteed well-defined/gauge-covariant when the first-order condition holds. It does not hold here, so (E_B, Omega_B) in the physical Chamseddine-Connes sense CANNOT be certified for this candidate -- there is no well-posed fluctuated operator D_A to take a Lichnerowicz-type decomposition of. The BARE, unfluctuated D_F^2 remains exactly computable (block-diagonal, confirms dirac_candidates.py's own diag(L0,d1^T d1) result), giving E_B=0 trivially for the unfluctuated operator -- but this is a much weaker statement than a genuine NCG spectral action, and a0^B..a6^B cannot be certified as physically meaningful moments on this basis. Per the explicit instruction that certification governs whether the spectral action can be touched: it cannot, for THIS candidate, until either (a) a genuinely different (A_F,J_F,gamma_F) is found that passes the first-order condition, or (b) the corpus explicitly accepts the trivial E_B=0 bare-operator reading, which none of its existing physical claims do.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>SPECTRAL-ACTION-A0-A6-FINITE-B</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Connes' inner-fluctuation formula D_A = D_F + omega + J*omega*J^-1 (omega = sum a[D_F,b]) is only guaranteed well-defined/gauge-covariant when the first-order condition holds. It does not hold here, so (E_B, Omega_B) in the physical Chamseddine-Connes sense CANNOT be certified for this candidate -- there is no well-posed fluctuated operator D_A to take a Lichnerowicz-type decomposition of. The BARE, unfluctuated D_F^2 remains exactly computable (block-diagonal, confirms dirac_candidates.py's own diag(L0,d1^T d1) result), giving E_B=0 trivially for the unfluctuated operator -- but this is a much weaker statement than a genuine NCG spectral action, and a0^B..a6^B cannot be certified as physically meaningful moments on this basis. Per the explicit instruction that certification governs whether the spectral action can be touched: it cannot, for THIS candidate, until either (a) a genuinely different (A_F,J_F,gamma_F) is found that passes the first-order condition, or (b) the corpus explicitly accepts the trivial E_B=0 bare-operator reading, which none of its existing physical claims do.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -15082,7 +16760,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -15094,79 +16772,79 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -15178,67 +16856,67 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -15250,7 +16928,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -15262,55 +16940,55 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -15322,22 +17000,106 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B100" t="inlineStr">
         <is>
           <t>The counterfactual manuscript's specific restatement of the gauge-closure claim (COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8).</t>
         </is>
@@ -15354,7 +17116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15661,6 +17423,60 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PROOF-T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>self-adjointness, grading, real-structure-sign, and first-order-condition checks against the concrete (A_F,H_F,D_F,J_F,gamma_F) candidate defined above</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>numpy exact linear algebra at n=200 (random f,g) plus sympy symbolic-general confirmation of the first-order-condition closed form at n=4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PROOF-T-DIRAC-SQUARED-FINITE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>T-DIRAC-SQUARED-FINITE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D_F^2 computed directly by matrix multiplication and compared block-by-block against d1 d1^T (vertex) and d1^T d1 (edge)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>numpy exact linear algebra, exact block match (not approximate)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15672,7 +17488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16539,6 +18355,50 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CALC-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>spectral_triple_axiom_certification</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>{'candidate': "D_F = D_B, the H2B block-incidence Dirac operator (dirac_candidates.py) on the SAME H2 ring graph (n=200, k=3) used throughout this corpus, for exact comparability. H_F = R^(N0+N1) (vertex block + edge block). A_F = C(V), the algebra of real-valued functions on the graph's vertex set -- genuinely derived from the graph itself, NOT the Standard Model's A_F = C (+) H (+) M_3(C) (which nothing in this project's own construction forces or produces -- see clifford_derivation.py::cliffo</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CALC-DIRAC-SQUARED-FINITE-D_B</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>finite_dirac_squared_block_decomposition</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1226,6 +1226,23 @@
       <c r="C41" t="inlineStr">
         <is>
           <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CALC-FINITE-SPECTRAL-TRIPLE-RECOVERY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>{'result_summary': "Self-adjointness, both grading axioms, and the first-order condition ALL hold exactly for this construction -- confirmed both numerically (n=200, genuine complex random test vectors, not real-valued stand-ins) and symbolically in general form (n=4, f left as a free symbol): [D_F',pi'(f)] has IDENTICALLY ZERO output on copy 2, for ANY f -- the exact structural fact that makes the first-order condition automatic, since J'pi'(g)J'^-1 only touches copy 2."}</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1619,12 +1636,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.966937+00:00</t>
+          <t>2026-08-21T03:59:41.013186+00:00</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1663,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.969504+00:00</t>
+          <t>2026-08-21T03:59:41.015425+00:00</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1690,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.971706+00:00</t>
+          <t>2026-08-21T03:59:41.017796+00:00</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1717,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.974228+00:00</t>
+          <t>2026-08-21T03:59:41.020448+00:00</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1744,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.976223+00:00</t>
+          <t>2026-08-21T03:59:41.022769+00:00</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1771,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.978944+00:00</t>
+          <t>2026-08-21T03:59:41.025747+00:00</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1798,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.981104+00:00</t>
+          <t>2026-08-21T03:59:41.027887+00:00</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1825,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.983486+00:00</t>
+          <t>2026-08-21T03:59:41.030011+00:00</t>
         </is>
       </c>
     </row>
@@ -1835,12 +1852,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.985840+00:00</t>
+          <t>2026-08-21T03:59:41.032066+00:00</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1879,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.988032+00:00</t>
+          <t>2026-08-21T03:59:41.034576+00:00</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1906,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.990352+00:00</t>
+          <t>2026-08-21T03:59:41.036539+00:00</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1933,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.992528+00:00</t>
+          <t>2026-08-21T03:59:41.038904+00:00</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1960,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.994634+00:00</t>
+          <t>2026-08-21T03:59:41.041009+00:00</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1987,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.996674+00:00</t>
+          <t>2026-08-21T03:59:41.042990+00:00</t>
         </is>
       </c>
     </row>
@@ -1997,12 +2014,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.998706+00:00</t>
+          <t>2026-08-21T03:59:41.045027+00:00</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2041,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.001028+00:00</t>
+          <t>2026-08-21T03:59:41.047379+00:00</t>
         </is>
       </c>
     </row>
@@ -2051,12 +2068,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.003008+00:00</t>
+          <t>2026-08-21T03:59:41.049433+00:00</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2095,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.005269+00:00</t>
+          <t>2026-08-21T03:59:41.051482+00:00</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2122,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.007392+00:00</t>
+          <t>2026-08-21T03:59:41.054025+00:00</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2149,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.009941+00:00</t>
+          <t>2026-08-21T03:59:41.056147+00:00</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2176,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.012130+00:00</t>
+          <t>2026-08-21T03:59:41.058219+00:00</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2203,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.198492+00:00</t>
+          <t>2026-08-21T03:59:41.205097+00:00</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2230,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.201686+00:00</t>
+          <t>2026-08-21T03:59:41.207882+00:00</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2257,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.204119+00:00</t>
+          <t>2026-08-21T03:59:41.210154+00:00</t>
         </is>
       </c>
     </row>
@@ -2267,12 +2284,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.206384+00:00</t>
+          <t>2026-08-21T03:59:41.214328+00:00</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2311,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.401792+00:00</t>
+          <t>2026-08-21T03:59:41.397123+00:00</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2338,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.404607+00:00</t>
+          <t>2026-08-21T03:59:41.399787+00:00</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2365,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.821166+00:00</t>
+          <t>2026-08-21T03:59:41.807198+00:00</t>
         </is>
       </c>
     </row>
@@ -2375,12 +2392,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.262410+00:00</t>
+          <t>2026-08-21T03:59:42.271096+00:00</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2419,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.265400+00:00</t>
+          <t>2026-08-21T03:59:42.274247+00:00</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2446,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.267993+00:00</t>
+          <t>2026-08-21T03:59:42.277366+00:00</t>
         </is>
       </c>
     </row>
@@ -2456,12 +2473,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.270356+00:00</t>
+          <t>2026-08-21T03:59:42.279645+00:00</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2500,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.272732+00:00</t>
+          <t>2026-08-21T03:59:42.282055+00:00</t>
         </is>
       </c>
     </row>
@@ -2510,12 +2527,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.275002+00:00</t>
+          <t>2026-08-21T03:59:42.284927+00:00</t>
         </is>
       </c>
     </row>
@@ -2537,12 +2554,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.277300+00:00</t>
+          <t>2026-08-21T03:59:42.287213+00:00</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2581,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.279486+00:00</t>
+          <t>2026-08-21T03:59:42.289385+00:00</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2608,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.281632+00:00</t>
+          <t>2026-08-21T03:59:42.292131+00:00</t>
         </is>
       </c>
     </row>
@@ -2618,12 +2635,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.283871+00:00</t>
+          <t>2026-08-21T03:59:42.294239+00:00</t>
         </is>
       </c>
     </row>
@@ -2645,12 +2662,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.435630+00:00</t>
+          <t>2026-08-21T03:59:42.450713+00:00</t>
         </is>
       </c>
     </row>
@@ -2672,12 +2689,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.438284+00:00</t>
+          <t>2026-08-21T03:59:42.453186+00:00</t>
         </is>
       </c>
     </row>
@@ -2699,12 +2716,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.440795+00:00</t>
+          <t>2026-08-21T03:59:42.455259+00:00</t>
         </is>
       </c>
     </row>
@@ -2726,12 +2743,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.443091+00:00</t>
+          <t>2026-08-21T03:59:42.458314+00:00</t>
         </is>
       </c>
     </row>
@@ -2753,12 +2770,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.445327+00:00</t>
+          <t>2026-08-21T03:59:42.460556+00:00</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2797,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.085578+00:00</t>
+          <t>2026-08-21T03:59:44.877550+00:00</t>
         </is>
       </c>
     </row>
@@ -2807,12 +2824,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.090943+00:00</t>
+          <t>2026-08-21T03:59:44.882799+00:00</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2851,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.093424+00:00</t>
+          <t>2026-08-21T03:59:44.885100+00:00</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2878,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.098455+00:00</t>
+          <t>2026-08-21T03:59:44.887771+00:00</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2905,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.100670+00:00</t>
+          <t>2026-08-21T03:59:44.890497+00:00</t>
         </is>
       </c>
     </row>
@@ -2915,12 +2932,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.102945+00:00</t>
+          <t>2026-08-21T03:59:44.893105+00:00</t>
         </is>
       </c>
     </row>
@@ -2942,12 +2959,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.105142+00:00</t>
+          <t>2026-08-21T03:59:44.895543+00:00</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2986,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.107206+00:00</t>
+          <t>2026-08-21T03:59:44.898204+00:00</t>
         </is>
       </c>
     </row>
@@ -2996,12 +3013,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.109398+00:00</t>
+          <t>2026-08-21T03:59:44.902810+00:00</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3040,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.114398+00:00</t>
+          <t>2026-08-21T03:59:44.905415+00:00</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3067,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.116569+00:00</t>
+          <t>2026-08-21T03:59:44.907934+00:00</t>
         </is>
       </c>
     </row>
@@ -3077,12 +3094,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.118656+00:00</t>
+          <t>2026-08-21T03:59:44.910464+00:00</t>
         </is>
       </c>
     </row>
@@ -3104,12 +3121,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.120826+00:00</t>
+          <t>2026-08-21T03:59:44.912984+00:00</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3148,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.126480+00:00</t>
+          <t>2026-08-21T03:59:44.915475+00:00</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3175,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.128561+00:00</t>
+          <t>2026-08-21T03:59:44.917920+00:00</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3202,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.562029+00:00</t>
+          <t>2026-08-21T03:59:45.357015+00:00</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3229,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.578451+00:00</t>
+          <t>2026-08-21T03:59:45.367403+00:00</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3256,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.583334+00:00</t>
+          <t>2026-08-21T03:59:45.371087+00:00</t>
         </is>
       </c>
     </row>
@@ -3266,12 +3283,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.593598+00:00</t>
+          <t>2026-08-21T03:59:45.379209+00:00</t>
         </is>
       </c>
     </row>
@@ -3293,12 +3310,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.597701+00:00</t>
+          <t>2026-08-21T03:59:45.381915+00:00</t>
         </is>
       </c>
     </row>
@@ -3320,12 +3337,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.606790+00:00</t>
+          <t>2026-08-21T03:59:45.386027+00:00</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3364,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.610044+00:00</t>
+          <t>2026-08-21T03:59:45.387972+00:00</t>
         </is>
       </c>
     </row>
@@ -3374,12 +3391,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.613218+00:00</t>
+          <t>2026-08-21T03:59:45.390490+00:00</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3418,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.903546+00:00</t>
+          <t>2026-08-21T03:59:45.648455+00:00</t>
         </is>
       </c>
     </row>
@@ -3428,12 +3445,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.896272+00:00</t>
+          <t>2026-08-21T03:59:51.829414+00:00</t>
         </is>
       </c>
     </row>
@@ -3455,12 +3472,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.901404+00:00</t>
+          <t>2026-08-21T03:59:51.835363+00:00</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3499,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.910862+00:00</t>
+          <t>2026-08-21T03:59:51.845110+00:00</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3526,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.915275+00:00</t>
+          <t>2026-08-21T03:59:51.850226+00:00</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3553,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.917644+00:00</t>
+          <t>2026-08-21T03:59:51.852572+00:00</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3580,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.920032+00:00</t>
+          <t>2026-08-21T03:59:51.854725+00:00</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3607,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.922235+00:00</t>
+          <t>2026-08-21T03:59:51.857316+00:00</t>
         </is>
       </c>
     </row>
@@ -3617,12 +3634,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.924341+00:00</t>
+          <t>2026-08-21T03:59:51.859443+00:00</t>
         </is>
       </c>
     </row>
@@ -3644,12 +3661,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.926354+00:00</t>
+          <t>2026-08-21T03:59:51.861571+00:00</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3688,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.928295+00:00</t>
+          <t>2026-08-21T03:59:51.863834+00:00</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3715,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.057098+00:00</t>
+          <t>2026-08-21T03:59:52.122660+00:00</t>
         </is>
       </c>
     </row>
@@ -3725,12 +3742,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.063339+00:00</t>
+          <t>2026-08-21T03:59:52.125352+00:00</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3769,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.066040+00:00</t>
+          <t>2026-08-21T03:59:52.127528+00:00</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3796,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.068130+00:00</t>
+          <t>2026-08-21T03:59:52.129623+00:00</t>
         </is>
       </c>
     </row>
@@ -3806,12 +3823,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.074433+00:00</t>
+          <t>2026-08-21T03:59:52.133669+00:00</t>
         </is>
       </c>
     </row>
@@ -3833,12 +3850,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.112321+00:00</t>
+          <t>2026-08-21T03:59:52.193447+00:00</t>
         </is>
       </c>
     </row>
@@ -3860,12 +3877,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.120872+00:00</t>
+          <t>2026-08-21T03:59:52.196182+00:00</t>
         </is>
       </c>
     </row>
@@ -3887,12 +3904,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.123339+00:00</t>
+          <t>2026-08-21T03:59:52.198380+00:00</t>
         </is>
       </c>
     </row>
@@ -3914,51 +3931,51 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.125650+00:00</t>
+          <t>2026-08-21T03:59:52.201158+00:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>AUDIT-1-D_B-DISCARDS-AVAILABLE-2-CELLS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>compiler/historical/finite_spectral_triple_audit_and_recovery.py</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:26.964337+00:00</t>
+          <t>2026-08-21T03:59:52.205851+00:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>AUDIT-2-NO-OTHER-CANDIDATE-CONSTRUCTIONS-MISSED</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/historical/finite_spectral_triple_audit_and_recovery.py</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3968,240 +3985,240 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.210381+00:00</t>
+          <t>2026-08-21T03:59:52.207864+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/finite_spectral_triple_recovery.py</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.216658+00:00</t>
+          <t>2026-08-21T03:59:54.688143+00:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>FINITE-ALGEBRA-A_F-PRIME</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/finite_spectral_triple_recovery.py</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.218935+00:00</t>
+          <t>2026-08-21T03:59:54.691029+00:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/finite_spectral_triple_recovery.py</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.222111+00:00</t>
+          <t>2026-08-21T03:59:54.693294+00:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/finite_spectral_triple_recovery.py</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.406869+00:00</t>
+          <t>2026-08-21T03:59:54.695287+00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/finite_spectral_triple_recovery.py::run_recovery_certification</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.408959+00:00</t>
+          <t>2026-08-21T03:59:54.697324+00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>compiler/backends/ollivier_ricci.py</t>
+          <t>compiler/ir/finite_spectral_triple_recovery.py</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.823902+00:00</t>
+          <t>2026-08-21T03:59:54.699323+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>spec section 10</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.449963+00:00</t>
+          <t>2026-08-21T03:59:41.010302+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.906359+00:00</t>
+          <t>2026-08-21T03:59:41.218614+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4211,24 +4228,24 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.899043+00:00</t>
+          <t>2026-08-21T03:59:41.220930+00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4238,51 +4255,51 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:37.913138+00:00</t>
+          <t>2026-08-21T03:59:41.223178+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.070253+00:00</t>
+          <t>2026-08-21T03:59:41.225488+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>T-DIRAC-SQUARED-FINITE</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4292,321 +4309,321 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:38.127786+00:00</t>
+          <t>2026-08-21T03:59:41.402217+00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.415211+00:00</t>
+          <t>2026-08-21T03:59:41.406464+00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_flow.py</t>
+          <t>compiler/backends/ollivier_ricci.py</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:27.417232+00:00</t>
+          <t>2026-08-21T03:59:41.810643+00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.359965+00:00</t>
+          <t>2026-08-21T03:59:42.465614+00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.363148+00:00</t>
+          <t>2026-08-21T03:59:45.651068+00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.365701+00:00</t>
+          <t>2026-08-21T03:59:51.832840+00:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.368426+00:00</t>
+          <t>2026-08-21T03:59:51.848012+00:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.370793+00:00</t>
+          <t>2026-08-21T03:59:52.131664+00:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.373211+00:00</t>
+          <t>2026-08-21T03:59:52.203741+00:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+          <t>compiler/backends/finite_spectral_triple_recovery.py</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.375485+00:00</t>
+          <t>2026-08-21T03:59:54.701337+00:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.377588+00:00</t>
+          <t>2026-08-21T03:59:41.412674+00:00</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+          <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.379704+00:00</t>
+          <t>2026-08-21T03:59:41.414909+00:00</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4616,24 +4633,24 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.381948+00:00</t>
+          <t>2026-08-21T03:59:42.366040+00:00</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4643,24 +4660,24 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.384046+00:00</t>
+          <t>2026-08-21T03:59:42.369200+00:00</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4670,24 +4687,24 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.386223+00:00</t>
+          <t>2026-08-21T03:59:42.371662+00:00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4697,24 +4714,24 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.388218+00:00</t>
+          <t>2026-08-21T03:59:42.374744+00:00</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4724,24 +4741,24 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.390497+00:00</t>
+          <t>2026-08-21T03:59:42.377306+00:00</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4751,24 +4768,24 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.392844+00:00</t>
+          <t>2026-08-21T03:59:42.380125+00:00</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4778,24 +4795,24 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.394909+00:00</t>
+          <t>2026-08-21T03:59:42.383033+00:00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4805,24 +4822,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.397127+00:00</t>
+          <t>2026-08-21T03:59:42.385179+00:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4832,24 +4849,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.399376+00:00</t>
+          <t>2026-08-21T03:59:42.388141+00:00</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4859,24 +4876,24 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.401455+00:00</t>
+          <t>2026-08-21T03:59:42.390947+00:00</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4886,24 +4903,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.403523+00:00</t>
+          <t>2026-08-21T03:59:42.393374+00:00</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4913,24 +4930,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.405797+00:00</t>
+          <t>2026-08-21T03:59:42.395865+00:00</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4940,24 +4957,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.407998+00:00</t>
+          <t>2026-08-21T03:59:42.398939+00:00</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4967,24 +4984,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.410142+00:00</t>
+          <t>2026-08-21T03:59:42.401341+00:00</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4994,24 +5011,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.412793+00:00</t>
+          <t>2026-08-21T03:59:42.404007+00:00</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5021,24 +5038,24 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.414924+00:00</t>
+          <t>2026-08-21T03:59:42.406989+00:00</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5048,24 +5065,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.417057+00:00</t>
+          <t>2026-08-21T03:59:42.409456+00:00</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5075,24 +5092,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.419202+00:00</t>
+          <t>2026-08-21T03:59:42.411777+00:00</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5102,24 +5119,24 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.421360+00:00</t>
+          <t>2026-08-21T03:59:42.414609+00:00</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5129,120 +5146,363 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.423714+00:00</t>
+          <t>2026-08-21T03:59:42.416919+00:00</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:28.447709+00:00</t>
+          <t>2026-08-21T03:59:42.419730+00:00</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.566693+00:00</t>
+          <t>2026-08-21T03:59:42.422551+00:00</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>5a1fc01640d0</t>
+          <t>6147d4a42e08</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-08-21T03:40:31.571123+00:00</t>
+          <t>2026-08-21T03:59:42.424675+00:00</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:42.427371+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:42.430133+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:42.432174+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:42.434989+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:42.437133+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:42.439303+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:42.463455+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:45.359547+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:45.361809+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>5a1fc01640d0</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>2026-08-21T03:40:31.603439+00:00</t>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>6147d4a42e08</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-08-21T03:59:45.383950+00:00</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5687,12 +5947,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+          <t>AUDIT-2-NO-OTHER-CANDIDATE-CONSTRUCTIONS-MISSED</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SU(3)</t>
+          <t>SU(2)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5704,6 +5964,32 @@
         <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>architecture_audit_finding
+A systematic grep sweep across compiler/, scientific_corpus/, and seit_lang/ for Dirac/spectral-triple/real-structure/order-zero content found no additional algebra represen</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SU(3)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>G2 (intersection via triality) Spin(8)
 SU(3) x SU(2) x U(1)
@@ -5712,26 +5998,26 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>SU(2)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>comparison</t>
         </is>
       </c>
-      <c r="D18" t="b">
+      <c r="D19" t="b">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>G2 (intersection via triality) Spin(8)
 SU(3) x SU(2) x U(1)
@@ -5740,26 +6026,26 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>U(1)</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>comparison</t>
         </is>
       </c>
-      <c r="D19" t="b">
+      <c r="D20" t="b">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>G2 (intersection via triality) Spin(8)
 SU(3) x SU(2) x U(1)
@@ -6550,7 +6836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8476,17 +8762,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>AUDIT-1-D_B-DISCARDS-AVAILABLE-2-CELLS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -8498,12 +8784,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>AUDIT-2-NO-OTHER-CANDIDATE-CONSTRUCTIONS-MISSED</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -8513,146 +8799,146 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>FINITE-ALGEBRA-A_F-PRIME</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['DOUBLED-HILBERT-SPACE-H_F-PRIME']</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['DOUBLED-HILBERT-SPACE-H_F-PRIME']</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['DOUBLED-HILBERT-SPACE-H_F-PRIME']</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>['FINITE-ALGEBRA-A_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME']</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['FINITE-DIRAC-D_B', 'DOUBLED-HILBERT-SPACE-H_F-PRIME', 'FINITE-ALGEBRA-A_F-PRIME', 'FINITE-GRADING-GAMMA_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME', 'AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY']</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8662,19 +8948,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8684,19 +8970,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>['CONTROL-FLAT-2D']</t>
+          <t>['GRAPH-G-SEED']</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8711,14 +8997,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>['CONTROL-MANIFOLD-S2']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8733,14 +9019,14 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8750,19 +9036,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-GRADING-GAMMA_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>T-DIRAC-SQUARED-FINITE</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8777,212 +9063,212 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>['FINITE-DIRAC-D_B']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['DIFFUSION-DISTANCE']</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CONTROL-FLAT-2D']</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['CONTROL-MANIFOLD-S2']</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-GRADING-GAMMA_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['FINITE-DIRAC-D_B', 'DOUBLED-HILBERT-SPACE-H_F-PRIME', 'FINITE-ALGEBRA-A_F-PRIME', 'FINITE-GRADING-GAMMA_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME']</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8992,19 +9278,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9014,19 +9300,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9048,7 +9334,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9070,7 +9356,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9092,7 +9378,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9114,7 +9400,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9136,7 +9422,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9158,7 +9444,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9180,7 +9466,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9202,7 +9488,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9224,7 +9510,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9246,7 +9532,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9268,7 +9554,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9290,7 +9576,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9312,7 +9598,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9334,7 +9620,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9356,7 +9642,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9378,7 +9664,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9400,7 +9686,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9422,7 +9708,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9444,7 +9730,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9466,7 +9752,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9476,19 +9762,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>['S3-CURVATURE-CLOSURE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9498,19 +9784,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9520,32 +9806,230 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>['S3-CURVATURE-CLOSURE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -10046,7 +10530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10560,6 +11044,30 @@
       <c r="B37" t="inlineStr">
         <is>
           <t>D_F^2 for a finite candidate Dirac operator, and whether its E_B/Omega_B decomposition is certifiable</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>architecture_audit_finding</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>a real, verified finding about a gap, inconsistency, or unused-richer-alternative in an already-built architecture, never itself a new physics claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>recovered_finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>one component of a recovery candidate (doubled Hilbert space, algebra, grading, real structure) built after an original candidate's certification genuinely failed</t>
         </is>
       </c>
     </row>
@@ -10574,7 +11082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12933,6 +13441,222 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AUDIT-1-D_B-DISCARDS-AVAILABLE-2-CELLS</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>architecture_audit_finding</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AUDIT-2-NO-OTHER-CANDIDATE-CONSTRUCTIONS-MISSED</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>architecture_audit_finding</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>recovered_finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B']</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FINITE-ALGEBRA-A_F-PRIME</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>recovered_finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>['DOUBLED-HILBERT-SPACE-H_F-PRIME']</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>recovered_finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>['DOUBLED-HILBERT-SPACE-H_F-PRIME']</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>recovered_finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>['DOUBLED-HILBERT-SPACE-H_F-PRIME']</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>recovered_finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>['FINITE-ALGEBRA-A_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME']</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>recovered_finite_spectral_triple_component</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B', 'DOUBLED-HILBERT-SPACE-H_F-PRIME', 'FINITE-ALGEBRA-A_F-PRIME', 'FINITE-GRADING-GAMMA_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME', 'AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY']</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12944,7 +13668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13432,6 +14156,38 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>['FINITE-DIRAC-D_B']</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FINITE-DIRAC-D_B</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>self-adjointness, grading, real-structure-sign, and first-order-condition checks against the DOUBLED candidate (A_F,H_F',D_F'=D_F(+)D_F,J_F',gamma_F')</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>['FINITE-DIRAC-D_B', 'DOUBLED-HILBERT-SPACE-H_F-PRIME', 'FINITE-ALGEBRA-A_F-PRIME', 'FINITE-GRADING-GAMMA_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME']</t>
         </is>
       </c>
     </row>
@@ -14620,7 +15376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15638,250 +16394,454 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GRAPH-G-SEED</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>FINITE-ALGEBRA-A_F-PRIME</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>FINITE-ALGEBRA-A_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DIFFUSION-DISTANCE</t>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CONTROL-FLAT-2D</t>
+          <t>FINITE-ALGEBRA-A_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CONTROL-MANIFOLD-S2</t>
+          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FINITE-DIRAC-D_B</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FINITE-ALGEBRA-A_F</t>
+          <t>GRAPH-G-SEED</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FINITE-GRADING-GAMMA_F</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FINITE-REAL-STRUCTURE-J_F</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>T-DIRAC-SQUARED-FINITE</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FINITE-DIRAC-D_B</t>
+          <t>HEAT-FLOW-R</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>DIFFUSION-DISTANCE</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CONTROL-FLAT-2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CONTROL-MANIFOLD-S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>S3-MANIFOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>FINITE-DIRAC-D_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>FINITE-ALGEBRA-A_F</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>FINITE-GRADING-GAMMA_F</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>T-DIRAC-SQUARED-FINITE</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>FINITE-DIRAC-D_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>FINITE-DIRAC-D_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>FINITE-ALGEBRA-A_F-PRIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
@@ -15898,7 +16858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16736,199 +17696,199 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>AUDIT-1-D_B-DISCARDS-AVAILABLE-2-CELLS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>Checked directly, not assumed: the SAME H2 ring graph (n=200, k=3) used throughout this corpus for D_B has 600 triangles (scientific_corpus.derivation.dirac_candidates._extract_triangles), confirmed by direct computation. simplicial.py's own TFT-002B (check_three_block_hodge_dirac_squaring) already implements and verifies the richer, standard 3-graded Hodge-Dirac operator D=[[0,d1,0],[d1^T,0,d2],[0,d2^T,0]] on C0 (+) C1 (+) C2, whose square gives the FULL graded Hodge Laplacian diag(L0,L1,L2) with L1=d1^Td1+d2d2^T -- this is external, established discrete exterior calculus (Horak &amp; Jost 2013), not a new claim.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>AUDIT-1-D_B-DISCARDS-AVAILABLE-2-CELLS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>D_B is not the richest Dirac-type candidate already available and already verified in this corpus for this exact graph. Using the 3-block Hodge-Dirac operator instead of the 2-block D_B as D_F -- combined with the recovery construction below -- is a legitimate next step, explicitly NOT attempted in this pass (kept as its own bounded piece of work per this project's 'new claim id, don't overreach in one pass' discipline, rather than folded into an already-large recovery attempt).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>AUDIT-2-NO-OTHER-CANDIDATE-CONSTRUCTIONS-MISSED</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>grep -rl for Dirac/spectral triple/real_structure/order.zero across the three top-level packages, each hit read.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>AUDIT-2-NO-OTHER-CANDIDATE-CONSTRUCTIONS-MISSED</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>The original certification's candidate scope was not missing an already-built alternative algebra/real-structure (only the richer D_F of AUDIT-1).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>(epsilon,epsilon',epsilon'')=(1,1,1) with this sign convention; the alternative asymmetric sign convention gives (-1,-1,-1) instead, also verified to pass the first-order condition -- see AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>CONTENT-INDEPENDENT MECHANISM: the argument above works for ANY D_F once doubled this way with a copy-1-only algebra action -- it is a structural consequence of the block-disjoint bimodule shape, not a discovery specific to D_B. This is the same mechanism the genuine Connes construction uses (not a criticism of using it), but passing the first-order condition here is not by itself evidence that D_B is a physically distinguished choice.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>ZERO INTER-COPY COUPLING: D_F' = D_F (+) D_F has no off-diagonal term between the two copies. A richer choice (an off-diagonal 'Dirac mass'-type term between copies, as the genuine Standard Model construction has between particle and antiparticle sectors) is NOT explored here -- this recovery is the minimal extension that passes the axiom, not a claim that it is the most physically interesting one.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>KO-DIMENSION STILL OPEN: (epsilon,epsilon',epsilon'') come out as either (+1,+1,+1) (symmetric J sign convention) or (-1,-1,-1) (asymmetric convention) -- both verified, both still a uniform/symmetric triple rather than an arbitrary combination, and this project does not restate Connes' full KO-dimension classification table from memory (ko_dimension.py's own established policy) to check either against the physically required KO=6 mod 8. Fixing the first-order condition does NOT by itself resolve the separate KO-dimension gap H2/ncg_branch.py already identified.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>AXIOM-CHECK-FIRST-ORDER-CONDITION-RECOVERY</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>AUDIT-1 (D_B vs the richer 3-block Hodge-Dirac operator) remains unresolved: this recovery was built on the SAME D_B as the original certification, not the richer TFT-002B operator.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>CONTENT-INDEPENDENT MECHANISM: the argument above works for ANY D_F once doubled this way with a copy-1-only algebra action -- it is a structural consequence of the block-disjoint bimodule shape, not a discovery specific to D_B. This is the same mechanism the genuine Connes construction uses (not a criticism of using it), but passing the first-order condition here is not by itself evidence that D_B is a physically distinguished choice.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>ZERO INTER-COPY COUPLING: D_F' = D_F (+) D_F has no off-diagonal term between the two copies. A richer choice (an off-diagonal 'Dirac mass'-type term between copies, as the genuine Standard Model construction has between particle and antiparticle sectors) is NOT explored here -- this recovery is the minimal extension that passes the axiom, not a claim that it is the most physically interesting one.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>KO-DIMENSION STILL OPEN: (epsilon,epsilon',epsilon'') come out as either (+1,+1,+1) (symmetric J sign convention) or (-1,-1,-1) (asymmetric convention) -- both verified, both still a uniform/symmetric triple rather than an arbitrary combination, and this project does not restate Connes' full KO-dimension classification table from memory (ko_dimension.py's own established policy) to check either against the physically required KO=6 mod 8. Fixing the first-order condition does NOT by itself resolve the separate KO-dimension gap H2/ncg_branch.py already identified.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>FINITE-SPECTRAL-TRIPLE-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>AUDIT-1 (D_B vs the richer 3-block Hodge-Dirac operator) remains unresolved: this recovery was built on the SAME D_B as the original certification, not the richer TFT-002B operator.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -16940,31 +17900,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -16976,7 +17936,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -16988,7 +17948,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -17000,106 +17960,262 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>EQ-017</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>EQ-018</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>EQ-019</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>EQ-020</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>EQ-021</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>EQ-022</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>EQ-023</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>EQ-024</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>EQ-025</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>The counterfactual manuscript's specific restatement of the gauge-closure claim (COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8).</t>
         </is>
@@ -17116,7 +18232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17477,6 +18593,33 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PROOF-T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>self-adjointness, grading, real-structure-sign, and first-order-condition checks against the DOUBLED candidate (A_F,H_F',D_F'=D_F(+)D_F,J_F',gamma_F')</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>numpy exact linear algebra at n=200 (genuine complex random f,g) plus sympy symbolic-general confirmation of the copy-2-support-is-zero closed form at n=4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17488,7 +18631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18399,6 +19542,28 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CALC-FINITE-SPECTRAL-TRIPLE-RECOVERY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>doubled_spectral_triple_recovery_certification</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>{'mechanism': "The prior candidate's first-order-condition failure had a precise structural cause: with J trivial (J b J^-1 = b for real b, since H_F was a plain real vector space), the condition collapses to [[D,a],b]=0 for ALL a,b in A_F, and nothing made a,b act from 'opposite sides' of D_F. The standard NCG fix for exactly this failure mode is Connes' own doubling construction: H_F' = H_F (+) H_F, genuinely COMPLEX (J being 'trivial conjugation on a real space' was exactly the degeneracy tha</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1241,6 +1241,40 @@
         </is>
       </c>
       <c r="C42" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CALC-TFT002B-EVALUATION</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>{'promote_to_canonical': True}</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CALC-COUPLED-RECOVERY-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>{'first_order_condition_holds_symbolic_general': True}</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1581,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1636,12 +1670,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.013186+00:00</t>
+          <t>2026-08-21T19:24:56.154621+00:00</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1697,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.015425+00:00</t>
+          <t>2026-08-21T19:24:56.157123+00:00</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1724,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.017796+00:00</t>
+          <t>2026-08-21T19:24:56.159525+00:00</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1751,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.020448+00:00</t>
+          <t>2026-08-21T19:24:56.161801+00:00</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1778,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.022769+00:00</t>
+          <t>2026-08-21T19:24:56.163720+00:00</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1805,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.025747+00:00</t>
+          <t>2026-08-21T19:24:56.166106+00:00</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1832,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.027887+00:00</t>
+          <t>2026-08-21T19:24:56.168374+00:00</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1859,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.030011+00:00</t>
+          <t>2026-08-21T19:24:56.170531+00:00</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1886,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.032066+00:00</t>
+          <t>2026-08-21T19:24:56.172495+00:00</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1913,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.034576+00:00</t>
+          <t>2026-08-21T19:24:56.174611+00:00</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1940,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.036539+00:00</t>
+          <t>2026-08-21T19:24:56.176467+00:00</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1967,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.038904+00:00</t>
+          <t>2026-08-21T19:24:56.178859+00:00</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1994,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.041009+00:00</t>
+          <t>2026-08-21T19:24:56.181148+00:00</t>
         </is>
       </c>
     </row>
@@ -1987,12 +2021,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.042990+00:00</t>
+          <t>2026-08-21T19:24:56.183253+00:00</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2048,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.045027+00:00</t>
+          <t>2026-08-21T19:24:56.185062+00:00</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2075,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.047379+00:00</t>
+          <t>2026-08-21T19:24:56.187573+00:00</t>
         </is>
       </c>
     </row>
@@ -2068,12 +2102,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.049433+00:00</t>
+          <t>2026-08-21T19:24:56.189525+00:00</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2129,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.051482+00:00</t>
+          <t>2026-08-21T19:24:56.192047+00:00</t>
         </is>
       </c>
     </row>
@@ -2122,12 +2156,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.054025+00:00</t>
+          <t>2026-08-21T19:24:56.194073+00:00</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2183,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.056147+00:00</t>
+          <t>2026-08-21T19:24:56.195966+00:00</t>
         </is>
       </c>
     </row>
@@ -2176,12 +2210,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.058219+00:00</t>
+          <t>2026-08-21T19:24:56.198190+00:00</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2237,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.205097+00:00</t>
+          <t>2026-08-21T19:24:56.432408+00:00</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2264,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.207882+00:00</t>
+          <t>2026-08-21T19:24:56.436828+00:00</t>
         </is>
       </c>
     </row>
@@ -2257,12 +2291,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.210154+00:00</t>
+          <t>2026-08-21T19:24:56.440005+00:00</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2318,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.214328+00:00</t>
+          <t>2026-08-21T19:24:56.443962+00:00</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2345,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.397123+00:00</t>
+          <t>2026-08-21T19:24:56.632841+00:00</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2372,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.399787+00:00</t>
+          <t>2026-08-21T19:24:56.635451+00:00</t>
         </is>
       </c>
     </row>
@@ -2365,12 +2399,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.807198+00:00</t>
+          <t>2026-08-21T19:24:57.066772+00:00</t>
         </is>
       </c>
     </row>
@@ -2392,12 +2426,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.271096+00:00</t>
+          <t>2026-08-21T19:24:57.471460+00:00</t>
         </is>
       </c>
     </row>
@@ -2419,12 +2453,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.274247+00:00</t>
+          <t>2026-08-21T19:24:57.473985+00:00</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2480,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.277366+00:00</t>
+          <t>2026-08-21T19:24:57.476060+00:00</t>
         </is>
       </c>
     </row>
@@ -2473,12 +2507,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.279645+00:00</t>
+          <t>2026-08-21T19:24:57.478109+00:00</t>
         </is>
       </c>
     </row>
@@ -2500,12 +2534,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.282055+00:00</t>
+          <t>2026-08-21T19:24:57.480101+00:00</t>
         </is>
       </c>
     </row>
@@ -2527,12 +2561,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.284927+00:00</t>
+          <t>2026-08-21T19:24:57.482048+00:00</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2588,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.287213+00:00</t>
+          <t>2026-08-21T19:24:57.483844+00:00</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2615,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.289385+00:00</t>
+          <t>2026-08-21T19:24:57.485738+00:00</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2642,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.292131+00:00</t>
+          <t>2026-08-21T19:24:57.487570+00:00</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2669,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.294239+00:00</t>
+          <t>2026-08-21T19:24:57.489391+00:00</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2696,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.450713+00:00</t>
+          <t>2026-08-21T19:24:57.629195+00:00</t>
         </is>
       </c>
     </row>
@@ -2689,12 +2723,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.453186+00:00</t>
+          <t>2026-08-21T19:24:57.631220+00:00</t>
         </is>
       </c>
     </row>
@@ -2716,12 +2750,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.455259+00:00</t>
+          <t>2026-08-21T19:24:57.633173+00:00</t>
         </is>
       </c>
     </row>
@@ -2743,12 +2777,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.458314+00:00</t>
+          <t>2026-08-21T19:24:57.635082+00:00</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2804,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.460556+00:00</t>
+          <t>2026-08-21T19:24:57.636805+00:00</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2831,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.877550+00:00</t>
+          <t>2026-08-21T19:25:00.385367+00:00</t>
         </is>
       </c>
     </row>
@@ -2824,12 +2858,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.882799+00:00</t>
+          <t>2026-08-21T19:25:00.388048+00:00</t>
         </is>
       </c>
     </row>
@@ -2851,12 +2885,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.885100+00:00</t>
+          <t>2026-08-21T19:25:00.391857+00:00</t>
         </is>
       </c>
     </row>
@@ -2878,12 +2912,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.887771+00:00</t>
+          <t>2026-08-21T19:25:00.396343+00:00</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2939,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.890497+00:00</t>
+          <t>2026-08-21T19:25:00.402130+00:00</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2966,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.893105+00:00</t>
+          <t>2026-08-21T19:25:00.404894+00:00</t>
         </is>
       </c>
     </row>
@@ -2959,12 +2993,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.895543+00:00</t>
+          <t>2026-08-21T19:25:00.408060+00:00</t>
         </is>
       </c>
     </row>
@@ -2986,12 +3020,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.898204+00:00</t>
+          <t>2026-08-21T19:25:00.411713+00:00</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3047,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.902810+00:00</t>
+          <t>2026-08-21T19:25:00.418148+00:00</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3074,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.905415+00:00</t>
+          <t>2026-08-21T19:25:00.420090+00:00</t>
         </is>
       </c>
     </row>
@@ -3067,12 +3101,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.907934+00:00</t>
+          <t>2026-08-21T19:25:00.426071+00:00</t>
         </is>
       </c>
     </row>
@@ -3094,12 +3128,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.910464+00:00</t>
+          <t>2026-08-21T19:25:00.427985+00:00</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3155,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.912984+00:00</t>
+          <t>2026-08-21T19:25:00.434088+00:00</t>
         </is>
       </c>
     </row>
@@ -3148,12 +3182,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.915475+00:00</t>
+          <t>2026-08-21T19:25:00.436177+00:00</t>
         </is>
       </c>
     </row>
@@ -3175,12 +3209,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:44.917920+00:00</t>
+          <t>2026-08-21T19:25:00.439617+00:00</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3236,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.357015+00:00</t>
+          <t>2026-08-21T19:25:00.860520+00:00</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3263,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.367403+00:00</t>
+          <t>2026-08-21T19:25:00.871089+00:00</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3290,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.371087+00:00</t>
+          <t>2026-08-21T19:25:00.875076+00:00</t>
         </is>
       </c>
     </row>
@@ -3283,12 +3317,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.379209+00:00</t>
+          <t>2026-08-21T19:25:00.882142+00:00</t>
         </is>
       </c>
     </row>
@@ -3310,12 +3344,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.381915+00:00</t>
+          <t>2026-08-21T19:25:00.888017+00:00</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3371,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.386027+00:00</t>
+          <t>2026-08-21T19:25:00.895714+00:00</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3398,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.387972+00:00</t>
+          <t>2026-08-21T19:25:00.902105+00:00</t>
         </is>
       </c>
     </row>
@@ -3391,12 +3425,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.390490+00:00</t>
+          <t>2026-08-21T19:25:00.904323+00:00</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3452,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.648455+00:00</t>
+          <t>2026-08-21T19:25:01.171465+00:00</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3479,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.829414+00:00</t>
+          <t>2026-08-21T19:25:07.128754+00:00</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3506,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.835363+00:00</t>
+          <t>2026-08-21T19:25:07.133963+00:00</t>
         </is>
       </c>
     </row>
@@ -3499,12 +3533,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.845110+00:00</t>
+          <t>2026-08-21T19:25:07.141103+00:00</t>
         </is>
       </c>
     </row>
@@ -3526,12 +3560,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.850226+00:00</t>
+          <t>2026-08-21T19:25:07.145110+00:00</t>
         </is>
       </c>
     </row>
@@ -3553,12 +3587,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.852572+00:00</t>
+          <t>2026-08-21T19:25:07.147141+00:00</t>
         </is>
       </c>
     </row>
@@ -3580,12 +3614,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.854725+00:00</t>
+          <t>2026-08-21T19:25:07.148904+00:00</t>
         </is>
       </c>
     </row>
@@ -3607,12 +3641,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.857316+00:00</t>
+          <t>2026-08-21T19:25:07.150744+00:00</t>
         </is>
       </c>
     </row>
@@ -3634,12 +3668,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.859443+00:00</t>
+          <t>2026-08-21T19:25:07.152492+00:00</t>
         </is>
       </c>
     </row>
@@ -3661,12 +3695,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.861571+00:00</t>
+          <t>2026-08-21T19:25:07.154399+00:00</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3722,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.863834+00:00</t>
+          <t>2026-08-21T19:25:07.156200+00:00</t>
         </is>
       </c>
     </row>
@@ -3715,12 +3749,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.122660+00:00</t>
+          <t>2026-08-21T19:25:07.347476+00:00</t>
         </is>
       </c>
     </row>
@@ -3742,12 +3776,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.125352+00:00</t>
+          <t>2026-08-21T19:25:07.350591+00:00</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3803,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.127528+00:00</t>
+          <t>2026-08-21T19:25:07.355692+00:00</t>
         </is>
       </c>
     </row>
@@ -3796,12 +3830,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.129623+00:00</t>
+          <t>2026-08-21T19:25:07.359716+00:00</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3857,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.133669+00:00</t>
+          <t>2026-08-21T19:25:07.368019+00:00</t>
         </is>
       </c>
     </row>
@@ -3850,12 +3884,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.193447+00:00</t>
+          <t>2026-08-21T19:25:07.418159+00:00</t>
         </is>
       </c>
     </row>
@@ -3877,12 +3911,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.196182+00:00</t>
+          <t>2026-08-21T19:25:07.421987+00:00</t>
         </is>
       </c>
     </row>
@@ -3904,12 +3938,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.198380+00:00</t>
+          <t>2026-08-21T19:25:07.423967+00:00</t>
         </is>
       </c>
     </row>
@@ -3931,12 +3965,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.201158+00:00</t>
+          <t>2026-08-21T19:25:07.427644+00:00</t>
         </is>
       </c>
     </row>
@@ -3958,12 +3992,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.205851+00:00</t>
+          <t>2026-08-21T19:25:07.435543+00:00</t>
         </is>
       </c>
     </row>
@@ -3985,12 +4019,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.207864+00:00</t>
+          <t>2026-08-21T19:25:07.439494+00:00</t>
         </is>
       </c>
     </row>
@@ -4012,12 +4046,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:54.688143+00:00</t>
+          <t>2026-08-21T19:25:09.280124+00:00</t>
         </is>
       </c>
     </row>
@@ -4039,12 +4073,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:54.691029+00:00</t>
+          <t>2026-08-21T19:25:09.282484+00:00</t>
         </is>
       </c>
     </row>
@@ -4066,12 +4100,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:54.693294+00:00</t>
+          <t>2026-08-21T19:25:09.287791+00:00</t>
         </is>
       </c>
     </row>
@@ -4093,12 +4127,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:54.695287+00:00</t>
+          <t>2026-08-21T19:25:09.291706+00:00</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4154,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:54.697324+00:00</t>
+          <t>2026-08-21T19:25:09.293600+00:00</t>
         </is>
       </c>
     </row>
@@ -4147,51 +4181,51 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:54.699323+00:00</t>
+          <t>2026-08-21T19:25:09.295575+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>TFT-002B-CANDIDATE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>compiler/backends/finite_spectral_triple_tft002b.py::evaluate_tft002b</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.010302+00:00</t>
+          <t>2026-08-21T19:25:09.739288+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>COUPLING-MATRIX-C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/finite_spectral_triple_recovery_coupled.py</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -4201,24 +4235,24 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.218614+00:00</t>
+          <t>2026-08-21T19:25:17.188222+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/ir/finite_spectral_triple_tft002b_and_coupled_recovery.py</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4228,78 +4262,78 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.220930+00:00</t>
+          <t>2026-08-21T19:25:17.191957+00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>PHASE3-KO-DIMENSION-SIGN-SCAN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/historical/finite_spectral_triple_tft002b_and_coupled_recovery.py</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.223178+00:00</t>
+          <t>2026-08-21T19:25:17.200602+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>spec section 10</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.225488+00:00</t>
+          <t>2026-08-21T19:24:56.151479+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4309,78 +4343,78 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.402217+00:00</t>
+          <t>2026-08-21T19:24:56.447746+00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.406464+00:00</t>
+          <t>2026-08-21T19:24:56.451731+00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>compiler/backends/ollivier_ricci.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.810643+00:00</t>
+          <t>2026-08-21T19:24:56.455650+00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4390,159 +4424,159 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.465614+00:00</t>
+          <t>2026-08-21T19:24:56.462097+00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.651068+00:00</t>
+          <t>2026-08-21T19:24:56.640022+00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.832840+00:00</t>
+          <t>2026-08-21T19:24:56.643859+00:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/ollivier_ricci.py</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:51.848012+00:00</t>
+          <t>2026-08-21T19:24:57.069495+00:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.131664+00:00</t>
+          <t>2026-08-21T19:24:57.640334+00:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>T-DIRAC-SQUARED-FINITE</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:52.203741+00:00</t>
+          <t>2026-08-21T19:25:01.173954+00:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_recovery.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4552,240 +4586,240 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:54.701337+00:00</t>
+          <t>2026-08-21T19:25:07.131397+00:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.412674+00:00</t>
+          <t>2026-08-21T19:25:07.143226+00:00</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_flow.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:41.414909+00:00</t>
+          <t>2026-08-21T19:25:07.366107+00:00</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.366040+00:00</t>
+          <t>2026-08-21T19:25:07.430977+00:00</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+          <t>compiler/backends/finite_spectral_triple_recovery.py</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.369200+00:00</t>
+          <t>2026-08-21T19:25:09.299578+00:00</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>T-TFT002B-EVALUATION</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+          <t>compiler/backends/finite_spectral_triple_tft002b.py</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.371662+00:00</t>
+          <t>2026-08-21T19:25:09.741613+00:00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+          <t>compiler/backends/finite_spectral_triple_recovery_coupled.py</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.374744+00:00</t>
+          <t>2026-08-21T19:25:17.195672+00:00</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.377306+00:00</t>
+          <t>2026-08-21T19:24:56.651985+00:00</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+          <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.380125+00:00</t>
+          <t>2026-08-21T19:24:56.654658+00:00</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4795,24 +4829,24 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.383033+00:00</t>
+          <t>2026-08-21T19:24:57.560199+00:00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4822,24 +4856,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.385179+00:00</t>
+          <t>2026-08-21T19:24:57.562913+00:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4849,24 +4883,24 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.388141+00:00</t>
+          <t>2026-08-21T19:24:57.565141+00:00</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4876,24 +4910,24 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.390947+00:00</t>
+          <t>2026-08-21T19:24:57.567230+00:00</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4903,24 +4937,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.393374+00:00</t>
+          <t>2026-08-21T19:24:57.569206+00:00</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4930,24 +4964,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.395865+00:00</t>
+          <t>2026-08-21T19:24:57.571333+00:00</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4957,24 +4991,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.398939+00:00</t>
+          <t>2026-08-21T19:24:57.573357+00:00</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4984,24 +5018,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.401341+00:00</t>
+          <t>2026-08-21T19:24:57.575503+00:00</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5011,24 +5045,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.404007+00:00</t>
+          <t>2026-08-21T19:24:57.577332+00:00</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5038,24 +5072,24 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.406989+00:00</t>
+          <t>2026-08-21T19:24:57.579253+00:00</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5065,24 +5099,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.409456+00:00</t>
+          <t>2026-08-21T19:24:57.581275+00:00</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5092,24 +5126,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.411777+00:00</t>
+          <t>2026-08-21T19:24:57.583250+00:00</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5119,24 +5153,24 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.414609+00:00</t>
+          <t>2026-08-21T19:24:57.585149+00:00</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5146,24 +5180,24 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.416919+00:00</t>
+          <t>2026-08-21T19:24:57.587068+00:00</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5173,24 +5207,24 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.419730+00:00</t>
+          <t>2026-08-21T19:24:57.588870+00:00</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5200,24 +5234,24 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.422551+00:00</t>
+          <t>2026-08-21T19:24:57.590814+00:00</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5227,24 +5261,24 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.424675+00:00</t>
+          <t>2026-08-21T19:24:57.592647+00:00</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5254,24 +5288,24 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.427371+00:00</t>
+          <t>2026-08-21T19:24:57.594744+00:00</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5281,24 +5315,24 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.430133+00:00</t>
+          <t>2026-08-21T19:24:57.596736+00:00</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5308,24 +5342,24 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.432174+00:00</t>
+          <t>2026-08-21T19:24:57.598965+00:00</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5335,24 +5369,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.434989+00:00</t>
+          <t>2026-08-21T19:24:57.600875+00:00</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5362,24 +5396,24 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.437133+00:00</t>
+          <t>2026-08-21T19:24:57.603386+00:00</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5389,120 +5423,282 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.439303+00:00</t>
+          <t>2026-08-21T19:24:57.605443+00:00</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:42.463455+00:00</t>
+          <t>2026-08-21T19:24:57.607374+00:00</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.359547+00:00</t>
+          <t>2026-08-21T19:24:57.609290+00:00</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>6147d4a42e08</t>
+          <t>379096514980</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-08-21T03:59:45.361809+00:00</t>
+          <t>2026-08-21T19:24:57.611242+00:00</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>379096514980</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-08-21T19:24:57.613180+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>379096514980</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-08-21T19:24:57.615222+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>379096514980</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-08-21T19:24:57.617243+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>379096514980</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-08-21T19:24:57.638574+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>379096514980</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-08-21T19:25:00.863463+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>379096514980</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2026-08-21T19:25:00.865616+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>6147d4a42e08</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>2026-08-21T03:59:45.383950+00:00</t>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>379096514980</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-08-21T19:25:00.891760+00:00</t>
         </is>
       </c>
     </row>
@@ -6836,7 +7032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8938,34 +9134,34 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>TFT-002B-CANDIDATE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['H2-GRAPH-CONTROL']</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>COUPLING-MATRIX-C</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8975,19 +9171,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>['TFT-002B-CANDIDATE']</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8997,36 +9193,36 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['TFT-002B-CANDIDATE', 'COUPLING-MATRIX-C']</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>PHASE3-KO-DIMENSION-SIGN-SCAN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['COUPLED-RECOVERY-CERTIFICATION']</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9036,19 +9232,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9063,14 +9259,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['GRAPH-G-SEED']</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9080,19 +9276,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9102,19 +9298,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9129,14 +9325,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9146,19 +9342,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>['CONTROL-FLAT-2D']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9168,19 +9364,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>['CONTROL-MANIFOLD-S2']</t>
+          <t>['DIFFUSION-DISTANCE']</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9190,19 +9386,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9212,19 +9408,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-GRADING-GAMMA_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>T-DIRAC-SQUARED-FINITE</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9234,19 +9430,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>['FINITE-DIRAC-D_B']</t>
+          <t>['CONTROL-FLAT-2D']</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9261,146 +9457,146 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>['FINITE-DIRAC-D_B', 'DOUBLED-HILBERT-SPACE-H_F-PRIME', 'FINITE-ALGEBRA-A_F-PRIME', 'FINITE-GRADING-GAMMA_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME']</t>
+          <t>['CONTROL-MANIFOLD-S2']</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-GRADING-GAMMA_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['FINITE-DIRAC-D_B', 'DOUBLED-HILBERT-SPACE-H_F-PRIME', 'FINITE-ALGEBRA-A_F-PRIME', 'FINITE-GRADING-GAMMA_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME']</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>T-TFT002B-EVALUATION</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['H2-GRAPH-CONTROL']</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['TFT-002B-CANDIDATE', 'COUPLING-MATRIX-C']</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9410,19 +9606,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9432,19 +9628,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9466,7 +9662,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9488,7 +9684,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9510,7 +9706,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9532,7 +9728,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9554,7 +9750,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9576,7 +9772,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9598,7 +9794,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9620,7 +9816,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9642,7 +9838,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9664,7 +9860,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9686,7 +9882,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9708,7 +9904,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9730,7 +9926,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9752,7 +9948,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9774,7 +9970,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9796,7 +9992,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9818,7 +10014,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9840,7 +10036,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9862,7 +10058,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9884,7 +10080,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9906,7 +10102,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9928,7 +10124,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9950,7 +10146,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9960,19 +10156,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>['S3-CURVATURE-CLOSURE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9982,19 +10178,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10004,32 +10200,164 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>['S3-CURVATURE-CLOSURE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -10530,7 +10858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11068,6 +11396,30 @@
       <c r="B39" t="inlineStr">
         <is>
           <t>one component of a recovery candidate (doubled Hilbert space, algebra, grading, real structure) built after an original candidate's certification genuinely failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>evaluated_dirac_candidate</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>a Dirac-type operator candidate with explicit invariant checks, promoted to canonical only if the checks pass and no dependency regression is introduced</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>coupled_recovery_component</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>a component of the nontrivially-coupled doubled recovery (Phase 2), extending the uncoupled recovery with a genuine inter-copy coupling</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13657,6 +14009,114 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TFT-002B-CANDIDATE</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>evaluated_dirac_candidate</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>['H2-GRAPH-CONTROL']</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>COUPLING-MATRIX-C</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>coupled_recovery_component</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>['TFT-002B-CANDIDATE']</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>coupled_recovery_component</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>['TFT-002B-CANDIDATE', 'COUPLING-MATRIX-C']</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PHASE3-KO-DIMENSION-SIGN-SCAN</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>coupled_recovery_component</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>['COUPLED-RECOVERY-CERTIFICATION']</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13668,7 +14128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14188,6 +14648,70 @@
       <c r="F16" t="inlineStr">
         <is>
           <t>['FINITE-DIRAC-D_B', 'DOUBLED-HILBERT-SPACE-H_F-PRIME', 'FINITE-ALGEBRA-A_F-PRIME', 'FINITE-GRADING-GAMMA_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME']</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T-TFT002B-EVALUATION</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H2-GRAPH-CONTROL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TFT-002B-CANDIDATE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>build the 3-graded Hodge-Dirac operator at full scale (n=200) and check self-adjointness, grading axioms, exact square, and comparison against D_B</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>['H2-GRAPH-CONTROL']</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TFT-002B-CANDIDATE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>self-adjointness, grading, real-structure-sign, and first-order-condition checks against the DOUBLED, NONTRIVIALLY-COUPLED candidate over TFT-002B</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>['TFT-002B-CANDIDATE', 'COUPLING-MATRIX-C']</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B122"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16538,79 +17062,79 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>TFT-002B-CANDIDATE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GRAPH-G-SEED</t>
+          <t>H2-GRAPH-CONTROL</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>COUPLING-MATRIX-C</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>TFT-002B-CANDIDATE</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>TFT-002B-CANDIDATE</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>COUPLING-MATRIX-C</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>PHASE3-KO-DIMENSION-SIGN-SCAN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DIFFUSION-DISTANCE</t>
+          <t>GRAPH-G-SEED</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -16622,115 +17146,115 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CONTROL-FLAT-2D</t>
+          <t>HEAT-FLOW-R</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CONTROL-MANIFOLD-S2</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>DIFFUSION-DISTANCE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FINITE-DIRAC-D_B</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FINITE-ALGEBRA-A_F</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FINITE-GRADING-GAMMA_F</t>
+          <t>CONTROL-FLAT-2D</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FINITE-REAL-STRUCTURE-J_F</t>
+          <t>CONTROL-MANIFOLD-S2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>T-DIRAC-SQUARED-FINITE</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FINITE-DIRAC-D_B</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -16742,106 +17266,202 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
+          <t>FINITE-ALGEBRA-A_F</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FINITE-ALGEBRA-A_F-PRIME</t>
+          <t>FINITE-GRADING-GAMMA_F</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>FINITE-ALGEBRA-A_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>T-TFT002B-EVALUATION</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>H2-GRAPH-CONTROL</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TFT-002B-CANDIDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>COUPLING-MATRIX-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
@@ -16858,7 +17478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B113"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17852,67 +18472,67 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>TFT-002B-CANDIDATE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>PROMOTED: all required invariants (self-adjointness, both grading axioms, exact square = full graded Hodge Laplacian) hold at full scale (n=200), the operator genuinely differs from D_B's restricted square (confirming the audit finding was real, not merely theoretical), and no dependency regression is introduced -- D_B itself is untouched (new claim id, not an overwrite) and every existing chainlink that depends on D_B's own square (block-diagonal, E_B=0) remains valid for D_B specifically; TFT-002B is registered as an independent, additional candidate.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Scanned (epsilon,epsilon',epsilon'') for four sign conventions of J' (symmetric +1/+1, symmetric -1/-1, and the two asymmetric mixed conventions). RESULT: the two symmetric conventions both give (+1,+1,+1) exactly (residual 0.0, first-order condition holds). The two ASYMMETRIC conventions give epsilon=epsilon''=-1 but epsilon' UNDETERMINED (JD_ppJ^-1 is neither +D_pp nor -D_pp exactly) -- because C is genuinely complex (carries the i*mu factor) while D3 is real, so C and D3 transform differently under an asymmetric J, unlike the uncoupled Phase 2 case where D_F'=D_F(+)D_F was entirely real and every sign convention gave a clean, uniform triple. This is reported as-is: only (+1,+1,+1) is a clean, fully-determined signature for this coupled construction.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>This project does NOT attempt to 'drive the system into compliance with Connes' canonical table for the physical KO=6 sector' by further tuning J' parameters. Doing so would require either (a) restating Connes' full (epsilon,epsilon',epsilon'') -&gt; KO-mod-8 classification table from memory to know what target to fit to -- explicitly refused by this project's own established policy (ko_dimension.py's module docstring: 'mis-deriving it from memory would be exactly the kind of unverified claim this module exists to avoid'), or (b) tuning parameters specifically to match a memorized/assumed target rather than reporting what the construction naturally produces -- the general failure mode this entire project's discipline exists to prevent. The honest state is: this construction's natural signs are (+1,+1,+1); whether that matches or fails to match KO=6 mod 8 remains OPEN, exactly as ncg_branch.py and h2_spectral_triple_locality_check already left it for every prior candidate in this corpus.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>PHASE3-KO-DIMENSION-SIGN-SCAN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>This project does NOT attempt to 'drive the system into compliance with Connes' canonical table for the physical KO=6 sector' by further tuning J' parameters. Doing so would require either (a) restating Connes' full (epsilon,epsilon',epsilon'') -&gt; KO-mod-8 classification table from memory to know what target to fit to -- explicitly refused by this project's own established policy (ko_dimension.py's module docstring: 'mis-deriving it from memory would be exactly the kind of unverified claim this module exists to avoid'), or (b) tuning parameters specifically to match a memorized/assumed target rather than reporting what the construction naturally produces -- the general failure mode this entire project's discipline exists to prevent. The honest state is: this construction's natural signs are (+1,+1,+1); whether that matches or fails to match KO=6 mod 8 remains OPEN, exactly as ncg_branch.py and h2_spectral_triple_locality_check already left it for every prior candidate in this corpus.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -17924,7 +18544,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -17936,7 +18556,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -17948,7 +18568,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -17960,7 +18580,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -17972,67 +18592,67 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -18044,55 +18664,55 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -18104,31 +18724,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -18140,19 +18760,19 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -18164,58 +18784,106 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B117" t="inlineStr">
         <is>
           <t>The counterfactual manuscript's specific restatement of the gauge-closure claim (COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8).</t>
         </is>
@@ -18232,7 +18900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18620,6 +19288,60 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PROOF-T-TFT002B-EVALUATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>T-TFT002B-EVALUATION</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>build the 3-graded Hodge-Dirac operator at full scale (n=200) and check self-adjointness, grading axioms, exact square, and comparison against D_B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>numpy exact linear algebra at n=200, all invariants checked directly</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PROOF-T-COUPLED-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>self-adjointness, grading, real-structure-sign, and first-order-condition checks against the DOUBLED, NONTRIVIALLY-COUPLED candidate over TFT-002B</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>numpy exact linear algebra at n=200 (genuine complex random f,g,C) plus sympy symbolic-general confirmation (f,g,coupling weights all free symbols) that pi(f) C pi(g) vanishes identically</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18631,7 +19353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19564,6 +20286,50 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CALC-TFT002B-EVALUATION</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>dirac_candidate_invariant_evaluation</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>{'n_triangles': 600}</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CALC-COUPLED-RECOVERY-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>nontrivially_coupled_doubled_spectral_triple_recovery</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>{'mechanism': "The verified Hilbert-doubling mechanism was re-applied over TFT-002B, this time with a genuinely nonzero, non-proportional Hermitian inter-copy coupling C = i*mu*(independently-weighted copy of the same (d1,d2) incidence pattern) -- the natural minimal choice satisfying the grading constraint {C,gamma3}=0 (itself required for {D_F'',gamma_F''}=0 to hold at all; derived, not assumed). Self-adjointness, both grading axioms, and the first-order condition ALL hold exactly (residual 0.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1670,12 +1670,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.154621+00:00</t>
+          <t>2026-08-21T20:17:14.864356+00:00</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.157123+00:00</t>
+          <t>2026-08-21T20:17:14.866689+00:00</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.159525+00:00</t>
+          <t>2026-08-21T20:17:14.868765+00:00</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.161801+00:00</t>
+          <t>2026-08-21T20:17:14.870877+00:00</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.163720+00:00</t>
+          <t>2026-08-21T20:17:14.872890+00:00</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.166106+00:00</t>
+          <t>2026-08-21T20:17:14.874907+00:00</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.168374+00:00</t>
+          <t>2026-08-21T20:17:14.876820+00:00</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.170531+00:00</t>
+          <t>2026-08-21T20:17:14.878925+00:00</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.172495+00:00</t>
+          <t>2026-08-21T20:17:14.880978+00:00</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.174611+00:00</t>
+          <t>2026-08-21T20:17:14.882989+00:00</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.176467+00:00</t>
+          <t>2026-08-21T20:17:14.884960+00:00</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.178859+00:00</t>
+          <t>2026-08-21T20:17:14.887056+00:00</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.181148+00:00</t>
+          <t>2026-08-21T20:17:14.888924+00:00</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.183253+00:00</t>
+          <t>2026-08-21T20:17:14.891004+00:00</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.185062+00:00</t>
+          <t>2026-08-21T20:17:14.892894+00:00</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.187573+00:00</t>
+          <t>2026-08-21T20:17:14.894819+00:00</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.189525+00:00</t>
+          <t>2026-08-21T20:17:14.896625+00:00</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.192047+00:00</t>
+          <t>2026-08-21T20:17:14.898419+00:00</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2156,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.194073+00:00</t>
+          <t>2026-08-21T20:17:14.900221+00:00</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.195966+00:00</t>
+          <t>2026-08-21T20:17:14.902239+00:00</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.198190+00:00</t>
+          <t>2026-08-21T20:17:14.904040+00:00</t>
         </is>
       </c>
     </row>
@@ -2237,12 +2237,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.432408+00:00</t>
+          <t>2026-08-21T20:17:15.014910+00:00</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2264,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.436828+00:00</t>
+          <t>2026-08-21T20:17:15.017273+00:00</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2291,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.440005+00:00</t>
+          <t>2026-08-21T20:17:15.019361+00:00</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.443962+00:00</t>
+          <t>2026-08-21T20:17:15.021290+00:00</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2345,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.632841+00:00</t>
+          <t>2026-08-21T20:17:15.216318+00:00</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.635451+00:00</t>
+          <t>2026-08-21T20:17:15.219157+00:00</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.066772+00:00</t>
+          <t>2026-08-21T20:17:15.637115+00:00</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.471460+00:00</t>
+          <t>2026-08-21T20:17:16.052301+00:00</t>
         </is>
       </c>
     </row>
@@ -2453,12 +2453,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.473985+00:00</t>
+          <t>2026-08-21T20:17:16.054794+00:00</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.476060+00:00</t>
+          <t>2026-08-21T20:17:16.056849+00:00</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2507,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.478109+00:00</t>
+          <t>2026-08-21T20:17:16.058766+00:00</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.480101+00:00</t>
+          <t>2026-08-21T20:17:16.060609+00:00</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.482048+00:00</t>
+          <t>2026-08-21T20:17:16.062534+00:00</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.483844+00:00</t>
+          <t>2026-08-21T20:17:16.064599+00:00</t>
         </is>
       </c>
     </row>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.485738+00:00</t>
+          <t>2026-08-21T20:17:16.066589+00:00</t>
         </is>
       </c>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.487570+00:00</t>
+          <t>2026-08-21T20:17:16.068477+00:00</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.489391+00:00</t>
+          <t>2026-08-21T20:17:16.070367+00:00</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.629195+00:00</t>
+          <t>2026-08-21T20:17:16.211781+00:00</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2723,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.631220+00:00</t>
+          <t>2026-08-21T20:17:16.213677+00:00</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.633173+00:00</t>
+          <t>2026-08-21T20:17:16.215621+00:00</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.635082+00:00</t>
+          <t>2026-08-21T20:17:16.217664+00:00</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.636805+00:00</t>
+          <t>2026-08-21T20:17:16.219469+00:00</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.385367+00:00</t>
+          <t>2026-08-21T20:17:18.172147+00:00</t>
         </is>
       </c>
     </row>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.388048+00:00</t>
+          <t>2026-08-21T20:17:18.175341+00:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.391857+00:00</t>
+          <t>2026-08-21T20:17:18.179062+00:00</t>
         </is>
       </c>
     </row>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.396343+00:00</t>
+          <t>2026-08-21T20:17:18.183045+00:00</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.402130+00:00</t>
+          <t>2026-08-21T20:17:18.189477+00:00</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.404894+00:00</t>
+          <t>2026-08-21T20:17:18.191528+00:00</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.408060+00:00</t>
+          <t>2026-08-21T20:17:18.195175+00:00</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.411713+00:00</t>
+          <t>2026-08-21T20:17:18.201548+00:00</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.418148+00:00</t>
+          <t>2026-08-21T20:17:18.203798+00:00</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3074,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.420090+00:00</t>
+          <t>2026-08-21T20:17:18.207336+00:00</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.426071+00:00</t>
+          <t>2026-08-21T20:17:18.213524+00:00</t>
         </is>
       </c>
     </row>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.427985+00:00</t>
+          <t>2026-08-21T20:17:18.217542+00:00</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3155,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.434088+00:00</t>
+          <t>2026-08-21T20:17:18.223058+00:00</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3182,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.436177+00:00</t>
+          <t>2026-08-21T20:17:18.227128+00:00</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3209,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.439617+00:00</t>
+          <t>2026-08-21T20:17:18.233454+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.860520+00:00</t>
+          <t>2026-08-21T20:17:18.686893+00:00</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3263,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.871089+00:00</t>
+          <t>2026-08-21T20:17:18.697736+00:00</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.875076+00:00</t>
+          <t>2026-08-21T20:17:18.701746+00:00</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.882142+00:00</t>
+          <t>2026-08-21T20:17:18.709058+00:00</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.888017+00:00</t>
+          <t>2026-08-21T20:17:18.715380+00:00</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3371,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.895714+00:00</t>
+          <t>2026-08-21T20:17:18.723052+00:00</t>
         </is>
       </c>
     </row>
@@ -3398,12 +3398,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.902105+00:00</t>
+          <t>2026-08-21T20:17:18.729498+00:00</t>
         </is>
       </c>
     </row>
@@ -3425,12 +3425,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.904323+00:00</t>
+          <t>2026-08-21T20:17:18.731370+00:00</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:01.171465+00:00</t>
+          <t>2026-08-21T20:17:19.016556+00:00</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.128754+00:00</t>
+          <t>2026-08-21T20:17:25.075472+00:00</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.133963+00:00</t>
+          <t>2026-08-21T20:17:25.080610+00:00</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3533,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.141103+00:00</t>
+          <t>2026-08-21T20:17:25.088437+00:00</t>
         </is>
       </c>
     </row>
@@ -3560,12 +3560,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.145110+00:00</t>
+          <t>2026-08-21T20:17:25.092476+00:00</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.147141+00:00</t>
+          <t>2026-08-21T20:17:25.094764+00:00</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.148904+00:00</t>
+          <t>2026-08-21T20:17:25.096728+00:00</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3641,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.150744+00:00</t>
+          <t>2026-08-21T20:17:25.098586+00:00</t>
         </is>
       </c>
     </row>
@@ -3668,12 +3668,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.152492+00:00</t>
+          <t>2026-08-21T20:17:25.100987+00:00</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.154399+00:00</t>
+          <t>2026-08-21T20:17:25.103014+00:00</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3722,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.156200+00:00</t>
+          <t>2026-08-21T20:17:25.105016+00:00</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.347476+00:00</t>
+          <t>2026-08-21T20:17:25.252148+00:00</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3776,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.350591+00:00</t>
+          <t>2026-08-21T20:17:25.255367+00:00</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.355692+00:00</t>
+          <t>2026-08-21T20:17:25.259093+00:00</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.359716+00:00</t>
+          <t>2026-08-21T20:17:25.263058+00:00</t>
         </is>
       </c>
     </row>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.368019+00:00</t>
+          <t>2026-08-21T20:17:25.271033+00:00</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3884,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.418159+00:00</t>
+          <t>2026-08-21T20:17:25.319636+00:00</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.421987+00:00</t>
+          <t>2026-08-21T20:17:25.322088+00:00</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.423967+00:00</t>
+          <t>2026-08-21T20:17:25.327160+00:00</t>
         </is>
       </c>
     </row>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.427644+00:00</t>
+          <t>2026-08-21T20:17:25.331118+00:00</t>
         </is>
       </c>
     </row>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.435543+00:00</t>
+          <t>2026-08-21T20:17:25.339378+00:00</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.439494+00:00</t>
+          <t>2026-08-21T20:17:25.341526+00:00</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:09.280124+00:00</t>
+          <t>2026-08-21T20:17:27.314290+00:00</t>
         </is>
       </c>
     </row>
@@ -4073,12 +4073,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:09.282484+00:00</t>
+          <t>2026-08-21T20:17:27.319765+00:00</t>
         </is>
       </c>
     </row>
@@ -4100,12 +4100,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:09.287791+00:00</t>
+          <t>2026-08-21T20:17:27.323036+00:00</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4127,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:09.291706+00:00</t>
+          <t>2026-08-21T20:17:27.327019+00:00</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:09.293600+00:00</t>
+          <t>2026-08-21T20:17:27.330958+00:00</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4181,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:09.295575+00:00</t>
+          <t>2026-08-21T20:17:27.335092+00:00</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4208,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:09.739288+00:00</t>
+          <t>2026-08-21T20:17:27.775915+00:00</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4235,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:17.188222+00:00</t>
+          <t>2026-08-21T20:17:34.874428+00:00</t>
         </is>
       </c>
     </row>
@@ -4262,12 +4262,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:17.191957+00:00</t>
+          <t>2026-08-21T20:17:34.876751+00:00</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:17.200602+00:00</t>
+          <t>2026-08-21T20:17:34.880386+00:00</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4316,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.151479+00:00</t>
+          <t>2026-08-21T20:17:14.861822+00:00</t>
         </is>
       </c>
     </row>
@@ -4343,12 +4343,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.447746+00:00</t>
+          <t>2026-08-21T20:17:15.023230+00:00</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.451731+00:00</t>
+          <t>2026-08-21T20:17:15.025127+00:00</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.455650+00:00</t>
+          <t>2026-08-21T20:17:15.027145+00:00</t>
         </is>
       </c>
     </row>
@@ -4424,12 +4424,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.462097+00:00</t>
+          <t>2026-08-21T20:17:15.029023+00:00</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4451,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.640022+00:00</t>
+          <t>2026-08-21T20:17:15.223223+00:00</t>
         </is>
       </c>
     </row>
@@ -4478,12 +4478,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.643859+00:00</t>
+          <t>2026-08-21T20:17:15.227376+00:00</t>
         </is>
       </c>
     </row>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.069495+00:00</t>
+          <t>2026-08-21T20:17:15.640401+00:00</t>
         </is>
       </c>
     </row>
@@ -4532,12 +4532,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.640334+00:00</t>
+          <t>2026-08-21T20:17:16.223323+00:00</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:01.173954+00:00</t>
+          <t>2026-08-21T20:17:19.018932+00:00</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.131397+00:00</t>
+          <t>2026-08-21T20:17:25.078422+00:00</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.143226+00:00</t>
+          <t>2026-08-21T20:17:25.090619+00:00</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.366107+00:00</t>
+          <t>2026-08-21T20:17:25.267043+00:00</t>
         </is>
       </c>
     </row>
@@ -4667,12 +4667,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:07.430977+00:00</t>
+          <t>2026-08-21T20:17:25.337497+00:00</t>
         </is>
       </c>
     </row>
@@ -4694,12 +4694,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:09.299578+00:00</t>
+          <t>2026-08-21T20:17:27.336880+00:00</t>
         </is>
       </c>
     </row>
@@ -4721,12 +4721,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:09.741613+00:00</t>
+          <t>2026-08-21T20:17:27.778387+00:00</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4748,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:17.195672+00:00</t>
+          <t>2026-08-21T20:17:34.878649+00:00</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4775,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.651985+00:00</t>
+          <t>2026-08-21T20:17:15.241935+00:00</t>
         </is>
       </c>
     </row>
@@ -4802,12 +4802,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:56.654658+00:00</t>
+          <t>2026-08-21T20:17:15.244013+00:00</t>
         </is>
       </c>
     </row>
@@ -4829,12 +4829,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.560199+00:00</t>
+          <t>2026-08-21T20:17:16.146768+00:00</t>
         </is>
       </c>
     </row>
@@ -4856,12 +4856,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.562913+00:00</t>
+          <t>2026-08-21T20:17:16.149042+00:00</t>
         </is>
       </c>
     </row>
@@ -4883,12 +4883,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.565141+00:00</t>
+          <t>2026-08-21T20:17:16.151116+00:00</t>
         </is>
       </c>
     </row>
@@ -4910,12 +4910,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.567230+00:00</t>
+          <t>2026-08-21T20:17:16.153015+00:00</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.569206+00:00</t>
+          <t>2026-08-21T20:17:16.155064+00:00</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.571333+00:00</t>
+          <t>2026-08-21T20:17:16.157111+00:00</t>
         </is>
       </c>
     </row>
@@ -4991,12 +4991,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.573357+00:00</t>
+          <t>2026-08-21T20:17:16.158997+00:00</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5018,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.575503+00:00</t>
+          <t>2026-08-21T20:17:16.160990+00:00</t>
         </is>
       </c>
     </row>
@@ -5045,12 +5045,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.577332+00:00</t>
+          <t>2026-08-21T20:17:16.162892+00:00</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.579253+00:00</t>
+          <t>2026-08-21T20:17:16.165127+00:00</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5099,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.581275+00:00</t>
+          <t>2026-08-21T20:17:16.167395+00:00</t>
         </is>
       </c>
     </row>
@@ -5126,12 +5126,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.583250+00:00</t>
+          <t>2026-08-21T20:17:16.169370+00:00</t>
         </is>
       </c>
     </row>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.585149+00:00</t>
+          <t>2026-08-21T20:17:16.171721+00:00</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.587068+00:00</t>
+          <t>2026-08-21T20:17:16.173737+00:00</t>
         </is>
       </c>
     </row>
@@ -5207,12 +5207,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.588870+00:00</t>
+          <t>2026-08-21T20:17:16.175853+00:00</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.590814+00:00</t>
+          <t>2026-08-21T20:17:16.177846+00:00</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.592647+00:00</t>
+          <t>2026-08-21T20:17:16.179771+00:00</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.594744+00:00</t>
+          <t>2026-08-21T20:17:16.181988+00:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.596736+00:00</t>
+          <t>2026-08-21T20:17:16.183757+00:00</t>
         </is>
       </c>
     </row>
@@ -5342,12 +5342,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.598965+00:00</t>
+          <t>2026-08-21T20:17:16.185678+00:00</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.600875+00:00</t>
+          <t>2026-08-21T20:17:16.187503+00:00</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.603386+00:00</t>
+          <t>2026-08-21T20:17:16.189252+00:00</t>
         </is>
       </c>
     </row>
@@ -5423,12 +5423,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.605443+00:00</t>
+          <t>2026-08-21T20:17:16.191055+00:00</t>
         </is>
       </c>
     </row>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.607374+00:00</t>
+          <t>2026-08-21T20:17:16.192873+00:00</t>
         </is>
       </c>
     </row>
@@ -5477,12 +5477,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.609290+00:00</t>
+          <t>2026-08-21T20:17:16.194723+00:00</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.611242+00:00</t>
+          <t>2026-08-21T20:17:16.196586+00:00</t>
         </is>
       </c>
     </row>
@@ -5531,12 +5531,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.613180+00:00</t>
+          <t>2026-08-21T20:17:16.198532+00:00</t>
         </is>
       </c>
     </row>
@@ -5558,12 +5558,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.615222+00:00</t>
+          <t>2026-08-21T20:17:16.200766+00:00</t>
         </is>
       </c>
     </row>
@@ -5585,12 +5585,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.617243+00:00</t>
+          <t>2026-08-21T20:17:16.202983+00:00</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-08-21T19:24:57.638574+00:00</t>
+          <t>2026-08-21T20:17:16.221488+00:00</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.863463+00:00</t>
+          <t>2026-08-21T20:17:18.689258+00:00</t>
         </is>
       </c>
     </row>
@@ -5666,12 +5666,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.865616+00:00</t>
+          <t>2026-08-21T20:17:18.691346+00:00</t>
         </is>
       </c>
     </row>
@@ -5693,12 +5693,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>379096514980</t>
+          <t>80fba4db6b95</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-08-21T19:25:00.891760+00:00</t>
+          <t>2026-08-21T20:17:18.719065+00:00</t>
         </is>
       </c>
     </row>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1277,6 +1277,40 @@
       <c r="C44" t="inlineStr">
         <is>
           <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CALC-COUPLED-RECOVERY-INNER-FLUCTUATION</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>{'well_posed': True}</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CALC-COUPLED-RECOVERY-FINITE-MOMENTS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>{'well_posed': True, 'max_imag_residual': 1.6315084125746656e-13}</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1670,12 +1704,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.864356+00:00</t>
+          <t>2026-08-21T21:17:12.828145+00:00</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1731,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.866689+00:00</t>
+          <t>2026-08-21T21:17:12.830634+00:00</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1758,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.868765+00:00</t>
+          <t>2026-08-21T21:17:12.832675+00:00</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1785,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.870877+00:00</t>
+          <t>2026-08-21T21:17:12.834641+00:00</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1812,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.872890+00:00</t>
+          <t>2026-08-21T21:17:12.836476+00:00</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1839,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.874907+00:00</t>
+          <t>2026-08-21T21:17:12.838434+00:00</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1866,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.876820+00:00</t>
+          <t>2026-08-21T21:17:12.840440+00:00</t>
         </is>
       </c>
     </row>
@@ -1859,12 +1893,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.878925+00:00</t>
+          <t>2026-08-21T21:17:12.842466+00:00</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1920,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.880978+00:00</t>
+          <t>2026-08-21T21:17:12.844405+00:00</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1947,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.882989+00:00</t>
+          <t>2026-08-21T21:17:12.846375+00:00</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1974,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.884960+00:00</t>
+          <t>2026-08-21T21:17:12.848133+00:00</t>
         </is>
       </c>
     </row>
@@ -1967,12 +2001,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.887056+00:00</t>
+          <t>2026-08-21T21:17:12.850099+00:00</t>
         </is>
       </c>
     </row>
@@ -1994,12 +2028,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.888924+00:00</t>
+          <t>2026-08-21T21:17:12.851899+00:00</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2055,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.891004+00:00</t>
+          <t>2026-08-21T21:17:12.853782+00:00</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2082,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.892894+00:00</t>
+          <t>2026-08-21T21:17:12.855911+00:00</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2109,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.894819+00:00</t>
+          <t>2026-08-21T21:17:12.857944+00:00</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2136,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.896625+00:00</t>
+          <t>2026-08-21T21:17:12.859817+00:00</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2163,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.898419+00:00</t>
+          <t>2026-08-21T21:17:12.861746+00:00</t>
         </is>
       </c>
     </row>
@@ -2156,12 +2190,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.900221+00:00</t>
+          <t>2026-08-21T21:17:12.863603+00:00</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2217,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.902239+00:00</t>
+          <t>2026-08-21T21:17:12.865510+00:00</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2244,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.904040+00:00</t>
+          <t>2026-08-21T21:17:12.867725+00:00</t>
         </is>
       </c>
     </row>
@@ -2237,12 +2271,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.014910+00:00</t>
+          <t>2026-08-21T21:17:12.982949+00:00</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2298,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.017273+00:00</t>
+          <t>2026-08-21T21:17:12.985573+00:00</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2325,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.019361+00:00</t>
+          <t>2026-08-21T21:17:12.987488+00:00</t>
         </is>
       </c>
     </row>
@@ -2318,12 +2352,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.021290+00:00</t>
+          <t>2026-08-21T21:17:12.989220+00:00</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2379,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.216318+00:00</t>
+          <t>2026-08-21T21:17:13.112187+00:00</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2406,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.219157+00:00</t>
+          <t>2026-08-21T21:17:13.114829+00:00</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2433,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.637115+00:00</t>
+          <t>2026-08-21T21:17:13.520999+00:00</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2460,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.052301+00:00</t>
+          <t>2026-08-21T21:17:13.930195+00:00</t>
         </is>
       </c>
     </row>
@@ -2453,12 +2487,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.054794+00:00</t>
+          <t>2026-08-21T21:17:13.932723+00:00</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2514,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.056849+00:00</t>
+          <t>2026-08-21T21:17:13.935448+00:00</t>
         </is>
       </c>
     </row>
@@ -2507,12 +2541,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.058766+00:00</t>
+          <t>2026-08-21T21:17:13.937547+00:00</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2568,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.060609+00:00</t>
+          <t>2026-08-21T21:17:13.940154+00:00</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2595,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.062534+00:00</t>
+          <t>2026-08-21T21:17:13.942189+00:00</t>
         </is>
       </c>
     </row>
@@ -2588,12 +2622,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.064599+00:00</t>
+          <t>2026-08-21T21:17:13.944140+00:00</t>
         </is>
       </c>
     </row>
@@ -2615,12 +2649,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.066589+00:00</t>
+          <t>2026-08-21T21:17:13.946609+00:00</t>
         </is>
       </c>
     </row>
@@ -2642,12 +2676,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.068477+00:00</t>
+          <t>2026-08-21T21:17:13.948462+00:00</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2703,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.070367+00:00</t>
+          <t>2026-08-21T21:17:13.950862+00:00</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2730,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.211781+00:00</t>
+          <t>2026-08-21T21:17:14.085287+00:00</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2757,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.213677+00:00</t>
+          <t>2026-08-21T21:17:14.087139+00:00</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2784,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.215621+00:00</t>
+          <t>2026-08-21T21:17:14.089093+00:00</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2811,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.217664+00:00</t>
+          <t>2026-08-21T21:17:14.091003+00:00</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2838,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.219469+00:00</t>
+          <t>2026-08-21T21:17:14.093007+00:00</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2865,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.172147+00:00</t>
+          <t>2026-08-21T21:17:15.976111+00:00</t>
         </is>
       </c>
     </row>
@@ -2858,12 +2892,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.175341+00:00</t>
+          <t>2026-08-21T21:17:15.979346+00:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2919,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.179062+00:00</t>
+          <t>2026-08-21T21:17:15.983181+00:00</t>
         </is>
       </c>
     </row>
@@ -2912,12 +2946,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.183045+00:00</t>
+          <t>2026-08-21T21:17:15.987124+00:00</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2973,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.189477+00:00</t>
+          <t>2026-08-21T21:17:15.993464+00:00</t>
         </is>
       </c>
     </row>
@@ -2966,12 +3000,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.191528+00:00</t>
+          <t>2026-08-21T21:17:15.995697+00:00</t>
         </is>
       </c>
     </row>
@@ -2993,12 +3027,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.195175+00:00</t>
+          <t>2026-08-21T21:17:15.999021+00:00</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3054,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.201548+00:00</t>
+          <t>2026-08-21T21:17:16.003064+00:00</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3081,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.203798+00:00</t>
+          <t>2026-08-21T21:17:16.007108+00:00</t>
         </is>
       </c>
     </row>
@@ -3074,12 +3108,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.207336+00:00</t>
+          <t>2026-08-21T21:17:16.010891+00:00</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3135,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.213524+00:00</t>
+          <t>2026-08-21T21:17:16.014913+00:00</t>
         </is>
       </c>
     </row>
@@ -3128,12 +3162,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.217542+00:00</t>
+          <t>2026-08-21T21:17:16.021461+00:00</t>
         </is>
       </c>
     </row>
@@ -3155,12 +3189,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.223058+00:00</t>
+          <t>2026-08-21T21:17:16.023344+00:00</t>
         </is>
       </c>
     </row>
@@ -3182,12 +3216,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.227128+00:00</t>
+          <t>2026-08-21T21:17:16.026939+00:00</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3243,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.233454+00:00</t>
+          <t>2026-08-21T21:17:16.030947+00:00</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3270,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.686893+00:00</t>
+          <t>2026-08-21T21:17:16.441989+00:00</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3297,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.697736+00:00</t>
+          <t>2026-08-21T21:17:16.452326+00:00</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3324,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.701746+00:00</t>
+          <t>2026-08-21T21:17:16.455842+00:00</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3351,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.709058+00:00</t>
+          <t>2026-08-21T21:17:16.462958+00:00</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3378,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.715380+00:00</t>
+          <t>2026-08-21T21:17:16.467200+00:00</t>
         </is>
       </c>
     </row>
@@ -3371,12 +3405,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.723052+00:00</t>
+          <t>2026-08-21T21:17:16.477483+00:00</t>
         </is>
       </c>
     </row>
@@ -3398,12 +3432,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.729498+00:00</t>
+          <t>2026-08-21T21:17:16.479492+00:00</t>
         </is>
       </c>
     </row>
@@ -3425,12 +3459,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.731370+00:00</t>
+          <t>2026-08-21T21:17:16.483118+00:00</t>
         </is>
       </c>
     </row>
@@ -3452,12 +3486,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:19.016556+00:00</t>
+          <t>2026-08-21T21:17:16.754738+00:00</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3513,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.075472+00:00</t>
+          <t>2026-08-21T21:17:22.662090+00:00</t>
         </is>
       </c>
     </row>
@@ -3506,12 +3540,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.080610+00:00</t>
+          <t>2026-08-21T21:17:22.667719+00:00</t>
         </is>
       </c>
     </row>
@@ -3533,12 +3567,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.088437+00:00</t>
+          <t>2026-08-21T21:17:22.674876+00:00</t>
         </is>
       </c>
     </row>
@@ -3560,12 +3594,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.092476+00:00</t>
+          <t>2026-08-21T21:17:22.679633+00:00</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3621,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.094764+00:00</t>
+          <t>2026-08-21T21:17:22.681555+00:00</t>
         </is>
       </c>
     </row>
@@ -3614,12 +3648,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.096728+00:00</t>
+          <t>2026-08-21T21:17:22.683867+00:00</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3675,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.098586+00:00</t>
+          <t>2026-08-21T21:17:22.685991+00:00</t>
         </is>
       </c>
     </row>
@@ -3668,12 +3702,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.100987+00:00</t>
+          <t>2026-08-21T21:17:22.688293+00:00</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3729,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.103014+00:00</t>
+          <t>2026-08-21T21:17:22.690247+00:00</t>
         </is>
       </c>
     </row>
@@ -3722,12 +3756,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.105016+00:00</t>
+          <t>2026-08-21T21:17:22.692521+00:00</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3783,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.252148+00:00</t>
+          <t>2026-08-21T21:17:22.883000+00:00</t>
         </is>
       </c>
     </row>
@@ -3776,12 +3810,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.255367+00:00</t>
+          <t>2026-08-21T21:17:22.885926+00:00</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3837,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.259093+00:00</t>
+          <t>2026-08-21T21:17:22.888378+00:00</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3864,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.263058+00:00</t>
+          <t>2026-08-21T21:17:22.890200+00:00</t>
         </is>
       </c>
     </row>
@@ -3857,12 +3891,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.271033+00:00</t>
+          <t>2026-08-21T21:17:22.893809+00:00</t>
         </is>
       </c>
     </row>
@@ -3884,12 +3918,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.319636+00:00</t>
+          <t>2026-08-21T21:17:22.935962+00:00</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3945,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.322088+00:00</t>
+          <t>2026-08-21T21:17:22.938399+00:00</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3972,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.327160+00:00</t>
+          <t>2026-08-21T21:17:22.940704+00:00</t>
         </is>
       </c>
     </row>
@@ -3965,12 +3999,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.331118+00:00</t>
+          <t>2026-08-21T21:17:22.942567+00:00</t>
         </is>
       </c>
     </row>
@@ -3992,12 +4026,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.339378+00:00</t>
+          <t>2026-08-21T21:17:22.946213+00:00</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4053,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.341526+00:00</t>
+          <t>2026-08-21T21:17:22.950906+00:00</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4080,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:27.314290+00:00</t>
+          <t>2026-08-21T21:17:24.939914+00:00</t>
         </is>
       </c>
     </row>
@@ -4073,12 +4107,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:27.319765+00:00</t>
+          <t>2026-08-21T21:17:24.942553+00:00</t>
         </is>
       </c>
     </row>
@@ -4100,12 +4134,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:27.323036+00:00</t>
+          <t>2026-08-21T21:17:24.944724+00:00</t>
         </is>
       </c>
     </row>
@@ -4127,12 +4161,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:27.327019+00:00</t>
+          <t>2026-08-21T21:17:24.946799+00:00</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4188,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:27.330958+00:00</t>
+          <t>2026-08-21T21:17:24.948925+00:00</t>
         </is>
       </c>
     </row>
@@ -4181,12 +4215,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:27.335092+00:00</t>
+          <t>2026-08-21T21:17:24.950947+00:00</t>
         </is>
       </c>
     </row>
@@ -4208,12 +4242,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:27.775915+00:00</t>
+          <t>2026-08-21T21:17:25.421780+00:00</t>
         </is>
       </c>
     </row>
@@ -4235,12 +4269,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:34.874428+00:00</t>
+          <t>2026-08-21T21:17:33.819683+00:00</t>
         </is>
       </c>
     </row>
@@ -4262,12 +4296,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:34.876751+00:00</t>
+          <t>2026-08-21T21:17:33.822125+00:00</t>
         </is>
       </c>
     </row>
@@ -4289,51 +4323,51 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:34.880386+00:00</t>
+          <t>2026-08-21T21:17:33.825806+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>spec section 10</t>
+          <t>compiler/backends/finite_spectral_triple_coupled_recovery_spectral_action.py</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:14.861822+00:00</t>
+          <t>2026-08-21T21:18:22.808650+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>SPECTRAL-ACTION-A0-A6-COUPLED-RECOVERY-B</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>compiler/backends/finite_spectral_triple_coupled_recovery_spectral_action.py</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4343,46 +4377,46 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.023230+00:00</t>
+          <t>2026-08-21T21:18:22.813898+00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>compiler/backends/pipeline_graph_heatflow.py</t>
+          <t>spec section 10</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.025127+00:00</t>
+          <t>2026-08-21T21:17:12.825582+00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4392,24 +4426,24 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.027145+00:00</t>
+          <t>2026-08-21T21:17:12.991144+00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4424,78 +4458,78 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.029023+00:00</t>
+          <t>2026-08-21T21:17:12.993070+00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.223223+00:00</t>
+          <t>2026-08-21T21:17:12.995019+00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>compiler/backends/diffusion_metric.py</t>
+          <t>compiler/backends/pipeline_graph_heatflow.py</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.227376+00:00</t>
+          <t>2026-08-21T21:17:12.996917+00:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>compiler/backends/ollivier_ricci.py</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4505,78 +4539,78 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.640401+00:00</t>
+          <t>2026-08-21T21:17:13.119242+00:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>compiler/backends/diffusion_metric.py</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.223323+00:00</t>
+          <t>2026-08-21T21:17:13.123146+00:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/ollivier_ricci.py</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:19.018932+00:00</t>
+          <t>2026-08-21T21:17:13.523780+00:00</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -4586,19 +4620,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.078422+00:00</t>
+          <t>2026-08-21T21:17:14.097220+00:00</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4613,132 +4647,132 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.090619+00:00</t>
+          <t>2026-08-21T21:17:16.757168+00:00</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.267043+00:00</t>
+          <t>2026-08-21T21:17:22.665181+00:00</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>T-DIRAC-SQUARED-FINITE</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
+          <t>compiler/backends/lichnerowicz_seeley_dewitt.py</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:25.337497+00:00</t>
+          <t>2026-08-21T21:17:22.677335+00:00</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_recovery.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:27.336880+00:00</t>
+          <t>2026-08-21T21:17:22.891993+00:00</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>T-TFT002B-EVALUATION</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_tft002b.py</t>
+          <t>compiler/backends/finite_spectral_triple_candidate.py</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:27.778387+00:00</t>
+          <t>2026-08-21T21:17:22.944400+00:00</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>T-COUPLED-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>compiler/backends/finite_spectral_triple_recovery_coupled.py</t>
+          <t>compiler/backends/finite_spectral_triple_recovery.py</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4748,51 +4782,51 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:34.878649+00:00</t>
+          <t>2026-08-21T21:17:24.952918+00:00</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-TFT002B-EVALUATION</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
+          <t>compiler/backends/finite_spectral_triple_tft002b.py</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.241935+00:00</t>
+          <t>2026-08-21T21:17:25.424244+00:00</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_flow.py</t>
+          <t>compiler/backends/finite_spectral_triple_recovery_coupled.py</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4802,132 +4836,132 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:15.244013+00:00</t>
+          <t>2026-08-21T21:17:33.824007+00:00</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-COUPLED-RECOVERY-INNER-FLUCTUATION</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
+          <t>compiler/backends/finite_spectral_triple_coupled_recovery_spectral_action.py</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.146768+00:00</t>
+          <t>2026-08-21T21:18:22.811831+00:00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-COUPLED-RECOVERY-SPECTRAL-ACTION</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
+          <t>compiler/backends/finite_spectral_triple_coupled_recovery_spectral_action.py</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.149042+00:00</t>
+          <t>2026-08-21T21:18:22.815687+00:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
+          <t>compiler/ir/executable_tests.py:_prove_laplacian_row_sum_zero</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.151116+00:00</t>
+          <t>2026-08-21T21:17:13.130990+00:00</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
+          <t>compiler/backends/heat_flow.py</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.153015+00:00</t>
+          <t>2026-08-21T21:17:13.132893+00:00</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-001</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4937,24 +4971,24 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.155064+00:00</t>
+          <t>2026-08-21T21:17:14.019588+00:00</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-002</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4964,24 +4998,24 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.157111+00:00</t>
+          <t>2026-08-21T21:17:14.022578+00:00</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-003</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4991,24 +5025,24 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.158997+00:00</t>
+          <t>2026-08-21T21:17:14.024683+00:00</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-004</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5018,24 +5052,24 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.160990+00:00</t>
+          <t>2026-08-21T21:17:14.026824+00:00</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-005</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5045,24 +5079,24 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.162892+00:00</t>
+          <t>2026-08-21T21:17:14.028807+00:00</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-006</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5072,24 +5106,24 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.165127+00:00</t>
+          <t>2026-08-21T21:17:14.031133+00:00</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-007</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5099,24 +5133,24 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.167395+00:00</t>
+          <t>2026-08-21T21:17:14.033114+00:00</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-008</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5126,24 +5160,24 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.169370+00:00</t>
+          <t>2026-08-21T21:17:14.035489+00:00</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-009</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5153,24 +5187,24 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.171721+00:00</t>
+          <t>2026-08-21T21:17:14.037279+00:00</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-010</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5180,24 +5214,24 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.173737+00:00</t>
+          <t>2026-08-21T21:17:14.039222+00:00</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-011</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5207,24 +5241,24 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.175853+00:00</t>
+          <t>2026-08-21T21:17:14.041198+00:00</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-012</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5234,24 +5268,24 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.177846+00:00</t>
+          <t>2026-08-21T21:17:14.043607+00:00</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-013</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5261,24 +5295,24 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.179771+00:00</t>
+          <t>2026-08-21T21:17:14.045521+00:00</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-014</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5288,24 +5322,24 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.181988+00:00</t>
+          <t>2026-08-21T21:17:14.047471+00:00</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-015</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5315,24 +5349,24 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.183757+00:00</t>
+          <t>2026-08-21T21:17:14.049231+00:00</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-016</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5342,24 +5376,24 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.185678+00:00</t>
+          <t>2026-08-21T21:17:14.051248+00:00</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-017</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -5369,24 +5403,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.187503+00:00</t>
+          <t>2026-08-21T21:17:14.053637+00:00</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-018</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5396,24 +5430,24 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.189252+00:00</t>
+          <t>2026-08-21T21:17:14.055496+00:00</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-019</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5423,24 +5457,24 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.191055+00:00</t>
+          <t>2026-08-21T21:17:14.057360+00:00</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-020</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5450,24 +5484,24 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.192873+00:00</t>
+          <t>2026-08-21T21:17:14.059166+00:00</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-021</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5477,24 +5511,24 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.194723+00:00</t>
+          <t>2026-08-21T21:17:14.060999+00:00</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-022</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5504,24 +5538,24 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.196586+00:00</t>
+          <t>2026-08-21T21:17:14.062909+00:00</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-023</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5531,24 +5565,24 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.198532+00:00</t>
+          <t>2026-08-21T21:17:14.064795+00:00</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-024</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5558,24 +5592,24 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.200766+00:00</t>
+          <t>2026-08-21T21:17:14.066515+00:00</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-025</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5585,120 +5619,228 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.202983+00:00</t>
+          <t>2026-08-21T21:17:14.068278+00:00</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>compiler/backends/heat_kernel_sphere.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:16.221488+00:00</t>
+          <t>2026-08-21T21:17:14.070486+00:00</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-027</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.689258+00:00</t>
+          <t>2026-08-21T21:17:14.072831+00:00</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-028</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>compiler/verification/fisher_information.py</t>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-028</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>80fba4db6b95</t>
+          <t>05902eefa453</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-08-21T20:17:18.691346+00:00</t>
+          <t>2026-08-21T21:17:14.074821+00:00</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>fc005_source_workbooks/04_fc005_primary_full_execution.xlsx::Equations::EQ-029</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>05902eefa453</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-08-21T21:17:14.076661+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>compiler/backends/heat_kernel_sphere.py</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>05902eefa453</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-08-21T21:17:14.095186+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>05902eefa453</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-08-21T21:17:16.444501+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>compiler/verification/fisher_information.py</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>05902eefa453</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-08-21T21:17:16.446960+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>compiler/backends/toe_closure_hypotheses.py::h4_g2_spin8_construction_check</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>80fba4db6b95</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>2026-08-21T20:17:18.719065+00:00</t>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>05902eefa453</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-08-21T21:17:16.471108+00:00</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9222,34 +9364,34 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['COUPLED-RECOVERY-CERTIFICATION']</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>SPECTRAL-ACTION-A0-A6-COUPLED-RECOVERY-B</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Transformation</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9259,14 +9401,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>['GRAPH-G-SEED']</t>
+          <t>['OMEGA_B-COUPLED-RECOVERY']</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9276,19 +9418,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9298,19 +9440,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>['SPECTRUM-L']</t>
+          <t>['GRAPH-G-SEED']</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9325,14 +9467,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9342,7 +9484,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9354,7 +9496,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9364,19 +9506,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CONDITIONAL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>['DIFFUSION-DISTANCE']</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9391,14 +9533,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['SPECTRUM-L']</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9408,19 +9550,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['DIFFUSION-DISTANCE']</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9430,19 +9572,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>['CONTROL-FLAT-2D']</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9457,14 +9599,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>['CONTROL-MANIFOLD-S2']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9479,14 +9621,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>['S3-MANIFOLD']</t>
+          <t>['CONTROL-FLAT-2D']</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9496,19 +9638,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-GRADING-GAMMA_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
+          <t>['CONTROL-MANIFOLD-S2']</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>T-DIRAC-SQUARED-FINITE</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9518,19 +9660,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CALCULATED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>['FINITE-DIRAC-D_B']</t>
+          <t>['S3-MANIFOLD']</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9540,19 +9682,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>['FINITE-DIRAC-D_B', 'DOUBLED-HILBERT-SPACE-H_F-PRIME', 'FINITE-ALGEBRA-A_F-PRIME', 'FINITE-GRADING-GAMMA_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME']</t>
+          <t>['FINITE-DIRAC-D_B', 'FINITE-ALGEBRA-A_F', 'FINITE-GRADING-GAMMA_F', 'FINITE-REAL-STRUCTURE-J_F']</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>T-TFT002B-EVALUATION</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9562,19 +9704,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>['H2-GRAPH-CONTROL']</t>
+          <t>['FINITE-DIRAC-D_B']</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>T-COUPLED-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9589,41 +9731,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>['TFT-002B-CANDIDATE', 'COUPLING-MATRIX-C']</t>
+          <t>['FINITE-DIRAC-D_B', 'DOUBLED-HILBERT-SPACE-H_F-PRIME', 'FINITE-ALGEBRA-A_F-PRIME', 'FINITE-GRADING-GAMMA_F-PRIME', 'FINITE-REAL-STRUCTURE-J_F-PRIME']</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-TFT002B-EVALUATION</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DERIVED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>['OPERATOR-L']</t>
+          <t>['H2-GRAPH-CONTROL']</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -9633,58 +9775,58 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>['HEAT-FLOW-R']</t>
+          <t>['TFT-002B-CANDIDATE', 'COUPLING-MATRIX-C']</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>T-COUPLED-RECOVERY-INNER-FLUCTUATION</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['COUPLED-RECOVERY-CERTIFICATION']</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>T-COUPLED-RECOVERY-SPECTRAL-ACTION</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Equation</t>
+          <t>Transformation</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>CALCULATED</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OMEGA_B-COUPLED-RECOVERY']</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9694,19 +9836,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['OPERATOR-L']</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9716,19 +9858,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PROPOSED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['HEAT-FLOW-R']</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9750,7 +9892,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9772,7 +9914,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9794,7 +9936,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9816,7 +9958,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9838,7 +9980,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9860,7 +10002,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9882,7 +10024,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9904,7 +10046,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9926,7 +10068,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9948,7 +10090,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9970,7 +10112,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9992,7 +10134,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10014,7 +10156,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10036,7 +10178,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10058,7 +10200,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10080,7 +10222,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10102,7 +10244,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10124,7 +10266,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10146,7 +10288,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10168,7 +10310,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10190,7 +10332,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10212,7 +10354,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10234,7 +10376,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10256,7 +10398,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10278,7 +10420,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>EQ-026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10288,19 +10430,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>['S3-CURVATURE-CLOSURE']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>EQ-027</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10310,19 +10452,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+          <t>EQ-028</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10332,32 +10474,120 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FALSIFIED</t>
+          <t>PROPOSED</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>['FISHER-STATISTICAL-FAMILY']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>PROPOSED</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>['S3-CURVATURE-CLOSURE']</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Equation</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>FALSIFIED</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>['FISHER-STATISTICAL-FAMILY']</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Equation</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>FALSIFIED</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -10858,7 +11088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11420,6 +11650,18 @@
       <c r="B41" t="inlineStr">
         <is>
           <t>a component of the nontrivially-coupled doubled recovery (Phase 2), extending the uncoupled recovery with a genuine inter-copy coupling</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>inner_fluctuation_component</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>a component (gauge potential, fluctuated Dirac operator, or curvature) of a Connes inner-fluctuation D_A=D+omega+J omega J^-1 attempted over a candidate that passes the first-order condition -- status always computed from real axiom checks</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14117,6 +14359,60 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>inner_fluctuation_component</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>['COUPLED-RECOVERY-CERTIFICATION']</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>upstream_construction</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SPECTRAL-ACTION-A0-A6-COUPLED-RECOVERY-B</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>inner_fluctuation_component</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>['OMEGA_B-COUPLED-RECOVERY']</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>comparison</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14128,7 +14424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14712,6 +15008,70 @@
       <c r="F18" t="inlineStr">
         <is>
           <t>['TFT-002B-CANDIDATE', 'COUPLING-MATRIX-C']</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T-COUPLED-RECOVERY-INNER-FLUCTUATION</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>build omega=i*[D_F'',pi'(f)], verify self-adjointness, form D_A''=D_F''+omega+eps'*J''omegaJ''^-1 via an explicit closed-form J-conjugation matrix (independently verified against the vector-level J definition), verify D_A'' self-adjoint and grading-anticommuting, compute Omega_B''=D_A''^2-D_F''^2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>['COUPLED-RECOVERY-CERTIFICATION']</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T-COUPLED-RECOVERY-SPECTRAL-ACTION</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SPECTRAL-ACTION-A0-A6-COUPLED-RECOVERY-B</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tr(D_A''^k) for k=0,2,4,6 -- exact finite-dimensional trace moments, not a continuum Seeley-DeWitt expansion</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>['OMEGA_B-COUPLED-RECOVERY']</t>
         </is>
       </c>
     </row>
@@ -15900,7 +16260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B130"/>
+  <dimension ref="A1:B134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17122,55 +17482,55 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>T-GRAPH-TO-OPERATOR</t>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GRAPH-G-SEED</t>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-SPECTRUM</t>
+          <t>SPECTRAL-ACTION-A0-A6-COUPLED-RECOVERY-B</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-HEATFLOW</t>
+          <t>T-GRAPH-TO-OPERATOR</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SPECTRUM-L</t>
+          <t>GRAPH-G-SEED</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>T-HEATFLOW-TO-KERNEL</t>
+          <t>T-OPERATOR-TO-SPECTRUM</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>T-SPECTRUM-TO-DIFFUSION</t>
+          <t>T-SPECTRUM-TO-HEATFLOW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -17182,96 +17542,96 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>T-DIFFUSION-TO-METRIC</t>
+          <t>T-HEATFLOW-TO-KERNEL</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DIFFUSION-DISTANCE</t>
+          <t>HEAT-FLOW-R</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>T-OPERATOR-TO-CURVATURE</t>
+          <t>T-SPECTRUM-TO-DIFFUSION</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>SPECTRUM-L</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>T-FC005-S3-CONTROL-CHAIN</t>
+          <t>T-DIFFUSION-TO-METRIC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>DIFFUSION-DISTANCE</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
+          <t>T-OPERATOR-TO-CURVATURE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>CONTROL-FLAT-2D</t>
+          <t>OPERATOR-L</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
+          <t>T-FC005-S3-CONTROL-CHAIN</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>CONTROL-MANIFOLD-S2</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
+          <t>T-LICHNEROWICZ-GAUGE-TERM</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>S3-MANIFOLD</t>
+          <t>CONTROL-FLAT-2D</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-LICHNEROWICZ-GRAVITY-TERM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FINITE-DIRAC-D_B</t>
+          <t>CONTROL-MANIFOLD-S2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
+          <t>T-SEELEY-DEWITT-A0-A2-A4-NUMERIC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FINITE-ALGEBRA-A_F</t>
+          <t>S3-MANIFOLD</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17643,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FINITE-GRADING-GAMMA_F</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
@@ -17295,43 +17655,43 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FINITE-REAL-STRUCTURE-J_F</t>
+          <t>FINITE-ALGEBRA-A_F</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>T-DIRAC-SQUARED-FINITE</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FINITE-DIRAC-D_B</t>
+          <t>FINITE-GRADING-GAMMA_F</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-AXIOMS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FINITE-DIRAC-D_B</t>
+          <t>FINITE-REAL-STRUCTURE-J_F</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
+          <t>T-DIRAC-SQUARED-FINITE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17703,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FINITE-ALGEBRA-A_F-PRIME</t>
+          <t>FINITE-DIRAC-D_B</t>
         </is>
       </c>
     </row>
@@ -17355,7 +17715,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
+          <t>DOUBLED-HILBERT-SPACE-H_F-PRIME</t>
         </is>
       </c>
     </row>
@@ -17367,101 +17727,149 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
+          <t>FINITE-ALGEBRA-A_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>T-TFT002B-EVALUATION</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>H2-GRAPH-CONTROL</t>
+          <t>FINITE-GRADING-GAMMA_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>T-COUPLED-RECOVERY-AXIOMS</t>
+          <t>T-FINITE-SPECTRAL-TRIPLE-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TFT-002B-CANDIDATE</t>
+          <t>FINITE-REAL-STRUCTURE-J_F-PRIME</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>T-COUPLED-RECOVERY-AXIOMS</t>
+          <t>T-TFT002B-EVALUATION</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>COUPLING-MATRIX-C</t>
+          <t>H2-GRAPH-CONTROL</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>OPERATOR-L</t>
+          <t>TFT-002B-CANDIDATE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+          <t>T-COUPLED-RECOVERY-AXIOMS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HEAT-FLOW-R</t>
+          <t>COUPLING-MATRIX-C</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+          <t>T-COUPLED-RECOVERY-INNER-FLUCTUATION</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>S3-CURVATURE-CLOSURE</t>
+          <t>COUPLED-RECOVERY-CERTIFICATION</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EQ-FC005-FISHER-PSD</t>
+          <t>T-COUPLED-RECOVERY-SPECTRAL-ACTION</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FISHER-STATISTICAL-FAMILY</t>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>EQ-LAPLACIAN-ROW-SUM-ZERO</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>OPERATOR-L</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>EQ-HEAT-KERNEL-EIGEN-ACTION</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>HEAT-FLOW-R</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>EQ-FC005-S3-CURVATURE-RESIDUAL</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>S3-CURVATURE-CLOSURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>EQ-FC005-FISHER-PSD</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>FISHER-STATISTICAL-FAMILY</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
           <t>EQ-FC005-FISHER-LORENTZIAN-OBSTRUCTION</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>FISHER-STATISTICAL-FAMILY</t>
         </is>
@@ -17478,7 +17886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18520,67 +18928,67 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SELECTION-SIGMA</t>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
+          <t>omega is ONE generator (single real f), not the fully general Omega^1_D(A_F) connection -- a different or larger generator set would give a different Omega_B''.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>EQ-001</t>
+          <t>OMEGA_B-COUPLED-RECOVERY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>real_structure_epsilon_prime used: 1 (the ACTUALLY MEASURED sign for this candidate, not assumed).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>EQ-002</t>
+          <t>SPECTRAL-ACTION-A0-A6-COUPLED-RECOVERY-B</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>physical_interpretation: NONE -- finite linear-algebra trace moments of a specific matrix, not physically-interpretable Seeley-DeWitt heat-kernel coefficients.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EQ-003</t>
+          <t>SPECTRAL-ACTION-A0-A6-COUPLED-RECOVERY-B</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>omega is a single generator (see OMEGA_B-COUPLED-RECOVERY); a different generator choice would give different moment values.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>EQ-004</t>
+          <t>SELECTION-SIGMA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>Registered as an UNRESOLVED compiler component (spec section 10): no non-arbitrary, unique, representation-invariant derivation of Sigma is registered in this build. A selector that uses the desired answer is invalid and none is substituted here.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>EQ-005</t>
+          <t>EQ-001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -18592,7 +19000,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>EQ-006</t>
+          <t>EQ-002</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -18604,7 +19012,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EQ-007</t>
+          <t>EQ-003</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -18616,7 +19024,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>EQ-008</t>
+          <t>EQ-004</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -18628,7 +19036,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EQ-009</t>
+          <t>EQ-005</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -18640,67 +19048,67 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>EQ-010</t>
+          <t>EQ-006</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>EQ-011</t>
+          <t>EQ-007</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>EQ-012</t>
+          <t>EQ-008</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>EQ-013</t>
+          <t>EQ-009</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>EQ-014</t>
+          <t>EQ-010</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>EQ-015</t>
+          <t>EQ-011</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -18712,55 +19120,55 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQ-016</t>
+          <t>EQ-012</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>EQ-017</t>
+          <t>EQ-013</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EQ-018</t>
+          <t>EQ-014</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CONDITIONAL' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQ-019</t>
+          <t>EQ-015</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQ-020</t>
+          <t>EQ-016</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -18772,31 +19180,31 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQ-021</t>
+          <t>EQ-017</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='ASSUMPTION' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQ-022</t>
+          <t>EQ-018</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='DERIVED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EQ-023</t>
+          <t>EQ-019</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -18808,19 +19216,19 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQ-024</t>
+          <t>EQ-020</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQ-025</t>
+          <t>EQ-021</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -18832,58 +19240,106 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQ-026</t>
+          <t>EQ-022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED*' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EQ-027</t>
+          <t>EQ-023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EQ-028</t>
+          <t>EQ-024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='PROOF' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>EQ-029</t>
+          <t>EQ-025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>EQ-026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='ESTABLISHED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>EQ-027</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='FALSIFIED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>EQ-028</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='CLOSED' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>EQ-029</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>workbook_claimed_status='TEST' -- NOT trusted at face value (spec section 2/4); PROPOSED until independently executed in this compiler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>EQ-H4-G2-TRIALITY-INTERSECTION-CLAIM</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>The counterfactual manuscript's specific restatement of the gauge-closure claim (COUNTERFACTUAL_MASTER_THEORY_OF_EVERYTHING.docx section 8).</t>
         </is>
@@ -18900,7 +19356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19342,6 +19798,60 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PROOF-T-COUPLED-RECOVERY-INNER-FLUCTUATION</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>T-COUPLED-RECOVERY-INNER-FLUCTUATION</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>build omega=i*[D_F'',pi'(f)], verify self-adjointness, form D_A''=D_F''+omega+eps'*J''omegaJ''^-1 via an explicit closed-form J-conjugation matrix (independently verified against the vector-level J definition), verify D_A'' self-adjoint and grading-anticommuting, compute Omega_B''=D_A''^2-D_F''^2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>numpy exact linear algebra at n=200 (dim=2800 doubled candidate); J_conjugate_matrix's closed form independently verified against the ground-truth vector-level J_apply composition on random complex inputs</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PROOF-T-COUPLED-RECOVERY-SPECTRAL-ACTION</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>T-COUPLED-RECOVERY-SPECTRAL-ACTION</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tr(D_A''^k) for k=0,2,4,6 -- exact finite-dimensional trace moments, not a continuum Seeley-DeWitt expansion</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>numpy exact finite-dimensional trace via repeated matrix multiplication (matrix_power), imaginary residual confirmed at float-noise scale (&lt;1e-12) for self-adjoint D_A''</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19353,7 +19863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20330,6 +20840,50 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CALC-COUPLED-RECOVERY-INNER-FLUCTUATION</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>connes_inner_fluctuation_attempt</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>{'generator': "omega = i*[D_F'',pi'(f)] for a single real f on the vertex block"}</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CALC-COUPLED-RECOVERY-FINITE-MOMENTS</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>finite_trace_moments</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CALCULATED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.828145+00:00</t>
+          <t>2026-08-21T22:03:33.009824+00:00</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.830634+00:00</t>
+          <t>2026-08-21T22:03:33.012009+00:00</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.832675+00:00</t>
+          <t>2026-08-21T22:03:33.014140+00:00</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.834641+00:00</t>
+          <t>2026-08-21T22:03:33.016506+00:00</t>
         </is>
       </c>
     </row>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.836476+00:00</t>
+          <t>2026-08-21T22:03:33.018433+00:00</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.838434+00:00</t>
+          <t>2026-08-21T22:03:33.020357+00:00</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.840440+00:00</t>
+          <t>2026-08-21T22:03:33.022407+00:00</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.842466+00:00</t>
+          <t>2026-08-21T22:03:33.024423+00:00</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.844405+00:00</t>
+          <t>2026-08-21T22:03:33.026354+00:00</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.846375+00:00</t>
+          <t>2026-08-21T22:03:33.028242+00:00</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.848133+00:00</t>
+          <t>2026-08-21T22:03:33.030301+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.850099+00:00</t>
+          <t>2026-08-21T22:03:33.032140+00:00</t>
         </is>
       </c>
     </row>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.851899+00:00</t>
+          <t>2026-08-21T22:03:33.034047+00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.853782+00:00</t>
+          <t>2026-08-21T22:03:33.035899+00:00</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.855911+00:00</t>
+          <t>2026-08-21T22:03:33.037818+00:00</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.857944+00:00</t>
+          <t>2026-08-21T22:03:33.039940+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.859817+00:00</t>
+          <t>2026-08-21T22:03:33.041815+00:00</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.861746+00:00</t>
+          <t>2026-08-21T22:03:33.043738+00:00</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.863603+00:00</t>
+          <t>2026-08-21T22:03:33.045633+00:00</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.865510+00:00</t>
+          <t>2026-08-21T22:03:33.047449+00:00</t>
         </is>
       </c>
     </row>
@@ -2244,12 +2244,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.867725+00:00</t>
+          <t>2026-08-21T22:03:33.049290+00:00</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.982949+00:00</t>
+          <t>2026-08-21T22:03:33.213495+00:00</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.985573+00:00</t>
+          <t>2026-08-21T22:03:33.216087+00:00</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.987488+00:00</t>
+          <t>2026-08-21T22:03:33.218043+00:00</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.989220+00:00</t>
+          <t>2026-08-21T22:03:33.219816+00:00</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2379,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.112187+00:00</t>
+          <t>2026-08-21T22:03:33.442957+00:00</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.114829+00:00</t>
+          <t>2026-08-21T22:03:33.445530+00:00</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.520999+00:00</t>
+          <t>2026-08-21T22:03:33.865269+00:00</t>
         </is>
       </c>
     </row>
@@ -2460,12 +2460,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.930195+00:00</t>
+          <t>2026-08-21T22:03:34.286807+00:00</t>
         </is>
       </c>
     </row>
@@ -2487,12 +2487,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.932723+00:00</t>
+          <t>2026-08-21T22:03:34.289185+00:00</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.935448+00:00</t>
+          <t>2026-08-21T22:03:34.291087+00:00</t>
         </is>
       </c>
     </row>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.937547+00:00</t>
+          <t>2026-08-21T22:03:34.293547+00:00</t>
         </is>
       </c>
     </row>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.940154+00:00</t>
+          <t>2026-08-21T22:03:34.295587+00:00</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.942189+00:00</t>
+          <t>2026-08-21T22:03:34.297681+00:00</t>
         </is>
       </c>
     </row>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.944140+00:00</t>
+          <t>2026-08-21T22:03:34.299920+00:00</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2649,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.946609+00:00</t>
+          <t>2026-08-21T22:03:34.301831+00:00</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.948462+00:00</t>
+          <t>2026-08-21T22:03:34.303727+00:00</t>
         </is>
       </c>
     </row>
@@ -2703,12 +2703,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.950862+00:00</t>
+          <t>2026-08-21T22:03:34.305528+00:00</t>
         </is>
       </c>
     </row>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.085287+00:00</t>
+          <t>2026-08-21T22:03:34.449591+00:00</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.087139+00:00</t>
+          <t>2026-08-21T22:03:34.451512+00:00</t>
         </is>
       </c>
     </row>
@@ -2784,12 +2784,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.089093+00:00</t>
+          <t>2026-08-21T22:03:34.453462+00:00</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2811,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.091003+00:00</t>
+          <t>2026-08-21T22:03:34.455334+00:00</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.093007+00:00</t>
+          <t>2026-08-21T22:03:34.457046+00:00</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:15.976111+00:00</t>
+          <t>2026-08-21T22:03:36.379217+00:00</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:15.979346+00:00</t>
+          <t>2026-08-21T22:03:36.383352+00:00</t>
         </is>
       </c>
     </row>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:15.983181+00:00</t>
+          <t>2026-08-21T22:03:36.387075+00:00</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:15.987124+00:00</t>
+          <t>2026-08-21T22:03:36.390931+00:00</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:15.993464+00:00</t>
+          <t>2026-08-21T22:03:36.394914+00:00</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:15.995697+00:00</t>
+          <t>2026-08-21T22:03:36.398965+00:00</t>
         </is>
       </c>
     </row>
@@ -3027,12 +3027,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:15.999021+00:00</t>
+          <t>2026-08-21T22:03:36.402927+00:00</t>
         </is>
       </c>
     </row>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.003064+00:00</t>
+          <t>2026-08-21T22:03:36.406940+00:00</t>
         </is>
       </c>
     </row>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.007108+00:00</t>
+          <t>2026-08-21T22:03:36.410917+00:00</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.010891+00:00</t>
+          <t>2026-08-21T22:03:36.417429+00:00</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.014913+00:00</t>
+          <t>2026-08-21T22:03:36.419347+00:00</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.021461+00:00</t>
+          <t>2026-08-21T22:03:36.423001+00:00</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.023344+00:00</t>
+          <t>2026-08-21T22:03:36.426921+00:00</t>
         </is>
       </c>
     </row>
@@ -3216,12 +3216,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.026939+00:00</t>
+          <t>2026-08-21T22:03:36.431323+00:00</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.030947+00:00</t>
+          <t>2026-08-21T22:03:36.433080+00:00</t>
         </is>
       </c>
     </row>
@@ -3270,12 +3270,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.441989+00:00</t>
+          <t>2026-08-21T22:03:36.851161+00:00</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.452326+00:00</t>
+          <t>2026-08-21T22:03:36.860712+00:00</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.455842+00:00</t>
+          <t>2026-08-21T22:03:36.864491+00:00</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.462958+00:00</t>
+          <t>2026-08-21T22:03:36.872311+00:00</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.467200+00:00</t>
+          <t>2026-08-21T22:03:36.875199+00:00</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.477483+00:00</t>
+          <t>2026-08-21T22:03:36.885537+00:00</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.479492+00:00</t>
+          <t>2026-08-21T22:03:36.887386+00:00</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.483118+00:00</t>
+          <t>2026-08-21T22:03:36.891000+00:00</t>
         </is>
       </c>
     </row>
@@ -3486,12 +3486,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.754738+00:00</t>
+          <t>2026-08-21T22:03:37.150489+00:00</t>
         </is>
       </c>
     </row>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.662090+00:00</t>
+          <t>2026-08-21T22:03:43.229559+00:00</t>
         </is>
       </c>
     </row>
@@ -3540,12 +3540,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.667719+00:00</t>
+          <t>2026-08-21T22:03:43.234567+00:00</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.674876+00:00</t>
+          <t>2026-08-21T22:03:43.242394+00:00</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.679633+00:00</t>
+          <t>2026-08-21T22:03:43.246400+00:00</t>
         </is>
       </c>
     </row>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.681555+00:00</t>
+          <t>2026-08-21T22:03:43.248285+00:00</t>
         </is>
       </c>
     </row>
@@ -3648,12 +3648,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.683867+00:00</t>
+          <t>2026-08-21T22:03:43.250354+00:00</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.685991+00:00</t>
+          <t>2026-08-21T22:03:43.252278+00:00</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.688293+00:00</t>
+          <t>2026-08-21T22:03:43.254234+00:00</t>
         </is>
       </c>
     </row>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.690247+00:00</t>
+          <t>2026-08-21T22:03:43.256146+00:00</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3756,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.692521+00:00</t>
+          <t>2026-08-21T22:03:43.258149+00:00</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3783,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.883000+00:00</t>
+          <t>2026-08-21T22:03:43.372489+00:00</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.885926+00:00</t>
+          <t>2026-08-21T22:03:43.375490+00:00</t>
         </is>
       </c>
     </row>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.888378+00:00</t>
+          <t>2026-08-21T22:03:43.379189+00:00</t>
         </is>
       </c>
     </row>
@@ -3864,12 +3864,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.890200+00:00</t>
+          <t>2026-08-21T22:03:43.385495+00:00</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.893809+00:00</t>
+          <t>2026-08-21T22:03:43.391628+00:00</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.935962+00:00</t>
+          <t>2026-08-21T22:03:43.450938+00:00</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.938399+00:00</t>
+          <t>2026-08-21T22:03:43.455821+00:00</t>
         </is>
       </c>
     </row>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.940704+00:00</t>
+          <t>2026-08-21T22:03:43.459621+00:00</t>
         </is>
       </c>
     </row>
@@ -3999,12 +3999,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.942567+00:00</t>
+          <t>2026-08-21T22:03:43.463060+00:00</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.946213+00:00</t>
+          <t>2026-08-21T22:03:43.471134+00:00</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.950906+00:00</t>
+          <t>2026-08-21T22:03:43.475008+00:00</t>
         </is>
       </c>
     </row>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:24.939914+00:00</t>
+          <t>2026-08-21T22:03:45.469924+00:00</t>
         </is>
       </c>
     </row>
@@ -4107,12 +4107,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:24.942553+00:00</t>
+          <t>2026-08-21T22:03:45.472287+00:00</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:24.944724+00:00</t>
+          <t>2026-08-21T22:03:45.475411+00:00</t>
         </is>
       </c>
     </row>
@@ -4161,12 +4161,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:24.946799+00:00</t>
+          <t>2026-08-21T22:03:45.479174+00:00</t>
         </is>
       </c>
     </row>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:24.948925+00:00</t>
+          <t>2026-08-21T22:03:45.481253+00:00</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:24.950947+00:00</t>
+          <t>2026-08-21T22:03:45.483165+00:00</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:25.421780+00:00</t>
+          <t>2026-08-21T22:03:45.934585+00:00</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:33.819683+00:00</t>
+          <t>2026-08-21T22:03:53.456941+00:00</t>
         </is>
       </c>
     </row>
@@ -4296,12 +4296,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:33.822125+00:00</t>
+          <t>2026-08-21T22:03:53.463384+00:00</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:33.825806+00:00</t>
+          <t>2026-08-21T22:03:53.473464+00:00</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-21T21:18:22.808650+00:00</t>
+          <t>2026-08-21T22:04:42.383094+00:00</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-21T21:18:22.813898+00:00</t>
+          <t>2026-08-21T22:04:42.391210+00:00</t>
         </is>
       </c>
     </row>
@@ -4404,12 +4404,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.825582+00:00</t>
+          <t>2026-08-21T22:03:33.007285+00:00</t>
         </is>
       </c>
     </row>
@@ -4431,12 +4431,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.991144+00:00</t>
+          <t>2026-08-21T22:03:33.221619+00:00</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.993070+00:00</t>
+          <t>2026-08-21T22:03:33.223379+00:00</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.995019+00:00</t>
+          <t>2026-08-21T22:03:33.225160+00:00</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:12.996917+00:00</t>
+          <t>2026-08-21T22:03:33.226916+00:00</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4539,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.119242+00:00</t>
+          <t>2026-08-21T22:03:33.451325+00:00</t>
         </is>
       </c>
     </row>
@@ -4566,12 +4566,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.123146+00:00</t>
+          <t>2026-08-21T22:03:33.455343+00:00</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.523780+00:00</t>
+          <t>2026-08-21T22:03:33.867824+00:00</t>
         </is>
       </c>
     </row>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.097220+00:00</t>
+          <t>2026-08-21T22:03:34.461084+00:00</t>
         </is>
       </c>
     </row>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.757168+00:00</t>
+          <t>2026-08-21T22:03:37.152949+00:00</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.665181+00:00</t>
+          <t>2026-08-21T22:03:43.232092+00:00</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.677335+00:00</t>
+          <t>2026-08-21T22:03:43.244458+00:00</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.891993+00:00</t>
+          <t>2026-08-21T22:03:43.388063+00:00</t>
         </is>
       </c>
     </row>
@@ -4755,12 +4755,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:22.944400+00:00</t>
+          <t>2026-08-21T22:03:43.467097+00:00</t>
         </is>
       </c>
     </row>
@@ -4782,12 +4782,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:24.952918+00:00</t>
+          <t>2026-08-21T22:03:45.487157+00:00</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:25.424244+00:00</t>
+          <t>2026-08-21T22:03:45.937076+00:00</t>
         </is>
       </c>
     </row>
@@ -4836,12 +4836,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:33.824007+00:00</t>
+          <t>2026-08-21T22:03:53.467052+00:00</t>
         </is>
       </c>
     </row>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-08-21T21:18:22.811831+00:00</t>
+          <t>2026-08-21T22:04:42.385962+00:00</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-08-21T21:18:22.815687+00:00</t>
+          <t>2026-08-21T22:04:42.395034+00:00</t>
         </is>
       </c>
     </row>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.130990+00:00</t>
+          <t>2026-08-21T22:03:33.463498+00:00</t>
         </is>
       </c>
     </row>
@@ -4944,12 +4944,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:13.132893+00:00</t>
+          <t>2026-08-21T22:03:33.465463+00:00</t>
         </is>
       </c>
     </row>
@@ -4971,12 +4971,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.019588+00:00</t>
+          <t>2026-08-21T22:03:34.380446+00:00</t>
         </is>
       </c>
     </row>
@@ -4998,12 +4998,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.022578+00:00</t>
+          <t>2026-08-21T22:03:34.383016+00:00</t>
         </is>
       </c>
     </row>
@@ -5025,12 +5025,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.024683+00:00</t>
+          <t>2026-08-21T22:03:34.385512+00:00</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.026824+00:00</t>
+          <t>2026-08-21T22:03:34.387790+00:00</t>
         </is>
       </c>
     </row>
@@ -5079,12 +5079,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.028807+00:00</t>
+          <t>2026-08-21T22:03:34.389815+00:00</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.031133+00:00</t>
+          <t>2026-08-21T22:03:34.391836+00:00</t>
         </is>
       </c>
     </row>
@@ -5133,12 +5133,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.033114+00:00</t>
+          <t>2026-08-21T22:03:34.394215+00:00</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5160,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.035489+00:00</t>
+          <t>2026-08-21T22:03:34.396623+00:00</t>
         </is>
       </c>
     </row>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.037279+00:00</t>
+          <t>2026-08-21T22:03:34.398549+00:00</t>
         </is>
       </c>
     </row>
@@ -5214,12 +5214,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.039222+00:00</t>
+          <t>2026-08-21T22:03:34.400959+00:00</t>
         </is>
       </c>
     </row>
@@ -5241,12 +5241,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.041198+00:00</t>
+          <t>2026-08-21T22:03:34.403416+00:00</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.043607+00:00</t>
+          <t>2026-08-21T22:03:34.405346+00:00</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.045521+00:00</t>
+          <t>2026-08-21T22:03:34.407728+00:00</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.047471+00:00</t>
+          <t>2026-08-21T22:03:34.409606+00:00</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5349,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.049231+00:00</t>
+          <t>2026-08-21T22:03:34.411896+00:00</t>
         </is>
       </c>
     </row>
@@ -5376,12 +5376,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.051248+00:00</t>
+          <t>2026-08-21T22:03:34.413881+00:00</t>
         </is>
       </c>
     </row>
@@ -5403,12 +5403,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.053637+00:00</t>
+          <t>2026-08-21T22:03:34.416231+00:00</t>
         </is>
       </c>
     </row>
@@ -5430,12 +5430,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.055496+00:00</t>
+          <t>2026-08-21T22:03:34.418148+00:00</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.057360+00:00</t>
+          <t>2026-08-21T22:03:34.420467+00:00</t>
         </is>
       </c>
     </row>
@@ -5484,12 +5484,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.059166+00:00</t>
+          <t>2026-08-21T22:03:34.422530+00:00</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.060999+00:00</t>
+          <t>2026-08-21T22:03:34.424351+00:00</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.062909+00:00</t>
+          <t>2026-08-21T22:03:34.426351+00:00</t>
         </is>
       </c>
     </row>
@@ -5565,12 +5565,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.064795+00:00</t>
+          <t>2026-08-21T22:03:34.428716+00:00</t>
         </is>
       </c>
     </row>
@@ -5592,12 +5592,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.066515+00:00</t>
+          <t>2026-08-21T22:03:34.430669+00:00</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.068278+00:00</t>
+          <t>2026-08-21T22:03:34.432504+00:00</t>
         </is>
       </c>
     </row>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.070486+00:00</t>
+          <t>2026-08-21T22:03:34.434921+00:00</t>
         </is>
       </c>
     </row>
@@ -5673,12 +5673,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.072831+00:00</t>
+          <t>2026-08-21T22:03:34.436809+00:00</t>
         </is>
       </c>
     </row>
@@ -5700,12 +5700,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.074821+00:00</t>
+          <t>2026-08-21T22:03:34.438629+00:00</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.076661+00:00</t>
+          <t>2026-08-21T22:03:34.440712+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:14.095186+00:00</t>
+          <t>2026-08-21T22:03:34.459389+00:00</t>
         </is>
       </c>
     </row>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.444501+00:00</t>
+          <t>2026-08-21T22:03:36.853553+00:00</t>
         </is>
       </c>
     </row>
@@ -5808,12 +5808,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.446960+00:00</t>
+          <t>2026-08-21T22:03:36.855482+00:00</t>
         </is>
       </c>
     </row>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>05902eefa453</t>
+          <t>ed99331a45c4</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-08-21T21:17:16.471108+00:00</t>
+          <t>2026-08-21T22:03:36.878970+00:00</t>
         </is>
       </c>
     </row>
